--- a/Body/5-Office/BOM表.xlsx
+++ b/Body/5-Office/BOM表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Win-daolaj3j0nc\F\internal class\N0000-MBW\N0000-3-office文件\供应\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Win-daolaj3j0nc\f\internal class\N2500-25N\N2531-AGV\N2531-3-office文件\供应\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A1481A-5ACA-4A3C-89DF-A3C20BEDAEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFE3553-CD74-489C-B147-30177D5ECCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4770" yWindow="4605" windowWidth="32085" windowHeight="16125" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revision History" sheetId="10" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="166">
   <si>
     <r>
       <rPr>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>INNOREV P/N</t>
+  </si>
+  <si>
+    <t>文档号</t>
   </si>
   <si>
     <r>
@@ -650,14 +653,637 @@
     </r>
   </si>
   <si>
+    <t>N2531-2113</t>
+  </si>
+  <si>
+    <t>变压器</t>
+  </si>
+  <si>
+    <t>input:48VDC output:24VDC 6.25A</t>
+  </si>
+  <si>
+    <t>JLZ150-48S24</t>
+  </si>
+  <si>
+    <t>JIANNUO</t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Total:</t>
-  </si>
-  <si>
-    <t>文档号</t>
-    <phoneticPr fontId="64" type="noConversion"/>
+    <t>N2531-2112</t>
+  </si>
+  <si>
+    <t>伺服驱动器</t>
+  </si>
+  <si>
+    <r>
+      <t>input:48VDC    output:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>均值</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">15VDC </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>峰值</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>30A</t>
+    </r>
+  </si>
+  <si>
+    <t>ZLAC8015D</t>
+  </si>
+  <si>
+    <t>ZLTECH</t>
+  </si>
+  <si>
+    <t>N2531-1411</t>
+  </si>
+  <si>
+    <t>雷达</t>
+  </si>
+  <si>
+    <t>N2531-0121</t>
+  </si>
+  <si>
+    <t>后外壳</t>
+  </si>
+  <si>
+    <t>N2531-0122</t>
+  </si>
+  <si>
+    <t>前外壳</t>
+  </si>
+  <si>
+    <t>N2531-0123</t>
+  </si>
+  <si>
+    <t>顶板</t>
+  </si>
+  <si>
+    <t>N2531-1111</t>
+  </si>
+  <si>
+    <t>电池</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>标称电压：48</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">V </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>充电电压：54.6</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">V </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>标称容量：20</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ah </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>放电电流：&lt;=30</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A</t>
+    </r>
+  </si>
+  <si>
+    <t>LS-DL48-20C</t>
+  </si>
+  <si>
+    <t>深圳市锂神能源科技有限公司</t>
+  </si>
+  <si>
+    <t>N2531-1121</t>
+  </si>
+  <si>
+    <t>底盘主体</t>
+  </si>
+  <si>
+    <t>N2531-1211</t>
+  </si>
+  <si>
+    <t>中菱科技</t>
+  </si>
+  <si>
+    <t>N2531-1221</t>
+  </si>
+  <si>
+    <t>前桥</t>
+  </si>
+  <si>
+    <t>N2531-1222</t>
+  </si>
+  <si>
+    <t>后桥</t>
+  </si>
+  <si>
+    <t>N2531-1223</t>
+  </si>
+  <si>
+    <t>梁</t>
+  </si>
+  <si>
+    <t>N2531-1311</t>
+  </si>
+  <si>
+    <t>轮毂架</t>
+  </si>
+  <si>
+    <t>RichLand</t>
+  </si>
+  <si>
+    <t>N2531-1312</t>
+  </si>
+  <si>
+    <t>辅助轮</t>
+  </si>
+  <si>
+    <t>N2531-2111</t>
+  </si>
+  <si>
+    <t>电箱din导轨300</t>
+  </si>
+  <si>
+    <t>296mm</t>
+  </si>
+  <si>
+    <t>N2531-2121</t>
+  </si>
+  <si>
+    <t>安装板</t>
+  </si>
+  <si>
+    <t>N2531-2122</t>
+  </si>
+  <si>
+    <t>架子</t>
+  </si>
+  <si>
+    <t>N2531-2123</t>
+  </si>
+  <si>
+    <t>挡板</t>
+  </si>
+  <si>
+    <t>N2531-2221</t>
+  </si>
+  <si>
+    <t>上安装板</t>
+  </si>
+  <si>
+    <t>N2531-0111 N2531-2115 N2531-1513 N2531-2211</t>
+  </si>
+  <si>
+    <t>内六角平圆头螺钉</t>
+  </si>
+  <si>
+    <t>M6*10</t>
+  </si>
+  <si>
+    <t>GBT70.2-2015</t>
+  </si>
+  <si>
+    <t>N2531-1412 N2531-2117</t>
+  </si>
+  <si>
+    <t>M4*10</t>
+  </si>
+  <si>
+    <t>N2531-2116</t>
+  </si>
+  <si>
+    <t>M3*10</t>
+  </si>
+  <si>
+    <t>N2531-1313 N2531-1413</t>
+  </si>
+  <si>
+    <t>M3*6</t>
+  </si>
+  <si>
+    <t>N2531-2400</t>
+  </si>
+  <si>
+    <t>紧固螺丝组</t>
+  </si>
+  <si>
+    <t>M8*50</t>
+  </si>
+  <si>
+    <t>N2531-1212</t>
+  </si>
+  <si>
+    <t>销</t>
+  </si>
+  <si>
+    <t>M5*34</t>
+  </si>
+  <si>
+    <t>N2531-1213</t>
+  </si>
+  <si>
+    <t>大垫圈</t>
+  </si>
+  <si>
+    <t>D30 d10</t>
+  </si>
+  <si>
+    <t>N2531-1214</t>
+  </si>
+  <si>
+    <t>小垫圈</t>
+  </si>
+  <si>
+    <t>D10 d6</t>
+  </si>
+  <si>
+    <t>N2531-1215</t>
+  </si>
+  <si>
+    <t>平头圆柱销</t>
+  </si>
+  <si>
+    <t>M10*36</t>
+  </si>
+  <si>
+    <t>N2531-1216</t>
+  </si>
+  <si>
+    <t>六角锁紧螺母</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>GBT6184-2000</t>
+  </si>
+  <si>
+    <t>N2531-1217</t>
+  </si>
+  <si>
+    <t>M6*20</t>
+  </si>
+  <si>
+    <t>N2531-1225</t>
+  </si>
+  <si>
+    <t>减震器</t>
+  </si>
+  <si>
+    <t>N2531-1218</t>
+  </si>
+  <si>
+    <t>弹簧</t>
+  </si>
+  <si>
+    <t>D10 d5 H20</t>
+  </si>
+  <si>
+    <t>N2531-1421</t>
+  </si>
+  <si>
+    <t>雷达安装板</t>
+  </si>
+  <si>
+    <t>N2531-211B</t>
+  </si>
+  <si>
+    <t>接触器</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TeSys K </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>直流控制三极接触器</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 12A, 24 V DC</t>
+    </r>
+  </si>
+  <si>
+    <t>LP1K1210DB</t>
+  </si>
+  <si>
+    <t>施耐德</t>
+  </si>
+  <si>
+    <t>N2531-1512</t>
+  </si>
+  <si>
+    <t>电箱din导轨100</t>
+  </si>
+  <si>
+    <t>N2531-2118</t>
+  </si>
+  <si>
+    <t>移动机器人导航控制器</t>
+  </si>
+  <si>
+    <t>N2531-211A</t>
+  </si>
+  <si>
+    <t>接线端子</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PT2.5-QUATTRO</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>灰色</t>
+    </r>
+  </si>
+  <si>
+    <t>N2531-2119</t>
+  </si>
+  <si>
+    <t>空开</t>
+  </si>
+  <si>
+    <t>IC60a</t>
+  </si>
+  <si>
+    <t>注：</t>
+  </si>
+  <si>
+    <t>为加工件</t>
+  </si>
+  <si>
+    <t>为采购件</t>
+  </si>
+  <si>
+    <t>仙工</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>更换仙工的控制器，增加接口转换模块</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏姜楠</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>宇泰</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>UT-2506A</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>RS232/485</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>转</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CANBUS</t>
+    </r>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>RS-232/485转CAN BUS协议转换器</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>N2531-211C</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.5寸轮毂带编码器机器人轮毂伺服</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZLG65ASM250 V3.0</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>M170 48V 250W 4N.m IP65</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>语音提示器</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>急停开关</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>N2531-211E</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>N2531-211D</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>开关按钮</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>N2531-211F</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除冗余变频器，修改轮毂选型,完善设备完整度（新增急停按钮和启动按钮）</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>一佳</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>YJ-LA16-11ZS 红</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝波</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>LB16A/19A</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>铝氧化</t>
+    </r>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2D</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>导航激光</t>
+    </r>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>H1E0-02C</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>SRC-880-t</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>触摸屏</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>昆仑通态</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>TPC1570Gn</t>
+    <phoneticPr fontId="62" type="noConversion"/>
+  </si>
+  <si>
+    <t>384*247</t>
+    <phoneticPr fontId="62" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -671,9 +1297,9 @@
     <numFmt numFmtId="177" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="000000"/>
-    <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="181" formatCode="0_ "/>
-    <numFmt numFmtId="182" formatCode="0.00_ "/>
+    <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="182" formatCode="0_ "/>
     <numFmt numFmtId="183" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="67" x14ac:knownFonts="1">
@@ -728,29 +1354,33 @@
       <b/>
       <sz val="18"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -769,6 +1399,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1067,7 +1698,8 @@
     <font>
       <sz val="14"/>
       <name val="Cordia New"/>
-      <family val="1"/>
+      <family val="2"/>
+      <charset val="222"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1083,20 +1715,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -1104,10 +1722,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1117,8 +1734,21 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF262626"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="30">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1128,6 +1758,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1321,19 +1957,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -1348,6 +1971,17 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1401,8 +2035,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1415,9 +2053,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1574,112 +2210,112 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="18" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="18" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
@@ -1702,16 +2338,16 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="11" fillId="22" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="22" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="22" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="22" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1747,7 +2383,7 @@
     <xf numFmtId="176" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="31" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0">
@@ -1840,331 +2476,331 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="36" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="37" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="37" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="37" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="38" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="37" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="37" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="37" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="37" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="37" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="39" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="40" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="40" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="41" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="42" fillId="12" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="43" fillId="4" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="44" fillId="24" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="45" fillId="24" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="42" fillId="13" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="43" fillId="5" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="44" fillId="25" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="45" fillId="25" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2208,37 +2844,37 @@
     <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="52" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="53" fillId="12" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="54" fillId="5" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="55" fillId="4" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="56" fillId="5" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="52" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="53" fillId="13" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="54" fillId="6" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="55" fillId="5" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="56" fillId="6" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="57" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2250,14 +2886,14 @@
     </xf>
     <xf numFmtId="176" fontId="51" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="59" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="60" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="29" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="60" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="30" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="90">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2271,9 +2907,21 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2283,9 +2931,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2301,13 +2946,16 @@
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2316,76 +2964,94 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2396,88 +3062,100 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="114" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="114" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="61" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="61" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="66" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="63" fillId="0" borderId="1" xfId="114" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="66" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="61" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="0" borderId="1" xfId="114" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="64" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="65" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3053,80 +3731,96 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.125" customWidth="1"/>
-    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="67.375" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="14.625" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="44" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:5" s="54" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="57" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-    </row>
-    <row r="3" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-    </row>
-    <row r="4" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="48"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-    </row>
-    <row r="5" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="48"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-    </row>
-    <row r="6" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="48"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-    </row>
-    <row r="7" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="48"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-    </row>
-    <row r="8" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="48"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
+    <row r="2" spans="1:5" s="55" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="58">
+        <v>1.01</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="59">
+        <v>45981</v>
+      </c>
+      <c r="D2" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" s="59"/>
+    </row>
+    <row r="3" spans="1:5" s="55" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="58">
+        <v>1.02</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="59">
+        <v>45989</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="59"/>
+    </row>
+    <row r="4" spans="1:5" s="55" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+    </row>
+    <row r="5" spans="1:5" s="55" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="58"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+    </row>
+    <row r="6" spans="1:5" s="55" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="58"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+    </row>
+    <row r="7" spans="1:5" s="55" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="58"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+    </row>
+    <row r="8" spans="1:5" s="55" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="58"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="64" type="noConversion"/>
+  <phoneticPr fontId="62" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3134,2182 +3828,2957 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:WVF1277"/>
+  <dimension ref="A1:WVF1276"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="6" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="17.5" style="8" customWidth="1"/>
+    <col min="1" max="1" width="5.625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="10" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="17.5" style="12" customWidth="1"/>
     <col min="5" max="5" width="18.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.875" style="2" customWidth="1"/>
     <col min="8" max="8" width="6.5" style="2" customWidth="1"/>
     <col min="9" max="10" width="5.75" style="9" customWidth="1"/>
     <col min="11" max="11" width="11.25" style="2" customWidth="1"/>
     <col min="12" max="12" width="9.75" style="2" customWidth="1"/>
     <col min="13" max="13" width="15.625" style="2" customWidth="1"/>
     <col min="14" max="14" width="11" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11.125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="11.25" style="11" customWidth="1"/>
-    <col min="17" max="250" width="9" style="11"/>
-    <col min="251" max="251" width="6.875" style="11" customWidth="1"/>
-    <col min="252" max="252" width="10.125" style="11" customWidth="1"/>
-    <col min="253" max="253" width="11.125" style="11" customWidth="1"/>
-    <col min="254" max="254" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="255" max="255" width="21.625" style="11" customWidth="1"/>
-    <col min="256" max="256" width="6.25" style="11" customWidth="1"/>
-    <col min="257" max="257" width="12.125" style="11" customWidth="1"/>
-    <col min="258" max="258" width="20.125" style="11" customWidth="1"/>
-    <col min="259" max="259" width="26.75" style="11" customWidth="1"/>
-    <col min="260" max="260" width="13.375" style="11" customWidth="1"/>
-    <col min="261" max="261" width="17" style="11" customWidth="1"/>
-    <col min="262" max="262" width="19.125" style="11" customWidth="1"/>
-    <col min="263" max="264" width="5.875" style="11" customWidth="1"/>
-    <col min="265" max="265" width="6.625" style="11" customWidth="1"/>
-    <col min="266" max="266" width="8.125" style="11" customWidth="1"/>
-    <col min="267" max="267" width="10.125" style="11" customWidth="1"/>
-    <col min="268" max="268" width="7.25" style="11" customWidth="1"/>
-    <col min="269" max="269" width="11.875" style="11" customWidth="1"/>
-    <col min="270" max="270" width="2.125" style="11" customWidth="1"/>
-    <col min="271" max="272" width="12.5" style="11" customWidth="1"/>
-    <col min="273" max="506" width="9" style="11"/>
-    <col min="507" max="507" width="6.875" style="11" customWidth="1"/>
-    <col min="508" max="508" width="10.125" style="11" customWidth="1"/>
-    <col min="509" max="509" width="11.125" style="11" customWidth="1"/>
-    <col min="510" max="510" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="511" max="511" width="21.625" style="11" customWidth="1"/>
-    <col min="512" max="512" width="6.25" style="11" customWidth="1"/>
-    <col min="513" max="513" width="12.125" style="11" customWidth="1"/>
-    <col min="514" max="514" width="20.125" style="11" customWidth="1"/>
-    <col min="515" max="515" width="26.75" style="11" customWidth="1"/>
-    <col min="516" max="516" width="13.375" style="11" customWidth="1"/>
-    <col min="517" max="517" width="17" style="11" customWidth="1"/>
-    <col min="518" max="518" width="19.125" style="11" customWidth="1"/>
-    <col min="519" max="520" width="5.875" style="11" customWidth="1"/>
-    <col min="521" max="521" width="6.625" style="11" customWidth="1"/>
-    <col min="522" max="522" width="8.125" style="11" customWidth="1"/>
-    <col min="523" max="523" width="10.125" style="11" customWidth="1"/>
-    <col min="524" max="524" width="7.25" style="11" customWidth="1"/>
-    <col min="525" max="525" width="11.875" style="11" customWidth="1"/>
-    <col min="526" max="526" width="2.125" style="11" customWidth="1"/>
-    <col min="527" max="528" width="12.5" style="11" customWidth="1"/>
-    <col min="529" max="762" width="9" style="11"/>
-    <col min="763" max="763" width="6.875" style="11" customWidth="1"/>
-    <col min="764" max="764" width="10.125" style="11" customWidth="1"/>
-    <col min="765" max="765" width="11.125" style="11" customWidth="1"/>
-    <col min="766" max="766" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="767" max="767" width="21.625" style="11" customWidth="1"/>
-    <col min="768" max="768" width="6.25" style="11" customWidth="1"/>
-    <col min="769" max="769" width="12.125" style="11" customWidth="1"/>
-    <col min="770" max="770" width="20.125" style="11" customWidth="1"/>
-    <col min="771" max="771" width="26.75" style="11" customWidth="1"/>
-    <col min="772" max="772" width="13.375" style="11" customWidth="1"/>
-    <col min="773" max="773" width="17" style="11" customWidth="1"/>
-    <col min="774" max="774" width="19.125" style="11" customWidth="1"/>
-    <col min="775" max="776" width="5.875" style="11" customWidth="1"/>
-    <col min="777" max="777" width="6.625" style="11" customWidth="1"/>
-    <col min="778" max="778" width="8.125" style="11" customWidth="1"/>
-    <col min="779" max="779" width="10.125" style="11" customWidth="1"/>
-    <col min="780" max="780" width="7.25" style="11" customWidth="1"/>
-    <col min="781" max="781" width="11.875" style="11" customWidth="1"/>
-    <col min="782" max="782" width="2.125" style="11" customWidth="1"/>
-    <col min="783" max="784" width="12.5" style="11" customWidth="1"/>
-    <col min="785" max="1018" width="9" style="11"/>
-    <col min="1019" max="1019" width="6.875" style="11" customWidth="1"/>
-    <col min="1020" max="1020" width="10.125" style="11" customWidth="1"/>
-    <col min="1021" max="1021" width="11.125" style="11" customWidth="1"/>
-    <col min="1022" max="1022" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="1023" max="1023" width="21.625" style="11" customWidth="1"/>
-    <col min="1024" max="1024" width="6.25" style="11" customWidth="1"/>
-    <col min="1025" max="1025" width="12.125" style="11" customWidth="1"/>
-    <col min="1026" max="1026" width="20.125" style="11" customWidth="1"/>
-    <col min="1027" max="1027" width="26.75" style="11" customWidth="1"/>
-    <col min="1028" max="1028" width="13.375" style="11" customWidth="1"/>
-    <col min="1029" max="1029" width="17" style="11" customWidth="1"/>
-    <col min="1030" max="1030" width="19.125" style="11" customWidth="1"/>
-    <col min="1031" max="1032" width="5.875" style="11" customWidth="1"/>
-    <col min="1033" max="1033" width="6.625" style="11" customWidth="1"/>
-    <col min="1034" max="1034" width="8.125" style="11" customWidth="1"/>
-    <col min="1035" max="1035" width="10.125" style="11" customWidth="1"/>
-    <col min="1036" max="1036" width="7.25" style="11" customWidth="1"/>
-    <col min="1037" max="1037" width="11.875" style="11" customWidth="1"/>
-    <col min="1038" max="1038" width="2.125" style="11" customWidth="1"/>
-    <col min="1039" max="1040" width="12.5" style="11" customWidth="1"/>
-    <col min="1041" max="1274" width="9" style="11"/>
-    <col min="1275" max="1275" width="6.875" style="11" customWidth="1"/>
-    <col min="1276" max="1276" width="10.125" style="11" customWidth="1"/>
-    <col min="1277" max="1277" width="11.125" style="11" customWidth="1"/>
-    <col min="1278" max="1278" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="1279" max="1279" width="21.625" style="11" customWidth="1"/>
-    <col min="1280" max="1280" width="6.25" style="11" customWidth="1"/>
-    <col min="1281" max="1281" width="12.125" style="11" customWidth="1"/>
-    <col min="1282" max="1282" width="20.125" style="11" customWidth="1"/>
-    <col min="1283" max="1283" width="26.75" style="11" customWidth="1"/>
-    <col min="1284" max="1284" width="13.375" style="11" customWidth="1"/>
-    <col min="1285" max="1285" width="17" style="11" customWidth="1"/>
-    <col min="1286" max="1286" width="19.125" style="11" customWidth="1"/>
-    <col min="1287" max="1288" width="5.875" style="11" customWidth="1"/>
-    <col min="1289" max="1289" width="6.625" style="11" customWidth="1"/>
-    <col min="1290" max="1290" width="8.125" style="11" customWidth="1"/>
-    <col min="1291" max="1291" width="10.125" style="11" customWidth="1"/>
-    <col min="1292" max="1292" width="7.25" style="11" customWidth="1"/>
-    <col min="1293" max="1293" width="11.875" style="11" customWidth="1"/>
-    <col min="1294" max="1294" width="2.125" style="11" customWidth="1"/>
-    <col min="1295" max="1296" width="12.5" style="11" customWidth="1"/>
-    <col min="1297" max="1530" width="9" style="11"/>
-    <col min="1531" max="1531" width="6.875" style="11" customWidth="1"/>
-    <col min="1532" max="1532" width="10.125" style="11" customWidth="1"/>
-    <col min="1533" max="1533" width="11.125" style="11" customWidth="1"/>
-    <col min="1534" max="1534" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="1535" max="1535" width="21.625" style="11" customWidth="1"/>
-    <col min="1536" max="1536" width="6.25" style="11" customWidth="1"/>
-    <col min="1537" max="1537" width="12.125" style="11" customWidth="1"/>
-    <col min="1538" max="1538" width="20.125" style="11" customWidth="1"/>
-    <col min="1539" max="1539" width="26.75" style="11" customWidth="1"/>
-    <col min="1540" max="1540" width="13.375" style="11" customWidth="1"/>
-    <col min="1541" max="1541" width="17" style="11" customWidth="1"/>
-    <col min="1542" max="1542" width="19.125" style="11" customWidth="1"/>
-    <col min="1543" max="1544" width="5.875" style="11" customWidth="1"/>
-    <col min="1545" max="1545" width="6.625" style="11" customWidth="1"/>
-    <col min="1546" max="1546" width="8.125" style="11" customWidth="1"/>
-    <col min="1547" max="1547" width="10.125" style="11" customWidth="1"/>
-    <col min="1548" max="1548" width="7.25" style="11" customWidth="1"/>
-    <col min="1549" max="1549" width="11.875" style="11" customWidth="1"/>
-    <col min="1550" max="1550" width="2.125" style="11" customWidth="1"/>
-    <col min="1551" max="1552" width="12.5" style="11" customWidth="1"/>
-    <col min="1553" max="1786" width="9" style="11"/>
-    <col min="1787" max="1787" width="6.875" style="11" customWidth="1"/>
-    <col min="1788" max="1788" width="10.125" style="11" customWidth="1"/>
-    <col min="1789" max="1789" width="11.125" style="11" customWidth="1"/>
-    <col min="1790" max="1790" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="1791" max="1791" width="21.625" style="11" customWidth="1"/>
-    <col min="1792" max="1792" width="6.25" style="11" customWidth="1"/>
-    <col min="1793" max="1793" width="12.125" style="11" customWidth="1"/>
-    <col min="1794" max="1794" width="20.125" style="11" customWidth="1"/>
-    <col min="1795" max="1795" width="26.75" style="11" customWidth="1"/>
-    <col min="1796" max="1796" width="13.375" style="11" customWidth="1"/>
-    <col min="1797" max="1797" width="17" style="11" customWidth="1"/>
-    <col min="1798" max="1798" width="19.125" style="11" customWidth="1"/>
-    <col min="1799" max="1800" width="5.875" style="11" customWidth="1"/>
-    <col min="1801" max="1801" width="6.625" style="11" customWidth="1"/>
-    <col min="1802" max="1802" width="8.125" style="11" customWidth="1"/>
-    <col min="1803" max="1803" width="10.125" style="11" customWidth="1"/>
-    <col min="1804" max="1804" width="7.25" style="11" customWidth="1"/>
-    <col min="1805" max="1805" width="11.875" style="11" customWidth="1"/>
-    <col min="1806" max="1806" width="2.125" style="11" customWidth="1"/>
-    <col min="1807" max="1808" width="12.5" style="11" customWidth="1"/>
-    <col min="1809" max="2042" width="9" style="11"/>
-    <col min="2043" max="2043" width="6.875" style="11" customWidth="1"/>
-    <col min="2044" max="2044" width="10.125" style="11" customWidth="1"/>
-    <col min="2045" max="2045" width="11.125" style="11" customWidth="1"/>
-    <col min="2046" max="2046" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="2047" max="2047" width="21.625" style="11" customWidth="1"/>
-    <col min="2048" max="2048" width="6.25" style="11" customWidth="1"/>
-    <col min="2049" max="2049" width="12.125" style="11" customWidth="1"/>
-    <col min="2050" max="2050" width="20.125" style="11" customWidth="1"/>
-    <col min="2051" max="2051" width="26.75" style="11" customWidth="1"/>
-    <col min="2052" max="2052" width="13.375" style="11" customWidth="1"/>
-    <col min="2053" max="2053" width="17" style="11" customWidth="1"/>
-    <col min="2054" max="2054" width="19.125" style="11" customWidth="1"/>
-    <col min="2055" max="2056" width="5.875" style="11" customWidth="1"/>
-    <col min="2057" max="2057" width="6.625" style="11" customWidth="1"/>
-    <col min="2058" max="2058" width="8.125" style="11" customWidth="1"/>
-    <col min="2059" max="2059" width="10.125" style="11" customWidth="1"/>
-    <col min="2060" max="2060" width="7.25" style="11" customWidth="1"/>
-    <col min="2061" max="2061" width="11.875" style="11" customWidth="1"/>
-    <col min="2062" max="2062" width="2.125" style="11" customWidth="1"/>
-    <col min="2063" max="2064" width="12.5" style="11" customWidth="1"/>
-    <col min="2065" max="2298" width="9" style="11"/>
-    <col min="2299" max="2299" width="6.875" style="11" customWidth="1"/>
-    <col min="2300" max="2300" width="10.125" style="11" customWidth="1"/>
-    <col min="2301" max="2301" width="11.125" style="11" customWidth="1"/>
-    <col min="2302" max="2302" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="2303" max="2303" width="21.625" style="11" customWidth="1"/>
-    <col min="2304" max="2304" width="6.25" style="11" customWidth="1"/>
-    <col min="2305" max="2305" width="12.125" style="11" customWidth="1"/>
-    <col min="2306" max="2306" width="20.125" style="11" customWidth="1"/>
-    <col min="2307" max="2307" width="26.75" style="11" customWidth="1"/>
-    <col min="2308" max="2308" width="13.375" style="11" customWidth="1"/>
-    <col min="2309" max="2309" width="17" style="11" customWidth="1"/>
-    <col min="2310" max="2310" width="19.125" style="11" customWidth="1"/>
-    <col min="2311" max="2312" width="5.875" style="11" customWidth="1"/>
-    <col min="2313" max="2313" width="6.625" style="11" customWidth="1"/>
-    <col min="2314" max="2314" width="8.125" style="11" customWidth="1"/>
-    <col min="2315" max="2315" width="10.125" style="11" customWidth="1"/>
-    <col min="2316" max="2316" width="7.25" style="11" customWidth="1"/>
-    <col min="2317" max="2317" width="11.875" style="11" customWidth="1"/>
-    <col min="2318" max="2318" width="2.125" style="11" customWidth="1"/>
-    <col min="2319" max="2320" width="12.5" style="11" customWidth="1"/>
-    <col min="2321" max="2554" width="9" style="11"/>
-    <col min="2555" max="2555" width="6.875" style="11" customWidth="1"/>
-    <col min="2556" max="2556" width="10.125" style="11" customWidth="1"/>
-    <col min="2557" max="2557" width="11.125" style="11" customWidth="1"/>
-    <col min="2558" max="2558" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="2559" max="2559" width="21.625" style="11" customWidth="1"/>
-    <col min="2560" max="2560" width="6.25" style="11" customWidth="1"/>
-    <col min="2561" max="2561" width="12.125" style="11" customWidth="1"/>
-    <col min="2562" max="2562" width="20.125" style="11" customWidth="1"/>
-    <col min="2563" max="2563" width="26.75" style="11" customWidth="1"/>
-    <col min="2564" max="2564" width="13.375" style="11" customWidth="1"/>
-    <col min="2565" max="2565" width="17" style="11" customWidth="1"/>
-    <col min="2566" max="2566" width="19.125" style="11" customWidth="1"/>
-    <col min="2567" max="2568" width="5.875" style="11" customWidth="1"/>
-    <col min="2569" max="2569" width="6.625" style="11" customWidth="1"/>
-    <col min="2570" max="2570" width="8.125" style="11" customWidth="1"/>
-    <col min="2571" max="2571" width="10.125" style="11" customWidth="1"/>
-    <col min="2572" max="2572" width="7.25" style="11" customWidth="1"/>
-    <col min="2573" max="2573" width="11.875" style="11" customWidth="1"/>
-    <col min="2574" max="2574" width="2.125" style="11" customWidth="1"/>
-    <col min="2575" max="2576" width="12.5" style="11" customWidth="1"/>
-    <col min="2577" max="2810" width="9" style="11"/>
-    <col min="2811" max="2811" width="6.875" style="11" customWidth="1"/>
-    <col min="2812" max="2812" width="10.125" style="11" customWidth="1"/>
-    <col min="2813" max="2813" width="11.125" style="11" customWidth="1"/>
-    <col min="2814" max="2814" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="2815" max="2815" width="21.625" style="11" customWidth="1"/>
-    <col min="2816" max="2816" width="6.25" style="11" customWidth="1"/>
-    <col min="2817" max="2817" width="12.125" style="11" customWidth="1"/>
-    <col min="2818" max="2818" width="20.125" style="11" customWidth="1"/>
-    <col min="2819" max="2819" width="26.75" style="11" customWidth="1"/>
-    <col min="2820" max="2820" width="13.375" style="11" customWidth="1"/>
-    <col min="2821" max="2821" width="17" style="11" customWidth="1"/>
-    <col min="2822" max="2822" width="19.125" style="11" customWidth="1"/>
-    <col min="2823" max="2824" width="5.875" style="11" customWidth="1"/>
-    <col min="2825" max="2825" width="6.625" style="11" customWidth="1"/>
-    <col min="2826" max="2826" width="8.125" style="11" customWidth="1"/>
-    <col min="2827" max="2827" width="10.125" style="11" customWidth="1"/>
-    <col min="2828" max="2828" width="7.25" style="11" customWidth="1"/>
-    <col min="2829" max="2829" width="11.875" style="11" customWidth="1"/>
-    <col min="2830" max="2830" width="2.125" style="11" customWidth="1"/>
-    <col min="2831" max="2832" width="12.5" style="11" customWidth="1"/>
-    <col min="2833" max="3066" width="9" style="11"/>
-    <col min="3067" max="3067" width="6.875" style="11" customWidth="1"/>
-    <col min="3068" max="3068" width="10.125" style="11" customWidth="1"/>
-    <col min="3069" max="3069" width="11.125" style="11" customWidth="1"/>
-    <col min="3070" max="3070" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="3071" max="3071" width="21.625" style="11" customWidth="1"/>
-    <col min="3072" max="3072" width="6.25" style="11" customWidth="1"/>
-    <col min="3073" max="3073" width="12.125" style="11" customWidth="1"/>
-    <col min="3074" max="3074" width="20.125" style="11" customWidth="1"/>
-    <col min="3075" max="3075" width="26.75" style="11" customWidth="1"/>
-    <col min="3076" max="3076" width="13.375" style="11" customWidth="1"/>
-    <col min="3077" max="3077" width="17" style="11" customWidth="1"/>
-    <col min="3078" max="3078" width="19.125" style="11" customWidth="1"/>
-    <col min="3079" max="3080" width="5.875" style="11" customWidth="1"/>
-    <col min="3081" max="3081" width="6.625" style="11" customWidth="1"/>
-    <col min="3082" max="3082" width="8.125" style="11" customWidth="1"/>
-    <col min="3083" max="3083" width="10.125" style="11" customWidth="1"/>
-    <col min="3084" max="3084" width="7.25" style="11" customWidth="1"/>
-    <col min="3085" max="3085" width="11.875" style="11" customWidth="1"/>
-    <col min="3086" max="3086" width="2.125" style="11" customWidth="1"/>
-    <col min="3087" max="3088" width="12.5" style="11" customWidth="1"/>
-    <col min="3089" max="3322" width="9" style="11"/>
-    <col min="3323" max="3323" width="6.875" style="11" customWidth="1"/>
-    <col min="3324" max="3324" width="10.125" style="11" customWidth="1"/>
-    <col min="3325" max="3325" width="11.125" style="11" customWidth="1"/>
-    <col min="3326" max="3326" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="3327" max="3327" width="21.625" style="11" customWidth="1"/>
-    <col min="3328" max="3328" width="6.25" style="11" customWidth="1"/>
-    <col min="3329" max="3329" width="12.125" style="11" customWidth="1"/>
-    <col min="3330" max="3330" width="20.125" style="11" customWidth="1"/>
-    <col min="3331" max="3331" width="26.75" style="11" customWidth="1"/>
-    <col min="3332" max="3332" width="13.375" style="11" customWidth="1"/>
-    <col min="3333" max="3333" width="17" style="11" customWidth="1"/>
-    <col min="3334" max="3334" width="19.125" style="11" customWidth="1"/>
-    <col min="3335" max="3336" width="5.875" style="11" customWidth="1"/>
-    <col min="3337" max="3337" width="6.625" style="11" customWidth="1"/>
-    <col min="3338" max="3338" width="8.125" style="11" customWidth="1"/>
-    <col min="3339" max="3339" width="10.125" style="11" customWidth="1"/>
-    <col min="3340" max="3340" width="7.25" style="11" customWidth="1"/>
-    <col min="3341" max="3341" width="11.875" style="11" customWidth="1"/>
-    <col min="3342" max="3342" width="2.125" style="11" customWidth="1"/>
-    <col min="3343" max="3344" width="12.5" style="11" customWidth="1"/>
-    <col min="3345" max="3578" width="9" style="11"/>
-    <col min="3579" max="3579" width="6.875" style="11" customWidth="1"/>
-    <col min="3580" max="3580" width="10.125" style="11" customWidth="1"/>
-    <col min="3581" max="3581" width="11.125" style="11" customWidth="1"/>
-    <col min="3582" max="3582" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="3583" max="3583" width="21.625" style="11" customWidth="1"/>
-    <col min="3584" max="3584" width="6.25" style="11" customWidth="1"/>
-    <col min="3585" max="3585" width="12.125" style="11" customWidth="1"/>
-    <col min="3586" max="3586" width="20.125" style="11" customWidth="1"/>
-    <col min="3587" max="3587" width="26.75" style="11" customWidth="1"/>
-    <col min="3588" max="3588" width="13.375" style="11" customWidth="1"/>
-    <col min="3589" max="3589" width="17" style="11" customWidth="1"/>
-    <col min="3590" max="3590" width="19.125" style="11" customWidth="1"/>
-    <col min="3591" max="3592" width="5.875" style="11" customWidth="1"/>
-    <col min="3593" max="3593" width="6.625" style="11" customWidth="1"/>
-    <col min="3594" max="3594" width="8.125" style="11" customWidth="1"/>
-    <col min="3595" max="3595" width="10.125" style="11" customWidth="1"/>
-    <col min="3596" max="3596" width="7.25" style="11" customWidth="1"/>
-    <col min="3597" max="3597" width="11.875" style="11" customWidth="1"/>
-    <col min="3598" max="3598" width="2.125" style="11" customWidth="1"/>
-    <col min="3599" max="3600" width="12.5" style="11" customWidth="1"/>
-    <col min="3601" max="3834" width="9" style="11"/>
-    <col min="3835" max="3835" width="6.875" style="11" customWidth="1"/>
-    <col min="3836" max="3836" width="10.125" style="11" customWidth="1"/>
-    <col min="3837" max="3837" width="11.125" style="11" customWidth="1"/>
-    <col min="3838" max="3838" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="3839" max="3839" width="21.625" style="11" customWidth="1"/>
-    <col min="3840" max="3840" width="6.25" style="11" customWidth="1"/>
-    <col min="3841" max="3841" width="12.125" style="11" customWidth="1"/>
-    <col min="3842" max="3842" width="20.125" style="11" customWidth="1"/>
-    <col min="3843" max="3843" width="26.75" style="11" customWidth="1"/>
-    <col min="3844" max="3844" width="13.375" style="11" customWidth="1"/>
-    <col min="3845" max="3845" width="17" style="11" customWidth="1"/>
-    <col min="3846" max="3846" width="19.125" style="11" customWidth="1"/>
-    <col min="3847" max="3848" width="5.875" style="11" customWidth="1"/>
-    <col min="3849" max="3849" width="6.625" style="11" customWidth="1"/>
-    <col min="3850" max="3850" width="8.125" style="11" customWidth="1"/>
-    <col min="3851" max="3851" width="10.125" style="11" customWidth="1"/>
-    <col min="3852" max="3852" width="7.25" style="11" customWidth="1"/>
-    <col min="3853" max="3853" width="11.875" style="11" customWidth="1"/>
-    <col min="3854" max="3854" width="2.125" style="11" customWidth="1"/>
-    <col min="3855" max="3856" width="12.5" style="11" customWidth="1"/>
-    <col min="3857" max="4090" width="9" style="11"/>
-    <col min="4091" max="4091" width="6.875" style="11" customWidth="1"/>
-    <col min="4092" max="4092" width="10.125" style="11" customWidth="1"/>
-    <col min="4093" max="4093" width="11.125" style="11" customWidth="1"/>
-    <col min="4094" max="4094" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="4095" max="4095" width="21.625" style="11" customWidth="1"/>
-    <col min="4096" max="4096" width="6.25" style="11" customWidth="1"/>
-    <col min="4097" max="4097" width="12.125" style="11" customWidth="1"/>
-    <col min="4098" max="4098" width="20.125" style="11" customWidth="1"/>
-    <col min="4099" max="4099" width="26.75" style="11" customWidth="1"/>
-    <col min="4100" max="4100" width="13.375" style="11" customWidth="1"/>
-    <col min="4101" max="4101" width="17" style="11" customWidth="1"/>
-    <col min="4102" max="4102" width="19.125" style="11" customWidth="1"/>
-    <col min="4103" max="4104" width="5.875" style="11" customWidth="1"/>
-    <col min="4105" max="4105" width="6.625" style="11" customWidth="1"/>
-    <col min="4106" max="4106" width="8.125" style="11" customWidth="1"/>
-    <col min="4107" max="4107" width="10.125" style="11" customWidth="1"/>
-    <col min="4108" max="4108" width="7.25" style="11" customWidth="1"/>
-    <col min="4109" max="4109" width="11.875" style="11" customWidth="1"/>
-    <col min="4110" max="4110" width="2.125" style="11" customWidth="1"/>
-    <col min="4111" max="4112" width="12.5" style="11" customWidth="1"/>
-    <col min="4113" max="4346" width="9" style="11"/>
-    <col min="4347" max="4347" width="6.875" style="11" customWidth="1"/>
-    <col min="4348" max="4348" width="10.125" style="11" customWidth="1"/>
-    <col min="4349" max="4349" width="11.125" style="11" customWidth="1"/>
-    <col min="4350" max="4350" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="4351" max="4351" width="21.625" style="11" customWidth="1"/>
-    <col min="4352" max="4352" width="6.25" style="11" customWidth="1"/>
-    <col min="4353" max="4353" width="12.125" style="11" customWidth="1"/>
-    <col min="4354" max="4354" width="20.125" style="11" customWidth="1"/>
-    <col min="4355" max="4355" width="26.75" style="11" customWidth="1"/>
-    <col min="4356" max="4356" width="13.375" style="11" customWidth="1"/>
-    <col min="4357" max="4357" width="17" style="11" customWidth="1"/>
-    <col min="4358" max="4358" width="19.125" style="11" customWidth="1"/>
-    <col min="4359" max="4360" width="5.875" style="11" customWidth="1"/>
-    <col min="4361" max="4361" width="6.625" style="11" customWidth="1"/>
-    <col min="4362" max="4362" width="8.125" style="11" customWidth="1"/>
-    <col min="4363" max="4363" width="10.125" style="11" customWidth="1"/>
-    <col min="4364" max="4364" width="7.25" style="11" customWidth="1"/>
-    <col min="4365" max="4365" width="11.875" style="11" customWidth="1"/>
-    <col min="4366" max="4366" width="2.125" style="11" customWidth="1"/>
-    <col min="4367" max="4368" width="12.5" style="11" customWidth="1"/>
-    <col min="4369" max="4602" width="9" style="11"/>
-    <col min="4603" max="4603" width="6.875" style="11" customWidth="1"/>
-    <col min="4604" max="4604" width="10.125" style="11" customWidth="1"/>
-    <col min="4605" max="4605" width="11.125" style="11" customWidth="1"/>
-    <col min="4606" max="4606" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="4607" max="4607" width="21.625" style="11" customWidth="1"/>
-    <col min="4608" max="4608" width="6.25" style="11" customWidth="1"/>
-    <col min="4609" max="4609" width="12.125" style="11" customWidth="1"/>
-    <col min="4610" max="4610" width="20.125" style="11" customWidth="1"/>
-    <col min="4611" max="4611" width="26.75" style="11" customWidth="1"/>
-    <col min="4612" max="4612" width="13.375" style="11" customWidth="1"/>
-    <col min="4613" max="4613" width="17" style="11" customWidth="1"/>
-    <col min="4614" max="4614" width="19.125" style="11" customWidth="1"/>
-    <col min="4615" max="4616" width="5.875" style="11" customWidth="1"/>
-    <col min="4617" max="4617" width="6.625" style="11" customWidth="1"/>
-    <col min="4618" max="4618" width="8.125" style="11" customWidth="1"/>
-    <col min="4619" max="4619" width="10.125" style="11" customWidth="1"/>
-    <col min="4620" max="4620" width="7.25" style="11" customWidth="1"/>
-    <col min="4621" max="4621" width="11.875" style="11" customWidth="1"/>
-    <col min="4622" max="4622" width="2.125" style="11" customWidth="1"/>
-    <col min="4623" max="4624" width="12.5" style="11" customWidth="1"/>
-    <col min="4625" max="4858" width="9" style="11"/>
-    <col min="4859" max="4859" width="6.875" style="11" customWidth="1"/>
-    <col min="4860" max="4860" width="10.125" style="11" customWidth="1"/>
-    <col min="4861" max="4861" width="11.125" style="11" customWidth="1"/>
-    <col min="4862" max="4862" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="4863" max="4863" width="21.625" style="11" customWidth="1"/>
-    <col min="4864" max="4864" width="6.25" style="11" customWidth="1"/>
-    <col min="4865" max="4865" width="12.125" style="11" customWidth="1"/>
-    <col min="4866" max="4866" width="20.125" style="11" customWidth="1"/>
-    <col min="4867" max="4867" width="26.75" style="11" customWidth="1"/>
-    <col min="4868" max="4868" width="13.375" style="11" customWidth="1"/>
-    <col min="4869" max="4869" width="17" style="11" customWidth="1"/>
-    <col min="4870" max="4870" width="19.125" style="11" customWidth="1"/>
-    <col min="4871" max="4872" width="5.875" style="11" customWidth="1"/>
-    <col min="4873" max="4873" width="6.625" style="11" customWidth="1"/>
-    <col min="4874" max="4874" width="8.125" style="11" customWidth="1"/>
-    <col min="4875" max="4875" width="10.125" style="11" customWidth="1"/>
-    <col min="4876" max="4876" width="7.25" style="11" customWidth="1"/>
-    <col min="4877" max="4877" width="11.875" style="11" customWidth="1"/>
-    <col min="4878" max="4878" width="2.125" style="11" customWidth="1"/>
-    <col min="4879" max="4880" width="12.5" style="11" customWidth="1"/>
-    <col min="4881" max="5114" width="9" style="11"/>
-    <col min="5115" max="5115" width="6.875" style="11" customWidth="1"/>
-    <col min="5116" max="5116" width="10.125" style="11" customWidth="1"/>
-    <col min="5117" max="5117" width="11.125" style="11" customWidth="1"/>
-    <col min="5118" max="5118" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="5119" max="5119" width="21.625" style="11" customWidth="1"/>
-    <col min="5120" max="5120" width="6.25" style="11" customWidth="1"/>
-    <col min="5121" max="5121" width="12.125" style="11" customWidth="1"/>
-    <col min="5122" max="5122" width="20.125" style="11" customWidth="1"/>
-    <col min="5123" max="5123" width="26.75" style="11" customWidth="1"/>
-    <col min="5124" max="5124" width="13.375" style="11" customWidth="1"/>
-    <col min="5125" max="5125" width="17" style="11" customWidth="1"/>
-    <col min="5126" max="5126" width="19.125" style="11" customWidth="1"/>
-    <col min="5127" max="5128" width="5.875" style="11" customWidth="1"/>
-    <col min="5129" max="5129" width="6.625" style="11" customWidth="1"/>
-    <col min="5130" max="5130" width="8.125" style="11" customWidth="1"/>
-    <col min="5131" max="5131" width="10.125" style="11" customWidth="1"/>
-    <col min="5132" max="5132" width="7.25" style="11" customWidth="1"/>
-    <col min="5133" max="5133" width="11.875" style="11" customWidth="1"/>
-    <col min="5134" max="5134" width="2.125" style="11" customWidth="1"/>
-    <col min="5135" max="5136" width="12.5" style="11" customWidth="1"/>
-    <col min="5137" max="5370" width="9" style="11"/>
-    <col min="5371" max="5371" width="6.875" style="11" customWidth="1"/>
-    <col min="5372" max="5372" width="10.125" style="11" customWidth="1"/>
-    <col min="5373" max="5373" width="11.125" style="11" customWidth="1"/>
-    <col min="5374" max="5374" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="5375" max="5375" width="21.625" style="11" customWidth="1"/>
-    <col min="5376" max="5376" width="6.25" style="11" customWidth="1"/>
-    <col min="5377" max="5377" width="12.125" style="11" customWidth="1"/>
-    <col min="5378" max="5378" width="20.125" style="11" customWidth="1"/>
-    <col min="5379" max="5379" width="26.75" style="11" customWidth="1"/>
-    <col min="5380" max="5380" width="13.375" style="11" customWidth="1"/>
-    <col min="5381" max="5381" width="17" style="11" customWidth="1"/>
-    <col min="5382" max="5382" width="19.125" style="11" customWidth="1"/>
-    <col min="5383" max="5384" width="5.875" style="11" customWidth="1"/>
-    <col min="5385" max="5385" width="6.625" style="11" customWidth="1"/>
-    <col min="5386" max="5386" width="8.125" style="11" customWidth="1"/>
-    <col min="5387" max="5387" width="10.125" style="11" customWidth="1"/>
-    <col min="5388" max="5388" width="7.25" style="11" customWidth="1"/>
-    <col min="5389" max="5389" width="11.875" style="11" customWidth="1"/>
-    <col min="5390" max="5390" width="2.125" style="11" customWidth="1"/>
-    <col min="5391" max="5392" width="12.5" style="11" customWidth="1"/>
-    <col min="5393" max="5626" width="9" style="11"/>
-    <col min="5627" max="5627" width="6.875" style="11" customWidth="1"/>
-    <col min="5628" max="5628" width="10.125" style="11" customWidth="1"/>
-    <col min="5629" max="5629" width="11.125" style="11" customWidth="1"/>
-    <col min="5630" max="5630" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="5631" max="5631" width="21.625" style="11" customWidth="1"/>
-    <col min="5632" max="5632" width="6.25" style="11" customWidth="1"/>
-    <col min="5633" max="5633" width="12.125" style="11" customWidth="1"/>
-    <col min="5634" max="5634" width="20.125" style="11" customWidth="1"/>
-    <col min="5635" max="5635" width="26.75" style="11" customWidth="1"/>
-    <col min="5636" max="5636" width="13.375" style="11" customWidth="1"/>
-    <col min="5637" max="5637" width="17" style="11" customWidth="1"/>
-    <col min="5638" max="5638" width="19.125" style="11" customWidth="1"/>
-    <col min="5639" max="5640" width="5.875" style="11" customWidth="1"/>
-    <col min="5641" max="5641" width="6.625" style="11" customWidth="1"/>
-    <col min="5642" max="5642" width="8.125" style="11" customWidth="1"/>
-    <col min="5643" max="5643" width="10.125" style="11" customWidth="1"/>
-    <col min="5644" max="5644" width="7.25" style="11" customWidth="1"/>
-    <col min="5645" max="5645" width="11.875" style="11" customWidth="1"/>
-    <col min="5646" max="5646" width="2.125" style="11" customWidth="1"/>
-    <col min="5647" max="5648" width="12.5" style="11" customWidth="1"/>
-    <col min="5649" max="5882" width="9" style="11"/>
-    <col min="5883" max="5883" width="6.875" style="11" customWidth="1"/>
-    <col min="5884" max="5884" width="10.125" style="11" customWidth="1"/>
-    <col min="5885" max="5885" width="11.125" style="11" customWidth="1"/>
-    <col min="5886" max="5886" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="5887" max="5887" width="21.625" style="11" customWidth="1"/>
-    <col min="5888" max="5888" width="6.25" style="11" customWidth="1"/>
-    <col min="5889" max="5889" width="12.125" style="11" customWidth="1"/>
-    <col min="5890" max="5890" width="20.125" style="11" customWidth="1"/>
-    <col min="5891" max="5891" width="26.75" style="11" customWidth="1"/>
-    <col min="5892" max="5892" width="13.375" style="11" customWidth="1"/>
-    <col min="5893" max="5893" width="17" style="11" customWidth="1"/>
-    <col min="5894" max="5894" width="19.125" style="11" customWidth="1"/>
-    <col min="5895" max="5896" width="5.875" style="11" customWidth="1"/>
-    <col min="5897" max="5897" width="6.625" style="11" customWidth="1"/>
-    <col min="5898" max="5898" width="8.125" style="11" customWidth="1"/>
-    <col min="5899" max="5899" width="10.125" style="11" customWidth="1"/>
-    <col min="5900" max="5900" width="7.25" style="11" customWidth="1"/>
-    <col min="5901" max="5901" width="11.875" style="11" customWidth="1"/>
-    <col min="5902" max="5902" width="2.125" style="11" customWidth="1"/>
-    <col min="5903" max="5904" width="12.5" style="11" customWidth="1"/>
-    <col min="5905" max="6138" width="9" style="11"/>
-    <col min="6139" max="6139" width="6.875" style="11" customWidth="1"/>
-    <col min="6140" max="6140" width="10.125" style="11" customWidth="1"/>
-    <col min="6141" max="6141" width="11.125" style="11" customWidth="1"/>
-    <col min="6142" max="6142" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="6143" max="6143" width="21.625" style="11" customWidth="1"/>
-    <col min="6144" max="6144" width="6.25" style="11" customWidth="1"/>
-    <col min="6145" max="6145" width="12.125" style="11" customWidth="1"/>
-    <col min="6146" max="6146" width="20.125" style="11" customWidth="1"/>
-    <col min="6147" max="6147" width="26.75" style="11" customWidth="1"/>
-    <col min="6148" max="6148" width="13.375" style="11" customWidth="1"/>
-    <col min="6149" max="6149" width="17" style="11" customWidth="1"/>
-    <col min="6150" max="6150" width="19.125" style="11" customWidth="1"/>
-    <col min="6151" max="6152" width="5.875" style="11" customWidth="1"/>
-    <col min="6153" max="6153" width="6.625" style="11" customWidth="1"/>
-    <col min="6154" max="6154" width="8.125" style="11" customWidth="1"/>
-    <col min="6155" max="6155" width="10.125" style="11" customWidth="1"/>
-    <col min="6156" max="6156" width="7.25" style="11" customWidth="1"/>
-    <col min="6157" max="6157" width="11.875" style="11" customWidth="1"/>
-    <col min="6158" max="6158" width="2.125" style="11" customWidth="1"/>
-    <col min="6159" max="6160" width="12.5" style="11" customWidth="1"/>
-    <col min="6161" max="6394" width="9" style="11"/>
-    <col min="6395" max="6395" width="6.875" style="11" customWidth="1"/>
-    <col min="6396" max="6396" width="10.125" style="11" customWidth="1"/>
-    <col min="6397" max="6397" width="11.125" style="11" customWidth="1"/>
-    <col min="6398" max="6398" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="6399" max="6399" width="21.625" style="11" customWidth="1"/>
-    <col min="6400" max="6400" width="6.25" style="11" customWidth="1"/>
-    <col min="6401" max="6401" width="12.125" style="11" customWidth="1"/>
-    <col min="6402" max="6402" width="20.125" style="11" customWidth="1"/>
-    <col min="6403" max="6403" width="26.75" style="11" customWidth="1"/>
-    <col min="6404" max="6404" width="13.375" style="11" customWidth="1"/>
-    <col min="6405" max="6405" width="17" style="11" customWidth="1"/>
-    <col min="6406" max="6406" width="19.125" style="11" customWidth="1"/>
-    <col min="6407" max="6408" width="5.875" style="11" customWidth="1"/>
-    <col min="6409" max="6409" width="6.625" style="11" customWidth="1"/>
-    <col min="6410" max="6410" width="8.125" style="11" customWidth="1"/>
-    <col min="6411" max="6411" width="10.125" style="11" customWidth="1"/>
-    <col min="6412" max="6412" width="7.25" style="11" customWidth="1"/>
-    <col min="6413" max="6413" width="11.875" style="11" customWidth="1"/>
-    <col min="6414" max="6414" width="2.125" style="11" customWidth="1"/>
-    <col min="6415" max="6416" width="12.5" style="11" customWidth="1"/>
-    <col min="6417" max="6650" width="9" style="11"/>
-    <col min="6651" max="6651" width="6.875" style="11" customWidth="1"/>
-    <col min="6652" max="6652" width="10.125" style="11" customWidth="1"/>
-    <col min="6653" max="6653" width="11.125" style="11" customWidth="1"/>
-    <col min="6654" max="6654" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="6655" max="6655" width="21.625" style="11" customWidth="1"/>
-    <col min="6656" max="6656" width="6.25" style="11" customWidth="1"/>
-    <col min="6657" max="6657" width="12.125" style="11" customWidth="1"/>
-    <col min="6658" max="6658" width="20.125" style="11" customWidth="1"/>
-    <col min="6659" max="6659" width="26.75" style="11" customWidth="1"/>
-    <col min="6660" max="6660" width="13.375" style="11" customWidth="1"/>
-    <col min="6661" max="6661" width="17" style="11" customWidth="1"/>
-    <col min="6662" max="6662" width="19.125" style="11" customWidth="1"/>
-    <col min="6663" max="6664" width="5.875" style="11" customWidth="1"/>
-    <col min="6665" max="6665" width="6.625" style="11" customWidth="1"/>
-    <col min="6666" max="6666" width="8.125" style="11" customWidth="1"/>
-    <col min="6667" max="6667" width="10.125" style="11" customWidth="1"/>
-    <col min="6668" max="6668" width="7.25" style="11" customWidth="1"/>
-    <col min="6669" max="6669" width="11.875" style="11" customWidth="1"/>
-    <col min="6670" max="6670" width="2.125" style="11" customWidth="1"/>
-    <col min="6671" max="6672" width="12.5" style="11" customWidth="1"/>
-    <col min="6673" max="6906" width="9" style="11"/>
-    <col min="6907" max="6907" width="6.875" style="11" customWidth="1"/>
-    <col min="6908" max="6908" width="10.125" style="11" customWidth="1"/>
-    <col min="6909" max="6909" width="11.125" style="11" customWidth="1"/>
-    <col min="6910" max="6910" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="6911" max="6911" width="21.625" style="11" customWidth="1"/>
-    <col min="6912" max="6912" width="6.25" style="11" customWidth="1"/>
-    <col min="6913" max="6913" width="12.125" style="11" customWidth="1"/>
-    <col min="6914" max="6914" width="20.125" style="11" customWidth="1"/>
-    <col min="6915" max="6915" width="26.75" style="11" customWidth="1"/>
-    <col min="6916" max="6916" width="13.375" style="11" customWidth="1"/>
-    <col min="6917" max="6917" width="17" style="11" customWidth="1"/>
-    <col min="6918" max="6918" width="19.125" style="11" customWidth="1"/>
-    <col min="6919" max="6920" width="5.875" style="11" customWidth="1"/>
-    <col min="6921" max="6921" width="6.625" style="11" customWidth="1"/>
-    <col min="6922" max="6922" width="8.125" style="11" customWidth="1"/>
-    <col min="6923" max="6923" width="10.125" style="11" customWidth="1"/>
-    <col min="6924" max="6924" width="7.25" style="11" customWidth="1"/>
-    <col min="6925" max="6925" width="11.875" style="11" customWidth="1"/>
-    <col min="6926" max="6926" width="2.125" style="11" customWidth="1"/>
-    <col min="6927" max="6928" width="12.5" style="11" customWidth="1"/>
-    <col min="6929" max="7162" width="9" style="11"/>
-    <col min="7163" max="7163" width="6.875" style="11" customWidth="1"/>
-    <col min="7164" max="7164" width="10.125" style="11" customWidth="1"/>
-    <col min="7165" max="7165" width="11.125" style="11" customWidth="1"/>
-    <col min="7166" max="7166" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="7167" max="7167" width="21.625" style="11" customWidth="1"/>
-    <col min="7168" max="7168" width="6.25" style="11" customWidth="1"/>
-    <col min="7169" max="7169" width="12.125" style="11" customWidth="1"/>
-    <col min="7170" max="7170" width="20.125" style="11" customWidth="1"/>
-    <col min="7171" max="7171" width="26.75" style="11" customWidth="1"/>
-    <col min="7172" max="7172" width="13.375" style="11" customWidth="1"/>
-    <col min="7173" max="7173" width="17" style="11" customWidth="1"/>
-    <col min="7174" max="7174" width="19.125" style="11" customWidth="1"/>
-    <col min="7175" max="7176" width="5.875" style="11" customWidth="1"/>
-    <col min="7177" max="7177" width="6.625" style="11" customWidth="1"/>
-    <col min="7178" max="7178" width="8.125" style="11" customWidth="1"/>
-    <col min="7179" max="7179" width="10.125" style="11" customWidth="1"/>
-    <col min="7180" max="7180" width="7.25" style="11" customWidth="1"/>
-    <col min="7181" max="7181" width="11.875" style="11" customWidth="1"/>
-    <col min="7182" max="7182" width="2.125" style="11" customWidth="1"/>
-    <col min="7183" max="7184" width="12.5" style="11" customWidth="1"/>
-    <col min="7185" max="7418" width="9" style="11"/>
-    <col min="7419" max="7419" width="6.875" style="11" customWidth="1"/>
-    <col min="7420" max="7420" width="10.125" style="11" customWidth="1"/>
-    <col min="7421" max="7421" width="11.125" style="11" customWidth="1"/>
-    <col min="7422" max="7422" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="7423" max="7423" width="21.625" style="11" customWidth="1"/>
-    <col min="7424" max="7424" width="6.25" style="11" customWidth="1"/>
-    <col min="7425" max="7425" width="12.125" style="11" customWidth="1"/>
-    <col min="7426" max="7426" width="20.125" style="11" customWidth="1"/>
-    <col min="7427" max="7427" width="26.75" style="11" customWidth="1"/>
-    <col min="7428" max="7428" width="13.375" style="11" customWidth="1"/>
-    <col min="7429" max="7429" width="17" style="11" customWidth="1"/>
-    <col min="7430" max="7430" width="19.125" style="11" customWidth="1"/>
-    <col min="7431" max="7432" width="5.875" style="11" customWidth="1"/>
-    <col min="7433" max="7433" width="6.625" style="11" customWidth="1"/>
-    <col min="7434" max="7434" width="8.125" style="11" customWidth="1"/>
-    <col min="7435" max="7435" width="10.125" style="11" customWidth="1"/>
-    <col min="7436" max="7436" width="7.25" style="11" customWidth="1"/>
-    <col min="7437" max="7437" width="11.875" style="11" customWidth="1"/>
-    <col min="7438" max="7438" width="2.125" style="11" customWidth="1"/>
-    <col min="7439" max="7440" width="12.5" style="11" customWidth="1"/>
-    <col min="7441" max="7674" width="9" style="11"/>
-    <col min="7675" max="7675" width="6.875" style="11" customWidth="1"/>
-    <col min="7676" max="7676" width="10.125" style="11" customWidth="1"/>
-    <col min="7677" max="7677" width="11.125" style="11" customWidth="1"/>
-    <col min="7678" max="7678" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="7679" max="7679" width="21.625" style="11" customWidth="1"/>
-    <col min="7680" max="7680" width="6.25" style="11" customWidth="1"/>
-    <col min="7681" max="7681" width="12.125" style="11" customWidth="1"/>
-    <col min="7682" max="7682" width="20.125" style="11" customWidth="1"/>
-    <col min="7683" max="7683" width="26.75" style="11" customWidth="1"/>
-    <col min="7684" max="7684" width="13.375" style="11" customWidth="1"/>
-    <col min="7685" max="7685" width="17" style="11" customWidth="1"/>
-    <col min="7686" max="7686" width="19.125" style="11" customWidth="1"/>
-    <col min="7687" max="7688" width="5.875" style="11" customWidth="1"/>
-    <col min="7689" max="7689" width="6.625" style="11" customWidth="1"/>
-    <col min="7690" max="7690" width="8.125" style="11" customWidth="1"/>
-    <col min="7691" max="7691" width="10.125" style="11" customWidth="1"/>
-    <col min="7692" max="7692" width="7.25" style="11" customWidth="1"/>
-    <col min="7693" max="7693" width="11.875" style="11" customWidth="1"/>
-    <col min="7694" max="7694" width="2.125" style="11" customWidth="1"/>
-    <col min="7695" max="7696" width="12.5" style="11" customWidth="1"/>
-    <col min="7697" max="7930" width="9" style="11"/>
-    <col min="7931" max="7931" width="6.875" style="11" customWidth="1"/>
-    <col min="7932" max="7932" width="10.125" style="11" customWidth="1"/>
-    <col min="7933" max="7933" width="11.125" style="11" customWidth="1"/>
-    <col min="7934" max="7934" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="7935" max="7935" width="21.625" style="11" customWidth="1"/>
-    <col min="7936" max="7936" width="6.25" style="11" customWidth="1"/>
-    <col min="7937" max="7937" width="12.125" style="11" customWidth="1"/>
-    <col min="7938" max="7938" width="20.125" style="11" customWidth="1"/>
-    <col min="7939" max="7939" width="26.75" style="11" customWidth="1"/>
-    <col min="7940" max="7940" width="13.375" style="11" customWidth="1"/>
-    <col min="7941" max="7941" width="17" style="11" customWidth="1"/>
-    <col min="7942" max="7942" width="19.125" style="11" customWidth="1"/>
-    <col min="7943" max="7944" width="5.875" style="11" customWidth="1"/>
-    <col min="7945" max="7945" width="6.625" style="11" customWidth="1"/>
-    <col min="7946" max="7946" width="8.125" style="11" customWidth="1"/>
-    <col min="7947" max="7947" width="10.125" style="11" customWidth="1"/>
-    <col min="7948" max="7948" width="7.25" style="11" customWidth="1"/>
-    <col min="7949" max="7949" width="11.875" style="11" customWidth="1"/>
-    <col min="7950" max="7950" width="2.125" style="11" customWidth="1"/>
-    <col min="7951" max="7952" width="12.5" style="11" customWidth="1"/>
-    <col min="7953" max="8186" width="9" style="11"/>
-    <col min="8187" max="8187" width="6.875" style="11" customWidth="1"/>
-    <col min="8188" max="8188" width="10.125" style="11" customWidth="1"/>
-    <col min="8189" max="8189" width="11.125" style="11" customWidth="1"/>
-    <col min="8190" max="8190" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="8191" max="8191" width="21.625" style="11" customWidth="1"/>
-    <col min="8192" max="8192" width="6.25" style="11" customWidth="1"/>
-    <col min="8193" max="8193" width="12.125" style="11" customWidth="1"/>
-    <col min="8194" max="8194" width="20.125" style="11" customWidth="1"/>
-    <col min="8195" max="8195" width="26.75" style="11" customWidth="1"/>
-    <col min="8196" max="8196" width="13.375" style="11" customWidth="1"/>
-    <col min="8197" max="8197" width="17" style="11" customWidth="1"/>
-    <col min="8198" max="8198" width="19.125" style="11" customWidth="1"/>
-    <col min="8199" max="8200" width="5.875" style="11" customWidth="1"/>
-    <col min="8201" max="8201" width="6.625" style="11" customWidth="1"/>
-    <col min="8202" max="8202" width="8.125" style="11" customWidth="1"/>
-    <col min="8203" max="8203" width="10.125" style="11" customWidth="1"/>
-    <col min="8204" max="8204" width="7.25" style="11" customWidth="1"/>
-    <col min="8205" max="8205" width="11.875" style="11" customWidth="1"/>
-    <col min="8206" max="8206" width="2.125" style="11" customWidth="1"/>
-    <col min="8207" max="8208" width="12.5" style="11" customWidth="1"/>
-    <col min="8209" max="8442" width="9" style="11"/>
-    <col min="8443" max="8443" width="6.875" style="11" customWidth="1"/>
-    <col min="8444" max="8444" width="10.125" style="11" customWidth="1"/>
-    <col min="8445" max="8445" width="11.125" style="11" customWidth="1"/>
-    <col min="8446" max="8446" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="8447" max="8447" width="21.625" style="11" customWidth="1"/>
-    <col min="8448" max="8448" width="6.25" style="11" customWidth="1"/>
-    <col min="8449" max="8449" width="12.125" style="11" customWidth="1"/>
-    <col min="8450" max="8450" width="20.125" style="11" customWidth="1"/>
-    <col min="8451" max="8451" width="26.75" style="11" customWidth="1"/>
-    <col min="8452" max="8452" width="13.375" style="11" customWidth="1"/>
-    <col min="8453" max="8453" width="17" style="11" customWidth="1"/>
-    <col min="8454" max="8454" width="19.125" style="11" customWidth="1"/>
-    <col min="8455" max="8456" width="5.875" style="11" customWidth="1"/>
-    <col min="8457" max="8457" width="6.625" style="11" customWidth="1"/>
-    <col min="8458" max="8458" width="8.125" style="11" customWidth="1"/>
-    <col min="8459" max="8459" width="10.125" style="11" customWidth="1"/>
-    <col min="8460" max="8460" width="7.25" style="11" customWidth="1"/>
-    <col min="8461" max="8461" width="11.875" style="11" customWidth="1"/>
-    <col min="8462" max="8462" width="2.125" style="11" customWidth="1"/>
-    <col min="8463" max="8464" width="12.5" style="11" customWidth="1"/>
-    <col min="8465" max="8698" width="9" style="11"/>
-    <col min="8699" max="8699" width="6.875" style="11" customWidth="1"/>
-    <col min="8700" max="8700" width="10.125" style="11" customWidth="1"/>
-    <col min="8701" max="8701" width="11.125" style="11" customWidth="1"/>
-    <col min="8702" max="8702" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="8703" max="8703" width="21.625" style="11" customWidth="1"/>
-    <col min="8704" max="8704" width="6.25" style="11" customWidth="1"/>
-    <col min="8705" max="8705" width="12.125" style="11" customWidth="1"/>
-    <col min="8706" max="8706" width="20.125" style="11" customWidth="1"/>
-    <col min="8707" max="8707" width="26.75" style="11" customWidth="1"/>
-    <col min="8708" max="8708" width="13.375" style="11" customWidth="1"/>
-    <col min="8709" max="8709" width="17" style="11" customWidth="1"/>
-    <col min="8710" max="8710" width="19.125" style="11" customWidth="1"/>
-    <col min="8711" max="8712" width="5.875" style="11" customWidth="1"/>
-    <col min="8713" max="8713" width="6.625" style="11" customWidth="1"/>
-    <col min="8714" max="8714" width="8.125" style="11" customWidth="1"/>
-    <col min="8715" max="8715" width="10.125" style="11" customWidth="1"/>
-    <col min="8716" max="8716" width="7.25" style="11" customWidth="1"/>
-    <col min="8717" max="8717" width="11.875" style="11" customWidth="1"/>
-    <col min="8718" max="8718" width="2.125" style="11" customWidth="1"/>
-    <col min="8719" max="8720" width="12.5" style="11" customWidth="1"/>
-    <col min="8721" max="8954" width="9" style="11"/>
-    <col min="8955" max="8955" width="6.875" style="11" customWidth="1"/>
-    <col min="8956" max="8956" width="10.125" style="11" customWidth="1"/>
-    <col min="8957" max="8957" width="11.125" style="11" customWidth="1"/>
-    <col min="8958" max="8958" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="8959" max="8959" width="21.625" style="11" customWidth="1"/>
-    <col min="8960" max="8960" width="6.25" style="11" customWidth="1"/>
-    <col min="8961" max="8961" width="12.125" style="11" customWidth="1"/>
-    <col min="8962" max="8962" width="20.125" style="11" customWidth="1"/>
-    <col min="8963" max="8963" width="26.75" style="11" customWidth="1"/>
-    <col min="8964" max="8964" width="13.375" style="11" customWidth="1"/>
-    <col min="8965" max="8965" width="17" style="11" customWidth="1"/>
-    <col min="8966" max="8966" width="19.125" style="11" customWidth="1"/>
-    <col min="8967" max="8968" width="5.875" style="11" customWidth="1"/>
-    <col min="8969" max="8969" width="6.625" style="11" customWidth="1"/>
-    <col min="8970" max="8970" width="8.125" style="11" customWidth="1"/>
-    <col min="8971" max="8971" width="10.125" style="11" customWidth="1"/>
-    <col min="8972" max="8972" width="7.25" style="11" customWidth="1"/>
-    <col min="8973" max="8973" width="11.875" style="11" customWidth="1"/>
-    <col min="8974" max="8974" width="2.125" style="11" customWidth="1"/>
-    <col min="8975" max="8976" width="12.5" style="11" customWidth="1"/>
-    <col min="8977" max="9210" width="9" style="11"/>
-    <col min="9211" max="9211" width="6.875" style="11" customWidth="1"/>
-    <col min="9212" max="9212" width="10.125" style="11" customWidth="1"/>
-    <col min="9213" max="9213" width="11.125" style="11" customWidth="1"/>
-    <col min="9214" max="9214" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="9215" max="9215" width="21.625" style="11" customWidth="1"/>
-    <col min="9216" max="9216" width="6.25" style="11" customWidth="1"/>
-    <col min="9217" max="9217" width="12.125" style="11" customWidth="1"/>
-    <col min="9218" max="9218" width="20.125" style="11" customWidth="1"/>
-    <col min="9219" max="9219" width="26.75" style="11" customWidth="1"/>
-    <col min="9220" max="9220" width="13.375" style="11" customWidth="1"/>
-    <col min="9221" max="9221" width="17" style="11" customWidth="1"/>
-    <col min="9222" max="9222" width="19.125" style="11" customWidth="1"/>
-    <col min="9223" max="9224" width="5.875" style="11" customWidth="1"/>
-    <col min="9225" max="9225" width="6.625" style="11" customWidth="1"/>
-    <col min="9226" max="9226" width="8.125" style="11" customWidth="1"/>
-    <col min="9227" max="9227" width="10.125" style="11" customWidth="1"/>
-    <col min="9228" max="9228" width="7.25" style="11" customWidth="1"/>
-    <col min="9229" max="9229" width="11.875" style="11" customWidth="1"/>
-    <col min="9230" max="9230" width="2.125" style="11" customWidth="1"/>
-    <col min="9231" max="9232" width="12.5" style="11" customWidth="1"/>
-    <col min="9233" max="9466" width="9" style="11"/>
-    <col min="9467" max="9467" width="6.875" style="11" customWidth="1"/>
-    <col min="9468" max="9468" width="10.125" style="11" customWidth="1"/>
-    <col min="9469" max="9469" width="11.125" style="11" customWidth="1"/>
-    <col min="9470" max="9470" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="9471" max="9471" width="21.625" style="11" customWidth="1"/>
-    <col min="9472" max="9472" width="6.25" style="11" customWidth="1"/>
-    <col min="9473" max="9473" width="12.125" style="11" customWidth="1"/>
-    <col min="9474" max="9474" width="20.125" style="11" customWidth="1"/>
-    <col min="9475" max="9475" width="26.75" style="11" customWidth="1"/>
-    <col min="9476" max="9476" width="13.375" style="11" customWidth="1"/>
-    <col min="9477" max="9477" width="17" style="11" customWidth="1"/>
-    <col min="9478" max="9478" width="19.125" style="11" customWidth="1"/>
-    <col min="9479" max="9480" width="5.875" style="11" customWidth="1"/>
-    <col min="9481" max="9481" width="6.625" style="11" customWidth="1"/>
-    <col min="9482" max="9482" width="8.125" style="11" customWidth="1"/>
-    <col min="9483" max="9483" width="10.125" style="11" customWidth="1"/>
-    <col min="9484" max="9484" width="7.25" style="11" customWidth="1"/>
-    <col min="9485" max="9485" width="11.875" style="11" customWidth="1"/>
-    <col min="9486" max="9486" width="2.125" style="11" customWidth="1"/>
-    <col min="9487" max="9488" width="12.5" style="11" customWidth="1"/>
-    <col min="9489" max="9722" width="9" style="11"/>
-    <col min="9723" max="9723" width="6.875" style="11" customWidth="1"/>
-    <col min="9724" max="9724" width="10.125" style="11" customWidth="1"/>
-    <col min="9725" max="9725" width="11.125" style="11" customWidth="1"/>
-    <col min="9726" max="9726" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="9727" max="9727" width="21.625" style="11" customWidth="1"/>
-    <col min="9728" max="9728" width="6.25" style="11" customWidth="1"/>
-    <col min="9729" max="9729" width="12.125" style="11" customWidth="1"/>
-    <col min="9730" max="9730" width="20.125" style="11" customWidth="1"/>
-    <col min="9731" max="9731" width="26.75" style="11" customWidth="1"/>
-    <col min="9732" max="9732" width="13.375" style="11" customWidth="1"/>
-    <col min="9733" max="9733" width="17" style="11" customWidth="1"/>
-    <col min="9734" max="9734" width="19.125" style="11" customWidth="1"/>
-    <col min="9735" max="9736" width="5.875" style="11" customWidth="1"/>
-    <col min="9737" max="9737" width="6.625" style="11" customWidth="1"/>
-    <col min="9738" max="9738" width="8.125" style="11" customWidth="1"/>
-    <col min="9739" max="9739" width="10.125" style="11" customWidth="1"/>
-    <col min="9740" max="9740" width="7.25" style="11" customWidth="1"/>
-    <col min="9741" max="9741" width="11.875" style="11" customWidth="1"/>
-    <col min="9742" max="9742" width="2.125" style="11" customWidth="1"/>
-    <col min="9743" max="9744" width="12.5" style="11" customWidth="1"/>
-    <col min="9745" max="9978" width="9" style="11"/>
-    <col min="9979" max="9979" width="6.875" style="11" customWidth="1"/>
-    <col min="9980" max="9980" width="10.125" style="11" customWidth="1"/>
-    <col min="9981" max="9981" width="11.125" style="11" customWidth="1"/>
-    <col min="9982" max="9982" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="9983" max="9983" width="21.625" style="11" customWidth="1"/>
-    <col min="9984" max="9984" width="6.25" style="11" customWidth="1"/>
-    <col min="9985" max="9985" width="12.125" style="11" customWidth="1"/>
-    <col min="9986" max="9986" width="20.125" style="11" customWidth="1"/>
-    <col min="9987" max="9987" width="26.75" style="11" customWidth="1"/>
-    <col min="9988" max="9988" width="13.375" style="11" customWidth="1"/>
-    <col min="9989" max="9989" width="17" style="11" customWidth="1"/>
-    <col min="9990" max="9990" width="19.125" style="11" customWidth="1"/>
-    <col min="9991" max="9992" width="5.875" style="11" customWidth="1"/>
-    <col min="9993" max="9993" width="6.625" style="11" customWidth="1"/>
-    <col min="9994" max="9994" width="8.125" style="11" customWidth="1"/>
-    <col min="9995" max="9995" width="10.125" style="11" customWidth="1"/>
-    <col min="9996" max="9996" width="7.25" style="11" customWidth="1"/>
-    <col min="9997" max="9997" width="11.875" style="11" customWidth="1"/>
-    <col min="9998" max="9998" width="2.125" style="11" customWidth="1"/>
-    <col min="9999" max="10000" width="12.5" style="11" customWidth="1"/>
-    <col min="10001" max="10234" width="9" style="11"/>
-    <col min="10235" max="10235" width="6.875" style="11" customWidth="1"/>
-    <col min="10236" max="10236" width="10.125" style="11" customWidth="1"/>
-    <col min="10237" max="10237" width="11.125" style="11" customWidth="1"/>
-    <col min="10238" max="10238" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="10239" max="10239" width="21.625" style="11" customWidth="1"/>
-    <col min="10240" max="10240" width="6.25" style="11" customWidth="1"/>
-    <col min="10241" max="10241" width="12.125" style="11" customWidth="1"/>
-    <col min="10242" max="10242" width="20.125" style="11" customWidth="1"/>
-    <col min="10243" max="10243" width="26.75" style="11" customWidth="1"/>
-    <col min="10244" max="10244" width="13.375" style="11" customWidth="1"/>
-    <col min="10245" max="10245" width="17" style="11" customWidth="1"/>
-    <col min="10246" max="10246" width="19.125" style="11" customWidth="1"/>
-    <col min="10247" max="10248" width="5.875" style="11" customWidth="1"/>
-    <col min="10249" max="10249" width="6.625" style="11" customWidth="1"/>
-    <col min="10250" max="10250" width="8.125" style="11" customWidth="1"/>
-    <col min="10251" max="10251" width="10.125" style="11" customWidth="1"/>
-    <col min="10252" max="10252" width="7.25" style="11" customWidth="1"/>
-    <col min="10253" max="10253" width="11.875" style="11" customWidth="1"/>
-    <col min="10254" max="10254" width="2.125" style="11" customWidth="1"/>
-    <col min="10255" max="10256" width="12.5" style="11" customWidth="1"/>
-    <col min="10257" max="10490" width="9" style="11"/>
-    <col min="10491" max="10491" width="6.875" style="11" customWidth="1"/>
-    <col min="10492" max="10492" width="10.125" style="11" customWidth="1"/>
-    <col min="10493" max="10493" width="11.125" style="11" customWidth="1"/>
-    <col min="10494" max="10494" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="10495" max="10495" width="21.625" style="11" customWidth="1"/>
-    <col min="10496" max="10496" width="6.25" style="11" customWidth="1"/>
-    <col min="10497" max="10497" width="12.125" style="11" customWidth="1"/>
-    <col min="10498" max="10498" width="20.125" style="11" customWidth="1"/>
-    <col min="10499" max="10499" width="26.75" style="11" customWidth="1"/>
-    <col min="10500" max="10500" width="13.375" style="11" customWidth="1"/>
-    <col min="10501" max="10501" width="17" style="11" customWidth="1"/>
-    <col min="10502" max="10502" width="19.125" style="11" customWidth="1"/>
-    <col min="10503" max="10504" width="5.875" style="11" customWidth="1"/>
-    <col min="10505" max="10505" width="6.625" style="11" customWidth="1"/>
-    <col min="10506" max="10506" width="8.125" style="11" customWidth="1"/>
-    <col min="10507" max="10507" width="10.125" style="11" customWidth="1"/>
-    <col min="10508" max="10508" width="7.25" style="11" customWidth="1"/>
-    <col min="10509" max="10509" width="11.875" style="11" customWidth="1"/>
-    <col min="10510" max="10510" width="2.125" style="11" customWidth="1"/>
-    <col min="10511" max="10512" width="12.5" style="11" customWidth="1"/>
-    <col min="10513" max="10746" width="9" style="11"/>
-    <col min="10747" max="10747" width="6.875" style="11" customWidth="1"/>
-    <col min="10748" max="10748" width="10.125" style="11" customWidth="1"/>
-    <col min="10749" max="10749" width="11.125" style="11" customWidth="1"/>
-    <col min="10750" max="10750" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="10751" max="10751" width="21.625" style="11" customWidth="1"/>
-    <col min="10752" max="10752" width="6.25" style="11" customWidth="1"/>
-    <col min="10753" max="10753" width="12.125" style="11" customWidth="1"/>
-    <col min="10754" max="10754" width="20.125" style="11" customWidth="1"/>
-    <col min="10755" max="10755" width="26.75" style="11" customWidth="1"/>
-    <col min="10756" max="10756" width="13.375" style="11" customWidth="1"/>
-    <col min="10757" max="10757" width="17" style="11" customWidth="1"/>
-    <col min="10758" max="10758" width="19.125" style="11" customWidth="1"/>
-    <col min="10759" max="10760" width="5.875" style="11" customWidth="1"/>
-    <col min="10761" max="10761" width="6.625" style="11" customWidth="1"/>
-    <col min="10762" max="10762" width="8.125" style="11" customWidth="1"/>
-    <col min="10763" max="10763" width="10.125" style="11" customWidth="1"/>
-    <col min="10764" max="10764" width="7.25" style="11" customWidth="1"/>
-    <col min="10765" max="10765" width="11.875" style="11" customWidth="1"/>
-    <col min="10766" max="10766" width="2.125" style="11" customWidth="1"/>
-    <col min="10767" max="10768" width="12.5" style="11" customWidth="1"/>
-    <col min="10769" max="11002" width="9" style="11"/>
-    <col min="11003" max="11003" width="6.875" style="11" customWidth="1"/>
-    <col min="11004" max="11004" width="10.125" style="11" customWidth="1"/>
-    <col min="11005" max="11005" width="11.125" style="11" customWidth="1"/>
-    <col min="11006" max="11006" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="11007" max="11007" width="21.625" style="11" customWidth="1"/>
-    <col min="11008" max="11008" width="6.25" style="11" customWidth="1"/>
-    <col min="11009" max="11009" width="12.125" style="11" customWidth="1"/>
-    <col min="11010" max="11010" width="20.125" style="11" customWidth="1"/>
-    <col min="11011" max="11011" width="26.75" style="11" customWidth="1"/>
-    <col min="11012" max="11012" width="13.375" style="11" customWidth="1"/>
-    <col min="11013" max="11013" width="17" style="11" customWidth="1"/>
-    <col min="11014" max="11014" width="19.125" style="11" customWidth="1"/>
-    <col min="11015" max="11016" width="5.875" style="11" customWidth="1"/>
-    <col min="11017" max="11017" width="6.625" style="11" customWidth="1"/>
-    <col min="11018" max="11018" width="8.125" style="11" customWidth="1"/>
-    <col min="11019" max="11019" width="10.125" style="11" customWidth="1"/>
-    <col min="11020" max="11020" width="7.25" style="11" customWidth="1"/>
-    <col min="11021" max="11021" width="11.875" style="11" customWidth="1"/>
-    <col min="11022" max="11022" width="2.125" style="11" customWidth="1"/>
-    <col min="11023" max="11024" width="12.5" style="11" customWidth="1"/>
-    <col min="11025" max="11258" width="9" style="11"/>
-    <col min="11259" max="11259" width="6.875" style="11" customWidth="1"/>
-    <col min="11260" max="11260" width="10.125" style="11" customWidth="1"/>
-    <col min="11261" max="11261" width="11.125" style="11" customWidth="1"/>
-    <col min="11262" max="11262" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="11263" max="11263" width="21.625" style="11" customWidth="1"/>
-    <col min="11264" max="11264" width="6.25" style="11" customWidth="1"/>
-    <col min="11265" max="11265" width="12.125" style="11" customWidth="1"/>
-    <col min="11266" max="11266" width="20.125" style="11" customWidth="1"/>
-    <col min="11267" max="11267" width="26.75" style="11" customWidth="1"/>
-    <col min="11268" max="11268" width="13.375" style="11" customWidth="1"/>
-    <col min="11269" max="11269" width="17" style="11" customWidth="1"/>
-    <col min="11270" max="11270" width="19.125" style="11" customWidth="1"/>
-    <col min="11271" max="11272" width="5.875" style="11" customWidth="1"/>
-    <col min="11273" max="11273" width="6.625" style="11" customWidth="1"/>
-    <col min="11274" max="11274" width="8.125" style="11" customWidth="1"/>
-    <col min="11275" max="11275" width="10.125" style="11" customWidth="1"/>
-    <col min="11276" max="11276" width="7.25" style="11" customWidth="1"/>
-    <col min="11277" max="11277" width="11.875" style="11" customWidth="1"/>
-    <col min="11278" max="11278" width="2.125" style="11" customWidth="1"/>
-    <col min="11279" max="11280" width="12.5" style="11" customWidth="1"/>
-    <col min="11281" max="11514" width="9" style="11"/>
-    <col min="11515" max="11515" width="6.875" style="11" customWidth="1"/>
-    <col min="11516" max="11516" width="10.125" style="11" customWidth="1"/>
-    <col min="11517" max="11517" width="11.125" style="11" customWidth="1"/>
-    <col min="11518" max="11518" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="11519" max="11519" width="21.625" style="11" customWidth="1"/>
-    <col min="11520" max="11520" width="6.25" style="11" customWidth="1"/>
-    <col min="11521" max="11521" width="12.125" style="11" customWidth="1"/>
-    <col min="11522" max="11522" width="20.125" style="11" customWidth="1"/>
-    <col min="11523" max="11523" width="26.75" style="11" customWidth="1"/>
-    <col min="11524" max="11524" width="13.375" style="11" customWidth="1"/>
-    <col min="11525" max="11525" width="17" style="11" customWidth="1"/>
-    <col min="11526" max="11526" width="19.125" style="11" customWidth="1"/>
-    <col min="11527" max="11528" width="5.875" style="11" customWidth="1"/>
-    <col min="11529" max="11529" width="6.625" style="11" customWidth="1"/>
-    <col min="11530" max="11530" width="8.125" style="11" customWidth="1"/>
-    <col min="11531" max="11531" width="10.125" style="11" customWidth="1"/>
-    <col min="11532" max="11532" width="7.25" style="11" customWidth="1"/>
-    <col min="11533" max="11533" width="11.875" style="11" customWidth="1"/>
-    <col min="11534" max="11534" width="2.125" style="11" customWidth="1"/>
-    <col min="11535" max="11536" width="12.5" style="11" customWidth="1"/>
-    <col min="11537" max="11770" width="9" style="11"/>
-    <col min="11771" max="11771" width="6.875" style="11" customWidth="1"/>
-    <col min="11772" max="11772" width="10.125" style="11" customWidth="1"/>
-    <col min="11773" max="11773" width="11.125" style="11" customWidth="1"/>
-    <col min="11774" max="11774" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="11775" max="11775" width="21.625" style="11" customWidth="1"/>
-    <col min="11776" max="11776" width="6.25" style="11" customWidth="1"/>
-    <col min="11777" max="11777" width="12.125" style="11" customWidth="1"/>
-    <col min="11778" max="11778" width="20.125" style="11" customWidth="1"/>
-    <col min="11779" max="11779" width="26.75" style="11" customWidth="1"/>
-    <col min="11780" max="11780" width="13.375" style="11" customWidth="1"/>
-    <col min="11781" max="11781" width="17" style="11" customWidth="1"/>
-    <col min="11782" max="11782" width="19.125" style="11" customWidth="1"/>
-    <col min="11783" max="11784" width="5.875" style="11" customWidth="1"/>
-    <col min="11785" max="11785" width="6.625" style="11" customWidth="1"/>
-    <col min="11786" max="11786" width="8.125" style="11" customWidth="1"/>
-    <col min="11787" max="11787" width="10.125" style="11" customWidth="1"/>
-    <col min="11788" max="11788" width="7.25" style="11" customWidth="1"/>
-    <col min="11789" max="11789" width="11.875" style="11" customWidth="1"/>
-    <col min="11790" max="11790" width="2.125" style="11" customWidth="1"/>
-    <col min="11791" max="11792" width="12.5" style="11" customWidth="1"/>
-    <col min="11793" max="12026" width="9" style="11"/>
-    <col min="12027" max="12027" width="6.875" style="11" customWidth="1"/>
-    <col min="12028" max="12028" width="10.125" style="11" customWidth="1"/>
-    <col min="12029" max="12029" width="11.125" style="11" customWidth="1"/>
-    <col min="12030" max="12030" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="12031" max="12031" width="21.625" style="11" customWidth="1"/>
-    <col min="12032" max="12032" width="6.25" style="11" customWidth="1"/>
-    <col min="12033" max="12033" width="12.125" style="11" customWidth="1"/>
-    <col min="12034" max="12034" width="20.125" style="11" customWidth="1"/>
-    <col min="12035" max="12035" width="26.75" style="11" customWidth="1"/>
-    <col min="12036" max="12036" width="13.375" style="11" customWidth="1"/>
-    <col min="12037" max="12037" width="17" style="11" customWidth="1"/>
-    <col min="12038" max="12038" width="19.125" style="11" customWidth="1"/>
-    <col min="12039" max="12040" width="5.875" style="11" customWidth="1"/>
-    <col min="12041" max="12041" width="6.625" style="11" customWidth="1"/>
-    <col min="12042" max="12042" width="8.125" style="11" customWidth="1"/>
-    <col min="12043" max="12043" width="10.125" style="11" customWidth="1"/>
-    <col min="12044" max="12044" width="7.25" style="11" customWidth="1"/>
-    <col min="12045" max="12045" width="11.875" style="11" customWidth="1"/>
-    <col min="12046" max="12046" width="2.125" style="11" customWidth="1"/>
-    <col min="12047" max="12048" width="12.5" style="11" customWidth="1"/>
-    <col min="12049" max="12282" width="9" style="11"/>
-    <col min="12283" max="12283" width="6.875" style="11" customWidth="1"/>
-    <col min="12284" max="12284" width="10.125" style="11" customWidth="1"/>
-    <col min="12285" max="12285" width="11.125" style="11" customWidth="1"/>
-    <col min="12286" max="12286" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="12287" max="12287" width="21.625" style="11" customWidth="1"/>
-    <col min="12288" max="12288" width="6.25" style="11" customWidth="1"/>
-    <col min="12289" max="12289" width="12.125" style="11" customWidth="1"/>
-    <col min="12290" max="12290" width="20.125" style="11" customWidth="1"/>
-    <col min="12291" max="12291" width="26.75" style="11" customWidth="1"/>
-    <col min="12292" max="12292" width="13.375" style="11" customWidth="1"/>
-    <col min="12293" max="12293" width="17" style="11" customWidth="1"/>
-    <col min="12294" max="12294" width="19.125" style="11" customWidth="1"/>
-    <col min="12295" max="12296" width="5.875" style="11" customWidth="1"/>
-    <col min="12297" max="12297" width="6.625" style="11" customWidth="1"/>
-    <col min="12298" max="12298" width="8.125" style="11" customWidth="1"/>
-    <col min="12299" max="12299" width="10.125" style="11" customWidth="1"/>
-    <col min="12300" max="12300" width="7.25" style="11" customWidth="1"/>
-    <col min="12301" max="12301" width="11.875" style="11" customWidth="1"/>
-    <col min="12302" max="12302" width="2.125" style="11" customWidth="1"/>
-    <col min="12303" max="12304" width="12.5" style="11" customWidth="1"/>
-    <col min="12305" max="12538" width="9" style="11"/>
-    <col min="12539" max="12539" width="6.875" style="11" customWidth="1"/>
-    <col min="12540" max="12540" width="10.125" style="11" customWidth="1"/>
-    <col min="12541" max="12541" width="11.125" style="11" customWidth="1"/>
-    <col min="12542" max="12542" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="12543" max="12543" width="21.625" style="11" customWidth="1"/>
-    <col min="12544" max="12544" width="6.25" style="11" customWidth="1"/>
-    <col min="12545" max="12545" width="12.125" style="11" customWidth="1"/>
-    <col min="12546" max="12546" width="20.125" style="11" customWidth="1"/>
-    <col min="12547" max="12547" width="26.75" style="11" customWidth="1"/>
-    <col min="12548" max="12548" width="13.375" style="11" customWidth="1"/>
-    <col min="12549" max="12549" width="17" style="11" customWidth="1"/>
-    <col min="12550" max="12550" width="19.125" style="11" customWidth="1"/>
-    <col min="12551" max="12552" width="5.875" style="11" customWidth="1"/>
-    <col min="12553" max="12553" width="6.625" style="11" customWidth="1"/>
-    <col min="12554" max="12554" width="8.125" style="11" customWidth="1"/>
-    <col min="12555" max="12555" width="10.125" style="11" customWidth="1"/>
-    <col min="12556" max="12556" width="7.25" style="11" customWidth="1"/>
-    <col min="12557" max="12557" width="11.875" style="11" customWidth="1"/>
-    <col min="12558" max="12558" width="2.125" style="11" customWidth="1"/>
-    <col min="12559" max="12560" width="12.5" style="11" customWidth="1"/>
-    <col min="12561" max="12794" width="9" style="11"/>
-    <col min="12795" max="12795" width="6.875" style="11" customWidth="1"/>
-    <col min="12796" max="12796" width="10.125" style="11" customWidth="1"/>
-    <col min="12797" max="12797" width="11.125" style="11" customWidth="1"/>
-    <col min="12798" max="12798" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="12799" max="12799" width="21.625" style="11" customWidth="1"/>
-    <col min="12800" max="12800" width="6.25" style="11" customWidth="1"/>
-    <col min="12801" max="12801" width="12.125" style="11" customWidth="1"/>
-    <col min="12802" max="12802" width="20.125" style="11" customWidth="1"/>
-    <col min="12803" max="12803" width="26.75" style="11" customWidth="1"/>
-    <col min="12804" max="12804" width="13.375" style="11" customWidth="1"/>
-    <col min="12805" max="12805" width="17" style="11" customWidth="1"/>
-    <col min="12806" max="12806" width="19.125" style="11" customWidth="1"/>
-    <col min="12807" max="12808" width="5.875" style="11" customWidth="1"/>
-    <col min="12809" max="12809" width="6.625" style="11" customWidth="1"/>
-    <col min="12810" max="12810" width="8.125" style="11" customWidth="1"/>
-    <col min="12811" max="12811" width="10.125" style="11" customWidth="1"/>
-    <col min="12812" max="12812" width="7.25" style="11" customWidth="1"/>
-    <col min="12813" max="12813" width="11.875" style="11" customWidth="1"/>
-    <col min="12814" max="12814" width="2.125" style="11" customWidth="1"/>
-    <col min="12815" max="12816" width="12.5" style="11" customWidth="1"/>
-    <col min="12817" max="13050" width="9" style="11"/>
-    <col min="13051" max="13051" width="6.875" style="11" customWidth="1"/>
-    <col min="13052" max="13052" width="10.125" style="11" customWidth="1"/>
-    <col min="13053" max="13053" width="11.125" style="11" customWidth="1"/>
-    <col min="13054" max="13054" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="13055" max="13055" width="21.625" style="11" customWidth="1"/>
-    <col min="13056" max="13056" width="6.25" style="11" customWidth="1"/>
-    <col min="13057" max="13057" width="12.125" style="11" customWidth="1"/>
-    <col min="13058" max="13058" width="20.125" style="11" customWidth="1"/>
-    <col min="13059" max="13059" width="26.75" style="11" customWidth="1"/>
-    <col min="13060" max="13060" width="13.375" style="11" customWidth="1"/>
-    <col min="13061" max="13061" width="17" style="11" customWidth="1"/>
-    <col min="13062" max="13062" width="19.125" style="11" customWidth="1"/>
-    <col min="13063" max="13064" width="5.875" style="11" customWidth="1"/>
-    <col min="13065" max="13065" width="6.625" style="11" customWidth="1"/>
-    <col min="13066" max="13066" width="8.125" style="11" customWidth="1"/>
-    <col min="13067" max="13067" width="10.125" style="11" customWidth="1"/>
-    <col min="13068" max="13068" width="7.25" style="11" customWidth="1"/>
-    <col min="13069" max="13069" width="11.875" style="11" customWidth="1"/>
-    <col min="13070" max="13070" width="2.125" style="11" customWidth="1"/>
-    <col min="13071" max="13072" width="12.5" style="11" customWidth="1"/>
-    <col min="13073" max="13306" width="9" style="11"/>
-    <col min="13307" max="13307" width="6.875" style="11" customWidth="1"/>
-    <col min="13308" max="13308" width="10.125" style="11" customWidth="1"/>
-    <col min="13309" max="13309" width="11.125" style="11" customWidth="1"/>
-    <col min="13310" max="13310" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="13311" max="13311" width="21.625" style="11" customWidth="1"/>
-    <col min="13312" max="13312" width="6.25" style="11" customWidth="1"/>
-    <col min="13313" max="13313" width="12.125" style="11" customWidth="1"/>
-    <col min="13314" max="13314" width="20.125" style="11" customWidth="1"/>
-    <col min="13315" max="13315" width="26.75" style="11" customWidth="1"/>
-    <col min="13316" max="13316" width="13.375" style="11" customWidth="1"/>
-    <col min="13317" max="13317" width="17" style="11" customWidth="1"/>
-    <col min="13318" max="13318" width="19.125" style="11" customWidth="1"/>
-    <col min="13319" max="13320" width="5.875" style="11" customWidth="1"/>
-    <col min="13321" max="13321" width="6.625" style="11" customWidth="1"/>
-    <col min="13322" max="13322" width="8.125" style="11" customWidth="1"/>
-    <col min="13323" max="13323" width="10.125" style="11" customWidth="1"/>
-    <col min="13324" max="13324" width="7.25" style="11" customWidth="1"/>
-    <col min="13325" max="13325" width="11.875" style="11" customWidth="1"/>
-    <col min="13326" max="13326" width="2.125" style="11" customWidth="1"/>
-    <col min="13327" max="13328" width="12.5" style="11" customWidth="1"/>
-    <col min="13329" max="13562" width="9" style="11"/>
-    <col min="13563" max="13563" width="6.875" style="11" customWidth="1"/>
-    <col min="13564" max="13564" width="10.125" style="11" customWidth="1"/>
-    <col min="13565" max="13565" width="11.125" style="11" customWidth="1"/>
-    <col min="13566" max="13566" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="13567" max="13567" width="21.625" style="11" customWidth="1"/>
-    <col min="13568" max="13568" width="6.25" style="11" customWidth="1"/>
-    <col min="13569" max="13569" width="12.125" style="11" customWidth="1"/>
-    <col min="13570" max="13570" width="20.125" style="11" customWidth="1"/>
-    <col min="13571" max="13571" width="26.75" style="11" customWidth="1"/>
-    <col min="13572" max="13572" width="13.375" style="11" customWidth="1"/>
-    <col min="13573" max="13573" width="17" style="11" customWidth="1"/>
-    <col min="13574" max="13574" width="19.125" style="11" customWidth="1"/>
-    <col min="13575" max="13576" width="5.875" style="11" customWidth="1"/>
-    <col min="13577" max="13577" width="6.625" style="11" customWidth="1"/>
-    <col min="13578" max="13578" width="8.125" style="11" customWidth="1"/>
-    <col min="13579" max="13579" width="10.125" style="11" customWidth="1"/>
-    <col min="13580" max="13580" width="7.25" style="11" customWidth="1"/>
-    <col min="13581" max="13581" width="11.875" style="11" customWidth="1"/>
-    <col min="13582" max="13582" width="2.125" style="11" customWidth="1"/>
-    <col min="13583" max="13584" width="12.5" style="11" customWidth="1"/>
-    <col min="13585" max="13818" width="9" style="11"/>
-    <col min="13819" max="13819" width="6.875" style="11" customWidth="1"/>
-    <col min="13820" max="13820" width="10.125" style="11" customWidth="1"/>
-    <col min="13821" max="13821" width="11.125" style="11" customWidth="1"/>
-    <col min="13822" max="13822" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="13823" max="13823" width="21.625" style="11" customWidth="1"/>
-    <col min="13824" max="13824" width="6.25" style="11" customWidth="1"/>
-    <col min="13825" max="13825" width="12.125" style="11" customWidth="1"/>
-    <col min="13826" max="13826" width="20.125" style="11" customWidth="1"/>
-    <col min="13827" max="13827" width="26.75" style="11" customWidth="1"/>
-    <col min="13828" max="13828" width="13.375" style="11" customWidth="1"/>
-    <col min="13829" max="13829" width="17" style="11" customWidth="1"/>
-    <col min="13830" max="13830" width="19.125" style="11" customWidth="1"/>
-    <col min="13831" max="13832" width="5.875" style="11" customWidth="1"/>
-    <col min="13833" max="13833" width="6.625" style="11" customWidth="1"/>
-    <col min="13834" max="13834" width="8.125" style="11" customWidth="1"/>
-    <col min="13835" max="13835" width="10.125" style="11" customWidth="1"/>
-    <col min="13836" max="13836" width="7.25" style="11" customWidth="1"/>
-    <col min="13837" max="13837" width="11.875" style="11" customWidth="1"/>
-    <col min="13838" max="13838" width="2.125" style="11" customWidth="1"/>
-    <col min="13839" max="13840" width="12.5" style="11" customWidth="1"/>
-    <col min="13841" max="14074" width="9" style="11"/>
-    <col min="14075" max="14075" width="6.875" style="11" customWidth="1"/>
-    <col min="14076" max="14076" width="10.125" style="11" customWidth="1"/>
-    <col min="14077" max="14077" width="11.125" style="11" customWidth="1"/>
-    <col min="14078" max="14078" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="14079" max="14079" width="21.625" style="11" customWidth="1"/>
-    <col min="14080" max="14080" width="6.25" style="11" customWidth="1"/>
-    <col min="14081" max="14081" width="12.125" style="11" customWidth="1"/>
-    <col min="14082" max="14082" width="20.125" style="11" customWidth="1"/>
-    <col min="14083" max="14083" width="26.75" style="11" customWidth="1"/>
-    <col min="14084" max="14084" width="13.375" style="11" customWidth="1"/>
-    <col min="14085" max="14085" width="17" style="11" customWidth="1"/>
-    <col min="14086" max="14086" width="19.125" style="11" customWidth="1"/>
-    <col min="14087" max="14088" width="5.875" style="11" customWidth="1"/>
-    <col min="14089" max="14089" width="6.625" style="11" customWidth="1"/>
-    <col min="14090" max="14090" width="8.125" style="11" customWidth="1"/>
-    <col min="14091" max="14091" width="10.125" style="11" customWidth="1"/>
-    <col min="14092" max="14092" width="7.25" style="11" customWidth="1"/>
-    <col min="14093" max="14093" width="11.875" style="11" customWidth="1"/>
-    <col min="14094" max="14094" width="2.125" style="11" customWidth="1"/>
-    <col min="14095" max="14096" width="12.5" style="11" customWidth="1"/>
-    <col min="14097" max="14330" width="9" style="11"/>
-    <col min="14331" max="14331" width="6.875" style="11" customWidth="1"/>
-    <col min="14332" max="14332" width="10.125" style="11" customWidth="1"/>
-    <col min="14333" max="14333" width="11.125" style="11" customWidth="1"/>
-    <col min="14334" max="14334" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="14335" max="14335" width="21.625" style="11" customWidth="1"/>
-    <col min="14336" max="14336" width="6.25" style="11" customWidth="1"/>
-    <col min="14337" max="14337" width="12.125" style="11" customWidth="1"/>
-    <col min="14338" max="14338" width="20.125" style="11" customWidth="1"/>
-    <col min="14339" max="14339" width="26.75" style="11" customWidth="1"/>
-    <col min="14340" max="14340" width="13.375" style="11" customWidth="1"/>
-    <col min="14341" max="14341" width="17" style="11" customWidth="1"/>
-    <col min="14342" max="14342" width="19.125" style="11" customWidth="1"/>
-    <col min="14343" max="14344" width="5.875" style="11" customWidth="1"/>
-    <col min="14345" max="14345" width="6.625" style="11" customWidth="1"/>
-    <col min="14346" max="14346" width="8.125" style="11" customWidth="1"/>
-    <col min="14347" max="14347" width="10.125" style="11" customWidth="1"/>
-    <col min="14348" max="14348" width="7.25" style="11" customWidth="1"/>
-    <col min="14349" max="14349" width="11.875" style="11" customWidth="1"/>
-    <col min="14350" max="14350" width="2.125" style="11" customWidth="1"/>
-    <col min="14351" max="14352" width="12.5" style="11" customWidth="1"/>
-    <col min="14353" max="14586" width="9" style="11"/>
-    <col min="14587" max="14587" width="6.875" style="11" customWidth="1"/>
-    <col min="14588" max="14588" width="10.125" style="11" customWidth="1"/>
-    <col min="14589" max="14589" width="11.125" style="11" customWidth="1"/>
-    <col min="14590" max="14590" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="14591" max="14591" width="21.625" style="11" customWidth="1"/>
-    <col min="14592" max="14592" width="6.25" style="11" customWidth="1"/>
-    <col min="14593" max="14593" width="12.125" style="11" customWidth="1"/>
-    <col min="14594" max="14594" width="20.125" style="11" customWidth="1"/>
-    <col min="14595" max="14595" width="26.75" style="11" customWidth="1"/>
-    <col min="14596" max="14596" width="13.375" style="11" customWidth="1"/>
-    <col min="14597" max="14597" width="17" style="11" customWidth="1"/>
-    <col min="14598" max="14598" width="19.125" style="11" customWidth="1"/>
-    <col min="14599" max="14600" width="5.875" style="11" customWidth="1"/>
-    <col min="14601" max="14601" width="6.625" style="11" customWidth="1"/>
-    <col min="14602" max="14602" width="8.125" style="11" customWidth="1"/>
-    <col min="14603" max="14603" width="10.125" style="11" customWidth="1"/>
-    <col min="14604" max="14604" width="7.25" style="11" customWidth="1"/>
-    <col min="14605" max="14605" width="11.875" style="11" customWidth="1"/>
-    <col min="14606" max="14606" width="2.125" style="11" customWidth="1"/>
-    <col min="14607" max="14608" width="12.5" style="11" customWidth="1"/>
-    <col min="14609" max="14842" width="9" style="11"/>
-    <col min="14843" max="14843" width="6.875" style="11" customWidth="1"/>
-    <col min="14844" max="14844" width="10.125" style="11" customWidth="1"/>
-    <col min="14845" max="14845" width="11.125" style="11" customWidth="1"/>
-    <col min="14846" max="14846" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="14847" max="14847" width="21.625" style="11" customWidth="1"/>
-    <col min="14848" max="14848" width="6.25" style="11" customWidth="1"/>
-    <col min="14849" max="14849" width="12.125" style="11" customWidth="1"/>
-    <col min="14850" max="14850" width="20.125" style="11" customWidth="1"/>
-    <col min="14851" max="14851" width="26.75" style="11" customWidth="1"/>
-    <col min="14852" max="14852" width="13.375" style="11" customWidth="1"/>
-    <col min="14853" max="14853" width="17" style="11" customWidth="1"/>
-    <col min="14854" max="14854" width="19.125" style="11" customWidth="1"/>
-    <col min="14855" max="14856" width="5.875" style="11" customWidth="1"/>
-    <col min="14857" max="14857" width="6.625" style="11" customWidth="1"/>
-    <col min="14858" max="14858" width="8.125" style="11" customWidth="1"/>
-    <col min="14859" max="14859" width="10.125" style="11" customWidth="1"/>
-    <col min="14860" max="14860" width="7.25" style="11" customWidth="1"/>
-    <col min="14861" max="14861" width="11.875" style="11" customWidth="1"/>
-    <col min="14862" max="14862" width="2.125" style="11" customWidth="1"/>
-    <col min="14863" max="14864" width="12.5" style="11" customWidth="1"/>
-    <col min="14865" max="15098" width="9" style="11"/>
-    <col min="15099" max="15099" width="6.875" style="11" customWidth="1"/>
-    <col min="15100" max="15100" width="10.125" style="11" customWidth="1"/>
-    <col min="15101" max="15101" width="11.125" style="11" customWidth="1"/>
-    <col min="15102" max="15102" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="15103" max="15103" width="21.625" style="11" customWidth="1"/>
-    <col min="15104" max="15104" width="6.25" style="11" customWidth="1"/>
-    <col min="15105" max="15105" width="12.125" style="11" customWidth="1"/>
-    <col min="15106" max="15106" width="20.125" style="11" customWidth="1"/>
-    <col min="15107" max="15107" width="26.75" style="11" customWidth="1"/>
-    <col min="15108" max="15108" width="13.375" style="11" customWidth="1"/>
-    <col min="15109" max="15109" width="17" style="11" customWidth="1"/>
-    <col min="15110" max="15110" width="19.125" style="11" customWidth="1"/>
-    <col min="15111" max="15112" width="5.875" style="11" customWidth="1"/>
-    <col min="15113" max="15113" width="6.625" style="11" customWidth="1"/>
-    <col min="15114" max="15114" width="8.125" style="11" customWidth="1"/>
-    <col min="15115" max="15115" width="10.125" style="11" customWidth="1"/>
-    <col min="15116" max="15116" width="7.25" style="11" customWidth="1"/>
-    <col min="15117" max="15117" width="11.875" style="11" customWidth="1"/>
-    <col min="15118" max="15118" width="2.125" style="11" customWidth="1"/>
-    <col min="15119" max="15120" width="12.5" style="11" customWidth="1"/>
-    <col min="15121" max="15354" width="9" style="11"/>
-    <col min="15355" max="15355" width="6.875" style="11" customWidth="1"/>
-    <col min="15356" max="15356" width="10.125" style="11" customWidth="1"/>
-    <col min="15357" max="15357" width="11.125" style="11" customWidth="1"/>
-    <col min="15358" max="15358" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="15359" max="15359" width="21.625" style="11" customWidth="1"/>
-    <col min="15360" max="15360" width="6.25" style="11" customWidth="1"/>
-    <col min="15361" max="15361" width="12.125" style="11" customWidth="1"/>
-    <col min="15362" max="15362" width="20.125" style="11" customWidth="1"/>
-    <col min="15363" max="15363" width="26.75" style="11" customWidth="1"/>
-    <col min="15364" max="15364" width="13.375" style="11" customWidth="1"/>
-    <col min="15365" max="15365" width="17" style="11" customWidth="1"/>
-    <col min="15366" max="15366" width="19.125" style="11" customWidth="1"/>
-    <col min="15367" max="15368" width="5.875" style="11" customWidth="1"/>
-    <col min="15369" max="15369" width="6.625" style="11" customWidth="1"/>
-    <col min="15370" max="15370" width="8.125" style="11" customWidth="1"/>
-    <col min="15371" max="15371" width="10.125" style="11" customWidth="1"/>
-    <col min="15372" max="15372" width="7.25" style="11" customWidth="1"/>
-    <col min="15373" max="15373" width="11.875" style="11" customWidth="1"/>
-    <col min="15374" max="15374" width="2.125" style="11" customWidth="1"/>
-    <col min="15375" max="15376" width="12.5" style="11" customWidth="1"/>
-    <col min="15377" max="15610" width="9" style="11"/>
-    <col min="15611" max="15611" width="6.875" style="11" customWidth="1"/>
-    <col min="15612" max="15612" width="10.125" style="11" customWidth="1"/>
-    <col min="15613" max="15613" width="11.125" style="11" customWidth="1"/>
-    <col min="15614" max="15614" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="15615" max="15615" width="21.625" style="11" customWidth="1"/>
-    <col min="15616" max="15616" width="6.25" style="11" customWidth="1"/>
-    <col min="15617" max="15617" width="12.125" style="11" customWidth="1"/>
-    <col min="15618" max="15618" width="20.125" style="11" customWidth="1"/>
-    <col min="15619" max="15619" width="26.75" style="11" customWidth="1"/>
-    <col min="15620" max="15620" width="13.375" style="11" customWidth="1"/>
-    <col min="15621" max="15621" width="17" style="11" customWidth="1"/>
-    <col min="15622" max="15622" width="19.125" style="11" customWidth="1"/>
-    <col min="15623" max="15624" width="5.875" style="11" customWidth="1"/>
-    <col min="15625" max="15625" width="6.625" style="11" customWidth="1"/>
-    <col min="15626" max="15626" width="8.125" style="11" customWidth="1"/>
-    <col min="15627" max="15627" width="10.125" style="11" customWidth="1"/>
-    <col min="15628" max="15628" width="7.25" style="11" customWidth="1"/>
-    <col min="15629" max="15629" width="11.875" style="11" customWidth="1"/>
-    <col min="15630" max="15630" width="2.125" style="11" customWidth="1"/>
-    <col min="15631" max="15632" width="12.5" style="11" customWidth="1"/>
-    <col min="15633" max="15866" width="9" style="11"/>
-    <col min="15867" max="15867" width="6.875" style="11" customWidth="1"/>
-    <col min="15868" max="15868" width="10.125" style="11" customWidth="1"/>
-    <col min="15869" max="15869" width="11.125" style="11" customWidth="1"/>
-    <col min="15870" max="15870" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="15871" max="15871" width="21.625" style="11" customWidth="1"/>
-    <col min="15872" max="15872" width="6.25" style="11" customWidth="1"/>
-    <col min="15873" max="15873" width="12.125" style="11" customWidth="1"/>
-    <col min="15874" max="15874" width="20.125" style="11" customWidth="1"/>
-    <col min="15875" max="15875" width="26.75" style="11" customWidth="1"/>
-    <col min="15876" max="15876" width="13.375" style="11" customWidth="1"/>
-    <col min="15877" max="15877" width="17" style="11" customWidth="1"/>
-    <col min="15878" max="15878" width="19.125" style="11" customWidth="1"/>
-    <col min="15879" max="15880" width="5.875" style="11" customWidth="1"/>
-    <col min="15881" max="15881" width="6.625" style="11" customWidth="1"/>
-    <col min="15882" max="15882" width="8.125" style="11" customWidth="1"/>
-    <col min="15883" max="15883" width="10.125" style="11" customWidth="1"/>
-    <col min="15884" max="15884" width="7.25" style="11" customWidth="1"/>
-    <col min="15885" max="15885" width="11.875" style="11" customWidth="1"/>
-    <col min="15886" max="15886" width="2.125" style="11" customWidth="1"/>
-    <col min="15887" max="15888" width="12.5" style="11" customWidth="1"/>
-    <col min="15889" max="16122" width="9" style="11"/>
-    <col min="16123" max="16123" width="6.875" style="11" customWidth="1"/>
-    <col min="16124" max="16124" width="10.125" style="11" customWidth="1"/>
-    <col min="16125" max="16125" width="11.125" style="11" customWidth="1"/>
-    <col min="16126" max="16126" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="16127" max="16127" width="21.625" style="11" customWidth="1"/>
-    <col min="16128" max="16128" width="6.25" style="11" customWidth="1"/>
-    <col min="16129" max="16129" width="12.125" style="11" customWidth="1"/>
-    <col min="16130" max="16130" width="20.125" style="11" customWidth="1"/>
-    <col min="16131" max="16131" width="26.75" style="11" customWidth="1"/>
-    <col min="16132" max="16132" width="13.375" style="11" customWidth="1"/>
-    <col min="16133" max="16133" width="17" style="11" customWidth="1"/>
-    <col min="16134" max="16134" width="19.125" style="11" customWidth="1"/>
-    <col min="16135" max="16136" width="5.875" style="11" customWidth="1"/>
-    <col min="16137" max="16137" width="6.625" style="11" customWidth="1"/>
-    <col min="16138" max="16138" width="8.125" style="11" customWidth="1"/>
-    <col min="16139" max="16139" width="10.125" style="11" customWidth="1"/>
-    <col min="16140" max="16140" width="7.25" style="11" customWidth="1"/>
-    <col min="16141" max="16141" width="11.875" style="11" customWidth="1"/>
-    <col min="16142" max="16142" width="2.125" style="11" customWidth="1"/>
-    <col min="16143" max="16144" width="12.5" style="11" customWidth="1"/>
-    <col min="16145" max="16384" width="9" style="11"/>
+    <col min="15" max="15" width="11.125" style="13" customWidth="1"/>
+    <col min="16" max="16" width="11.25" style="14" customWidth="1"/>
+    <col min="17" max="250" width="9" style="14"/>
+    <col min="251" max="251" width="6.875" style="14" customWidth="1"/>
+    <col min="252" max="252" width="10.125" style="14" customWidth="1"/>
+    <col min="253" max="253" width="11.125" style="14" customWidth="1"/>
+    <col min="254" max="254" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="255" max="255" width="21.625" style="14" customWidth="1"/>
+    <col min="256" max="256" width="6.25" style="14" customWidth="1"/>
+    <col min="257" max="257" width="12.125" style="14" customWidth="1"/>
+    <col min="258" max="258" width="20.125" style="14" customWidth="1"/>
+    <col min="259" max="259" width="26.75" style="14" customWidth="1"/>
+    <col min="260" max="260" width="13.375" style="14" customWidth="1"/>
+    <col min="261" max="261" width="17" style="14" customWidth="1"/>
+    <col min="262" max="262" width="19.125" style="14" customWidth="1"/>
+    <col min="263" max="264" width="5.875" style="14" customWidth="1"/>
+    <col min="265" max="265" width="6.625" style="14" customWidth="1"/>
+    <col min="266" max="266" width="8.125" style="14" customWidth="1"/>
+    <col min="267" max="267" width="10.125" style="14" customWidth="1"/>
+    <col min="268" max="268" width="7.25" style="14" customWidth="1"/>
+    <col min="269" max="269" width="11.875" style="14" customWidth="1"/>
+    <col min="270" max="270" width="2.125" style="14" customWidth="1"/>
+    <col min="271" max="272" width="12.5" style="14" customWidth="1"/>
+    <col min="273" max="506" width="9" style="14"/>
+    <col min="507" max="507" width="6.875" style="14" customWidth="1"/>
+    <col min="508" max="508" width="10.125" style="14" customWidth="1"/>
+    <col min="509" max="509" width="11.125" style="14" customWidth="1"/>
+    <col min="510" max="510" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="511" max="511" width="21.625" style="14" customWidth="1"/>
+    <col min="512" max="512" width="6.25" style="14" customWidth="1"/>
+    <col min="513" max="513" width="12.125" style="14" customWidth="1"/>
+    <col min="514" max="514" width="20.125" style="14" customWidth="1"/>
+    <col min="515" max="515" width="26.75" style="14" customWidth="1"/>
+    <col min="516" max="516" width="13.375" style="14" customWidth="1"/>
+    <col min="517" max="517" width="17" style="14" customWidth="1"/>
+    <col min="518" max="518" width="19.125" style="14" customWidth="1"/>
+    <col min="519" max="520" width="5.875" style="14" customWidth="1"/>
+    <col min="521" max="521" width="6.625" style="14" customWidth="1"/>
+    <col min="522" max="522" width="8.125" style="14" customWidth="1"/>
+    <col min="523" max="523" width="10.125" style="14" customWidth="1"/>
+    <col min="524" max="524" width="7.25" style="14" customWidth="1"/>
+    <col min="525" max="525" width="11.875" style="14" customWidth="1"/>
+    <col min="526" max="526" width="2.125" style="14" customWidth="1"/>
+    <col min="527" max="528" width="12.5" style="14" customWidth="1"/>
+    <col min="529" max="762" width="9" style="14"/>
+    <col min="763" max="763" width="6.875" style="14" customWidth="1"/>
+    <col min="764" max="764" width="10.125" style="14" customWidth="1"/>
+    <col min="765" max="765" width="11.125" style="14" customWidth="1"/>
+    <col min="766" max="766" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="767" max="767" width="21.625" style="14" customWidth="1"/>
+    <col min="768" max="768" width="6.25" style="14" customWidth="1"/>
+    <col min="769" max="769" width="12.125" style="14" customWidth="1"/>
+    <col min="770" max="770" width="20.125" style="14" customWidth="1"/>
+    <col min="771" max="771" width="26.75" style="14" customWidth="1"/>
+    <col min="772" max="772" width="13.375" style="14" customWidth="1"/>
+    <col min="773" max="773" width="17" style="14" customWidth="1"/>
+    <col min="774" max="774" width="19.125" style="14" customWidth="1"/>
+    <col min="775" max="776" width="5.875" style="14" customWidth="1"/>
+    <col min="777" max="777" width="6.625" style="14" customWidth="1"/>
+    <col min="778" max="778" width="8.125" style="14" customWidth="1"/>
+    <col min="779" max="779" width="10.125" style="14" customWidth="1"/>
+    <col min="780" max="780" width="7.25" style="14" customWidth="1"/>
+    <col min="781" max="781" width="11.875" style="14" customWidth="1"/>
+    <col min="782" max="782" width="2.125" style="14" customWidth="1"/>
+    <col min="783" max="784" width="12.5" style="14" customWidth="1"/>
+    <col min="785" max="1018" width="9" style="14"/>
+    <col min="1019" max="1019" width="6.875" style="14" customWidth="1"/>
+    <col min="1020" max="1020" width="10.125" style="14" customWidth="1"/>
+    <col min="1021" max="1021" width="11.125" style="14" customWidth="1"/>
+    <col min="1022" max="1022" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="1023" max="1023" width="21.625" style="14" customWidth="1"/>
+    <col min="1024" max="1024" width="6.25" style="14" customWidth="1"/>
+    <col min="1025" max="1025" width="12.125" style="14" customWidth="1"/>
+    <col min="1026" max="1026" width="20.125" style="14" customWidth="1"/>
+    <col min="1027" max="1027" width="26.75" style="14" customWidth="1"/>
+    <col min="1028" max="1028" width="13.375" style="14" customWidth="1"/>
+    <col min="1029" max="1029" width="17" style="14" customWidth="1"/>
+    <col min="1030" max="1030" width="19.125" style="14" customWidth="1"/>
+    <col min="1031" max="1032" width="5.875" style="14" customWidth="1"/>
+    <col min="1033" max="1033" width="6.625" style="14" customWidth="1"/>
+    <col min="1034" max="1034" width="8.125" style="14" customWidth="1"/>
+    <col min="1035" max="1035" width="10.125" style="14" customWidth="1"/>
+    <col min="1036" max="1036" width="7.25" style="14" customWidth="1"/>
+    <col min="1037" max="1037" width="11.875" style="14" customWidth="1"/>
+    <col min="1038" max="1038" width="2.125" style="14" customWidth="1"/>
+    <col min="1039" max="1040" width="12.5" style="14" customWidth="1"/>
+    <col min="1041" max="1274" width="9" style="14"/>
+    <col min="1275" max="1275" width="6.875" style="14" customWidth="1"/>
+    <col min="1276" max="1276" width="10.125" style="14" customWidth="1"/>
+    <col min="1277" max="1277" width="11.125" style="14" customWidth="1"/>
+    <col min="1278" max="1278" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="1279" max="1279" width="21.625" style="14" customWidth="1"/>
+    <col min="1280" max="1280" width="6.25" style="14" customWidth="1"/>
+    <col min="1281" max="1281" width="12.125" style="14" customWidth="1"/>
+    <col min="1282" max="1282" width="20.125" style="14" customWidth="1"/>
+    <col min="1283" max="1283" width="26.75" style="14" customWidth="1"/>
+    <col min="1284" max="1284" width="13.375" style="14" customWidth="1"/>
+    <col min="1285" max="1285" width="17" style="14" customWidth="1"/>
+    <col min="1286" max="1286" width="19.125" style="14" customWidth="1"/>
+    <col min="1287" max="1288" width="5.875" style="14" customWidth="1"/>
+    <col min="1289" max="1289" width="6.625" style="14" customWidth="1"/>
+    <col min="1290" max="1290" width="8.125" style="14" customWidth="1"/>
+    <col min="1291" max="1291" width="10.125" style="14" customWidth="1"/>
+    <col min="1292" max="1292" width="7.25" style="14" customWidth="1"/>
+    <col min="1293" max="1293" width="11.875" style="14" customWidth="1"/>
+    <col min="1294" max="1294" width="2.125" style="14" customWidth="1"/>
+    <col min="1295" max="1296" width="12.5" style="14" customWidth="1"/>
+    <col min="1297" max="1530" width="9" style="14"/>
+    <col min="1531" max="1531" width="6.875" style="14" customWidth="1"/>
+    <col min="1532" max="1532" width="10.125" style="14" customWidth="1"/>
+    <col min="1533" max="1533" width="11.125" style="14" customWidth="1"/>
+    <col min="1534" max="1534" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="1535" max="1535" width="21.625" style="14" customWidth="1"/>
+    <col min="1536" max="1536" width="6.25" style="14" customWidth="1"/>
+    <col min="1537" max="1537" width="12.125" style="14" customWidth="1"/>
+    <col min="1538" max="1538" width="20.125" style="14" customWidth="1"/>
+    <col min="1539" max="1539" width="26.75" style="14" customWidth="1"/>
+    <col min="1540" max="1540" width="13.375" style="14" customWidth="1"/>
+    <col min="1541" max="1541" width="17" style="14" customWidth="1"/>
+    <col min="1542" max="1542" width="19.125" style="14" customWidth="1"/>
+    <col min="1543" max="1544" width="5.875" style="14" customWidth="1"/>
+    <col min="1545" max="1545" width="6.625" style="14" customWidth="1"/>
+    <col min="1546" max="1546" width="8.125" style="14" customWidth="1"/>
+    <col min="1547" max="1547" width="10.125" style="14" customWidth="1"/>
+    <col min="1548" max="1548" width="7.25" style="14" customWidth="1"/>
+    <col min="1549" max="1549" width="11.875" style="14" customWidth="1"/>
+    <col min="1550" max="1550" width="2.125" style="14" customWidth="1"/>
+    <col min="1551" max="1552" width="12.5" style="14" customWidth="1"/>
+    <col min="1553" max="1786" width="9" style="14"/>
+    <col min="1787" max="1787" width="6.875" style="14" customWidth="1"/>
+    <col min="1788" max="1788" width="10.125" style="14" customWidth="1"/>
+    <col min="1789" max="1789" width="11.125" style="14" customWidth="1"/>
+    <col min="1790" max="1790" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="1791" max="1791" width="21.625" style="14" customWidth="1"/>
+    <col min="1792" max="1792" width="6.25" style="14" customWidth="1"/>
+    <col min="1793" max="1793" width="12.125" style="14" customWidth="1"/>
+    <col min="1794" max="1794" width="20.125" style="14" customWidth="1"/>
+    <col min="1795" max="1795" width="26.75" style="14" customWidth="1"/>
+    <col min="1796" max="1796" width="13.375" style="14" customWidth="1"/>
+    <col min="1797" max="1797" width="17" style="14" customWidth="1"/>
+    <col min="1798" max="1798" width="19.125" style="14" customWidth="1"/>
+    <col min="1799" max="1800" width="5.875" style="14" customWidth="1"/>
+    <col min="1801" max="1801" width="6.625" style="14" customWidth="1"/>
+    <col min="1802" max="1802" width="8.125" style="14" customWidth="1"/>
+    <col min="1803" max="1803" width="10.125" style="14" customWidth="1"/>
+    <col min="1804" max="1804" width="7.25" style="14" customWidth="1"/>
+    <col min="1805" max="1805" width="11.875" style="14" customWidth="1"/>
+    <col min="1806" max="1806" width="2.125" style="14" customWidth="1"/>
+    <col min="1807" max="1808" width="12.5" style="14" customWidth="1"/>
+    <col min="1809" max="2042" width="9" style="14"/>
+    <col min="2043" max="2043" width="6.875" style="14" customWidth="1"/>
+    <col min="2044" max="2044" width="10.125" style="14" customWidth="1"/>
+    <col min="2045" max="2045" width="11.125" style="14" customWidth="1"/>
+    <col min="2046" max="2046" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="2047" max="2047" width="21.625" style="14" customWidth="1"/>
+    <col min="2048" max="2048" width="6.25" style="14" customWidth="1"/>
+    <col min="2049" max="2049" width="12.125" style="14" customWidth="1"/>
+    <col min="2050" max="2050" width="20.125" style="14" customWidth="1"/>
+    <col min="2051" max="2051" width="26.75" style="14" customWidth="1"/>
+    <col min="2052" max="2052" width="13.375" style="14" customWidth="1"/>
+    <col min="2053" max="2053" width="17" style="14" customWidth="1"/>
+    <col min="2054" max="2054" width="19.125" style="14" customWidth="1"/>
+    <col min="2055" max="2056" width="5.875" style="14" customWidth="1"/>
+    <col min="2057" max="2057" width="6.625" style="14" customWidth="1"/>
+    <col min="2058" max="2058" width="8.125" style="14" customWidth="1"/>
+    <col min="2059" max="2059" width="10.125" style="14" customWidth="1"/>
+    <col min="2060" max="2060" width="7.25" style="14" customWidth="1"/>
+    <col min="2061" max="2061" width="11.875" style="14" customWidth="1"/>
+    <col min="2062" max="2062" width="2.125" style="14" customWidth="1"/>
+    <col min="2063" max="2064" width="12.5" style="14" customWidth="1"/>
+    <col min="2065" max="2298" width="9" style="14"/>
+    <col min="2299" max="2299" width="6.875" style="14" customWidth="1"/>
+    <col min="2300" max="2300" width="10.125" style="14" customWidth="1"/>
+    <col min="2301" max="2301" width="11.125" style="14" customWidth="1"/>
+    <col min="2302" max="2302" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="2303" max="2303" width="21.625" style="14" customWidth="1"/>
+    <col min="2304" max="2304" width="6.25" style="14" customWidth="1"/>
+    <col min="2305" max="2305" width="12.125" style="14" customWidth="1"/>
+    <col min="2306" max="2306" width="20.125" style="14" customWidth="1"/>
+    <col min="2307" max="2307" width="26.75" style="14" customWidth="1"/>
+    <col min="2308" max="2308" width="13.375" style="14" customWidth="1"/>
+    <col min="2309" max="2309" width="17" style="14" customWidth="1"/>
+    <col min="2310" max="2310" width="19.125" style="14" customWidth="1"/>
+    <col min="2311" max="2312" width="5.875" style="14" customWidth="1"/>
+    <col min="2313" max="2313" width="6.625" style="14" customWidth="1"/>
+    <col min="2314" max="2314" width="8.125" style="14" customWidth="1"/>
+    <col min="2315" max="2315" width="10.125" style="14" customWidth="1"/>
+    <col min="2316" max="2316" width="7.25" style="14" customWidth="1"/>
+    <col min="2317" max="2317" width="11.875" style="14" customWidth="1"/>
+    <col min="2318" max="2318" width="2.125" style="14" customWidth="1"/>
+    <col min="2319" max="2320" width="12.5" style="14" customWidth="1"/>
+    <col min="2321" max="2554" width="9" style="14"/>
+    <col min="2555" max="2555" width="6.875" style="14" customWidth="1"/>
+    <col min="2556" max="2556" width="10.125" style="14" customWidth="1"/>
+    <col min="2557" max="2557" width="11.125" style="14" customWidth="1"/>
+    <col min="2558" max="2558" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="2559" max="2559" width="21.625" style="14" customWidth="1"/>
+    <col min="2560" max="2560" width="6.25" style="14" customWidth="1"/>
+    <col min="2561" max="2561" width="12.125" style="14" customWidth="1"/>
+    <col min="2562" max="2562" width="20.125" style="14" customWidth="1"/>
+    <col min="2563" max="2563" width="26.75" style="14" customWidth="1"/>
+    <col min="2564" max="2564" width="13.375" style="14" customWidth="1"/>
+    <col min="2565" max="2565" width="17" style="14" customWidth="1"/>
+    <col min="2566" max="2566" width="19.125" style="14" customWidth="1"/>
+    <col min="2567" max="2568" width="5.875" style="14" customWidth="1"/>
+    <col min="2569" max="2569" width="6.625" style="14" customWidth="1"/>
+    <col min="2570" max="2570" width="8.125" style="14" customWidth="1"/>
+    <col min="2571" max="2571" width="10.125" style="14" customWidth="1"/>
+    <col min="2572" max="2572" width="7.25" style="14" customWidth="1"/>
+    <col min="2573" max="2573" width="11.875" style="14" customWidth="1"/>
+    <col min="2574" max="2574" width="2.125" style="14" customWidth="1"/>
+    <col min="2575" max="2576" width="12.5" style="14" customWidth="1"/>
+    <col min="2577" max="2810" width="9" style="14"/>
+    <col min="2811" max="2811" width="6.875" style="14" customWidth="1"/>
+    <col min="2812" max="2812" width="10.125" style="14" customWidth="1"/>
+    <col min="2813" max="2813" width="11.125" style="14" customWidth="1"/>
+    <col min="2814" max="2814" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="2815" max="2815" width="21.625" style="14" customWidth="1"/>
+    <col min="2816" max="2816" width="6.25" style="14" customWidth="1"/>
+    <col min="2817" max="2817" width="12.125" style="14" customWidth="1"/>
+    <col min="2818" max="2818" width="20.125" style="14" customWidth="1"/>
+    <col min="2819" max="2819" width="26.75" style="14" customWidth="1"/>
+    <col min="2820" max="2820" width="13.375" style="14" customWidth="1"/>
+    <col min="2821" max="2821" width="17" style="14" customWidth="1"/>
+    <col min="2822" max="2822" width="19.125" style="14" customWidth="1"/>
+    <col min="2823" max="2824" width="5.875" style="14" customWidth="1"/>
+    <col min="2825" max="2825" width="6.625" style="14" customWidth="1"/>
+    <col min="2826" max="2826" width="8.125" style="14" customWidth="1"/>
+    <col min="2827" max="2827" width="10.125" style="14" customWidth="1"/>
+    <col min="2828" max="2828" width="7.25" style="14" customWidth="1"/>
+    <col min="2829" max="2829" width="11.875" style="14" customWidth="1"/>
+    <col min="2830" max="2830" width="2.125" style="14" customWidth="1"/>
+    <col min="2831" max="2832" width="12.5" style="14" customWidth="1"/>
+    <col min="2833" max="3066" width="9" style="14"/>
+    <col min="3067" max="3067" width="6.875" style="14" customWidth="1"/>
+    <col min="3068" max="3068" width="10.125" style="14" customWidth="1"/>
+    <col min="3069" max="3069" width="11.125" style="14" customWidth="1"/>
+    <col min="3070" max="3070" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="3071" max="3071" width="21.625" style="14" customWidth="1"/>
+    <col min="3072" max="3072" width="6.25" style="14" customWidth="1"/>
+    <col min="3073" max="3073" width="12.125" style="14" customWidth="1"/>
+    <col min="3074" max="3074" width="20.125" style="14" customWidth="1"/>
+    <col min="3075" max="3075" width="26.75" style="14" customWidth="1"/>
+    <col min="3076" max="3076" width="13.375" style="14" customWidth="1"/>
+    <col min="3077" max="3077" width="17" style="14" customWidth="1"/>
+    <col min="3078" max="3078" width="19.125" style="14" customWidth="1"/>
+    <col min="3079" max="3080" width="5.875" style="14" customWidth="1"/>
+    <col min="3081" max="3081" width="6.625" style="14" customWidth="1"/>
+    <col min="3082" max="3082" width="8.125" style="14" customWidth="1"/>
+    <col min="3083" max="3083" width="10.125" style="14" customWidth="1"/>
+    <col min="3084" max="3084" width="7.25" style="14" customWidth="1"/>
+    <col min="3085" max="3085" width="11.875" style="14" customWidth="1"/>
+    <col min="3086" max="3086" width="2.125" style="14" customWidth="1"/>
+    <col min="3087" max="3088" width="12.5" style="14" customWidth="1"/>
+    <col min="3089" max="3322" width="9" style="14"/>
+    <col min="3323" max="3323" width="6.875" style="14" customWidth="1"/>
+    <col min="3324" max="3324" width="10.125" style="14" customWidth="1"/>
+    <col min="3325" max="3325" width="11.125" style="14" customWidth="1"/>
+    <col min="3326" max="3326" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="3327" max="3327" width="21.625" style="14" customWidth="1"/>
+    <col min="3328" max="3328" width="6.25" style="14" customWidth="1"/>
+    <col min="3329" max="3329" width="12.125" style="14" customWidth="1"/>
+    <col min="3330" max="3330" width="20.125" style="14" customWidth="1"/>
+    <col min="3331" max="3331" width="26.75" style="14" customWidth="1"/>
+    <col min="3332" max="3332" width="13.375" style="14" customWidth="1"/>
+    <col min="3333" max="3333" width="17" style="14" customWidth="1"/>
+    <col min="3334" max="3334" width="19.125" style="14" customWidth="1"/>
+    <col min="3335" max="3336" width="5.875" style="14" customWidth="1"/>
+    <col min="3337" max="3337" width="6.625" style="14" customWidth="1"/>
+    <col min="3338" max="3338" width="8.125" style="14" customWidth="1"/>
+    <col min="3339" max="3339" width="10.125" style="14" customWidth="1"/>
+    <col min="3340" max="3340" width="7.25" style="14" customWidth="1"/>
+    <col min="3341" max="3341" width="11.875" style="14" customWidth="1"/>
+    <col min="3342" max="3342" width="2.125" style="14" customWidth="1"/>
+    <col min="3343" max="3344" width="12.5" style="14" customWidth="1"/>
+    <col min="3345" max="3578" width="9" style="14"/>
+    <col min="3579" max="3579" width="6.875" style="14" customWidth="1"/>
+    <col min="3580" max="3580" width="10.125" style="14" customWidth="1"/>
+    <col min="3581" max="3581" width="11.125" style="14" customWidth="1"/>
+    <col min="3582" max="3582" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="3583" max="3583" width="21.625" style="14" customWidth="1"/>
+    <col min="3584" max="3584" width="6.25" style="14" customWidth="1"/>
+    <col min="3585" max="3585" width="12.125" style="14" customWidth="1"/>
+    <col min="3586" max="3586" width="20.125" style="14" customWidth="1"/>
+    <col min="3587" max="3587" width="26.75" style="14" customWidth="1"/>
+    <col min="3588" max="3588" width="13.375" style="14" customWidth="1"/>
+    <col min="3589" max="3589" width="17" style="14" customWidth="1"/>
+    <col min="3590" max="3590" width="19.125" style="14" customWidth="1"/>
+    <col min="3591" max="3592" width="5.875" style="14" customWidth="1"/>
+    <col min="3593" max="3593" width="6.625" style="14" customWidth="1"/>
+    <col min="3594" max="3594" width="8.125" style="14" customWidth="1"/>
+    <col min="3595" max="3595" width="10.125" style="14" customWidth="1"/>
+    <col min="3596" max="3596" width="7.25" style="14" customWidth="1"/>
+    <col min="3597" max="3597" width="11.875" style="14" customWidth="1"/>
+    <col min="3598" max="3598" width="2.125" style="14" customWidth="1"/>
+    <col min="3599" max="3600" width="12.5" style="14" customWidth="1"/>
+    <col min="3601" max="3834" width="9" style="14"/>
+    <col min="3835" max="3835" width="6.875" style="14" customWidth="1"/>
+    <col min="3836" max="3836" width="10.125" style="14" customWidth="1"/>
+    <col min="3837" max="3837" width="11.125" style="14" customWidth="1"/>
+    <col min="3838" max="3838" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="3839" max="3839" width="21.625" style="14" customWidth="1"/>
+    <col min="3840" max="3840" width="6.25" style="14" customWidth="1"/>
+    <col min="3841" max="3841" width="12.125" style="14" customWidth="1"/>
+    <col min="3842" max="3842" width="20.125" style="14" customWidth="1"/>
+    <col min="3843" max="3843" width="26.75" style="14" customWidth="1"/>
+    <col min="3844" max="3844" width="13.375" style="14" customWidth="1"/>
+    <col min="3845" max="3845" width="17" style="14" customWidth="1"/>
+    <col min="3846" max="3846" width="19.125" style="14" customWidth="1"/>
+    <col min="3847" max="3848" width="5.875" style="14" customWidth="1"/>
+    <col min="3849" max="3849" width="6.625" style="14" customWidth="1"/>
+    <col min="3850" max="3850" width="8.125" style="14" customWidth="1"/>
+    <col min="3851" max="3851" width="10.125" style="14" customWidth="1"/>
+    <col min="3852" max="3852" width="7.25" style="14" customWidth="1"/>
+    <col min="3853" max="3853" width="11.875" style="14" customWidth="1"/>
+    <col min="3854" max="3854" width="2.125" style="14" customWidth="1"/>
+    <col min="3855" max="3856" width="12.5" style="14" customWidth="1"/>
+    <col min="3857" max="4090" width="9" style="14"/>
+    <col min="4091" max="4091" width="6.875" style="14" customWidth="1"/>
+    <col min="4092" max="4092" width="10.125" style="14" customWidth="1"/>
+    <col min="4093" max="4093" width="11.125" style="14" customWidth="1"/>
+    <col min="4094" max="4094" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="4095" max="4095" width="21.625" style="14" customWidth="1"/>
+    <col min="4096" max="4096" width="6.25" style="14" customWidth="1"/>
+    <col min="4097" max="4097" width="12.125" style="14" customWidth="1"/>
+    <col min="4098" max="4098" width="20.125" style="14" customWidth="1"/>
+    <col min="4099" max="4099" width="26.75" style="14" customWidth="1"/>
+    <col min="4100" max="4100" width="13.375" style="14" customWidth="1"/>
+    <col min="4101" max="4101" width="17" style="14" customWidth="1"/>
+    <col min="4102" max="4102" width="19.125" style="14" customWidth="1"/>
+    <col min="4103" max="4104" width="5.875" style="14" customWidth="1"/>
+    <col min="4105" max="4105" width="6.625" style="14" customWidth="1"/>
+    <col min="4106" max="4106" width="8.125" style="14" customWidth="1"/>
+    <col min="4107" max="4107" width="10.125" style="14" customWidth="1"/>
+    <col min="4108" max="4108" width="7.25" style="14" customWidth="1"/>
+    <col min="4109" max="4109" width="11.875" style="14" customWidth="1"/>
+    <col min="4110" max="4110" width="2.125" style="14" customWidth="1"/>
+    <col min="4111" max="4112" width="12.5" style="14" customWidth="1"/>
+    <col min="4113" max="4346" width="9" style="14"/>
+    <col min="4347" max="4347" width="6.875" style="14" customWidth="1"/>
+    <col min="4348" max="4348" width="10.125" style="14" customWidth="1"/>
+    <col min="4349" max="4349" width="11.125" style="14" customWidth="1"/>
+    <col min="4350" max="4350" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="4351" max="4351" width="21.625" style="14" customWidth="1"/>
+    <col min="4352" max="4352" width="6.25" style="14" customWidth="1"/>
+    <col min="4353" max="4353" width="12.125" style="14" customWidth="1"/>
+    <col min="4354" max="4354" width="20.125" style="14" customWidth="1"/>
+    <col min="4355" max="4355" width="26.75" style="14" customWidth="1"/>
+    <col min="4356" max="4356" width="13.375" style="14" customWidth="1"/>
+    <col min="4357" max="4357" width="17" style="14" customWidth="1"/>
+    <col min="4358" max="4358" width="19.125" style="14" customWidth="1"/>
+    <col min="4359" max="4360" width="5.875" style="14" customWidth="1"/>
+    <col min="4361" max="4361" width="6.625" style="14" customWidth="1"/>
+    <col min="4362" max="4362" width="8.125" style="14" customWidth="1"/>
+    <col min="4363" max="4363" width="10.125" style="14" customWidth="1"/>
+    <col min="4364" max="4364" width="7.25" style="14" customWidth="1"/>
+    <col min="4365" max="4365" width="11.875" style="14" customWidth="1"/>
+    <col min="4366" max="4366" width="2.125" style="14" customWidth="1"/>
+    <col min="4367" max="4368" width="12.5" style="14" customWidth="1"/>
+    <col min="4369" max="4602" width="9" style="14"/>
+    <col min="4603" max="4603" width="6.875" style="14" customWidth="1"/>
+    <col min="4604" max="4604" width="10.125" style="14" customWidth="1"/>
+    <col min="4605" max="4605" width="11.125" style="14" customWidth="1"/>
+    <col min="4606" max="4606" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="4607" max="4607" width="21.625" style="14" customWidth="1"/>
+    <col min="4608" max="4608" width="6.25" style="14" customWidth="1"/>
+    <col min="4609" max="4609" width="12.125" style="14" customWidth="1"/>
+    <col min="4610" max="4610" width="20.125" style="14" customWidth="1"/>
+    <col min="4611" max="4611" width="26.75" style="14" customWidth="1"/>
+    <col min="4612" max="4612" width="13.375" style="14" customWidth="1"/>
+    <col min="4613" max="4613" width="17" style="14" customWidth="1"/>
+    <col min="4614" max="4614" width="19.125" style="14" customWidth="1"/>
+    <col min="4615" max="4616" width="5.875" style="14" customWidth="1"/>
+    <col min="4617" max="4617" width="6.625" style="14" customWidth="1"/>
+    <col min="4618" max="4618" width="8.125" style="14" customWidth="1"/>
+    <col min="4619" max="4619" width="10.125" style="14" customWidth="1"/>
+    <col min="4620" max="4620" width="7.25" style="14" customWidth="1"/>
+    <col min="4621" max="4621" width="11.875" style="14" customWidth="1"/>
+    <col min="4622" max="4622" width="2.125" style="14" customWidth="1"/>
+    <col min="4623" max="4624" width="12.5" style="14" customWidth="1"/>
+    <col min="4625" max="4858" width="9" style="14"/>
+    <col min="4859" max="4859" width="6.875" style="14" customWidth="1"/>
+    <col min="4860" max="4860" width="10.125" style="14" customWidth="1"/>
+    <col min="4861" max="4861" width="11.125" style="14" customWidth="1"/>
+    <col min="4862" max="4862" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="4863" max="4863" width="21.625" style="14" customWidth="1"/>
+    <col min="4864" max="4864" width="6.25" style="14" customWidth="1"/>
+    <col min="4865" max="4865" width="12.125" style="14" customWidth="1"/>
+    <col min="4866" max="4866" width="20.125" style="14" customWidth="1"/>
+    <col min="4867" max="4867" width="26.75" style="14" customWidth="1"/>
+    <col min="4868" max="4868" width="13.375" style="14" customWidth="1"/>
+    <col min="4869" max="4869" width="17" style="14" customWidth="1"/>
+    <col min="4870" max="4870" width="19.125" style="14" customWidth="1"/>
+    <col min="4871" max="4872" width="5.875" style="14" customWidth="1"/>
+    <col min="4873" max="4873" width="6.625" style="14" customWidth="1"/>
+    <col min="4874" max="4874" width="8.125" style="14" customWidth="1"/>
+    <col min="4875" max="4875" width="10.125" style="14" customWidth="1"/>
+    <col min="4876" max="4876" width="7.25" style="14" customWidth="1"/>
+    <col min="4877" max="4877" width="11.875" style="14" customWidth="1"/>
+    <col min="4878" max="4878" width="2.125" style="14" customWidth="1"/>
+    <col min="4879" max="4880" width="12.5" style="14" customWidth="1"/>
+    <col min="4881" max="5114" width="9" style="14"/>
+    <col min="5115" max="5115" width="6.875" style="14" customWidth="1"/>
+    <col min="5116" max="5116" width="10.125" style="14" customWidth="1"/>
+    <col min="5117" max="5117" width="11.125" style="14" customWidth="1"/>
+    <col min="5118" max="5118" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="5119" max="5119" width="21.625" style="14" customWidth="1"/>
+    <col min="5120" max="5120" width="6.25" style="14" customWidth="1"/>
+    <col min="5121" max="5121" width="12.125" style="14" customWidth="1"/>
+    <col min="5122" max="5122" width="20.125" style="14" customWidth="1"/>
+    <col min="5123" max="5123" width="26.75" style="14" customWidth="1"/>
+    <col min="5124" max="5124" width="13.375" style="14" customWidth="1"/>
+    <col min="5125" max="5125" width="17" style="14" customWidth="1"/>
+    <col min="5126" max="5126" width="19.125" style="14" customWidth="1"/>
+    <col min="5127" max="5128" width="5.875" style="14" customWidth="1"/>
+    <col min="5129" max="5129" width="6.625" style="14" customWidth="1"/>
+    <col min="5130" max="5130" width="8.125" style="14" customWidth="1"/>
+    <col min="5131" max="5131" width="10.125" style="14" customWidth="1"/>
+    <col min="5132" max="5132" width="7.25" style="14" customWidth="1"/>
+    <col min="5133" max="5133" width="11.875" style="14" customWidth="1"/>
+    <col min="5134" max="5134" width="2.125" style="14" customWidth="1"/>
+    <col min="5135" max="5136" width="12.5" style="14" customWidth="1"/>
+    <col min="5137" max="5370" width="9" style="14"/>
+    <col min="5371" max="5371" width="6.875" style="14" customWidth="1"/>
+    <col min="5372" max="5372" width="10.125" style="14" customWidth="1"/>
+    <col min="5373" max="5373" width="11.125" style="14" customWidth="1"/>
+    <col min="5374" max="5374" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="5375" max="5375" width="21.625" style="14" customWidth="1"/>
+    <col min="5376" max="5376" width="6.25" style="14" customWidth="1"/>
+    <col min="5377" max="5377" width="12.125" style="14" customWidth="1"/>
+    <col min="5378" max="5378" width="20.125" style="14" customWidth="1"/>
+    <col min="5379" max="5379" width="26.75" style="14" customWidth="1"/>
+    <col min="5380" max="5380" width="13.375" style="14" customWidth="1"/>
+    <col min="5381" max="5381" width="17" style="14" customWidth="1"/>
+    <col min="5382" max="5382" width="19.125" style="14" customWidth="1"/>
+    <col min="5383" max="5384" width="5.875" style="14" customWidth="1"/>
+    <col min="5385" max="5385" width="6.625" style="14" customWidth="1"/>
+    <col min="5386" max="5386" width="8.125" style="14" customWidth="1"/>
+    <col min="5387" max="5387" width="10.125" style="14" customWidth="1"/>
+    <col min="5388" max="5388" width="7.25" style="14" customWidth="1"/>
+    <col min="5389" max="5389" width="11.875" style="14" customWidth="1"/>
+    <col min="5390" max="5390" width="2.125" style="14" customWidth="1"/>
+    <col min="5391" max="5392" width="12.5" style="14" customWidth="1"/>
+    <col min="5393" max="5626" width="9" style="14"/>
+    <col min="5627" max="5627" width="6.875" style="14" customWidth="1"/>
+    <col min="5628" max="5628" width="10.125" style="14" customWidth="1"/>
+    <col min="5629" max="5629" width="11.125" style="14" customWidth="1"/>
+    <col min="5630" max="5630" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="5631" max="5631" width="21.625" style="14" customWidth="1"/>
+    <col min="5632" max="5632" width="6.25" style="14" customWidth="1"/>
+    <col min="5633" max="5633" width="12.125" style="14" customWidth="1"/>
+    <col min="5634" max="5634" width="20.125" style="14" customWidth="1"/>
+    <col min="5635" max="5635" width="26.75" style="14" customWidth="1"/>
+    <col min="5636" max="5636" width="13.375" style="14" customWidth="1"/>
+    <col min="5637" max="5637" width="17" style="14" customWidth="1"/>
+    <col min="5638" max="5638" width="19.125" style="14" customWidth="1"/>
+    <col min="5639" max="5640" width="5.875" style="14" customWidth="1"/>
+    <col min="5641" max="5641" width="6.625" style="14" customWidth="1"/>
+    <col min="5642" max="5642" width="8.125" style="14" customWidth="1"/>
+    <col min="5643" max="5643" width="10.125" style="14" customWidth="1"/>
+    <col min="5644" max="5644" width="7.25" style="14" customWidth="1"/>
+    <col min="5645" max="5645" width="11.875" style="14" customWidth="1"/>
+    <col min="5646" max="5646" width="2.125" style="14" customWidth="1"/>
+    <col min="5647" max="5648" width="12.5" style="14" customWidth="1"/>
+    <col min="5649" max="5882" width="9" style="14"/>
+    <col min="5883" max="5883" width="6.875" style="14" customWidth="1"/>
+    <col min="5884" max="5884" width="10.125" style="14" customWidth="1"/>
+    <col min="5885" max="5885" width="11.125" style="14" customWidth="1"/>
+    <col min="5886" max="5886" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="5887" max="5887" width="21.625" style="14" customWidth="1"/>
+    <col min="5888" max="5888" width="6.25" style="14" customWidth="1"/>
+    <col min="5889" max="5889" width="12.125" style="14" customWidth="1"/>
+    <col min="5890" max="5890" width="20.125" style="14" customWidth="1"/>
+    <col min="5891" max="5891" width="26.75" style="14" customWidth="1"/>
+    <col min="5892" max="5892" width="13.375" style="14" customWidth="1"/>
+    <col min="5893" max="5893" width="17" style="14" customWidth="1"/>
+    <col min="5894" max="5894" width="19.125" style="14" customWidth="1"/>
+    <col min="5895" max="5896" width="5.875" style="14" customWidth="1"/>
+    <col min="5897" max="5897" width="6.625" style="14" customWidth="1"/>
+    <col min="5898" max="5898" width="8.125" style="14" customWidth="1"/>
+    <col min="5899" max="5899" width="10.125" style="14" customWidth="1"/>
+    <col min="5900" max="5900" width="7.25" style="14" customWidth="1"/>
+    <col min="5901" max="5901" width="11.875" style="14" customWidth="1"/>
+    <col min="5902" max="5902" width="2.125" style="14" customWidth="1"/>
+    <col min="5903" max="5904" width="12.5" style="14" customWidth="1"/>
+    <col min="5905" max="6138" width="9" style="14"/>
+    <col min="6139" max="6139" width="6.875" style="14" customWidth="1"/>
+    <col min="6140" max="6140" width="10.125" style="14" customWidth="1"/>
+    <col min="6141" max="6141" width="11.125" style="14" customWidth="1"/>
+    <col min="6142" max="6142" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="6143" max="6143" width="21.625" style="14" customWidth="1"/>
+    <col min="6144" max="6144" width="6.25" style="14" customWidth="1"/>
+    <col min="6145" max="6145" width="12.125" style="14" customWidth="1"/>
+    <col min="6146" max="6146" width="20.125" style="14" customWidth="1"/>
+    <col min="6147" max="6147" width="26.75" style="14" customWidth="1"/>
+    <col min="6148" max="6148" width="13.375" style="14" customWidth="1"/>
+    <col min="6149" max="6149" width="17" style="14" customWidth="1"/>
+    <col min="6150" max="6150" width="19.125" style="14" customWidth="1"/>
+    <col min="6151" max="6152" width="5.875" style="14" customWidth="1"/>
+    <col min="6153" max="6153" width="6.625" style="14" customWidth="1"/>
+    <col min="6154" max="6154" width="8.125" style="14" customWidth="1"/>
+    <col min="6155" max="6155" width="10.125" style="14" customWidth="1"/>
+    <col min="6156" max="6156" width="7.25" style="14" customWidth="1"/>
+    <col min="6157" max="6157" width="11.875" style="14" customWidth="1"/>
+    <col min="6158" max="6158" width="2.125" style="14" customWidth="1"/>
+    <col min="6159" max="6160" width="12.5" style="14" customWidth="1"/>
+    <col min="6161" max="6394" width="9" style="14"/>
+    <col min="6395" max="6395" width="6.875" style="14" customWidth="1"/>
+    <col min="6396" max="6396" width="10.125" style="14" customWidth="1"/>
+    <col min="6397" max="6397" width="11.125" style="14" customWidth="1"/>
+    <col min="6398" max="6398" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="6399" max="6399" width="21.625" style="14" customWidth="1"/>
+    <col min="6400" max="6400" width="6.25" style="14" customWidth="1"/>
+    <col min="6401" max="6401" width="12.125" style="14" customWidth="1"/>
+    <col min="6402" max="6402" width="20.125" style="14" customWidth="1"/>
+    <col min="6403" max="6403" width="26.75" style="14" customWidth="1"/>
+    <col min="6404" max="6404" width="13.375" style="14" customWidth="1"/>
+    <col min="6405" max="6405" width="17" style="14" customWidth="1"/>
+    <col min="6406" max="6406" width="19.125" style="14" customWidth="1"/>
+    <col min="6407" max="6408" width="5.875" style="14" customWidth="1"/>
+    <col min="6409" max="6409" width="6.625" style="14" customWidth="1"/>
+    <col min="6410" max="6410" width="8.125" style="14" customWidth="1"/>
+    <col min="6411" max="6411" width="10.125" style="14" customWidth="1"/>
+    <col min="6412" max="6412" width="7.25" style="14" customWidth="1"/>
+    <col min="6413" max="6413" width="11.875" style="14" customWidth="1"/>
+    <col min="6414" max="6414" width="2.125" style="14" customWidth="1"/>
+    <col min="6415" max="6416" width="12.5" style="14" customWidth="1"/>
+    <col min="6417" max="6650" width="9" style="14"/>
+    <col min="6651" max="6651" width="6.875" style="14" customWidth="1"/>
+    <col min="6652" max="6652" width="10.125" style="14" customWidth="1"/>
+    <col min="6653" max="6653" width="11.125" style="14" customWidth="1"/>
+    <col min="6654" max="6654" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="6655" max="6655" width="21.625" style="14" customWidth="1"/>
+    <col min="6656" max="6656" width="6.25" style="14" customWidth="1"/>
+    <col min="6657" max="6657" width="12.125" style="14" customWidth="1"/>
+    <col min="6658" max="6658" width="20.125" style="14" customWidth="1"/>
+    <col min="6659" max="6659" width="26.75" style="14" customWidth="1"/>
+    <col min="6660" max="6660" width="13.375" style="14" customWidth="1"/>
+    <col min="6661" max="6661" width="17" style="14" customWidth="1"/>
+    <col min="6662" max="6662" width="19.125" style="14" customWidth="1"/>
+    <col min="6663" max="6664" width="5.875" style="14" customWidth="1"/>
+    <col min="6665" max="6665" width="6.625" style="14" customWidth="1"/>
+    <col min="6666" max="6666" width="8.125" style="14" customWidth="1"/>
+    <col min="6667" max="6667" width="10.125" style="14" customWidth="1"/>
+    <col min="6668" max="6668" width="7.25" style="14" customWidth="1"/>
+    <col min="6669" max="6669" width="11.875" style="14" customWidth="1"/>
+    <col min="6670" max="6670" width="2.125" style="14" customWidth="1"/>
+    <col min="6671" max="6672" width="12.5" style="14" customWidth="1"/>
+    <col min="6673" max="6906" width="9" style="14"/>
+    <col min="6907" max="6907" width="6.875" style="14" customWidth="1"/>
+    <col min="6908" max="6908" width="10.125" style="14" customWidth="1"/>
+    <col min="6909" max="6909" width="11.125" style="14" customWidth="1"/>
+    <col min="6910" max="6910" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="6911" max="6911" width="21.625" style="14" customWidth="1"/>
+    <col min="6912" max="6912" width="6.25" style="14" customWidth="1"/>
+    <col min="6913" max="6913" width="12.125" style="14" customWidth="1"/>
+    <col min="6914" max="6914" width="20.125" style="14" customWidth="1"/>
+    <col min="6915" max="6915" width="26.75" style="14" customWidth="1"/>
+    <col min="6916" max="6916" width="13.375" style="14" customWidth="1"/>
+    <col min="6917" max="6917" width="17" style="14" customWidth="1"/>
+    <col min="6918" max="6918" width="19.125" style="14" customWidth="1"/>
+    <col min="6919" max="6920" width="5.875" style="14" customWidth="1"/>
+    <col min="6921" max="6921" width="6.625" style="14" customWidth="1"/>
+    <col min="6922" max="6922" width="8.125" style="14" customWidth="1"/>
+    <col min="6923" max="6923" width="10.125" style="14" customWidth="1"/>
+    <col min="6924" max="6924" width="7.25" style="14" customWidth="1"/>
+    <col min="6925" max="6925" width="11.875" style="14" customWidth="1"/>
+    <col min="6926" max="6926" width="2.125" style="14" customWidth="1"/>
+    <col min="6927" max="6928" width="12.5" style="14" customWidth="1"/>
+    <col min="6929" max="7162" width="9" style="14"/>
+    <col min="7163" max="7163" width="6.875" style="14" customWidth="1"/>
+    <col min="7164" max="7164" width="10.125" style="14" customWidth="1"/>
+    <col min="7165" max="7165" width="11.125" style="14" customWidth="1"/>
+    <col min="7166" max="7166" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="7167" max="7167" width="21.625" style="14" customWidth="1"/>
+    <col min="7168" max="7168" width="6.25" style="14" customWidth="1"/>
+    <col min="7169" max="7169" width="12.125" style="14" customWidth="1"/>
+    <col min="7170" max="7170" width="20.125" style="14" customWidth="1"/>
+    <col min="7171" max="7171" width="26.75" style="14" customWidth="1"/>
+    <col min="7172" max="7172" width="13.375" style="14" customWidth="1"/>
+    <col min="7173" max="7173" width="17" style="14" customWidth="1"/>
+    <col min="7174" max="7174" width="19.125" style="14" customWidth="1"/>
+    <col min="7175" max="7176" width="5.875" style="14" customWidth="1"/>
+    <col min="7177" max="7177" width="6.625" style="14" customWidth="1"/>
+    <col min="7178" max="7178" width="8.125" style="14" customWidth="1"/>
+    <col min="7179" max="7179" width="10.125" style="14" customWidth="1"/>
+    <col min="7180" max="7180" width="7.25" style="14" customWidth="1"/>
+    <col min="7181" max="7181" width="11.875" style="14" customWidth="1"/>
+    <col min="7182" max="7182" width="2.125" style="14" customWidth="1"/>
+    <col min="7183" max="7184" width="12.5" style="14" customWidth="1"/>
+    <col min="7185" max="7418" width="9" style="14"/>
+    <col min="7419" max="7419" width="6.875" style="14" customWidth="1"/>
+    <col min="7420" max="7420" width="10.125" style="14" customWidth="1"/>
+    <col min="7421" max="7421" width="11.125" style="14" customWidth="1"/>
+    <col min="7422" max="7422" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="7423" max="7423" width="21.625" style="14" customWidth="1"/>
+    <col min="7424" max="7424" width="6.25" style="14" customWidth="1"/>
+    <col min="7425" max="7425" width="12.125" style="14" customWidth="1"/>
+    <col min="7426" max="7426" width="20.125" style="14" customWidth="1"/>
+    <col min="7427" max="7427" width="26.75" style="14" customWidth="1"/>
+    <col min="7428" max="7428" width="13.375" style="14" customWidth="1"/>
+    <col min="7429" max="7429" width="17" style="14" customWidth="1"/>
+    <col min="7430" max="7430" width="19.125" style="14" customWidth="1"/>
+    <col min="7431" max="7432" width="5.875" style="14" customWidth="1"/>
+    <col min="7433" max="7433" width="6.625" style="14" customWidth="1"/>
+    <col min="7434" max="7434" width="8.125" style="14" customWidth="1"/>
+    <col min="7435" max="7435" width="10.125" style="14" customWidth="1"/>
+    <col min="7436" max="7436" width="7.25" style="14" customWidth="1"/>
+    <col min="7437" max="7437" width="11.875" style="14" customWidth="1"/>
+    <col min="7438" max="7438" width="2.125" style="14" customWidth="1"/>
+    <col min="7439" max="7440" width="12.5" style="14" customWidth="1"/>
+    <col min="7441" max="7674" width="9" style="14"/>
+    <col min="7675" max="7675" width="6.875" style="14" customWidth="1"/>
+    <col min="7676" max="7676" width="10.125" style="14" customWidth="1"/>
+    <col min="7677" max="7677" width="11.125" style="14" customWidth="1"/>
+    <col min="7678" max="7678" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="7679" max="7679" width="21.625" style="14" customWidth="1"/>
+    <col min="7680" max="7680" width="6.25" style="14" customWidth="1"/>
+    <col min="7681" max="7681" width="12.125" style="14" customWidth="1"/>
+    <col min="7682" max="7682" width="20.125" style="14" customWidth="1"/>
+    <col min="7683" max="7683" width="26.75" style="14" customWidth="1"/>
+    <col min="7684" max="7684" width="13.375" style="14" customWidth="1"/>
+    <col min="7685" max="7685" width="17" style="14" customWidth="1"/>
+    <col min="7686" max="7686" width="19.125" style="14" customWidth="1"/>
+    <col min="7687" max="7688" width="5.875" style="14" customWidth="1"/>
+    <col min="7689" max="7689" width="6.625" style="14" customWidth="1"/>
+    <col min="7690" max="7690" width="8.125" style="14" customWidth="1"/>
+    <col min="7691" max="7691" width="10.125" style="14" customWidth="1"/>
+    <col min="7692" max="7692" width="7.25" style="14" customWidth="1"/>
+    <col min="7693" max="7693" width="11.875" style="14" customWidth="1"/>
+    <col min="7694" max="7694" width="2.125" style="14" customWidth="1"/>
+    <col min="7695" max="7696" width="12.5" style="14" customWidth="1"/>
+    <col min="7697" max="7930" width="9" style="14"/>
+    <col min="7931" max="7931" width="6.875" style="14" customWidth="1"/>
+    <col min="7932" max="7932" width="10.125" style="14" customWidth="1"/>
+    <col min="7933" max="7933" width="11.125" style="14" customWidth="1"/>
+    <col min="7934" max="7934" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="7935" max="7935" width="21.625" style="14" customWidth="1"/>
+    <col min="7936" max="7936" width="6.25" style="14" customWidth="1"/>
+    <col min="7937" max="7937" width="12.125" style="14" customWidth="1"/>
+    <col min="7938" max="7938" width="20.125" style="14" customWidth="1"/>
+    <col min="7939" max="7939" width="26.75" style="14" customWidth="1"/>
+    <col min="7940" max="7940" width="13.375" style="14" customWidth="1"/>
+    <col min="7941" max="7941" width="17" style="14" customWidth="1"/>
+    <col min="7942" max="7942" width="19.125" style="14" customWidth="1"/>
+    <col min="7943" max="7944" width="5.875" style="14" customWidth="1"/>
+    <col min="7945" max="7945" width="6.625" style="14" customWidth="1"/>
+    <col min="7946" max="7946" width="8.125" style="14" customWidth="1"/>
+    <col min="7947" max="7947" width="10.125" style="14" customWidth="1"/>
+    <col min="7948" max="7948" width="7.25" style="14" customWidth="1"/>
+    <col min="7949" max="7949" width="11.875" style="14" customWidth="1"/>
+    <col min="7950" max="7950" width="2.125" style="14" customWidth="1"/>
+    <col min="7951" max="7952" width="12.5" style="14" customWidth="1"/>
+    <col min="7953" max="8186" width="9" style="14"/>
+    <col min="8187" max="8187" width="6.875" style="14" customWidth="1"/>
+    <col min="8188" max="8188" width="10.125" style="14" customWidth="1"/>
+    <col min="8189" max="8189" width="11.125" style="14" customWidth="1"/>
+    <col min="8190" max="8190" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="8191" max="8191" width="21.625" style="14" customWidth="1"/>
+    <col min="8192" max="8192" width="6.25" style="14" customWidth="1"/>
+    <col min="8193" max="8193" width="12.125" style="14" customWidth="1"/>
+    <col min="8194" max="8194" width="20.125" style="14" customWidth="1"/>
+    <col min="8195" max="8195" width="26.75" style="14" customWidth="1"/>
+    <col min="8196" max="8196" width="13.375" style="14" customWidth="1"/>
+    <col min="8197" max="8197" width="17" style="14" customWidth="1"/>
+    <col min="8198" max="8198" width="19.125" style="14" customWidth="1"/>
+    <col min="8199" max="8200" width="5.875" style="14" customWidth="1"/>
+    <col min="8201" max="8201" width="6.625" style="14" customWidth="1"/>
+    <col min="8202" max="8202" width="8.125" style="14" customWidth="1"/>
+    <col min="8203" max="8203" width="10.125" style="14" customWidth="1"/>
+    <col min="8204" max="8204" width="7.25" style="14" customWidth="1"/>
+    <col min="8205" max="8205" width="11.875" style="14" customWidth="1"/>
+    <col min="8206" max="8206" width="2.125" style="14" customWidth="1"/>
+    <col min="8207" max="8208" width="12.5" style="14" customWidth="1"/>
+    <col min="8209" max="8442" width="9" style="14"/>
+    <col min="8443" max="8443" width="6.875" style="14" customWidth="1"/>
+    <col min="8444" max="8444" width="10.125" style="14" customWidth="1"/>
+    <col min="8445" max="8445" width="11.125" style="14" customWidth="1"/>
+    <col min="8446" max="8446" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="8447" max="8447" width="21.625" style="14" customWidth="1"/>
+    <col min="8448" max="8448" width="6.25" style="14" customWidth="1"/>
+    <col min="8449" max="8449" width="12.125" style="14" customWidth="1"/>
+    <col min="8450" max="8450" width="20.125" style="14" customWidth="1"/>
+    <col min="8451" max="8451" width="26.75" style="14" customWidth="1"/>
+    <col min="8452" max="8452" width="13.375" style="14" customWidth="1"/>
+    <col min="8453" max="8453" width="17" style="14" customWidth="1"/>
+    <col min="8454" max="8454" width="19.125" style="14" customWidth="1"/>
+    <col min="8455" max="8456" width="5.875" style="14" customWidth="1"/>
+    <col min="8457" max="8457" width="6.625" style="14" customWidth="1"/>
+    <col min="8458" max="8458" width="8.125" style="14" customWidth="1"/>
+    <col min="8459" max="8459" width="10.125" style="14" customWidth="1"/>
+    <col min="8460" max="8460" width="7.25" style="14" customWidth="1"/>
+    <col min="8461" max="8461" width="11.875" style="14" customWidth="1"/>
+    <col min="8462" max="8462" width="2.125" style="14" customWidth="1"/>
+    <col min="8463" max="8464" width="12.5" style="14" customWidth="1"/>
+    <col min="8465" max="8698" width="9" style="14"/>
+    <col min="8699" max="8699" width="6.875" style="14" customWidth="1"/>
+    <col min="8700" max="8700" width="10.125" style="14" customWidth="1"/>
+    <col min="8701" max="8701" width="11.125" style="14" customWidth="1"/>
+    <col min="8702" max="8702" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="8703" max="8703" width="21.625" style="14" customWidth="1"/>
+    <col min="8704" max="8704" width="6.25" style="14" customWidth="1"/>
+    <col min="8705" max="8705" width="12.125" style="14" customWidth="1"/>
+    <col min="8706" max="8706" width="20.125" style="14" customWidth="1"/>
+    <col min="8707" max="8707" width="26.75" style="14" customWidth="1"/>
+    <col min="8708" max="8708" width="13.375" style="14" customWidth="1"/>
+    <col min="8709" max="8709" width="17" style="14" customWidth="1"/>
+    <col min="8710" max="8710" width="19.125" style="14" customWidth="1"/>
+    <col min="8711" max="8712" width="5.875" style="14" customWidth="1"/>
+    <col min="8713" max="8713" width="6.625" style="14" customWidth="1"/>
+    <col min="8714" max="8714" width="8.125" style="14" customWidth="1"/>
+    <col min="8715" max="8715" width="10.125" style="14" customWidth="1"/>
+    <col min="8716" max="8716" width="7.25" style="14" customWidth="1"/>
+    <col min="8717" max="8717" width="11.875" style="14" customWidth="1"/>
+    <col min="8718" max="8718" width="2.125" style="14" customWidth="1"/>
+    <col min="8719" max="8720" width="12.5" style="14" customWidth="1"/>
+    <col min="8721" max="8954" width="9" style="14"/>
+    <col min="8955" max="8955" width="6.875" style="14" customWidth="1"/>
+    <col min="8956" max="8956" width="10.125" style="14" customWidth="1"/>
+    <col min="8957" max="8957" width="11.125" style="14" customWidth="1"/>
+    <col min="8958" max="8958" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="8959" max="8959" width="21.625" style="14" customWidth="1"/>
+    <col min="8960" max="8960" width="6.25" style="14" customWidth="1"/>
+    <col min="8961" max="8961" width="12.125" style="14" customWidth="1"/>
+    <col min="8962" max="8962" width="20.125" style="14" customWidth="1"/>
+    <col min="8963" max="8963" width="26.75" style="14" customWidth="1"/>
+    <col min="8964" max="8964" width="13.375" style="14" customWidth="1"/>
+    <col min="8965" max="8965" width="17" style="14" customWidth="1"/>
+    <col min="8966" max="8966" width="19.125" style="14" customWidth="1"/>
+    <col min="8967" max="8968" width="5.875" style="14" customWidth="1"/>
+    <col min="8969" max="8969" width="6.625" style="14" customWidth="1"/>
+    <col min="8970" max="8970" width="8.125" style="14" customWidth="1"/>
+    <col min="8971" max="8971" width="10.125" style="14" customWidth="1"/>
+    <col min="8972" max="8972" width="7.25" style="14" customWidth="1"/>
+    <col min="8973" max="8973" width="11.875" style="14" customWidth="1"/>
+    <col min="8974" max="8974" width="2.125" style="14" customWidth="1"/>
+    <col min="8975" max="8976" width="12.5" style="14" customWidth="1"/>
+    <col min="8977" max="9210" width="9" style="14"/>
+    <col min="9211" max="9211" width="6.875" style="14" customWidth="1"/>
+    <col min="9212" max="9212" width="10.125" style="14" customWidth="1"/>
+    <col min="9213" max="9213" width="11.125" style="14" customWidth="1"/>
+    <col min="9214" max="9214" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="9215" max="9215" width="21.625" style="14" customWidth="1"/>
+    <col min="9216" max="9216" width="6.25" style="14" customWidth="1"/>
+    <col min="9217" max="9217" width="12.125" style="14" customWidth="1"/>
+    <col min="9218" max="9218" width="20.125" style="14" customWidth="1"/>
+    <col min="9219" max="9219" width="26.75" style="14" customWidth="1"/>
+    <col min="9220" max="9220" width="13.375" style="14" customWidth="1"/>
+    <col min="9221" max="9221" width="17" style="14" customWidth="1"/>
+    <col min="9222" max="9222" width="19.125" style="14" customWidth="1"/>
+    <col min="9223" max="9224" width="5.875" style="14" customWidth="1"/>
+    <col min="9225" max="9225" width="6.625" style="14" customWidth="1"/>
+    <col min="9226" max="9226" width="8.125" style="14" customWidth="1"/>
+    <col min="9227" max="9227" width="10.125" style="14" customWidth="1"/>
+    <col min="9228" max="9228" width="7.25" style="14" customWidth="1"/>
+    <col min="9229" max="9229" width="11.875" style="14" customWidth="1"/>
+    <col min="9230" max="9230" width="2.125" style="14" customWidth="1"/>
+    <col min="9231" max="9232" width="12.5" style="14" customWidth="1"/>
+    <col min="9233" max="9466" width="9" style="14"/>
+    <col min="9467" max="9467" width="6.875" style="14" customWidth="1"/>
+    <col min="9468" max="9468" width="10.125" style="14" customWidth="1"/>
+    <col min="9469" max="9469" width="11.125" style="14" customWidth="1"/>
+    <col min="9470" max="9470" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="9471" max="9471" width="21.625" style="14" customWidth="1"/>
+    <col min="9472" max="9472" width="6.25" style="14" customWidth="1"/>
+    <col min="9473" max="9473" width="12.125" style="14" customWidth="1"/>
+    <col min="9474" max="9474" width="20.125" style="14" customWidth="1"/>
+    <col min="9475" max="9475" width="26.75" style="14" customWidth="1"/>
+    <col min="9476" max="9476" width="13.375" style="14" customWidth="1"/>
+    <col min="9477" max="9477" width="17" style="14" customWidth="1"/>
+    <col min="9478" max="9478" width="19.125" style="14" customWidth="1"/>
+    <col min="9479" max="9480" width="5.875" style="14" customWidth="1"/>
+    <col min="9481" max="9481" width="6.625" style="14" customWidth="1"/>
+    <col min="9482" max="9482" width="8.125" style="14" customWidth="1"/>
+    <col min="9483" max="9483" width="10.125" style="14" customWidth="1"/>
+    <col min="9484" max="9484" width="7.25" style="14" customWidth="1"/>
+    <col min="9485" max="9485" width="11.875" style="14" customWidth="1"/>
+    <col min="9486" max="9486" width="2.125" style="14" customWidth="1"/>
+    <col min="9487" max="9488" width="12.5" style="14" customWidth="1"/>
+    <col min="9489" max="9722" width="9" style="14"/>
+    <col min="9723" max="9723" width="6.875" style="14" customWidth="1"/>
+    <col min="9724" max="9724" width="10.125" style="14" customWidth="1"/>
+    <col min="9725" max="9725" width="11.125" style="14" customWidth="1"/>
+    <col min="9726" max="9726" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="9727" max="9727" width="21.625" style="14" customWidth="1"/>
+    <col min="9728" max="9728" width="6.25" style="14" customWidth="1"/>
+    <col min="9729" max="9729" width="12.125" style="14" customWidth="1"/>
+    <col min="9730" max="9730" width="20.125" style="14" customWidth="1"/>
+    <col min="9731" max="9731" width="26.75" style="14" customWidth="1"/>
+    <col min="9732" max="9732" width="13.375" style="14" customWidth="1"/>
+    <col min="9733" max="9733" width="17" style="14" customWidth="1"/>
+    <col min="9734" max="9734" width="19.125" style="14" customWidth="1"/>
+    <col min="9735" max="9736" width="5.875" style="14" customWidth="1"/>
+    <col min="9737" max="9737" width="6.625" style="14" customWidth="1"/>
+    <col min="9738" max="9738" width="8.125" style="14" customWidth="1"/>
+    <col min="9739" max="9739" width="10.125" style="14" customWidth="1"/>
+    <col min="9740" max="9740" width="7.25" style="14" customWidth="1"/>
+    <col min="9741" max="9741" width="11.875" style="14" customWidth="1"/>
+    <col min="9742" max="9742" width="2.125" style="14" customWidth="1"/>
+    <col min="9743" max="9744" width="12.5" style="14" customWidth="1"/>
+    <col min="9745" max="9978" width="9" style="14"/>
+    <col min="9979" max="9979" width="6.875" style="14" customWidth="1"/>
+    <col min="9980" max="9980" width="10.125" style="14" customWidth="1"/>
+    <col min="9981" max="9981" width="11.125" style="14" customWidth="1"/>
+    <col min="9982" max="9982" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="9983" max="9983" width="21.625" style="14" customWidth="1"/>
+    <col min="9984" max="9984" width="6.25" style="14" customWidth="1"/>
+    <col min="9985" max="9985" width="12.125" style="14" customWidth="1"/>
+    <col min="9986" max="9986" width="20.125" style="14" customWidth="1"/>
+    <col min="9987" max="9987" width="26.75" style="14" customWidth="1"/>
+    <col min="9988" max="9988" width="13.375" style="14" customWidth="1"/>
+    <col min="9989" max="9989" width="17" style="14" customWidth="1"/>
+    <col min="9990" max="9990" width="19.125" style="14" customWidth="1"/>
+    <col min="9991" max="9992" width="5.875" style="14" customWidth="1"/>
+    <col min="9993" max="9993" width="6.625" style="14" customWidth="1"/>
+    <col min="9994" max="9994" width="8.125" style="14" customWidth="1"/>
+    <col min="9995" max="9995" width="10.125" style="14" customWidth="1"/>
+    <col min="9996" max="9996" width="7.25" style="14" customWidth="1"/>
+    <col min="9997" max="9997" width="11.875" style="14" customWidth="1"/>
+    <col min="9998" max="9998" width="2.125" style="14" customWidth="1"/>
+    <col min="9999" max="10000" width="12.5" style="14" customWidth="1"/>
+    <col min="10001" max="10234" width="9" style="14"/>
+    <col min="10235" max="10235" width="6.875" style="14" customWidth="1"/>
+    <col min="10236" max="10236" width="10.125" style="14" customWidth="1"/>
+    <col min="10237" max="10237" width="11.125" style="14" customWidth="1"/>
+    <col min="10238" max="10238" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="10239" max="10239" width="21.625" style="14" customWidth="1"/>
+    <col min="10240" max="10240" width="6.25" style="14" customWidth="1"/>
+    <col min="10241" max="10241" width="12.125" style="14" customWidth="1"/>
+    <col min="10242" max="10242" width="20.125" style="14" customWidth="1"/>
+    <col min="10243" max="10243" width="26.75" style="14" customWidth="1"/>
+    <col min="10244" max="10244" width="13.375" style="14" customWidth="1"/>
+    <col min="10245" max="10245" width="17" style="14" customWidth="1"/>
+    <col min="10246" max="10246" width="19.125" style="14" customWidth="1"/>
+    <col min="10247" max="10248" width="5.875" style="14" customWidth="1"/>
+    <col min="10249" max="10249" width="6.625" style="14" customWidth="1"/>
+    <col min="10250" max="10250" width="8.125" style="14" customWidth="1"/>
+    <col min="10251" max="10251" width="10.125" style="14" customWidth="1"/>
+    <col min="10252" max="10252" width="7.25" style="14" customWidth="1"/>
+    <col min="10253" max="10253" width="11.875" style="14" customWidth="1"/>
+    <col min="10254" max="10254" width="2.125" style="14" customWidth="1"/>
+    <col min="10255" max="10256" width="12.5" style="14" customWidth="1"/>
+    <col min="10257" max="10490" width="9" style="14"/>
+    <col min="10491" max="10491" width="6.875" style="14" customWidth="1"/>
+    <col min="10492" max="10492" width="10.125" style="14" customWidth="1"/>
+    <col min="10493" max="10493" width="11.125" style="14" customWidth="1"/>
+    <col min="10494" max="10494" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="10495" max="10495" width="21.625" style="14" customWidth="1"/>
+    <col min="10496" max="10496" width="6.25" style="14" customWidth="1"/>
+    <col min="10497" max="10497" width="12.125" style="14" customWidth="1"/>
+    <col min="10498" max="10498" width="20.125" style="14" customWidth="1"/>
+    <col min="10499" max="10499" width="26.75" style="14" customWidth="1"/>
+    <col min="10500" max="10500" width="13.375" style="14" customWidth="1"/>
+    <col min="10501" max="10501" width="17" style="14" customWidth="1"/>
+    <col min="10502" max="10502" width="19.125" style="14" customWidth="1"/>
+    <col min="10503" max="10504" width="5.875" style="14" customWidth="1"/>
+    <col min="10505" max="10505" width="6.625" style="14" customWidth="1"/>
+    <col min="10506" max="10506" width="8.125" style="14" customWidth="1"/>
+    <col min="10507" max="10507" width="10.125" style="14" customWidth="1"/>
+    <col min="10508" max="10508" width="7.25" style="14" customWidth="1"/>
+    <col min="10509" max="10509" width="11.875" style="14" customWidth="1"/>
+    <col min="10510" max="10510" width="2.125" style="14" customWidth="1"/>
+    <col min="10511" max="10512" width="12.5" style="14" customWidth="1"/>
+    <col min="10513" max="10746" width="9" style="14"/>
+    <col min="10747" max="10747" width="6.875" style="14" customWidth="1"/>
+    <col min="10748" max="10748" width="10.125" style="14" customWidth="1"/>
+    <col min="10749" max="10749" width="11.125" style="14" customWidth="1"/>
+    <col min="10750" max="10750" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="10751" max="10751" width="21.625" style="14" customWidth="1"/>
+    <col min="10752" max="10752" width="6.25" style="14" customWidth="1"/>
+    <col min="10753" max="10753" width="12.125" style="14" customWidth="1"/>
+    <col min="10754" max="10754" width="20.125" style="14" customWidth="1"/>
+    <col min="10755" max="10755" width="26.75" style="14" customWidth="1"/>
+    <col min="10756" max="10756" width="13.375" style="14" customWidth="1"/>
+    <col min="10757" max="10757" width="17" style="14" customWidth="1"/>
+    <col min="10758" max="10758" width="19.125" style="14" customWidth="1"/>
+    <col min="10759" max="10760" width="5.875" style="14" customWidth="1"/>
+    <col min="10761" max="10761" width="6.625" style="14" customWidth="1"/>
+    <col min="10762" max="10762" width="8.125" style="14" customWidth="1"/>
+    <col min="10763" max="10763" width="10.125" style="14" customWidth="1"/>
+    <col min="10764" max="10764" width="7.25" style="14" customWidth="1"/>
+    <col min="10765" max="10765" width="11.875" style="14" customWidth="1"/>
+    <col min="10766" max="10766" width="2.125" style="14" customWidth="1"/>
+    <col min="10767" max="10768" width="12.5" style="14" customWidth="1"/>
+    <col min="10769" max="11002" width="9" style="14"/>
+    <col min="11003" max="11003" width="6.875" style="14" customWidth="1"/>
+    <col min="11004" max="11004" width="10.125" style="14" customWidth="1"/>
+    <col min="11005" max="11005" width="11.125" style="14" customWidth="1"/>
+    <col min="11006" max="11006" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="11007" max="11007" width="21.625" style="14" customWidth="1"/>
+    <col min="11008" max="11008" width="6.25" style="14" customWidth="1"/>
+    <col min="11009" max="11009" width="12.125" style="14" customWidth="1"/>
+    <col min="11010" max="11010" width="20.125" style="14" customWidth="1"/>
+    <col min="11011" max="11011" width="26.75" style="14" customWidth="1"/>
+    <col min="11012" max="11012" width="13.375" style="14" customWidth="1"/>
+    <col min="11013" max="11013" width="17" style="14" customWidth="1"/>
+    <col min="11014" max="11014" width="19.125" style="14" customWidth="1"/>
+    <col min="11015" max="11016" width="5.875" style="14" customWidth="1"/>
+    <col min="11017" max="11017" width="6.625" style="14" customWidth="1"/>
+    <col min="11018" max="11018" width="8.125" style="14" customWidth="1"/>
+    <col min="11019" max="11019" width="10.125" style="14" customWidth="1"/>
+    <col min="11020" max="11020" width="7.25" style="14" customWidth="1"/>
+    <col min="11021" max="11021" width="11.875" style="14" customWidth="1"/>
+    <col min="11022" max="11022" width="2.125" style="14" customWidth="1"/>
+    <col min="11023" max="11024" width="12.5" style="14" customWidth="1"/>
+    <col min="11025" max="11258" width="9" style="14"/>
+    <col min="11259" max="11259" width="6.875" style="14" customWidth="1"/>
+    <col min="11260" max="11260" width="10.125" style="14" customWidth="1"/>
+    <col min="11261" max="11261" width="11.125" style="14" customWidth="1"/>
+    <col min="11262" max="11262" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="11263" max="11263" width="21.625" style="14" customWidth="1"/>
+    <col min="11264" max="11264" width="6.25" style="14" customWidth="1"/>
+    <col min="11265" max="11265" width="12.125" style="14" customWidth="1"/>
+    <col min="11266" max="11266" width="20.125" style="14" customWidth="1"/>
+    <col min="11267" max="11267" width="26.75" style="14" customWidth="1"/>
+    <col min="11268" max="11268" width="13.375" style="14" customWidth="1"/>
+    <col min="11269" max="11269" width="17" style="14" customWidth="1"/>
+    <col min="11270" max="11270" width="19.125" style="14" customWidth="1"/>
+    <col min="11271" max="11272" width="5.875" style="14" customWidth="1"/>
+    <col min="11273" max="11273" width="6.625" style="14" customWidth="1"/>
+    <col min="11274" max="11274" width="8.125" style="14" customWidth="1"/>
+    <col min="11275" max="11275" width="10.125" style="14" customWidth="1"/>
+    <col min="11276" max="11276" width="7.25" style="14" customWidth="1"/>
+    <col min="11277" max="11277" width="11.875" style="14" customWidth="1"/>
+    <col min="11278" max="11278" width="2.125" style="14" customWidth="1"/>
+    <col min="11279" max="11280" width="12.5" style="14" customWidth="1"/>
+    <col min="11281" max="11514" width="9" style="14"/>
+    <col min="11515" max="11515" width="6.875" style="14" customWidth="1"/>
+    <col min="11516" max="11516" width="10.125" style="14" customWidth="1"/>
+    <col min="11517" max="11517" width="11.125" style="14" customWidth="1"/>
+    <col min="11518" max="11518" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="11519" max="11519" width="21.625" style="14" customWidth="1"/>
+    <col min="11520" max="11520" width="6.25" style="14" customWidth="1"/>
+    <col min="11521" max="11521" width="12.125" style="14" customWidth="1"/>
+    <col min="11522" max="11522" width="20.125" style="14" customWidth="1"/>
+    <col min="11523" max="11523" width="26.75" style="14" customWidth="1"/>
+    <col min="11524" max="11524" width="13.375" style="14" customWidth="1"/>
+    <col min="11525" max="11525" width="17" style="14" customWidth="1"/>
+    <col min="11526" max="11526" width="19.125" style="14" customWidth="1"/>
+    <col min="11527" max="11528" width="5.875" style="14" customWidth="1"/>
+    <col min="11529" max="11529" width="6.625" style="14" customWidth="1"/>
+    <col min="11530" max="11530" width="8.125" style="14" customWidth="1"/>
+    <col min="11531" max="11531" width="10.125" style="14" customWidth="1"/>
+    <col min="11532" max="11532" width="7.25" style="14" customWidth="1"/>
+    <col min="11533" max="11533" width="11.875" style="14" customWidth="1"/>
+    <col min="11534" max="11534" width="2.125" style="14" customWidth="1"/>
+    <col min="11535" max="11536" width="12.5" style="14" customWidth="1"/>
+    <col min="11537" max="11770" width="9" style="14"/>
+    <col min="11771" max="11771" width="6.875" style="14" customWidth="1"/>
+    <col min="11772" max="11772" width="10.125" style="14" customWidth="1"/>
+    <col min="11773" max="11773" width="11.125" style="14" customWidth="1"/>
+    <col min="11774" max="11774" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="11775" max="11775" width="21.625" style="14" customWidth="1"/>
+    <col min="11776" max="11776" width="6.25" style="14" customWidth="1"/>
+    <col min="11777" max="11777" width="12.125" style="14" customWidth="1"/>
+    <col min="11778" max="11778" width="20.125" style="14" customWidth="1"/>
+    <col min="11779" max="11779" width="26.75" style="14" customWidth="1"/>
+    <col min="11780" max="11780" width="13.375" style="14" customWidth="1"/>
+    <col min="11781" max="11781" width="17" style="14" customWidth="1"/>
+    <col min="11782" max="11782" width="19.125" style="14" customWidth="1"/>
+    <col min="11783" max="11784" width="5.875" style="14" customWidth="1"/>
+    <col min="11785" max="11785" width="6.625" style="14" customWidth="1"/>
+    <col min="11786" max="11786" width="8.125" style="14" customWidth="1"/>
+    <col min="11787" max="11787" width="10.125" style="14" customWidth="1"/>
+    <col min="11788" max="11788" width="7.25" style="14" customWidth="1"/>
+    <col min="11789" max="11789" width="11.875" style="14" customWidth="1"/>
+    <col min="11790" max="11790" width="2.125" style="14" customWidth="1"/>
+    <col min="11791" max="11792" width="12.5" style="14" customWidth="1"/>
+    <col min="11793" max="12026" width="9" style="14"/>
+    <col min="12027" max="12027" width="6.875" style="14" customWidth="1"/>
+    <col min="12028" max="12028" width="10.125" style="14" customWidth="1"/>
+    <col min="12029" max="12029" width="11.125" style="14" customWidth="1"/>
+    <col min="12030" max="12030" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="12031" max="12031" width="21.625" style="14" customWidth="1"/>
+    <col min="12032" max="12032" width="6.25" style="14" customWidth="1"/>
+    <col min="12033" max="12033" width="12.125" style="14" customWidth="1"/>
+    <col min="12034" max="12034" width="20.125" style="14" customWidth="1"/>
+    <col min="12035" max="12035" width="26.75" style="14" customWidth="1"/>
+    <col min="12036" max="12036" width="13.375" style="14" customWidth="1"/>
+    <col min="12037" max="12037" width="17" style="14" customWidth="1"/>
+    <col min="12038" max="12038" width="19.125" style="14" customWidth="1"/>
+    <col min="12039" max="12040" width="5.875" style="14" customWidth="1"/>
+    <col min="12041" max="12041" width="6.625" style="14" customWidth="1"/>
+    <col min="12042" max="12042" width="8.125" style="14" customWidth="1"/>
+    <col min="12043" max="12043" width="10.125" style="14" customWidth="1"/>
+    <col min="12044" max="12044" width="7.25" style="14" customWidth="1"/>
+    <col min="12045" max="12045" width="11.875" style="14" customWidth="1"/>
+    <col min="12046" max="12046" width="2.125" style="14" customWidth="1"/>
+    <col min="12047" max="12048" width="12.5" style="14" customWidth="1"/>
+    <col min="12049" max="12282" width="9" style="14"/>
+    <col min="12283" max="12283" width="6.875" style="14" customWidth="1"/>
+    <col min="12284" max="12284" width="10.125" style="14" customWidth="1"/>
+    <col min="12285" max="12285" width="11.125" style="14" customWidth="1"/>
+    <col min="12286" max="12286" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="12287" max="12287" width="21.625" style="14" customWidth="1"/>
+    <col min="12288" max="12288" width="6.25" style="14" customWidth="1"/>
+    <col min="12289" max="12289" width="12.125" style="14" customWidth="1"/>
+    <col min="12290" max="12290" width="20.125" style="14" customWidth="1"/>
+    <col min="12291" max="12291" width="26.75" style="14" customWidth="1"/>
+    <col min="12292" max="12292" width="13.375" style="14" customWidth="1"/>
+    <col min="12293" max="12293" width="17" style="14" customWidth="1"/>
+    <col min="12294" max="12294" width="19.125" style="14" customWidth="1"/>
+    <col min="12295" max="12296" width="5.875" style="14" customWidth="1"/>
+    <col min="12297" max="12297" width="6.625" style="14" customWidth="1"/>
+    <col min="12298" max="12298" width="8.125" style="14" customWidth="1"/>
+    <col min="12299" max="12299" width="10.125" style="14" customWidth="1"/>
+    <col min="12300" max="12300" width="7.25" style="14" customWidth="1"/>
+    <col min="12301" max="12301" width="11.875" style="14" customWidth="1"/>
+    <col min="12302" max="12302" width="2.125" style="14" customWidth="1"/>
+    <col min="12303" max="12304" width="12.5" style="14" customWidth="1"/>
+    <col min="12305" max="12538" width="9" style="14"/>
+    <col min="12539" max="12539" width="6.875" style="14" customWidth="1"/>
+    <col min="12540" max="12540" width="10.125" style="14" customWidth="1"/>
+    <col min="12541" max="12541" width="11.125" style="14" customWidth="1"/>
+    <col min="12542" max="12542" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="12543" max="12543" width="21.625" style="14" customWidth="1"/>
+    <col min="12544" max="12544" width="6.25" style="14" customWidth="1"/>
+    <col min="12545" max="12545" width="12.125" style="14" customWidth="1"/>
+    <col min="12546" max="12546" width="20.125" style="14" customWidth="1"/>
+    <col min="12547" max="12547" width="26.75" style="14" customWidth="1"/>
+    <col min="12548" max="12548" width="13.375" style="14" customWidth="1"/>
+    <col min="12549" max="12549" width="17" style="14" customWidth="1"/>
+    <col min="12550" max="12550" width="19.125" style="14" customWidth="1"/>
+    <col min="12551" max="12552" width="5.875" style="14" customWidth="1"/>
+    <col min="12553" max="12553" width="6.625" style="14" customWidth="1"/>
+    <col min="12554" max="12554" width="8.125" style="14" customWidth="1"/>
+    <col min="12555" max="12555" width="10.125" style="14" customWidth="1"/>
+    <col min="12556" max="12556" width="7.25" style="14" customWidth="1"/>
+    <col min="12557" max="12557" width="11.875" style="14" customWidth="1"/>
+    <col min="12558" max="12558" width="2.125" style="14" customWidth="1"/>
+    <col min="12559" max="12560" width="12.5" style="14" customWidth="1"/>
+    <col min="12561" max="12794" width="9" style="14"/>
+    <col min="12795" max="12795" width="6.875" style="14" customWidth="1"/>
+    <col min="12796" max="12796" width="10.125" style="14" customWidth="1"/>
+    <col min="12797" max="12797" width="11.125" style="14" customWidth="1"/>
+    <col min="12798" max="12798" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="12799" max="12799" width="21.625" style="14" customWidth="1"/>
+    <col min="12800" max="12800" width="6.25" style="14" customWidth="1"/>
+    <col min="12801" max="12801" width="12.125" style="14" customWidth="1"/>
+    <col min="12802" max="12802" width="20.125" style="14" customWidth="1"/>
+    <col min="12803" max="12803" width="26.75" style="14" customWidth="1"/>
+    <col min="12804" max="12804" width="13.375" style="14" customWidth="1"/>
+    <col min="12805" max="12805" width="17" style="14" customWidth="1"/>
+    <col min="12806" max="12806" width="19.125" style="14" customWidth="1"/>
+    <col min="12807" max="12808" width="5.875" style="14" customWidth="1"/>
+    <col min="12809" max="12809" width="6.625" style="14" customWidth="1"/>
+    <col min="12810" max="12810" width="8.125" style="14" customWidth="1"/>
+    <col min="12811" max="12811" width="10.125" style="14" customWidth="1"/>
+    <col min="12812" max="12812" width="7.25" style="14" customWidth="1"/>
+    <col min="12813" max="12813" width="11.875" style="14" customWidth="1"/>
+    <col min="12814" max="12814" width="2.125" style="14" customWidth="1"/>
+    <col min="12815" max="12816" width="12.5" style="14" customWidth="1"/>
+    <col min="12817" max="13050" width="9" style="14"/>
+    <col min="13051" max="13051" width="6.875" style="14" customWidth="1"/>
+    <col min="13052" max="13052" width="10.125" style="14" customWidth="1"/>
+    <col min="13053" max="13053" width="11.125" style="14" customWidth="1"/>
+    <col min="13054" max="13054" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="13055" max="13055" width="21.625" style="14" customWidth="1"/>
+    <col min="13056" max="13056" width="6.25" style="14" customWidth="1"/>
+    <col min="13057" max="13057" width="12.125" style="14" customWidth="1"/>
+    <col min="13058" max="13058" width="20.125" style="14" customWidth="1"/>
+    <col min="13059" max="13059" width="26.75" style="14" customWidth="1"/>
+    <col min="13060" max="13060" width="13.375" style="14" customWidth="1"/>
+    <col min="13061" max="13061" width="17" style="14" customWidth="1"/>
+    <col min="13062" max="13062" width="19.125" style="14" customWidth="1"/>
+    <col min="13063" max="13064" width="5.875" style="14" customWidth="1"/>
+    <col min="13065" max="13065" width="6.625" style="14" customWidth="1"/>
+    <col min="13066" max="13066" width="8.125" style="14" customWidth="1"/>
+    <col min="13067" max="13067" width="10.125" style="14" customWidth="1"/>
+    <col min="13068" max="13068" width="7.25" style="14" customWidth="1"/>
+    <col min="13069" max="13069" width="11.875" style="14" customWidth="1"/>
+    <col min="13070" max="13070" width="2.125" style="14" customWidth="1"/>
+    <col min="13071" max="13072" width="12.5" style="14" customWidth="1"/>
+    <col min="13073" max="13306" width="9" style="14"/>
+    <col min="13307" max="13307" width="6.875" style="14" customWidth="1"/>
+    <col min="13308" max="13308" width="10.125" style="14" customWidth="1"/>
+    <col min="13309" max="13309" width="11.125" style="14" customWidth="1"/>
+    <col min="13310" max="13310" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="13311" max="13311" width="21.625" style="14" customWidth="1"/>
+    <col min="13312" max="13312" width="6.25" style="14" customWidth="1"/>
+    <col min="13313" max="13313" width="12.125" style="14" customWidth="1"/>
+    <col min="13314" max="13314" width="20.125" style="14" customWidth="1"/>
+    <col min="13315" max="13315" width="26.75" style="14" customWidth="1"/>
+    <col min="13316" max="13316" width="13.375" style="14" customWidth="1"/>
+    <col min="13317" max="13317" width="17" style="14" customWidth="1"/>
+    <col min="13318" max="13318" width="19.125" style="14" customWidth="1"/>
+    <col min="13319" max="13320" width="5.875" style="14" customWidth="1"/>
+    <col min="13321" max="13321" width="6.625" style="14" customWidth="1"/>
+    <col min="13322" max="13322" width="8.125" style="14" customWidth="1"/>
+    <col min="13323" max="13323" width="10.125" style="14" customWidth="1"/>
+    <col min="13324" max="13324" width="7.25" style="14" customWidth="1"/>
+    <col min="13325" max="13325" width="11.875" style="14" customWidth="1"/>
+    <col min="13326" max="13326" width="2.125" style="14" customWidth="1"/>
+    <col min="13327" max="13328" width="12.5" style="14" customWidth="1"/>
+    <col min="13329" max="13562" width="9" style="14"/>
+    <col min="13563" max="13563" width="6.875" style="14" customWidth="1"/>
+    <col min="13564" max="13564" width="10.125" style="14" customWidth="1"/>
+    <col min="13565" max="13565" width="11.125" style="14" customWidth="1"/>
+    <col min="13566" max="13566" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="13567" max="13567" width="21.625" style="14" customWidth="1"/>
+    <col min="13568" max="13568" width="6.25" style="14" customWidth="1"/>
+    <col min="13569" max="13569" width="12.125" style="14" customWidth="1"/>
+    <col min="13570" max="13570" width="20.125" style="14" customWidth="1"/>
+    <col min="13571" max="13571" width="26.75" style="14" customWidth="1"/>
+    <col min="13572" max="13572" width="13.375" style="14" customWidth="1"/>
+    <col min="13573" max="13573" width="17" style="14" customWidth="1"/>
+    <col min="13574" max="13574" width="19.125" style="14" customWidth="1"/>
+    <col min="13575" max="13576" width="5.875" style="14" customWidth="1"/>
+    <col min="13577" max="13577" width="6.625" style="14" customWidth="1"/>
+    <col min="13578" max="13578" width="8.125" style="14" customWidth="1"/>
+    <col min="13579" max="13579" width="10.125" style="14" customWidth="1"/>
+    <col min="13580" max="13580" width="7.25" style="14" customWidth="1"/>
+    <col min="13581" max="13581" width="11.875" style="14" customWidth="1"/>
+    <col min="13582" max="13582" width="2.125" style="14" customWidth="1"/>
+    <col min="13583" max="13584" width="12.5" style="14" customWidth="1"/>
+    <col min="13585" max="13818" width="9" style="14"/>
+    <col min="13819" max="13819" width="6.875" style="14" customWidth="1"/>
+    <col min="13820" max="13820" width="10.125" style="14" customWidth="1"/>
+    <col min="13821" max="13821" width="11.125" style="14" customWidth="1"/>
+    <col min="13822" max="13822" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="13823" max="13823" width="21.625" style="14" customWidth="1"/>
+    <col min="13824" max="13824" width="6.25" style="14" customWidth="1"/>
+    <col min="13825" max="13825" width="12.125" style="14" customWidth="1"/>
+    <col min="13826" max="13826" width="20.125" style="14" customWidth="1"/>
+    <col min="13827" max="13827" width="26.75" style="14" customWidth="1"/>
+    <col min="13828" max="13828" width="13.375" style="14" customWidth="1"/>
+    <col min="13829" max="13829" width="17" style="14" customWidth="1"/>
+    <col min="13830" max="13830" width="19.125" style="14" customWidth="1"/>
+    <col min="13831" max="13832" width="5.875" style="14" customWidth="1"/>
+    <col min="13833" max="13833" width="6.625" style="14" customWidth="1"/>
+    <col min="13834" max="13834" width="8.125" style="14" customWidth="1"/>
+    <col min="13835" max="13835" width="10.125" style="14" customWidth="1"/>
+    <col min="13836" max="13836" width="7.25" style="14" customWidth="1"/>
+    <col min="13837" max="13837" width="11.875" style="14" customWidth="1"/>
+    <col min="13838" max="13838" width="2.125" style="14" customWidth="1"/>
+    <col min="13839" max="13840" width="12.5" style="14" customWidth="1"/>
+    <col min="13841" max="14074" width="9" style="14"/>
+    <col min="14075" max="14075" width="6.875" style="14" customWidth="1"/>
+    <col min="14076" max="14076" width="10.125" style="14" customWidth="1"/>
+    <col min="14077" max="14077" width="11.125" style="14" customWidth="1"/>
+    <col min="14078" max="14078" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="14079" max="14079" width="21.625" style="14" customWidth="1"/>
+    <col min="14080" max="14080" width="6.25" style="14" customWidth="1"/>
+    <col min="14081" max="14081" width="12.125" style="14" customWidth="1"/>
+    <col min="14082" max="14082" width="20.125" style="14" customWidth="1"/>
+    <col min="14083" max="14083" width="26.75" style="14" customWidth="1"/>
+    <col min="14084" max="14084" width="13.375" style="14" customWidth="1"/>
+    <col min="14085" max="14085" width="17" style="14" customWidth="1"/>
+    <col min="14086" max="14086" width="19.125" style="14" customWidth="1"/>
+    <col min="14087" max="14088" width="5.875" style="14" customWidth="1"/>
+    <col min="14089" max="14089" width="6.625" style="14" customWidth="1"/>
+    <col min="14090" max="14090" width="8.125" style="14" customWidth="1"/>
+    <col min="14091" max="14091" width="10.125" style="14" customWidth="1"/>
+    <col min="14092" max="14092" width="7.25" style="14" customWidth="1"/>
+    <col min="14093" max="14093" width="11.875" style="14" customWidth="1"/>
+    <col min="14094" max="14094" width="2.125" style="14" customWidth="1"/>
+    <col min="14095" max="14096" width="12.5" style="14" customWidth="1"/>
+    <col min="14097" max="14330" width="9" style="14"/>
+    <col min="14331" max="14331" width="6.875" style="14" customWidth="1"/>
+    <col min="14332" max="14332" width="10.125" style="14" customWidth="1"/>
+    <col min="14333" max="14333" width="11.125" style="14" customWidth="1"/>
+    <col min="14334" max="14334" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="14335" max="14335" width="21.625" style="14" customWidth="1"/>
+    <col min="14336" max="14336" width="6.25" style="14" customWidth="1"/>
+    <col min="14337" max="14337" width="12.125" style="14" customWidth="1"/>
+    <col min="14338" max="14338" width="20.125" style="14" customWidth="1"/>
+    <col min="14339" max="14339" width="26.75" style="14" customWidth="1"/>
+    <col min="14340" max="14340" width="13.375" style="14" customWidth="1"/>
+    <col min="14341" max="14341" width="17" style="14" customWidth="1"/>
+    <col min="14342" max="14342" width="19.125" style="14" customWidth="1"/>
+    <col min="14343" max="14344" width="5.875" style="14" customWidth="1"/>
+    <col min="14345" max="14345" width="6.625" style="14" customWidth="1"/>
+    <col min="14346" max="14346" width="8.125" style="14" customWidth="1"/>
+    <col min="14347" max="14347" width="10.125" style="14" customWidth="1"/>
+    <col min="14348" max="14348" width="7.25" style="14" customWidth="1"/>
+    <col min="14349" max="14349" width="11.875" style="14" customWidth="1"/>
+    <col min="14350" max="14350" width="2.125" style="14" customWidth="1"/>
+    <col min="14351" max="14352" width="12.5" style="14" customWidth="1"/>
+    <col min="14353" max="14586" width="9" style="14"/>
+    <col min="14587" max="14587" width="6.875" style="14" customWidth="1"/>
+    <col min="14588" max="14588" width="10.125" style="14" customWidth="1"/>
+    <col min="14589" max="14589" width="11.125" style="14" customWidth="1"/>
+    <col min="14590" max="14590" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="14591" max="14591" width="21.625" style="14" customWidth="1"/>
+    <col min="14592" max="14592" width="6.25" style="14" customWidth="1"/>
+    <col min="14593" max="14593" width="12.125" style="14" customWidth="1"/>
+    <col min="14594" max="14594" width="20.125" style="14" customWidth="1"/>
+    <col min="14595" max="14595" width="26.75" style="14" customWidth="1"/>
+    <col min="14596" max="14596" width="13.375" style="14" customWidth="1"/>
+    <col min="14597" max="14597" width="17" style="14" customWidth="1"/>
+    <col min="14598" max="14598" width="19.125" style="14" customWidth="1"/>
+    <col min="14599" max="14600" width="5.875" style="14" customWidth="1"/>
+    <col min="14601" max="14601" width="6.625" style="14" customWidth="1"/>
+    <col min="14602" max="14602" width="8.125" style="14" customWidth="1"/>
+    <col min="14603" max="14603" width="10.125" style="14" customWidth="1"/>
+    <col min="14604" max="14604" width="7.25" style="14" customWidth="1"/>
+    <col min="14605" max="14605" width="11.875" style="14" customWidth="1"/>
+    <col min="14606" max="14606" width="2.125" style="14" customWidth="1"/>
+    <col min="14607" max="14608" width="12.5" style="14" customWidth="1"/>
+    <col min="14609" max="14842" width="9" style="14"/>
+    <col min="14843" max="14843" width="6.875" style="14" customWidth="1"/>
+    <col min="14844" max="14844" width="10.125" style="14" customWidth="1"/>
+    <col min="14845" max="14845" width="11.125" style="14" customWidth="1"/>
+    <col min="14846" max="14846" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="14847" max="14847" width="21.625" style="14" customWidth="1"/>
+    <col min="14848" max="14848" width="6.25" style="14" customWidth="1"/>
+    <col min="14849" max="14849" width="12.125" style="14" customWidth="1"/>
+    <col min="14850" max="14850" width="20.125" style="14" customWidth="1"/>
+    <col min="14851" max="14851" width="26.75" style="14" customWidth="1"/>
+    <col min="14852" max="14852" width="13.375" style="14" customWidth="1"/>
+    <col min="14853" max="14853" width="17" style="14" customWidth="1"/>
+    <col min="14854" max="14854" width="19.125" style="14" customWidth="1"/>
+    <col min="14855" max="14856" width="5.875" style="14" customWidth="1"/>
+    <col min="14857" max="14857" width="6.625" style="14" customWidth="1"/>
+    <col min="14858" max="14858" width="8.125" style="14" customWidth="1"/>
+    <col min="14859" max="14859" width="10.125" style="14" customWidth="1"/>
+    <col min="14860" max="14860" width="7.25" style="14" customWidth="1"/>
+    <col min="14861" max="14861" width="11.875" style="14" customWidth="1"/>
+    <col min="14862" max="14862" width="2.125" style="14" customWidth="1"/>
+    <col min="14863" max="14864" width="12.5" style="14" customWidth="1"/>
+    <col min="14865" max="15098" width="9" style="14"/>
+    <col min="15099" max="15099" width="6.875" style="14" customWidth="1"/>
+    <col min="15100" max="15100" width="10.125" style="14" customWidth="1"/>
+    <col min="15101" max="15101" width="11.125" style="14" customWidth="1"/>
+    <col min="15102" max="15102" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="15103" max="15103" width="21.625" style="14" customWidth="1"/>
+    <col min="15104" max="15104" width="6.25" style="14" customWidth="1"/>
+    <col min="15105" max="15105" width="12.125" style="14" customWidth="1"/>
+    <col min="15106" max="15106" width="20.125" style="14" customWidth="1"/>
+    <col min="15107" max="15107" width="26.75" style="14" customWidth="1"/>
+    <col min="15108" max="15108" width="13.375" style="14" customWidth="1"/>
+    <col min="15109" max="15109" width="17" style="14" customWidth="1"/>
+    <col min="15110" max="15110" width="19.125" style="14" customWidth="1"/>
+    <col min="15111" max="15112" width="5.875" style="14" customWidth="1"/>
+    <col min="15113" max="15113" width="6.625" style="14" customWidth="1"/>
+    <col min="15114" max="15114" width="8.125" style="14" customWidth="1"/>
+    <col min="15115" max="15115" width="10.125" style="14" customWidth="1"/>
+    <col min="15116" max="15116" width="7.25" style="14" customWidth="1"/>
+    <col min="15117" max="15117" width="11.875" style="14" customWidth="1"/>
+    <col min="15118" max="15118" width="2.125" style="14" customWidth="1"/>
+    <col min="15119" max="15120" width="12.5" style="14" customWidth="1"/>
+    <col min="15121" max="15354" width="9" style="14"/>
+    <col min="15355" max="15355" width="6.875" style="14" customWidth="1"/>
+    <col min="15356" max="15356" width="10.125" style="14" customWidth="1"/>
+    <col min="15357" max="15357" width="11.125" style="14" customWidth="1"/>
+    <col min="15358" max="15358" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="15359" max="15359" width="21.625" style="14" customWidth="1"/>
+    <col min="15360" max="15360" width="6.25" style="14" customWidth="1"/>
+    <col min="15361" max="15361" width="12.125" style="14" customWidth="1"/>
+    <col min="15362" max="15362" width="20.125" style="14" customWidth="1"/>
+    <col min="15363" max="15363" width="26.75" style="14" customWidth="1"/>
+    <col min="15364" max="15364" width="13.375" style="14" customWidth="1"/>
+    <col min="15365" max="15365" width="17" style="14" customWidth="1"/>
+    <col min="15366" max="15366" width="19.125" style="14" customWidth="1"/>
+    <col min="15367" max="15368" width="5.875" style="14" customWidth="1"/>
+    <col min="15369" max="15369" width="6.625" style="14" customWidth="1"/>
+    <col min="15370" max="15370" width="8.125" style="14" customWidth="1"/>
+    <col min="15371" max="15371" width="10.125" style="14" customWidth="1"/>
+    <col min="15372" max="15372" width="7.25" style="14" customWidth="1"/>
+    <col min="15373" max="15373" width="11.875" style="14" customWidth="1"/>
+    <col min="15374" max="15374" width="2.125" style="14" customWidth="1"/>
+    <col min="15375" max="15376" width="12.5" style="14" customWidth="1"/>
+    <col min="15377" max="15610" width="9" style="14"/>
+    <col min="15611" max="15611" width="6.875" style="14" customWidth="1"/>
+    <col min="15612" max="15612" width="10.125" style="14" customWidth="1"/>
+    <col min="15613" max="15613" width="11.125" style="14" customWidth="1"/>
+    <col min="15614" max="15614" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="15615" max="15615" width="21.625" style="14" customWidth="1"/>
+    <col min="15616" max="15616" width="6.25" style="14" customWidth="1"/>
+    <col min="15617" max="15617" width="12.125" style="14" customWidth="1"/>
+    <col min="15618" max="15618" width="20.125" style="14" customWidth="1"/>
+    <col min="15619" max="15619" width="26.75" style="14" customWidth="1"/>
+    <col min="15620" max="15620" width="13.375" style="14" customWidth="1"/>
+    <col min="15621" max="15621" width="17" style="14" customWidth="1"/>
+    <col min="15622" max="15622" width="19.125" style="14" customWidth="1"/>
+    <col min="15623" max="15624" width="5.875" style="14" customWidth="1"/>
+    <col min="15625" max="15625" width="6.625" style="14" customWidth="1"/>
+    <col min="15626" max="15626" width="8.125" style="14" customWidth="1"/>
+    <col min="15627" max="15627" width="10.125" style="14" customWidth="1"/>
+    <col min="15628" max="15628" width="7.25" style="14" customWidth="1"/>
+    <col min="15629" max="15629" width="11.875" style="14" customWidth="1"/>
+    <col min="15630" max="15630" width="2.125" style="14" customWidth="1"/>
+    <col min="15631" max="15632" width="12.5" style="14" customWidth="1"/>
+    <col min="15633" max="15866" width="9" style="14"/>
+    <col min="15867" max="15867" width="6.875" style="14" customWidth="1"/>
+    <col min="15868" max="15868" width="10.125" style="14" customWidth="1"/>
+    <col min="15869" max="15869" width="11.125" style="14" customWidth="1"/>
+    <col min="15870" max="15870" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="15871" max="15871" width="21.625" style="14" customWidth="1"/>
+    <col min="15872" max="15872" width="6.25" style="14" customWidth="1"/>
+    <col min="15873" max="15873" width="12.125" style="14" customWidth="1"/>
+    <col min="15874" max="15874" width="20.125" style="14" customWidth="1"/>
+    <col min="15875" max="15875" width="26.75" style="14" customWidth="1"/>
+    <col min="15876" max="15876" width="13.375" style="14" customWidth="1"/>
+    <col min="15877" max="15877" width="17" style="14" customWidth="1"/>
+    <col min="15878" max="15878" width="19.125" style="14" customWidth="1"/>
+    <col min="15879" max="15880" width="5.875" style="14" customWidth="1"/>
+    <col min="15881" max="15881" width="6.625" style="14" customWidth="1"/>
+    <col min="15882" max="15882" width="8.125" style="14" customWidth="1"/>
+    <col min="15883" max="15883" width="10.125" style="14" customWidth="1"/>
+    <col min="15884" max="15884" width="7.25" style="14" customWidth="1"/>
+    <col min="15885" max="15885" width="11.875" style="14" customWidth="1"/>
+    <col min="15886" max="15886" width="2.125" style="14" customWidth="1"/>
+    <col min="15887" max="15888" width="12.5" style="14" customWidth="1"/>
+    <col min="15889" max="16122" width="9" style="14"/>
+    <col min="16123" max="16123" width="6.875" style="14" customWidth="1"/>
+    <col min="16124" max="16124" width="10.125" style="14" customWidth="1"/>
+    <col min="16125" max="16125" width="11.125" style="14" customWidth="1"/>
+    <col min="16126" max="16126" width="9" style="14" hidden="1" customWidth="1"/>
+    <col min="16127" max="16127" width="21.625" style="14" customWidth="1"/>
+    <col min="16128" max="16128" width="6.25" style="14" customWidth="1"/>
+    <col min="16129" max="16129" width="12.125" style="14" customWidth="1"/>
+    <col min="16130" max="16130" width="20.125" style="14" customWidth="1"/>
+    <col min="16131" max="16131" width="26.75" style="14" customWidth="1"/>
+    <col min="16132" max="16132" width="13.375" style="14" customWidth="1"/>
+    <col min="16133" max="16133" width="17" style="14" customWidth="1"/>
+    <col min="16134" max="16134" width="19.125" style="14" customWidth="1"/>
+    <col min="16135" max="16136" width="5.875" style="14" customWidth="1"/>
+    <col min="16137" max="16137" width="6.625" style="14" customWidth="1"/>
+    <col min="16138" max="16138" width="8.125" style="14" customWidth="1"/>
+    <col min="16139" max="16139" width="10.125" style="14" customWidth="1"/>
+    <col min="16140" max="16140" width="7.25" style="14" customWidth="1"/>
+    <col min="16141" max="16141" width="11.875" style="14" customWidth="1"/>
+    <col min="16142" max="16142" width="2.125" style="14" customWidth="1"/>
+    <col min="16143" max="16144" width="12.5" style="14" customWidth="1"/>
+    <col min="16145" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="57"/>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="67"/>
+      <c r="B1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="72" t="s">
+      <c r="C1" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="72"/>
-      <c r="E1" s="53" t="s">
+      <c r="D1" s="83"/>
+      <c r="E1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="54"/>
-      <c r="G1" s="57" t="s">
+      <c r="F1" s="77"/>
+      <c r="G1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="57"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="53" t="s">
+      <c r="H1" s="67"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="57" t="s">
+      <c r="K1" s="77"/>
+      <c r="L1" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="57"/>
-      <c r="N1" s="53" t="s">
+      <c r="M1" s="67"/>
+      <c r="N1" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="56"/>
-      <c r="P1" s="54"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="77"/>
     </row>
     <row r="2" spans="1:16" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="57"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="66" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="70">
+      <c r="F2" s="75"/>
+      <c r="G2" s="73">
+        <v>1.02</v>
+      </c>
+      <c r="H2" s="73"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="77"/>
+    </row>
+    <row r="3" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="67"/>
+      <c r="B3" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="84"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="77"/>
+      <c r="L3" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="67"/>
+      <c r="N3" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" s="89"/>
+      <c r="P3" s="77"/>
+    </row>
+    <row r="4" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="78"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="78" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="78"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="78"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="77"/>
+    </row>
+    <row r="5" spans="1:16" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="67"/>
+      <c r="H5" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="72" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="67" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.15">
+      <c r="A6" s="79"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="70"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="18">
         <v>1</v>
       </c>
-      <c r="H2" s="70"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="54"/>
-    </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="57"/>
-      <c r="B3" s="14" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="24"/>
+      <c r="I7" s="20">
+        <v>1</v>
+      </c>
+      <c r="J7" s="23"/>
+      <c r="K7" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+    </row>
+    <row r="8" spans="1:16" s="4" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="18">
+        <v>1</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="24"/>
+      <c r="I8" s="20">
+        <v>1</v>
+      </c>
+      <c r="J8" s="23"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+    </row>
+    <row r="9" spans="1:16" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A9" s="18">
+        <v>2</v>
+      </c>
+      <c r="B9" s="31"/>
+      <c r="C9" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="G9" s="66" t="s">
+        <v>137</v>
+      </c>
+      <c r="H9" s="30"/>
+      <c r="I9" s="28">
+        <v>1</v>
+      </c>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="31"/>
+    </row>
+    <row r="10" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="18">
+        <v>3</v>
+      </c>
+      <c r="B10" s="33"/>
+      <c r="C10" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="34">
+        <v>1</v>
+      </c>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+    </row>
+    <row r="11" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="18">
+        <v>4</v>
+      </c>
+      <c r="B11" s="33"/>
+      <c r="C11" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="34">
+        <v>1</v>
+      </c>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+    </row>
+    <row r="12" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="18">
+        <v>5</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="34">
+        <v>1</v>
+      </c>
+      <c r="J12" s="34"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+    </row>
+    <row r="13" spans="1:16" s="7" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="18">
+        <v>6</v>
+      </c>
+      <c r="B13" s="37"/>
+      <c r="C13" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="30"/>
+      <c r="I13" s="29">
+        <v>1</v>
+      </c>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+    </row>
+    <row r="14" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="18">
+        <v>7</v>
+      </c>
+      <c r="B14" s="42"/>
+      <c r="C14" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="34">
+        <v>1</v>
+      </c>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+    </row>
+    <row r="15" spans="1:16" s="7" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="18">
+        <v>8</v>
+      </c>
+      <c r="B15" s="37"/>
+      <c r="C15" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="30"/>
+      <c r="I15" s="29">
+        <v>2</v>
+      </c>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="41"/>
+    </row>
+    <row r="16" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="18">
+        <v>9</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="34">
+        <v>2</v>
+      </c>
+      <c r="J16" s="34"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+    </row>
+    <row r="17" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="18">
+        <v>10</v>
+      </c>
+      <c r="B17" s="43"/>
+      <c r="C17" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="34">
+        <v>2</v>
+      </c>
+      <c r="J17" s="34"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+    </row>
+    <row r="18" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="18">
+        <v>11</v>
+      </c>
+      <c r="B18" s="42"/>
+      <c r="C18" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="34">
+        <v>2</v>
+      </c>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+    </row>
+    <row r="19" spans="1:16" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="18">
         <v>12</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="53" t="s">
+      <c r="B19" s="37"/>
+      <c r="C19" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="28"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H19" s="30"/>
+      <c r="I19" s="29">
+        <v>4</v>
+      </c>
+      <c r="J19" s="39"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
+    </row>
+    <row r="20" spans="1:16" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="18">
         <v>13</v>
       </c>
-      <c r="K3" s="54"/>
-      <c r="L3" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" s="57"/>
-      <c r="N3" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" s="56"/>
-      <c r="P3" s="54"/>
-    </row>
-    <row r="4" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="55"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="55" t="s">
+      <c r="B20" s="37"/>
+      <c r="C20" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="28"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="30"/>
+      <c r="I20" s="29">
+        <v>4</v>
+      </c>
+      <c r="J20" s="39"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41"/>
+    </row>
+    <row r="21" spans="1:16" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="18">
         <v>14</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="54"/>
-    </row>
-    <row r="5" spans="1:16" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="58" t="s">
+      <c r="B21" s="45"/>
+      <c r="C21" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="29"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="29">
+        <v>1</v>
+      </c>
+      <c r="J21" s="20"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="41"/>
+    </row>
+    <row r="22" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="18">
         <v>15</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B22" s="42"/>
+      <c r="C22" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="34">
+        <v>1</v>
+      </c>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+    </row>
+    <row r="23" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="18">
         <v>16</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="B23" s="42"/>
+      <c r="C23" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="34">
+        <v>1</v>
+      </c>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+    </row>
+    <row r="24" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="18">
+        <v>17</v>
+      </c>
+      <c r="B24" s="42"/>
+      <c r="C24" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="34">
+        <v>1</v>
+      </c>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+    </row>
+    <row r="25" spans="1:16" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="18">
+        <v>18</v>
+      </c>
+      <c r="B25" s="33"/>
+      <c r="C25" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="34">
+        <v>1</v>
+      </c>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+    </row>
+    <row r="26" spans="1:16" s="7" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="18">
+        <v>19</v>
+      </c>
+      <c r="B26" s="48"/>
+      <c r="C26" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26" s="20"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="29">
+        <v>33</v>
+      </c>
+      <c r="J26" s="39"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="41"/>
+    </row>
+    <row r="27" spans="1:16" s="7" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="18">
+        <v>20</v>
+      </c>
+      <c r="B27" s="48"/>
+      <c r="C27" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="20"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="29">
+        <v>6</v>
+      </c>
+      <c r="J27" s="39"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+    </row>
+    <row r="28" spans="1:16" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="18">
+        <v>21</v>
+      </c>
+      <c r="B28" s="48"/>
+      <c r="C28" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="G28" s="20"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="29">
+        <v>2</v>
+      </c>
+      <c r="J28" s="39"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="41"/>
+    </row>
+    <row r="29" spans="1:16" s="7" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="18">
+        <v>22</v>
+      </c>
+      <c r="B29" s="48"/>
+      <c r="C29" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" s="20"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="29">
+        <v>20</v>
+      </c>
+      <c r="J29" s="39"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="41"/>
+    </row>
+    <row r="30" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A30" s="18">
+        <v>23</v>
+      </c>
+      <c r="B30" s="48"/>
+      <c r="C30" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="29">
+        <v>6</v>
+      </c>
+      <c r="J30" s="39"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="41"/>
+    </row>
+    <row r="31" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A31" s="18">
+        <v>24</v>
+      </c>
+      <c r="B31" s="48"/>
+      <c r="C31" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" s="29"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="29">
+        <v>2</v>
+      </c>
+      <c r="J31" s="39"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="41"/>
+    </row>
+    <row r="32" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A32" s="18">
+        <v>25</v>
+      </c>
+      <c r="B32" s="48"/>
+      <c r="C32" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="29">
+        <v>4</v>
+      </c>
+      <c r="J32" s="39"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="39"/>
+      <c r="M32" s="41"/>
+      <c r="N32" s="41"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+    </row>
+    <row r="33" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A33" s="18">
+        <v>26</v>
+      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="29"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="29">
+        <v>4</v>
+      </c>
+      <c r="J33" s="39"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+    </row>
+    <row r="34" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A34" s="18">
+        <v>27</v>
+      </c>
+      <c r="B34" s="48"/>
+      <c r="C34" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" s="29"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="29">
+        <v>2</v>
+      </c>
+      <c r="J34" s="39"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="41"/>
+    </row>
+    <row r="35" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A35" s="18">
+        <v>28</v>
+      </c>
+      <c r="B35" s="48"/>
+      <c r="C35" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F35" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="G35" s="20"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="29">
+        <v>2</v>
+      </c>
+      <c r="J35" s="39"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="41"/>
+    </row>
+    <row r="36" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A36" s="18">
+        <v>29</v>
+      </c>
+      <c r="B36" s="48"/>
+      <c r="C36" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="G36" s="20"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="29">
+        <v>8</v>
+      </c>
+      <c r="J36" s="39"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="39"/>
+      <c r="M36" s="41"/>
+      <c r="N36" s="41"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="41"/>
+    </row>
+    <row r="37" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A37" s="18">
+        <v>30</v>
+      </c>
+      <c r="B37" s="48"/>
+      <c r="C37" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" s="28"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="29">
+        <v>2</v>
+      </c>
+      <c r="J37" s="39"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="39"/>
+      <c r="M37" s="41"/>
+      <c r="N37" s="41"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="41"/>
+    </row>
+    <row r="38" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A38" s="18">
+        <v>31</v>
+      </c>
+      <c r="B38" s="18">
+        <v>33</v>
+      </c>
+      <c r="C38" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F38" s="29"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="29">
+        <v>2</v>
+      </c>
+      <c r="J38" s="39"/>
+      <c r="K38" s="40"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="41"/>
+      <c r="N38" s="41"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="41"/>
+    </row>
+    <row r="39" spans="1:16" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A39" s="18">
         <v>32</v>
       </c>
-      <c r="D5" s="62" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="62" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="57"/>
-      <c r="H5" s="62" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="63" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="M5" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="57" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.15">
-      <c r="A6" s="58"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="62"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="57"/>
-      <c r="P6" s="57"/>
-    </row>
-    <row r="7" spans="1:16" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="15">
+      <c r="B39" s="32">
+        <v>33</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="34">
         <v>1</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-    </row>
-    <row r="8" spans="1:16" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="15">
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
+    </row>
+    <row r="40" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="A40" s="18">
+        <v>33</v>
+      </c>
+      <c r="B40" s="18">
+        <v>33</v>
+      </c>
+      <c r="C40" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="F40" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="H40" s="30"/>
+      <c r="I40" s="29">
+        <v>1</v>
+      </c>
+      <c r="J40" s="39"/>
+      <c r="K40" s="40"/>
+      <c r="L40" s="39"/>
+      <c r="M40" s="41"/>
+      <c r="N40" s="41"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="41"/>
+    </row>
+    <row r="41" spans="1:16" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.15">
+      <c r="A41" s="18">
+        <v>34</v>
+      </c>
+      <c r="B41" s="30">
+        <v>33</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="28">
+        <v>1</v>
+      </c>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="31"/>
+    </row>
+    <row r="42" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="18">
+        <v>35</v>
+      </c>
+      <c r="B42" s="18">
+        <v>33</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="G42" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="H42" s="30"/>
+      <c r="I42" s="29">
+        <v>1</v>
+      </c>
+      <c r="J42" s="39"/>
+      <c r="K42" s="40"/>
+      <c r="L42" s="39"/>
+      <c r="M42" s="41"/>
+      <c r="N42" s="41"/>
+      <c r="O42" s="41"/>
+      <c r="P42" s="41"/>
+    </row>
+    <row r="43" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A43" s="18">
+        <v>36</v>
+      </c>
+      <c r="B43" s="18">
+        <v>33</v>
+      </c>
+      <c r="C43" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="E43" s="28"/>
+      <c r="F43" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="G43" s="20"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="29">
+        <v>12</v>
+      </c>
+      <c r="J43" s="39"/>
+      <c r="K43" s="40"/>
+      <c r="L43" s="39"/>
+      <c r="M43" s="41"/>
+      <c r="N43" s="41"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="41"/>
+    </row>
+    <row r="44" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A44" s="18">
+        <v>37</v>
+      </c>
+      <c r="B44" s="18">
+        <v>33</v>
+      </c>
+      <c r="C44" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="E44" s="28"/>
+      <c r="F44" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G44" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="H44" s="30"/>
+      <c r="I44" s="29">
         <v>2</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-    </row>
-    <row r="9" spans="1:16" s="4" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="15">
-        <v>3</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-    </row>
-    <row r="10" spans="1:16" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A10" s="15">
-        <v>4</v>
-      </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-    </row>
-    <row r="11" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="15">
-        <v>5</v>
-      </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-    </row>
-    <row r="12" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="15">
-        <v>6</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-    </row>
-    <row r="13" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="15">
-        <v>7</v>
-      </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-    </row>
-    <row r="14" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="15">
-        <v>8</v>
-      </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-    </row>
-    <row r="15" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="15">
-        <v>9</v>
-      </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-    </row>
-    <row r="16" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="15">
-        <v>10</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-    </row>
-    <row r="17" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="15">
-        <v>11</v>
-      </c>
-      <c r="B17" s="31"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-    </row>
-    <row r="18" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="15">
-        <v>12</v>
-      </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-    </row>
-    <row r="19" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="15">
-        <v>13</v>
-      </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-    </row>
-    <row r="20" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="15">
-        <v>14</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-    </row>
-    <row r="21" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="15">
-        <v>15</v>
-      </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-    </row>
-    <row r="22" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="15">
-        <v>16</v>
-      </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-    </row>
-    <row r="23" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="15">
-        <v>17</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
-    </row>
-    <row r="24" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="15">
-        <v>18</v>
-      </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="37"/>
-      <c r="P24" s="37"/>
-    </row>
-    <row r="25" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="15">
-        <v>19</v>
-      </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-    </row>
-    <row r="26" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="15">
-        <v>20</v>
-      </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="37"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="37"/>
-      <c r="P26" s="37"/>
-    </row>
-    <row r="27" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="P27" s="42" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="32"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="P28" s="43"/>
-    </row>
-    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
+      <c r="J44" s="39"/>
+      <c r="K44" s="40"/>
+      <c r="L44" s="39"/>
+      <c r="M44" s="41"/>
+      <c r="N44" s="41"/>
+      <c r="O44" s="41"/>
+      <c r="P44" s="41"/>
+    </row>
+    <row r="45" spans="1:16" ht="30" x14ac:dyDescent="0.15">
+      <c r="A45" s="18">
+        <v>38</v>
+      </c>
+      <c r="B45" s="18">
+        <v>33</v>
+      </c>
+      <c r="C45" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D45" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="F45" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="G45" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="H45" s="30"/>
+      <c r="I45" s="29">
+        <v>1</v>
+      </c>
+      <c r="J45" s="39"/>
+      <c r="K45" s="40"/>
+      <c r="L45" s="39"/>
+      <c r="M45" s="41"/>
+      <c r="N45" s="41"/>
+      <c r="O45" s="41"/>
+      <c r="P45" s="41"/>
+    </row>
+    <row r="46" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A46" s="18">
+        <v>39</v>
+      </c>
+      <c r="B46" s="18">
+        <v>33</v>
+      </c>
+      <c r="C46" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D46" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="E46" s="28"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="29">
+        <v>1</v>
+      </c>
+      <c r="J46" s="39"/>
+      <c r="K46" s="40"/>
+      <c r="L46" s="39"/>
+      <c r="M46" s="41"/>
+      <c r="N46" s="41"/>
+      <c r="O46" s="41"/>
+      <c r="P46" s="41"/>
+    </row>
+    <row r="47" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A47" s="18">
+        <v>40</v>
+      </c>
+      <c r="B47" s="18">
+        <v>33</v>
+      </c>
+      <c r="C47" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="E47" s="28"/>
+      <c r="F47" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="G47" s="62" t="s">
+        <v>155</v>
+      </c>
+      <c r="H47" s="30"/>
+      <c r="I47" s="29">
+        <v>1</v>
+      </c>
+      <c r="J47" s="39"/>
+      <c r="K47" s="40"/>
+      <c r="L47" s="39"/>
+      <c r="M47" s="41"/>
+      <c r="N47" s="41"/>
+      <c r="O47" s="41"/>
+      <c r="P47" s="41"/>
+    </row>
+    <row r="48" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A48" s="18">
+        <v>41</v>
+      </c>
+      <c r="B48" s="18">
+        <v>33</v>
+      </c>
+      <c r="C48" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="D48" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="F48" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="G48" s="62" t="s">
+        <v>157</v>
+      </c>
+      <c r="H48" s="30"/>
+      <c r="I48" s="29">
+        <v>1</v>
+      </c>
+      <c r="J48" s="39"/>
+      <c r="K48" s="40"/>
+      <c r="L48" s="39"/>
+      <c r="M48" s="41"/>
+      <c r="N48" s="41"/>
+      <c r="O48" s="41"/>
+      <c r="P48" s="41"/>
+    </row>
+    <row r="49" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A49" s="18">
+        <v>42</v>
+      </c>
+      <c r="B49" s="18">
+        <v>33</v>
+      </c>
+      <c r="C49" s="29"/>
+      <c r="D49" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="F49" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="G49" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="H49" s="30"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="39"/>
+      <c r="K49" s="40"/>
+      <c r="L49" s="39"/>
+      <c r="M49" s="41"/>
+      <c r="N49" s="41"/>
+      <c r="O49" s="41"/>
+      <c r="P49" s="41"/>
+    </row>
+    <row r="50" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A50" s="18">
+        <v>43</v>
+      </c>
+      <c r="B50" s="18">
+        <v>33</v>
+      </c>
+      <c r="C50" s="29"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="29"/>
+      <c r="J50" s="39"/>
+      <c r="K50" s="40"/>
+      <c r="L50" s="39"/>
+      <c r="M50" s="41"/>
+      <c r="N50" s="41"/>
+      <c r="O50" s="41"/>
+      <c r="P50" s="41"/>
+    </row>
+    <row r="51" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A51" s="18">
+        <v>44</v>
+      </c>
+      <c r="B51" s="18">
+        <v>33</v>
+      </c>
+      <c r="C51" s="29"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="39"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="39"/>
+      <c r="M51" s="41"/>
+      <c r="N51" s="41"/>
+      <c r="O51" s="41"/>
+      <c r="P51" s="41"/>
+    </row>
+    <row r="52" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A52" s="18">
+        <v>45</v>
+      </c>
+      <c r="B52" s="18">
+        <v>33</v>
+      </c>
+      <c r="C52" s="29"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="39"/>
+      <c r="K52" s="40"/>
+      <c r="L52" s="39"/>
+      <c r="M52" s="41"/>
+      <c r="N52" s="41"/>
+      <c r="O52" s="41"/>
+      <c r="P52" s="41"/>
+    </row>
+    <row r="53" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A53" s="18">
+        <v>46</v>
+      </c>
+      <c r="B53" s="18">
+        <v>33</v>
+      </c>
+      <c r="C53" s="29"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="39"/>
+      <c r="K53" s="40"/>
+      <c r="L53" s="39"/>
+      <c r="M53" s="41"/>
+      <c r="N53" s="41"/>
+      <c r="O53" s="41"/>
+      <c r="P53" s="41"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A54" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B54" s="12"/>
+      <c r="C54" s="50"/>
+      <c r="D54" s="51" t="s">
+        <v>135</v>
+      </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="51" t="s">
+        <v>136</v>
+      </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="49"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A58" s="12"/>
+      <c r="B58" s="12"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
+      <c r="A65" s="12"/>
+      <c r="B65" s="12"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8"/>
+      <c r="A66" s="12"/>
+      <c r="B66" s="12"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
+      <c r="A67" s="12"/>
+      <c r="B67" s="12"/>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
+      <c r="A68" s="12"/>
+      <c r="B68" s="12"/>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A69" s="8"/>
-      <c r="B69" s="8"/>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
     </row>
@@ -10141,51 +11610,47 @@
       <c r="I1276" s="2"/>
       <c r="J1276" s="2"/>
     </row>
-    <row r="1277" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1277" s="2"/>
-      <c r="J1277" s="2"/>
-    </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="C1:D2"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="E2:F3"/>
-    <mergeCell ref="G2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:P1"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N1:P1"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="N3:P3"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="E2:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="G2:H3"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="P5:P6"/>
   </mergeCells>
-  <phoneticPr fontId="64" type="noConversion"/>
+  <phoneticPr fontId="62" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="68" orientation="landscape"/>

--- a/Body/5-Office/BOM表.xlsx
+++ b/Body/5-Office/BOM表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Win-daolaj3j0nc\F\internal class\N0000-MBW\N0000-3-office文件\供应\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\win-daolaj3j0nc\F\internal class\N2500-25N\N2571-YBJ\N2571-YBJ-2603\3-office文件\供应\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A1481A-5ACA-4A3C-89DF-A3C20BEDAEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E153A097-F61A-4577-ACB2-D0A134EE198D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="120">
   <si>
     <r>
       <rPr>
@@ -426,30 +426,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">RoHS
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>有毒
-元素
-控制</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">QTY
 </t>
     </r>
@@ -484,37 +460,6 @@
         <charset val="134"/>
       </rPr>
       <t>单位</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Substitute P/N
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>替代料</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>P/N</t>
     </r>
   </si>
   <si>
@@ -650,14 +595,755 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Total:</t>
-  </si>
-  <si>
     <t>文档号</t>
-    <phoneticPr fontId="64" type="noConversion"/>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>1121-底盘主体</t>
+  </si>
+  <si>
+    <t>2122-架子</t>
+  </si>
+  <si>
+    <t>1113-内六角平圆头螺钉-GBT70.2-2015_M6X16</t>
+  </si>
+  <si>
+    <t>1312-内六角平圆头螺钉-GBT70.2-2015_M6X10</t>
+  </si>
+  <si>
+    <t>1221-前桥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1222-后桥 </t>
+  </si>
+  <si>
+    <t>1213-大垫圈</t>
+  </si>
+  <si>
+    <t>1224-减震器</t>
+  </si>
+  <si>
+    <t>1214-小垫圈</t>
+  </si>
+  <si>
+    <t>1218-弹簧</t>
+  </si>
+  <si>
+    <t>1225-左梁</t>
+  </si>
+  <si>
+    <t>1215-平头圆柱销</t>
+  </si>
+  <si>
+    <t>1212-销</t>
+  </si>
+  <si>
+    <t>1217-内六角平圆头螺钉-GBT70.2-2015_M6X20</t>
+  </si>
+  <si>
+    <t>1218-内六角平圆头螺钉-GBT70.2-2015_M5X16</t>
+  </si>
+  <si>
+    <t>1216-1型全金属六角锁紧螺母-GBT6184-2000_M10</t>
+  </si>
+  <si>
+    <t>1223-右梁</t>
+  </si>
+  <si>
+    <t>1521-安装板</t>
+  </si>
+  <si>
+    <t>1515-内六角平圆头螺钉-GBT70.2-2015_M4X8</t>
+  </si>
+  <si>
+    <t>1516-内六角平圆头螺钉-GBT70.2-2015_M3X8</t>
+  </si>
+  <si>
+    <t>1522-电脑安装板</t>
+  </si>
+  <si>
+    <t>1517-内六角平圆头螺钉-GBT70.2-2015_M6X12</t>
+  </si>
+  <si>
+    <t>1411-底轮</t>
+  </si>
+  <si>
+    <t>1421-底轮安装板</t>
+  </si>
+  <si>
+    <t>1621-导航雷达安装板</t>
+  </si>
+  <si>
+    <t>1713-1型非金属嵌件六角锁紧螺母-GBT889.1-2015_M6</t>
+  </si>
+  <si>
+    <t>1712-内六角平圆头螺钉-GBT70.2-2015_M3X10</t>
+  </si>
+  <si>
+    <t>1721-避障雷达安装板</t>
+  </si>
+  <si>
+    <t>2121-安装板</t>
+  </si>
+  <si>
+    <t>0121-屏幕支架</t>
+  </si>
+  <si>
+    <t>0123-变压器安装2</t>
+  </si>
+  <si>
+    <t>0116-内六角平圆头螺钉-GBT70.2-2015_M5X12</t>
+  </si>
+  <si>
+    <t>0124-钢轧带</t>
+  </si>
+  <si>
+    <t>0125-电器架</t>
+  </si>
+  <si>
+    <t>0122-变压器安装板</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6*20</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>M5*16</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6*16</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6*10</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>M4*8</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3*8</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6*12</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>M6</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3*10</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>M5*12</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material 材料</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>【淘宝】</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">https://e.tb.cn/h.7ml5gZPPQkVISMc?tk=tJbsUfdvDEd CZ005 </t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>【淘宝】</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>https://e.tb.cn/h.7ml5gZPPQkVISMc?tk=tJbsUfdvDEd CZ006</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>铝</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>【淘宝】</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>天无理由退货</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> https://e.tb.cn/h.7mlCpa3CT8fUR1f?tk=w2zsUfW92Ot </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>【淘宝】大促价保</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> https://e.tb.cn/h.7mOc2Ra9KZEBda1?tk=7f3aUfWpWek</t>
+    </r>
+  </si>
+  <si>
+    <t>直径8</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>直径10</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>M10</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3.82</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>2111-电箱din导轨 130</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>【淘宝】7天无理由退货 https://e.tb.cn/h.7LmgfPhmD1WJjfq?tk=UthlUghUNJc CZ321 「国标卡固氧化C45导轨U型TH35MM宽断路器端子空开电气加厚铝卡轨条」
+点击链接直接打开 或者 淘宝搜索直接打开</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【淘宝】假一赔四</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> https://e.tb.cn/h.7MJcgNyqDq0lb4x?tk=nxhCUgh63I7 CZ193 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>304</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不锈钢垫片圆形加大加厚金属螺丝平垫圈超薄介子华司平垫大全」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击链接直接打开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>淘宝搜索直接打开</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【淘宝】退货运费险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> https://e.tb.cn/h.7Lm8guSC0Ux0SfB?tk=6AuNUghRivr CZ028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「进口模具弹簧高强度耐高温矩形扁线压缩磨具压簧黄蓝红绿棕褐茶色」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击链接直接打开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>淘宝搜索直接打开</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【淘宝】大促价保</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> https://e.tb.cn/h.7MJ4SWmHd5yGuXb?tk=qO5IUghjzTA CZ028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寸重型万向轮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>低重心尼龙脚轮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寸双轮轱辘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寸推车带刹加重轮子」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击链接直接打开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>淘宝搜索直接打开</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0126-miniPC电源</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>19V10A</t>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?id=553788314091&amp;last_time=1768143784&amp;mi_id=0000i7eOrBKgQD4GnhXhm9jjujyg938wVli_lWGICSqSW3s&amp;scm=1007.13982.82927.0&amp;skuId=4092429570913&amp;spm=tbpc.mytb_footmark.item.goods&amp;upStreamPrice=3915</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0127-变压器</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>24V6.35A</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>24V15A</t>
+  </si>
+  <si>
+    <t>https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1563820041%3AH%3AjEXVXFz29uWhSPA32SdLxq18tbGVRP6N%3Ab1e44a53e68312397166bdb38376f31f&amp;ali_trackid=318_b1e44a53e68312397166bdb38376f31f&amp;id=668804973431&amp;mi_id=0000kh4JsEhs_IKQwaZwLe5GPzZBrKEtnqIAl4nMzgEcpGs&amp;mm_sceneid=0_0_2198670068_0&amp;priceTId=213e097817677727727551092e11ab&amp;skuId=6072168990782&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%220ce0092ebee4bb5c990e1ed0aae83472%22%7D&amp;xxc=ad_ztc</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0128-屏幕电源</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0129-接触器</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>12A, 24 V</t>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=15&amp;id=684180101591&amp;mi_id=0000kHsnKO9vrl_xXRKAYuWwfk1ZxpJzkY1oGgmAntBdN2A&amp;ns=1&amp;priceTId=215040db17693197452846906e10bd&amp;skuId=5066190559427&amp;spm=a21n57.1.hoverItem.13&amp;utparam=%7B%22aplus_abtest%22%3A%2200fb48171d68baf920a6c2997ba800f5%22%7D&amp;xxc=taobaoSearch</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0130-空开</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=15&amp;id=885444239746&amp;mi_id=00004gN7JSgLTLqH9NscZa5BV-fDjGIRhn7dS2llqgBEm-I&amp;ns=1&amp;priceTId=215040db17693199893824488e10bd&amp;skuId=5729109569961&amp;spm=a21n57.1.hoverItem.3&amp;utparam=%7B%22aplus_abtest%22%3A%220d184a79d8dee207c56cd615483888e0%22%7D&amp;xxc=taobaoSearch</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.jndz021.com/dc/132（淘宝没有货源，在官网上采购）</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1202830031%3AH%3A5NEVSZWkfH5vk10Gx8WsEg%3D%3D%3A0e3224a199436b146fadd1013df40d50&amp;ali_trackid=282_0e3224a199436b146fadd1013df40d50&amp;id=589213401941&amp;mi_id=0000tXboOyQ6vKwx8WiuBo_0I904yCwGgBZQ-DEtp9Eidvc&amp;mm_sceneid=1_0_343370108_0&amp;priceTId=214782f517694062736734983e1fe1&amp;skuId=4715656587781&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%2243f96ce6df79319aabdbd4973057b1b5%22%7D&amp;xxc=ad_ztc</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0132-焊枪（一套）</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0133-电池</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>电池客服：13662632158</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>48V20AH</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0134-仙工控制器</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经购买</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0135-激光雷达</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0135-导航雷达</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0131-接线端子</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>PT2.5-QUATTRO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>灰色</t>
+    </r>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?ali_refid=a3_430673_1006%3A1109974134%3AH%3AS9mt8%2FS9IPRAnlGXK23dCRerfi2%2BAYZj%3A75421c7a1bf937df626379b8de81db84&amp;ali_trackid=282_75421c7a1bf937df626379b8de81db84&amp;id=774427618182&amp;loginBonus=1&amp;mi_id=0000OtzXamOT9vAra9TbUQiBvRLBsdZJRcmzsekmz3yUyS0&amp;mm_sceneid=1_0_99588015_0&amp;priceTId=2150467817696032421462002e22b0&amp;skuId=5300832301565&amp;spm=a21n57.sem.item.4&amp;utparam=%7B%22aplus_abtest%22%3A%22c7bbb9e8de08729fc098be83e797fb13%22%7D&amp;xxc=ad_ztc</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>1312-电机</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否验收</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>对</t>
+    <phoneticPr fontId="61" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -676,11 +1362,19 @@
     <numFmt numFmtId="182" formatCode="0.00_ "/>
     <numFmt numFmtId="183" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="67" x14ac:knownFonts="1">
+  <fonts count="69" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -728,6 +1422,7 @@
       <b/>
       <sz val="18"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -740,18 +1435,14 @@
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -769,6 +1460,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1076,27 +1768,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -1114,11 +1785,44 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1293,8 +1997,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1569,8 +2297,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="266">
+  <cellStyleXfs count="267">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="17" fillId="0" borderId="0"/>
@@ -1682,36 +2425,36 @@
     <xf numFmtId="176" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="177" fontId="22" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="21" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1753,11 +2496,11 @@
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -1765,77 +2508,77 @@
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="32" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="33" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="34" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -2183,31 +2926,31 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="51" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="51" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="51" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="51" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="176" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2244,7 +2987,7 @@
     <xf numFmtId="176" fontId="57" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="58" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2256,232 +2999,233 @@
     <xf numFmtId="176" fontId="17" fillId="29" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="67" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="76">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="181" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="183" fontId="2" fillId="0" borderId="1" xfId="114" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="114" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="114" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="65" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="64" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="65" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="63" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="63" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="63" fillId="32" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="66" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="64" fillId="33" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="64" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="67" fillId="30" borderId="1" xfId="266" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="68" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="65" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="65" fillId="33" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="62" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="62" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="62" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="183" fontId="1" fillId="0" borderId="1" xfId="114" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="114" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="114" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="61" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="66" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="66" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="65" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="266">
+  <cellStyles count="267">
     <cellStyle name="? 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="_ET_STYLE_NoName_00_" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
     <cellStyle name="20% - 輔色1" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
@@ -2598,6 +3342,7 @@
     <cellStyle name="常规 9" xfId="113" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
     <cellStyle name="常规_Alpha BOM" xfId="114" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
     <cellStyle name="超级链接" xfId="115" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
+    <cellStyle name="超链接" xfId="266" builtinId="8"/>
     <cellStyle name="輔色1" xfId="116" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
     <cellStyle name="輔色2" xfId="117" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
     <cellStyle name="輔色3" xfId="118" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
@@ -3059,74 +3804,74 @@
     <col min="5" max="5" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="44" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:5" s="29" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="32" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-    </row>
-    <row r="3" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-    </row>
-    <row r="4" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="48"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-    </row>
-    <row r="5" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="48"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-    </row>
-    <row r="6" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="48"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-    </row>
-    <row r="7" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="48"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-    </row>
-    <row r="8" spans="1:5" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="48"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
+    <row r="2" spans="1:5" s="30" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+    </row>
+    <row r="3" spans="1:5" s="30" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="33"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+    </row>
+    <row r="4" spans="1:5" s="30" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="33"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+    </row>
+    <row r="5" spans="1:5" s="30" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="33"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+    </row>
+    <row r="6" spans="1:5" s="30" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="33"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+    </row>
+    <row r="7" spans="1:5" s="30" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="33"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+    </row>
+    <row r="8" spans="1:5" s="30" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="33"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="64" type="noConversion"/>
+  <phoneticPr fontId="61" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3134,2226 +3879,3049 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:WVF1277"/>
+  <dimension ref="A1:WVF1221"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="6" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="17.5" style="8" customWidth="1"/>
+    <col min="1" max="1" width="5.625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="5" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="47.125" style="7" customWidth="1"/>
     <col min="5" max="5" width="18.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.75" style="2" customWidth="1"/>
     <col min="8" max="8" width="6.5" style="2" customWidth="1"/>
-    <col min="9" max="10" width="5.75" style="9" customWidth="1"/>
+    <col min="9" max="10" width="5.75" style="8" customWidth="1"/>
     <col min="11" max="11" width="11.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="26.875" style="2" customWidth="1"/>
     <col min="13" max="13" width="15.625" style="2" customWidth="1"/>
     <col min="14" max="14" width="11" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11.125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="11.25" style="11" customWidth="1"/>
-    <col min="17" max="250" width="9" style="11"/>
-    <col min="251" max="251" width="6.875" style="11" customWidth="1"/>
-    <col min="252" max="252" width="10.125" style="11" customWidth="1"/>
-    <col min="253" max="253" width="11.125" style="11" customWidth="1"/>
-    <col min="254" max="254" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="255" max="255" width="21.625" style="11" customWidth="1"/>
-    <col min="256" max="256" width="6.25" style="11" customWidth="1"/>
-    <col min="257" max="257" width="12.125" style="11" customWidth="1"/>
-    <col min="258" max="258" width="20.125" style="11" customWidth="1"/>
-    <col min="259" max="259" width="26.75" style="11" customWidth="1"/>
-    <col min="260" max="260" width="13.375" style="11" customWidth="1"/>
-    <col min="261" max="261" width="17" style="11" customWidth="1"/>
-    <col min="262" max="262" width="19.125" style="11" customWidth="1"/>
-    <col min="263" max="264" width="5.875" style="11" customWidth="1"/>
-    <col min="265" max="265" width="6.625" style="11" customWidth="1"/>
-    <col min="266" max="266" width="8.125" style="11" customWidth="1"/>
-    <col min="267" max="267" width="10.125" style="11" customWidth="1"/>
-    <col min="268" max="268" width="7.25" style="11" customWidth="1"/>
-    <col min="269" max="269" width="11.875" style="11" customWidth="1"/>
-    <col min="270" max="270" width="2.125" style="11" customWidth="1"/>
-    <col min="271" max="272" width="12.5" style="11" customWidth="1"/>
-    <col min="273" max="506" width="9" style="11"/>
-    <col min="507" max="507" width="6.875" style="11" customWidth="1"/>
-    <col min="508" max="508" width="10.125" style="11" customWidth="1"/>
-    <col min="509" max="509" width="11.125" style="11" customWidth="1"/>
-    <col min="510" max="510" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="511" max="511" width="21.625" style="11" customWidth="1"/>
-    <col min="512" max="512" width="6.25" style="11" customWidth="1"/>
-    <col min="513" max="513" width="12.125" style="11" customWidth="1"/>
-    <col min="514" max="514" width="20.125" style="11" customWidth="1"/>
-    <col min="515" max="515" width="26.75" style="11" customWidth="1"/>
-    <col min="516" max="516" width="13.375" style="11" customWidth="1"/>
-    <col min="517" max="517" width="17" style="11" customWidth="1"/>
-    <col min="518" max="518" width="19.125" style="11" customWidth="1"/>
-    <col min="519" max="520" width="5.875" style="11" customWidth="1"/>
-    <col min="521" max="521" width="6.625" style="11" customWidth="1"/>
-    <col min="522" max="522" width="8.125" style="11" customWidth="1"/>
-    <col min="523" max="523" width="10.125" style="11" customWidth="1"/>
-    <col min="524" max="524" width="7.25" style="11" customWidth="1"/>
-    <col min="525" max="525" width="11.875" style="11" customWidth="1"/>
-    <col min="526" max="526" width="2.125" style="11" customWidth="1"/>
-    <col min="527" max="528" width="12.5" style="11" customWidth="1"/>
-    <col min="529" max="762" width="9" style="11"/>
-    <col min="763" max="763" width="6.875" style="11" customWidth="1"/>
-    <col min="764" max="764" width="10.125" style="11" customWidth="1"/>
-    <col min="765" max="765" width="11.125" style="11" customWidth="1"/>
-    <col min="766" max="766" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="767" max="767" width="21.625" style="11" customWidth="1"/>
-    <col min="768" max="768" width="6.25" style="11" customWidth="1"/>
-    <col min="769" max="769" width="12.125" style="11" customWidth="1"/>
-    <col min="770" max="770" width="20.125" style="11" customWidth="1"/>
-    <col min="771" max="771" width="26.75" style="11" customWidth="1"/>
-    <col min="772" max="772" width="13.375" style="11" customWidth="1"/>
-    <col min="773" max="773" width="17" style="11" customWidth="1"/>
-    <col min="774" max="774" width="19.125" style="11" customWidth="1"/>
-    <col min="775" max="776" width="5.875" style="11" customWidth="1"/>
-    <col min="777" max="777" width="6.625" style="11" customWidth="1"/>
-    <col min="778" max="778" width="8.125" style="11" customWidth="1"/>
-    <col min="779" max="779" width="10.125" style="11" customWidth="1"/>
-    <col min="780" max="780" width="7.25" style="11" customWidth="1"/>
-    <col min="781" max="781" width="11.875" style="11" customWidth="1"/>
-    <col min="782" max="782" width="2.125" style="11" customWidth="1"/>
-    <col min="783" max="784" width="12.5" style="11" customWidth="1"/>
-    <col min="785" max="1018" width="9" style="11"/>
-    <col min="1019" max="1019" width="6.875" style="11" customWidth="1"/>
-    <col min="1020" max="1020" width="10.125" style="11" customWidth="1"/>
-    <col min="1021" max="1021" width="11.125" style="11" customWidth="1"/>
-    <col min="1022" max="1022" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="1023" max="1023" width="21.625" style="11" customWidth="1"/>
-    <col min="1024" max="1024" width="6.25" style="11" customWidth="1"/>
-    <col min="1025" max="1025" width="12.125" style="11" customWidth="1"/>
-    <col min="1026" max="1026" width="20.125" style="11" customWidth="1"/>
-    <col min="1027" max="1027" width="26.75" style="11" customWidth="1"/>
-    <col min="1028" max="1028" width="13.375" style="11" customWidth="1"/>
-    <col min="1029" max="1029" width="17" style="11" customWidth="1"/>
-    <col min="1030" max="1030" width="19.125" style="11" customWidth="1"/>
-    <col min="1031" max="1032" width="5.875" style="11" customWidth="1"/>
-    <col min="1033" max="1033" width="6.625" style="11" customWidth="1"/>
-    <col min="1034" max="1034" width="8.125" style="11" customWidth="1"/>
-    <col min="1035" max="1035" width="10.125" style="11" customWidth="1"/>
-    <col min="1036" max="1036" width="7.25" style="11" customWidth="1"/>
-    <col min="1037" max="1037" width="11.875" style="11" customWidth="1"/>
-    <col min="1038" max="1038" width="2.125" style="11" customWidth="1"/>
-    <col min="1039" max="1040" width="12.5" style="11" customWidth="1"/>
-    <col min="1041" max="1274" width="9" style="11"/>
-    <col min="1275" max="1275" width="6.875" style="11" customWidth="1"/>
-    <col min="1276" max="1276" width="10.125" style="11" customWidth="1"/>
-    <col min="1277" max="1277" width="11.125" style="11" customWidth="1"/>
-    <col min="1278" max="1278" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="1279" max="1279" width="21.625" style="11" customWidth="1"/>
-    <col min="1280" max="1280" width="6.25" style="11" customWidth="1"/>
-    <col min="1281" max="1281" width="12.125" style="11" customWidth="1"/>
-    <col min="1282" max="1282" width="20.125" style="11" customWidth="1"/>
-    <col min="1283" max="1283" width="26.75" style="11" customWidth="1"/>
-    <col min="1284" max="1284" width="13.375" style="11" customWidth="1"/>
-    <col min="1285" max="1285" width="17" style="11" customWidth="1"/>
-    <col min="1286" max="1286" width="19.125" style="11" customWidth="1"/>
-    <col min="1287" max="1288" width="5.875" style="11" customWidth="1"/>
-    <col min="1289" max="1289" width="6.625" style="11" customWidth="1"/>
-    <col min="1290" max="1290" width="8.125" style="11" customWidth="1"/>
-    <col min="1291" max="1291" width="10.125" style="11" customWidth="1"/>
-    <col min="1292" max="1292" width="7.25" style="11" customWidth="1"/>
-    <col min="1293" max="1293" width="11.875" style="11" customWidth="1"/>
-    <col min="1294" max="1294" width="2.125" style="11" customWidth="1"/>
-    <col min="1295" max="1296" width="12.5" style="11" customWidth="1"/>
-    <col min="1297" max="1530" width="9" style="11"/>
-    <col min="1531" max="1531" width="6.875" style="11" customWidth="1"/>
-    <col min="1532" max="1532" width="10.125" style="11" customWidth="1"/>
-    <col min="1533" max="1533" width="11.125" style="11" customWidth="1"/>
-    <col min="1534" max="1534" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="1535" max="1535" width="21.625" style="11" customWidth="1"/>
-    <col min="1536" max="1536" width="6.25" style="11" customWidth="1"/>
-    <col min="1537" max="1537" width="12.125" style="11" customWidth="1"/>
-    <col min="1538" max="1538" width="20.125" style="11" customWidth="1"/>
-    <col min="1539" max="1539" width="26.75" style="11" customWidth="1"/>
-    <col min="1540" max="1540" width="13.375" style="11" customWidth="1"/>
-    <col min="1541" max="1541" width="17" style="11" customWidth="1"/>
-    <col min="1542" max="1542" width="19.125" style="11" customWidth="1"/>
-    <col min="1543" max="1544" width="5.875" style="11" customWidth="1"/>
-    <col min="1545" max="1545" width="6.625" style="11" customWidth="1"/>
-    <col min="1546" max="1546" width="8.125" style="11" customWidth="1"/>
-    <col min="1547" max="1547" width="10.125" style="11" customWidth="1"/>
-    <col min="1548" max="1548" width="7.25" style="11" customWidth="1"/>
-    <col min="1549" max="1549" width="11.875" style="11" customWidth="1"/>
-    <col min="1550" max="1550" width="2.125" style="11" customWidth="1"/>
-    <col min="1551" max="1552" width="12.5" style="11" customWidth="1"/>
-    <col min="1553" max="1786" width="9" style="11"/>
-    <col min="1787" max="1787" width="6.875" style="11" customWidth="1"/>
-    <col min="1788" max="1788" width="10.125" style="11" customWidth="1"/>
-    <col min="1789" max="1789" width="11.125" style="11" customWidth="1"/>
-    <col min="1790" max="1790" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="1791" max="1791" width="21.625" style="11" customWidth="1"/>
-    <col min="1792" max="1792" width="6.25" style="11" customWidth="1"/>
-    <col min="1793" max="1793" width="12.125" style="11" customWidth="1"/>
-    <col min="1794" max="1794" width="20.125" style="11" customWidth="1"/>
-    <col min="1795" max="1795" width="26.75" style="11" customWidth="1"/>
-    <col min="1796" max="1796" width="13.375" style="11" customWidth="1"/>
-    <col min="1797" max="1797" width="17" style="11" customWidth="1"/>
-    <col min="1798" max="1798" width="19.125" style="11" customWidth="1"/>
-    <col min="1799" max="1800" width="5.875" style="11" customWidth="1"/>
-    <col min="1801" max="1801" width="6.625" style="11" customWidth="1"/>
-    <col min="1802" max="1802" width="8.125" style="11" customWidth="1"/>
-    <col min="1803" max="1803" width="10.125" style="11" customWidth="1"/>
-    <col min="1804" max="1804" width="7.25" style="11" customWidth="1"/>
-    <col min="1805" max="1805" width="11.875" style="11" customWidth="1"/>
-    <col min="1806" max="1806" width="2.125" style="11" customWidth="1"/>
-    <col min="1807" max="1808" width="12.5" style="11" customWidth="1"/>
-    <col min="1809" max="2042" width="9" style="11"/>
-    <col min="2043" max="2043" width="6.875" style="11" customWidth="1"/>
-    <col min="2044" max="2044" width="10.125" style="11" customWidth="1"/>
-    <col min="2045" max="2045" width="11.125" style="11" customWidth="1"/>
-    <col min="2046" max="2046" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="2047" max="2047" width="21.625" style="11" customWidth="1"/>
-    <col min="2048" max="2048" width="6.25" style="11" customWidth="1"/>
-    <col min="2049" max="2049" width="12.125" style="11" customWidth="1"/>
-    <col min="2050" max="2050" width="20.125" style="11" customWidth="1"/>
-    <col min="2051" max="2051" width="26.75" style="11" customWidth="1"/>
-    <col min="2052" max="2052" width="13.375" style="11" customWidth="1"/>
-    <col min="2053" max="2053" width="17" style="11" customWidth="1"/>
-    <col min="2054" max="2054" width="19.125" style="11" customWidth="1"/>
-    <col min="2055" max="2056" width="5.875" style="11" customWidth="1"/>
-    <col min="2057" max="2057" width="6.625" style="11" customWidth="1"/>
-    <col min="2058" max="2058" width="8.125" style="11" customWidth="1"/>
-    <col min="2059" max="2059" width="10.125" style="11" customWidth="1"/>
-    <col min="2060" max="2060" width="7.25" style="11" customWidth="1"/>
-    <col min="2061" max="2061" width="11.875" style="11" customWidth="1"/>
-    <col min="2062" max="2062" width="2.125" style="11" customWidth="1"/>
-    <col min="2063" max="2064" width="12.5" style="11" customWidth="1"/>
-    <col min="2065" max="2298" width="9" style="11"/>
-    <col min="2299" max="2299" width="6.875" style="11" customWidth="1"/>
-    <col min="2300" max="2300" width="10.125" style="11" customWidth="1"/>
-    <col min="2301" max="2301" width="11.125" style="11" customWidth="1"/>
-    <col min="2302" max="2302" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="2303" max="2303" width="21.625" style="11" customWidth="1"/>
-    <col min="2304" max="2304" width="6.25" style="11" customWidth="1"/>
-    <col min="2305" max="2305" width="12.125" style="11" customWidth="1"/>
-    <col min="2306" max="2306" width="20.125" style="11" customWidth="1"/>
-    <col min="2307" max="2307" width="26.75" style="11" customWidth="1"/>
-    <col min="2308" max="2308" width="13.375" style="11" customWidth="1"/>
-    <col min="2309" max="2309" width="17" style="11" customWidth="1"/>
-    <col min="2310" max="2310" width="19.125" style="11" customWidth="1"/>
-    <col min="2311" max="2312" width="5.875" style="11" customWidth="1"/>
-    <col min="2313" max="2313" width="6.625" style="11" customWidth="1"/>
-    <col min="2314" max="2314" width="8.125" style="11" customWidth="1"/>
-    <col min="2315" max="2315" width="10.125" style="11" customWidth="1"/>
-    <col min="2316" max="2316" width="7.25" style="11" customWidth="1"/>
-    <col min="2317" max="2317" width="11.875" style="11" customWidth="1"/>
-    <col min="2318" max="2318" width="2.125" style="11" customWidth="1"/>
-    <col min="2319" max="2320" width="12.5" style="11" customWidth="1"/>
-    <col min="2321" max="2554" width="9" style="11"/>
-    <col min="2555" max="2555" width="6.875" style="11" customWidth="1"/>
-    <col min="2556" max="2556" width="10.125" style="11" customWidth="1"/>
-    <col min="2557" max="2557" width="11.125" style="11" customWidth="1"/>
-    <col min="2558" max="2558" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="2559" max="2559" width="21.625" style="11" customWidth="1"/>
-    <col min="2560" max="2560" width="6.25" style="11" customWidth="1"/>
-    <col min="2561" max="2561" width="12.125" style="11" customWidth="1"/>
-    <col min="2562" max="2562" width="20.125" style="11" customWidth="1"/>
-    <col min="2563" max="2563" width="26.75" style="11" customWidth="1"/>
-    <col min="2564" max="2564" width="13.375" style="11" customWidth="1"/>
-    <col min="2565" max="2565" width="17" style="11" customWidth="1"/>
-    <col min="2566" max="2566" width="19.125" style="11" customWidth="1"/>
-    <col min="2567" max="2568" width="5.875" style="11" customWidth="1"/>
-    <col min="2569" max="2569" width="6.625" style="11" customWidth="1"/>
-    <col min="2570" max="2570" width="8.125" style="11" customWidth="1"/>
-    <col min="2571" max="2571" width="10.125" style="11" customWidth="1"/>
-    <col min="2572" max="2572" width="7.25" style="11" customWidth="1"/>
-    <col min="2573" max="2573" width="11.875" style="11" customWidth="1"/>
-    <col min="2574" max="2574" width="2.125" style="11" customWidth="1"/>
-    <col min="2575" max="2576" width="12.5" style="11" customWidth="1"/>
-    <col min="2577" max="2810" width="9" style="11"/>
-    <col min="2811" max="2811" width="6.875" style="11" customWidth="1"/>
-    <col min="2812" max="2812" width="10.125" style="11" customWidth="1"/>
-    <col min="2813" max="2813" width="11.125" style="11" customWidth="1"/>
-    <col min="2814" max="2814" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="2815" max="2815" width="21.625" style="11" customWidth="1"/>
-    <col min="2816" max="2816" width="6.25" style="11" customWidth="1"/>
-    <col min="2817" max="2817" width="12.125" style="11" customWidth="1"/>
-    <col min="2818" max="2818" width="20.125" style="11" customWidth="1"/>
-    <col min="2819" max="2819" width="26.75" style="11" customWidth="1"/>
-    <col min="2820" max="2820" width="13.375" style="11" customWidth="1"/>
-    <col min="2821" max="2821" width="17" style="11" customWidth="1"/>
-    <col min="2822" max="2822" width="19.125" style="11" customWidth="1"/>
-    <col min="2823" max="2824" width="5.875" style="11" customWidth="1"/>
-    <col min="2825" max="2825" width="6.625" style="11" customWidth="1"/>
-    <col min="2826" max="2826" width="8.125" style="11" customWidth="1"/>
-    <col min="2827" max="2827" width="10.125" style="11" customWidth="1"/>
-    <col min="2828" max="2828" width="7.25" style="11" customWidth="1"/>
-    <col min="2829" max="2829" width="11.875" style="11" customWidth="1"/>
-    <col min="2830" max="2830" width="2.125" style="11" customWidth="1"/>
-    <col min="2831" max="2832" width="12.5" style="11" customWidth="1"/>
-    <col min="2833" max="3066" width="9" style="11"/>
-    <col min="3067" max="3067" width="6.875" style="11" customWidth="1"/>
-    <col min="3068" max="3068" width="10.125" style="11" customWidth="1"/>
-    <col min="3069" max="3069" width="11.125" style="11" customWidth="1"/>
-    <col min="3070" max="3070" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="3071" max="3071" width="21.625" style="11" customWidth="1"/>
-    <col min="3072" max="3072" width="6.25" style="11" customWidth="1"/>
-    <col min="3073" max="3073" width="12.125" style="11" customWidth="1"/>
-    <col min="3074" max="3074" width="20.125" style="11" customWidth="1"/>
-    <col min="3075" max="3075" width="26.75" style="11" customWidth="1"/>
-    <col min="3076" max="3076" width="13.375" style="11" customWidth="1"/>
-    <col min="3077" max="3077" width="17" style="11" customWidth="1"/>
-    <col min="3078" max="3078" width="19.125" style="11" customWidth="1"/>
-    <col min="3079" max="3080" width="5.875" style="11" customWidth="1"/>
-    <col min="3081" max="3081" width="6.625" style="11" customWidth="1"/>
-    <col min="3082" max="3082" width="8.125" style="11" customWidth="1"/>
-    <col min="3083" max="3083" width="10.125" style="11" customWidth="1"/>
-    <col min="3084" max="3084" width="7.25" style="11" customWidth="1"/>
-    <col min="3085" max="3085" width="11.875" style="11" customWidth="1"/>
-    <col min="3086" max="3086" width="2.125" style="11" customWidth="1"/>
-    <col min="3087" max="3088" width="12.5" style="11" customWidth="1"/>
-    <col min="3089" max="3322" width="9" style="11"/>
-    <col min="3323" max="3323" width="6.875" style="11" customWidth="1"/>
-    <col min="3324" max="3324" width="10.125" style="11" customWidth="1"/>
-    <col min="3325" max="3325" width="11.125" style="11" customWidth="1"/>
-    <col min="3326" max="3326" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="3327" max="3327" width="21.625" style="11" customWidth="1"/>
-    <col min="3328" max="3328" width="6.25" style="11" customWidth="1"/>
-    <col min="3329" max="3329" width="12.125" style="11" customWidth="1"/>
-    <col min="3330" max="3330" width="20.125" style="11" customWidth="1"/>
-    <col min="3331" max="3331" width="26.75" style="11" customWidth="1"/>
-    <col min="3332" max="3332" width="13.375" style="11" customWidth="1"/>
-    <col min="3333" max="3333" width="17" style="11" customWidth="1"/>
-    <col min="3334" max="3334" width="19.125" style="11" customWidth="1"/>
-    <col min="3335" max="3336" width="5.875" style="11" customWidth="1"/>
-    <col min="3337" max="3337" width="6.625" style="11" customWidth="1"/>
-    <col min="3338" max="3338" width="8.125" style="11" customWidth="1"/>
-    <col min="3339" max="3339" width="10.125" style="11" customWidth="1"/>
-    <col min="3340" max="3340" width="7.25" style="11" customWidth="1"/>
-    <col min="3341" max="3341" width="11.875" style="11" customWidth="1"/>
-    <col min="3342" max="3342" width="2.125" style="11" customWidth="1"/>
-    <col min="3343" max="3344" width="12.5" style="11" customWidth="1"/>
-    <col min="3345" max="3578" width="9" style="11"/>
-    <col min="3579" max="3579" width="6.875" style="11" customWidth="1"/>
-    <col min="3580" max="3580" width="10.125" style="11" customWidth="1"/>
-    <col min="3581" max="3581" width="11.125" style="11" customWidth="1"/>
-    <col min="3582" max="3582" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="3583" max="3583" width="21.625" style="11" customWidth="1"/>
-    <col min="3584" max="3584" width="6.25" style="11" customWidth="1"/>
-    <col min="3585" max="3585" width="12.125" style="11" customWidth="1"/>
-    <col min="3586" max="3586" width="20.125" style="11" customWidth="1"/>
-    <col min="3587" max="3587" width="26.75" style="11" customWidth="1"/>
-    <col min="3588" max="3588" width="13.375" style="11" customWidth="1"/>
-    <col min="3589" max="3589" width="17" style="11" customWidth="1"/>
-    <col min="3590" max="3590" width="19.125" style="11" customWidth="1"/>
-    <col min="3591" max="3592" width="5.875" style="11" customWidth="1"/>
-    <col min="3593" max="3593" width="6.625" style="11" customWidth="1"/>
-    <col min="3594" max="3594" width="8.125" style="11" customWidth="1"/>
-    <col min="3595" max="3595" width="10.125" style="11" customWidth="1"/>
-    <col min="3596" max="3596" width="7.25" style="11" customWidth="1"/>
-    <col min="3597" max="3597" width="11.875" style="11" customWidth="1"/>
-    <col min="3598" max="3598" width="2.125" style="11" customWidth="1"/>
-    <col min="3599" max="3600" width="12.5" style="11" customWidth="1"/>
-    <col min="3601" max="3834" width="9" style="11"/>
-    <col min="3835" max="3835" width="6.875" style="11" customWidth="1"/>
-    <col min="3836" max="3836" width="10.125" style="11" customWidth="1"/>
-    <col min="3837" max="3837" width="11.125" style="11" customWidth="1"/>
-    <col min="3838" max="3838" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="3839" max="3839" width="21.625" style="11" customWidth="1"/>
-    <col min="3840" max="3840" width="6.25" style="11" customWidth="1"/>
-    <col min="3841" max="3841" width="12.125" style="11" customWidth="1"/>
-    <col min="3842" max="3842" width="20.125" style="11" customWidth="1"/>
-    <col min="3843" max="3843" width="26.75" style="11" customWidth="1"/>
-    <col min="3844" max="3844" width="13.375" style="11" customWidth="1"/>
-    <col min="3845" max="3845" width="17" style="11" customWidth="1"/>
-    <col min="3846" max="3846" width="19.125" style="11" customWidth="1"/>
-    <col min="3847" max="3848" width="5.875" style="11" customWidth="1"/>
-    <col min="3849" max="3849" width="6.625" style="11" customWidth="1"/>
-    <col min="3850" max="3850" width="8.125" style="11" customWidth="1"/>
-    <col min="3851" max="3851" width="10.125" style="11" customWidth="1"/>
-    <col min="3852" max="3852" width="7.25" style="11" customWidth="1"/>
-    <col min="3853" max="3853" width="11.875" style="11" customWidth="1"/>
-    <col min="3854" max="3854" width="2.125" style="11" customWidth="1"/>
-    <col min="3855" max="3856" width="12.5" style="11" customWidth="1"/>
-    <col min="3857" max="4090" width="9" style="11"/>
-    <col min="4091" max="4091" width="6.875" style="11" customWidth="1"/>
-    <col min="4092" max="4092" width="10.125" style="11" customWidth="1"/>
-    <col min="4093" max="4093" width="11.125" style="11" customWidth="1"/>
-    <col min="4094" max="4094" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="4095" max="4095" width="21.625" style="11" customWidth="1"/>
-    <col min="4096" max="4096" width="6.25" style="11" customWidth="1"/>
-    <col min="4097" max="4097" width="12.125" style="11" customWidth="1"/>
-    <col min="4098" max="4098" width="20.125" style="11" customWidth="1"/>
-    <col min="4099" max="4099" width="26.75" style="11" customWidth="1"/>
-    <col min="4100" max="4100" width="13.375" style="11" customWidth="1"/>
-    <col min="4101" max="4101" width="17" style="11" customWidth="1"/>
-    <col min="4102" max="4102" width="19.125" style="11" customWidth="1"/>
-    <col min="4103" max="4104" width="5.875" style="11" customWidth="1"/>
-    <col min="4105" max="4105" width="6.625" style="11" customWidth="1"/>
-    <col min="4106" max="4106" width="8.125" style="11" customWidth="1"/>
-    <col min="4107" max="4107" width="10.125" style="11" customWidth="1"/>
-    <col min="4108" max="4108" width="7.25" style="11" customWidth="1"/>
-    <col min="4109" max="4109" width="11.875" style="11" customWidth="1"/>
-    <col min="4110" max="4110" width="2.125" style="11" customWidth="1"/>
-    <col min="4111" max="4112" width="12.5" style="11" customWidth="1"/>
-    <col min="4113" max="4346" width="9" style="11"/>
-    <col min="4347" max="4347" width="6.875" style="11" customWidth="1"/>
-    <col min="4348" max="4348" width="10.125" style="11" customWidth="1"/>
-    <col min="4349" max="4349" width="11.125" style="11" customWidth="1"/>
-    <col min="4350" max="4350" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="4351" max="4351" width="21.625" style="11" customWidth="1"/>
-    <col min="4352" max="4352" width="6.25" style="11" customWidth="1"/>
-    <col min="4353" max="4353" width="12.125" style="11" customWidth="1"/>
-    <col min="4354" max="4354" width="20.125" style="11" customWidth="1"/>
-    <col min="4355" max="4355" width="26.75" style="11" customWidth="1"/>
-    <col min="4356" max="4356" width="13.375" style="11" customWidth="1"/>
-    <col min="4357" max="4357" width="17" style="11" customWidth="1"/>
-    <col min="4358" max="4358" width="19.125" style="11" customWidth="1"/>
-    <col min="4359" max="4360" width="5.875" style="11" customWidth="1"/>
-    <col min="4361" max="4361" width="6.625" style="11" customWidth="1"/>
-    <col min="4362" max="4362" width="8.125" style="11" customWidth="1"/>
-    <col min="4363" max="4363" width="10.125" style="11" customWidth="1"/>
-    <col min="4364" max="4364" width="7.25" style="11" customWidth="1"/>
-    <col min="4365" max="4365" width="11.875" style="11" customWidth="1"/>
-    <col min="4366" max="4366" width="2.125" style="11" customWidth="1"/>
-    <col min="4367" max="4368" width="12.5" style="11" customWidth="1"/>
-    <col min="4369" max="4602" width="9" style="11"/>
-    <col min="4603" max="4603" width="6.875" style="11" customWidth="1"/>
-    <col min="4604" max="4604" width="10.125" style="11" customWidth="1"/>
-    <col min="4605" max="4605" width="11.125" style="11" customWidth="1"/>
-    <col min="4606" max="4606" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="4607" max="4607" width="21.625" style="11" customWidth="1"/>
-    <col min="4608" max="4608" width="6.25" style="11" customWidth="1"/>
-    <col min="4609" max="4609" width="12.125" style="11" customWidth="1"/>
-    <col min="4610" max="4610" width="20.125" style="11" customWidth="1"/>
-    <col min="4611" max="4611" width="26.75" style="11" customWidth="1"/>
-    <col min="4612" max="4612" width="13.375" style="11" customWidth="1"/>
-    <col min="4613" max="4613" width="17" style="11" customWidth="1"/>
-    <col min="4614" max="4614" width="19.125" style="11" customWidth="1"/>
-    <col min="4615" max="4616" width="5.875" style="11" customWidth="1"/>
-    <col min="4617" max="4617" width="6.625" style="11" customWidth="1"/>
-    <col min="4618" max="4618" width="8.125" style="11" customWidth="1"/>
-    <col min="4619" max="4619" width="10.125" style="11" customWidth="1"/>
-    <col min="4620" max="4620" width="7.25" style="11" customWidth="1"/>
-    <col min="4621" max="4621" width="11.875" style="11" customWidth="1"/>
-    <col min="4622" max="4622" width="2.125" style="11" customWidth="1"/>
-    <col min="4623" max="4624" width="12.5" style="11" customWidth="1"/>
-    <col min="4625" max="4858" width="9" style="11"/>
-    <col min="4859" max="4859" width="6.875" style="11" customWidth="1"/>
-    <col min="4860" max="4860" width="10.125" style="11" customWidth="1"/>
-    <col min="4861" max="4861" width="11.125" style="11" customWidth="1"/>
-    <col min="4862" max="4862" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="4863" max="4863" width="21.625" style="11" customWidth="1"/>
-    <col min="4864" max="4864" width="6.25" style="11" customWidth="1"/>
-    <col min="4865" max="4865" width="12.125" style="11" customWidth="1"/>
-    <col min="4866" max="4866" width="20.125" style="11" customWidth="1"/>
-    <col min="4867" max="4867" width="26.75" style="11" customWidth="1"/>
-    <col min="4868" max="4868" width="13.375" style="11" customWidth="1"/>
-    <col min="4869" max="4869" width="17" style="11" customWidth="1"/>
-    <col min="4870" max="4870" width="19.125" style="11" customWidth="1"/>
-    <col min="4871" max="4872" width="5.875" style="11" customWidth="1"/>
-    <col min="4873" max="4873" width="6.625" style="11" customWidth="1"/>
-    <col min="4874" max="4874" width="8.125" style="11" customWidth="1"/>
-    <col min="4875" max="4875" width="10.125" style="11" customWidth="1"/>
-    <col min="4876" max="4876" width="7.25" style="11" customWidth="1"/>
-    <col min="4877" max="4877" width="11.875" style="11" customWidth="1"/>
-    <col min="4878" max="4878" width="2.125" style="11" customWidth="1"/>
-    <col min="4879" max="4880" width="12.5" style="11" customWidth="1"/>
-    <col min="4881" max="5114" width="9" style="11"/>
-    <col min="5115" max="5115" width="6.875" style="11" customWidth="1"/>
-    <col min="5116" max="5116" width="10.125" style="11" customWidth="1"/>
-    <col min="5117" max="5117" width="11.125" style="11" customWidth="1"/>
-    <col min="5118" max="5118" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="5119" max="5119" width="21.625" style="11" customWidth="1"/>
-    <col min="5120" max="5120" width="6.25" style="11" customWidth="1"/>
-    <col min="5121" max="5121" width="12.125" style="11" customWidth="1"/>
-    <col min="5122" max="5122" width="20.125" style="11" customWidth="1"/>
-    <col min="5123" max="5123" width="26.75" style="11" customWidth="1"/>
-    <col min="5124" max="5124" width="13.375" style="11" customWidth="1"/>
-    <col min="5125" max="5125" width="17" style="11" customWidth="1"/>
-    <col min="5126" max="5126" width="19.125" style="11" customWidth="1"/>
-    <col min="5127" max="5128" width="5.875" style="11" customWidth="1"/>
-    <col min="5129" max="5129" width="6.625" style="11" customWidth="1"/>
-    <col min="5130" max="5130" width="8.125" style="11" customWidth="1"/>
-    <col min="5131" max="5131" width="10.125" style="11" customWidth="1"/>
-    <col min="5132" max="5132" width="7.25" style="11" customWidth="1"/>
-    <col min="5133" max="5133" width="11.875" style="11" customWidth="1"/>
-    <col min="5134" max="5134" width="2.125" style="11" customWidth="1"/>
-    <col min="5135" max="5136" width="12.5" style="11" customWidth="1"/>
-    <col min="5137" max="5370" width="9" style="11"/>
-    <col min="5371" max="5371" width="6.875" style="11" customWidth="1"/>
-    <col min="5372" max="5372" width="10.125" style="11" customWidth="1"/>
-    <col min="5373" max="5373" width="11.125" style="11" customWidth="1"/>
-    <col min="5374" max="5374" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="5375" max="5375" width="21.625" style="11" customWidth="1"/>
-    <col min="5376" max="5376" width="6.25" style="11" customWidth="1"/>
-    <col min="5377" max="5377" width="12.125" style="11" customWidth="1"/>
-    <col min="5378" max="5378" width="20.125" style="11" customWidth="1"/>
-    <col min="5379" max="5379" width="26.75" style="11" customWidth="1"/>
-    <col min="5380" max="5380" width="13.375" style="11" customWidth="1"/>
-    <col min="5381" max="5381" width="17" style="11" customWidth="1"/>
-    <col min="5382" max="5382" width="19.125" style="11" customWidth="1"/>
-    <col min="5383" max="5384" width="5.875" style="11" customWidth="1"/>
-    <col min="5385" max="5385" width="6.625" style="11" customWidth="1"/>
-    <col min="5386" max="5386" width="8.125" style="11" customWidth="1"/>
-    <col min="5387" max="5387" width="10.125" style="11" customWidth="1"/>
-    <col min="5388" max="5388" width="7.25" style="11" customWidth="1"/>
-    <col min="5389" max="5389" width="11.875" style="11" customWidth="1"/>
-    <col min="5390" max="5390" width="2.125" style="11" customWidth="1"/>
-    <col min="5391" max="5392" width="12.5" style="11" customWidth="1"/>
-    <col min="5393" max="5626" width="9" style="11"/>
-    <col min="5627" max="5627" width="6.875" style="11" customWidth="1"/>
-    <col min="5628" max="5628" width="10.125" style="11" customWidth="1"/>
-    <col min="5629" max="5629" width="11.125" style="11" customWidth="1"/>
-    <col min="5630" max="5630" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="5631" max="5631" width="21.625" style="11" customWidth="1"/>
-    <col min="5632" max="5632" width="6.25" style="11" customWidth="1"/>
-    <col min="5633" max="5633" width="12.125" style="11" customWidth="1"/>
-    <col min="5634" max="5634" width="20.125" style="11" customWidth="1"/>
-    <col min="5635" max="5635" width="26.75" style="11" customWidth="1"/>
-    <col min="5636" max="5636" width="13.375" style="11" customWidth="1"/>
-    <col min="5637" max="5637" width="17" style="11" customWidth="1"/>
-    <col min="5638" max="5638" width="19.125" style="11" customWidth="1"/>
-    <col min="5639" max="5640" width="5.875" style="11" customWidth="1"/>
-    <col min="5641" max="5641" width="6.625" style="11" customWidth="1"/>
-    <col min="5642" max="5642" width="8.125" style="11" customWidth="1"/>
-    <col min="5643" max="5643" width="10.125" style="11" customWidth="1"/>
-    <col min="5644" max="5644" width="7.25" style="11" customWidth="1"/>
-    <col min="5645" max="5645" width="11.875" style="11" customWidth="1"/>
-    <col min="5646" max="5646" width="2.125" style="11" customWidth="1"/>
-    <col min="5647" max="5648" width="12.5" style="11" customWidth="1"/>
-    <col min="5649" max="5882" width="9" style="11"/>
-    <col min="5883" max="5883" width="6.875" style="11" customWidth="1"/>
-    <col min="5884" max="5884" width="10.125" style="11" customWidth="1"/>
-    <col min="5885" max="5885" width="11.125" style="11" customWidth="1"/>
-    <col min="5886" max="5886" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="5887" max="5887" width="21.625" style="11" customWidth="1"/>
-    <col min="5888" max="5888" width="6.25" style="11" customWidth="1"/>
-    <col min="5889" max="5889" width="12.125" style="11" customWidth="1"/>
-    <col min="5890" max="5890" width="20.125" style="11" customWidth="1"/>
-    <col min="5891" max="5891" width="26.75" style="11" customWidth="1"/>
-    <col min="5892" max="5892" width="13.375" style="11" customWidth="1"/>
-    <col min="5893" max="5893" width="17" style="11" customWidth="1"/>
-    <col min="5894" max="5894" width="19.125" style="11" customWidth="1"/>
-    <col min="5895" max="5896" width="5.875" style="11" customWidth="1"/>
-    <col min="5897" max="5897" width="6.625" style="11" customWidth="1"/>
-    <col min="5898" max="5898" width="8.125" style="11" customWidth="1"/>
-    <col min="5899" max="5899" width="10.125" style="11" customWidth="1"/>
-    <col min="5900" max="5900" width="7.25" style="11" customWidth="1"/>
-    <col min="5901" max="5901" width="11.875" style="11" customWidth="1"/>
-    <col min="5902" max="5902" width="2.125" style="11" customWidth="1"/>
-    <col min="5903" max="5904" width="12.5" style="11" customWidth="1"/>
-    <col min="5905" max="6138" width="9" style="11"/>
-    <col min="6139" max="6139" width="6.875" style="11" customWidth="1"/>
-    <col min="6140" max="6140" width="10.125" style="11" customWidth="1"/>
-    <col min="6141" max="6141" width="11.125" style="11" customWidth="1"/>
-    <col min="6142" max="6142" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="6143" max="6143" width="21.625" style="11" customWidth="1"/>
-    <col min="6144" max="6144" width="6.25" style="11" customWidth="1"/>
-    <col min="6145" max="6145" width="12.125" style="11" customWidth="1"/>
-    <col min="6146" max="6146" width="20.125" style="11" customWidth="1"/>
-    <col min="6147" max="6147" width="26.75" style="11" customWidth="1"/>
-    <col min="6148" max="6148" width="13.375" style="11" customWidth="1"/>
-    <col min="6149" max="6149" width="17" style="11" customWidth="1"/>
-    <col min="6150" max="6150" width="19.125" style="11" customWidth="1"/>
-    <col min="6151" max="6152" width="5.875" style="11" customWidth="1"/>
-    <col min="6153" max="6153" width="6.625" style="11" customWidth="1"/>
-    <col min="6154" max="6154" width="8.125" style="11" customWidth="1"/>
-    <col min="6155" max="6155" width="10.125" style="11" customWidth="1"/>
-    <col min="6156" max="6156" width="7.25" style="11" customWidth="1"/>
-    <col min="6157" max="6157" width="11.875" style="11" customWidth="1"/>
-    <col min="6158" max="6158" width="2.125" style="11" customWidth="1"/>
-    <col min="6159" max="6160" width="12.5" style="11" customWidth="1"/>
-    <col min="6161" max="6394" width="9" style="11"/>
-    <col min="6395" max="6395" width="6.875" style="11" customWidth="1"/>
-    <col min="6396" max="6396" width="10.125" style="11" customWidth="1"/>
-    <col min="6397" max="6397" width="11.125" style="11" customWidth="1"/>
-    <col min="6398" max="6398" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="6399" max="6399" width="21.625" style="11" customWidth="1"/>
-    <col min="6400" max="6400" width="6.25" style="11" customWidth="1"/>
-    <col min="6401" max="6401" width="12.125" style="11" customWidth="1"/>
-    <col min="6402" max="6402" width="20.125" style="11" customWidth="1"/>
-    <col min="6403" max="6403" width="26.75" style="11" customWidth="1"/>
-    <col min="6404" max="6404" width="13.375" style="11" customWidth="1"/>
-    <col min="6405" max="6405" width="17" style="11" customWidth="1"/>
-    <col min="6406" max="6406" width="19.125" style="11" customWidth="1"/>
-    <col min="6407" max="6408" width="5.875" style="11" customWidth="1"/>
-    <col min="6409" max="6409" width="6.625" style="11" customWidth="1"/>
-    <col min="6410" max="6410" width="8.125" style="11" customWidth="1"/>
-    <col min="6411" max="6411" width="10.125" style="11" customWidth="1"/>
-    <col min="6412" max="6412" width="7.25" style="11" customWidth="1"/>
-    <col min="6413" max="6413" width="11.875" style="11" customWidth="1"/>
-    <col min="6414" max="6414" width="2.125" style="11" customWidth="1"/>
-    <col min="6415" max="6416" width="12.5" style="11" customWidth="1"/>
-    <col min="6417" max="6650" width="9" style="11"/>
-    <col min="6651" max="6651" width="6.875" style="11" customWidth="1"/>
-    <col min="6652" max="6652" width="10.125" style="11" customWidth="1"/>
-    <col min="6653" max="6653" width="11.125" style="11" customWidth="1"/>
-    <col min="6654" max="6654" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="6655" max="6655" width="21.625" style="11" customWidth="1"/>
-    <col min="6656" max="6656" width="6.25" style="11" customWidth="1"/>
-    <col min="6657" max="6657" width="12.125" style="11" customWidth="1"/>
-    <col min="6658" max="6658" width="20.125" style="11" customWidth="1"/>
-    <col min="6659" max="6659" width="26.75" style="11" customWidth="1"/>
-    <col min="6660" max="6660" width="13.375" style="11" customWidth="1"/>
-    <col min="6661" max="6661" width="17" style="11" customWidth="1"/>
-    <col min="6662" max="6662" width="19.125" style="11" customWidth="1"/>
-    <col min="6663" max="6664" width="5.875" style="11" customWidth="1"/>
-    <col min="6665" max="6665" width="6.625" style="11" customWidth="1"/>
-    <col min="6666" max="6666" width="8.125" style="11" customWidth="1"/>
-    <col min="6667" max="6667" width="10.125" style="11" customWidth="1"/>
-    <col min="6668" max="6668" width="7.25" style="11" customWidth="1"/>
-    <col min="6669" max="6669" width="11.875" style="11" customWidth="1"/>
-    <col min="6670" max="6670" width="2.125" style="11" customWidth="1"/>
-    <col min="6671" max="6672" width="12.5" style="11" customWidth="1"/>
-    <col min="6673" max="6906" width="9" style="11"/>
-    <col min="6907" max="6907" width="6.875" style="11" customWidth="1"/>
-    <col min="6908" max="6908" width="10.125" style="11" customWidth="1"/>
-    <col min="6909" max="6909" width="11.125" style="11" customWidth="1"/>
-    <col min="6910" max="6910" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="6911" max="6911" width="21.625" style="11" customWidth="1"/>
-    <col min="6912" max="6912" width="6.25" style="11" customWidth="1"/>
-    <col min="6913" max="6913" width="12.125" style="11" customWidth="1"/>
-    <col min="6914" max="6914" width="20.125" style="11" customWidth="1"/>
-    <col min="6915" max="6915" width="26.75" style="11" customWidth="1"/>
-    <col min="6916" max="6916" width="13.375" style="11" customWidth="1"/>
-    <col min="6917" max="6917" width="17" style="11" customWidth="1"/>
-    <col min="6918" max="6918" width="19.125" style="11" customWidth="1"/>
-    <col min="6919" max="6920" width="5.875" style="11" customWidth="1"/>
-    <col min="6921" max="6921" width="6.625" style="11" customWidth="1"/>
-    <col min="6922" max="6922" width="8.125" style="11" customWidth="1"/>
-    <col min="6923" max="6923" width="10.125" style="11" customWidth="1"/>
-    <col min="6924" max="6924" width="7.25" style="11" customWidth="1"/>
-    <col min="6925" max="6925" width="11.875" style="11" customWidth="1"/>
-    <col min="6926" max="6926" width="2.125" style="11" customWidth="1"/>
-    <col min="6927" max="6928" width="12.5" style="11" customWidth="1"/>
-    <col min="6929" max="7162" width="9" style="11"/>
-    <col min="7163" max="7163" width="6.875" style="11" customWidth="1"/>
-    <col min="7164" max="7164" width="10.125" style="11" customWidth="1"/>
-    <col min="7165" max="7165" width="11.125" style="11" customWidth="1"/>
-    <col min="7166" max="7166" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="7167" max="7167" width="21.625" style="11" customWidth="1"/>
-    <col min="7168" max="7168" width="6.25" style="11" customWidth="1"/>
-    <col min="7169" max="7169" width="12.125" style="11" customWidth="1"/>
-    <col min="7170" max="7170" width="20.125" style="11" customWidth="1"/>
-    <col min="7171" max="7171" width="26.75" style="11" customWidth="1"/>
-    <col min="7172" max="7172" width="13.375" style="11" customWidth="1"/>
-    <col min="7173" max="7173" width="17" style="11" customWidth="1"/>
-    <col min="7174" max="7174" width="19.125" style="11" customWidth="1"/>
-    <col min="7175" max="7176" width="5.875" style="11" customWidth="1"/>
-    <col min="7177" max="7177" width="6.625" style="11" customWidth="1"/>
-    <col min="7178" max="7178" width="8.125" style="11" customWidth="1"/>
-    <col min="7179" max="7179" width="10.125" style="11" customWidth="1"/>
-    <col min="7180" max="7180" width="7.25" style="11" customWidth="1"/>
-    <col min="7181" max="7181" width="11.875" style="11" customWidth="1"/>
-    <col min="7182" max="7182" width="2.125" style="11" customWidth="1"/>
-    <col min="7183" max="7184" width="12.5" style="11" customWidth="1"/>
-    <col min="7185" max="7418" width="9" style="11"/>
-    <col min="7419" max="7419" width="6.875" style="11" customWidth="1"/>
-    <col min="7420" max="7420" width="10.125" style="11" customWidth="1"/>
-    <col min="7421" max="7421" width="11.125" style="11" customWidth="1"/>
-    <col min="7422" max="7422" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="7423" max="7423" width="21.625" style="11" customWidth="1"/>
-    <col min="7424" max="7424" width="6.25" style="11" customWidth="1"/>
-    <col min="7425" max="7425" width="12.125" style="11" customWidth="1"/>
-    <col min="7426" max="7426" width="20.125" style="11" customWidth="1"/>
-    <col min="7427" max="7427" width="26.75" style="11" customWidth="1"/>
-    <col min="7428" max="7428" width="13.375" style="11" customWidth="1"/>
-    <col min="7429" max="7429" width="17" style="11" customWidth="1"/>
-    <col min="7430" max="7430" width="19.125" style="11" customWidth="1"/>
-    <col min="7431" max="7432" width="5.875" style="11" customWidth="1"/>
-    <col min="7433" max="7433" width="6.625" style="11" customWidth="1"/>
-    <col min="7434" max="7434" width="8.125" style="11" customWidth="1"/>
-    <col min="7435" max="7435" width="10.125" style="11" customWidth="1"/>
-    <col min="7436" max="7436" width="7.25" style="11" customWidth="1"/>
-    <col min="7437" max="7437" width="11.875" style="11" customWidth="1"/>
-    <col min="7438" max="7438" width="2.125" style="11" customWidth="1"/>
-    <col min="7439" max="7440" width="12.5" style="11" customWidth="1"/>
-    <col min="7441" max="7674" width="9" style="11"/>
-    <col min="7675" max="7675" width="6.875" style="11" customWidth="1"/>
-    <col min="7676" max="7676" width="10.125" style="11" customWidth="1"/>
-    <col min="7677" max="7677" width="11.125" style="11" customWidth="1"/>
-    <col min="7678" max="7678" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="7679" max="7679" width="21.625" style="11" customWidth="1"/>
-    <col min="7680" max="7680" width="6.25" style="11" customWidth="1"/>
-    <col min="7681" max="7681" width="12.125" style="11" customWidth="1"/>
-    <col min="7682" max="7682" width="20.125" style="11" customWidth="1"/>
-    <col min="7683" max="7683" width="26.75" style="11" customWidth="1"/>
-    <col min="7684" max="7684" width="13.375" style="11" customWidth="1"/>
-    <col min="7685" max="7685" width="17" style="11" customWidth="1"/>
-    <col min="7686" max="7686" width="19.125" style="11" customWidth="1"/>
-    <col min="7687" max="7688" width="5.875" style="11" customWidth="1"/>
-    <col min="7689" max="7689" width="6.625" style="11" customWidth="1"/>
-    <col min="7690" max="7690" width="8.125" style="11" customWidth="1"/>
-    <col min="7691" max="7691" width="10.125" style="11" customWidth="1"/>
-    <col min="7692" max="7692" width="7.25" style="11" customWidth="1"/>
-    <col min="7693" max="7693" width="11.875" style="11" customWidth="1"/>
-    <col min="7694" max="7694" width="2.125" style="11" customWidth="1"/>
-    <col min="7695" max="7696" width="12.5" style="11" customWidth="1"/>
-    <col min="7697" max="7930" width="9" style="11"/>
-    <col min="7931" max="7931" width="6.875" style="11" customWidth="1"/>
-    <col min="7932" max="7932" width="10.125" style="11" customWidth="1"/>
-    <col min="7933" max="7933" width="11.125" style="11" customWidth="1"/>
-    <col min="7934" max="7934" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="7935" max="7935" width="21.625" style="11" customWidth="1"/>
-    <col min="7936" max="7936" width="6.25" style="11" customWidth="1"/>
-    <col min="7937" max="7937" width="12.125" style="11" customWidth="1"/>
-    <col min="7938" max="7938" width="20.125" style="11" customWidth="1"/>
-    <col min="7939" max="7939" width="26.75" style="11" customWidth="1"/>
-    <col min="7940" max="7940" width="13.375" style="11" customWidth="1"/>
-    <col min="7941" max="7941" width="17" style="11" customWidth="1"/>
-    <col min="7942" max="7942" width="19.125" style="11" customWidth="1"/>
-    <col min="7943" max="7944" width="5.875" style="11" customWidth="1"/>
-    <col min="7945" max="7945" width="6.625" style="11" customWidth="1"/>
-    <col min="7946" max="7946" width="8.125" style="11" customWidth="1"/>
-    <col min="7947" max="7947" width="10.125" style="11" customWidth="1"/>
-    <col min="7948" max="7948" width="7.25" style="11" customWidth="1"/>
-    <col min="7949" max="7949" width="11.875" style="11" customWidth="1"/>
-    <col min="7950" max="7950" width="2.125" style="11" customWidth="1"/>
-    <col min="7951" max="7952" width="12.5" style="11" customWidth="1"/>
-    <col min="7953" max="8186" width="9" style="11"/>
-    <col min="8187" max="8187" width="6.875" style="11" customWidth="1"/>
-    <col min="8188" max="8188" width="10.125" style="11" customWidth="1"/>
-    <col min="8189" max="8189" width="11.125" style="11" customWidth="1"/>
-    <col min="8190" max="8190" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="8191" max="8191" width="21.625" style="11" customWidth="1"/>
-    <col min="8192" max="8192" width="6.25" style="11" customWidth="1"/>
-    <col min="8193" max="8193" width="12.125" style="11" customWidth="1"/>
-    <col min="8194" max="8194" width="20.125" style="11" customWidth="1"/>
-    <col min="8195" max="8195" width="26.75" style="11" customWidth="1"/>
-    <col min="8196" max="8196" width="13.375" style="11" customWidth="1"/>
-    <col min="8197" max="8197" width="17" style="11" customWidth="1"/>
-    <col min="8198" max="8198" width="19.125" style="11" customWidth="1"/>
-    <col min="8199" max="8200" width="5.875" style="11" customWidth="1"/>
-    <col min="8201" max="8201" width="6.625" style="11" customWidth="1"/>
-    <col min="8202" max="8202" width="8.125" style="11" customWidth="1"/>
-    <col min="8203" max="8203" width="10.125" style="11" customWidth="1"/>
-    <col min="8204" max="8204" width="7.25" style="11" customWidth="1"/>
-    <col min="8205" max="8205" width="11.875" style="11" customWidth="1"/>
-    <col min="8206" max="8206" width="2.125" style="11" customWidth="1"/>
-    <col min="8207" max="8208" width="12.5" style="11" customWidth="1"/>
-    <col min="8209" max="8442" width="9" style="11"/>
-    <col min="8443" max="8443" width="6.875" style="11" customWidth="1"/>
-    <col min="8444" max="8444" width="10.125" style="11" customWidth="1"/>
-    <col min="8445" max="8445" width="11.125" style="11" customWidth="1"/>
-    <col min="8446" max="8446" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="8447" max="8447" width="21.625" style="11" customWidth="1"/>
-    <col min="8448" max="8448" width="6.25" style="11" customWidth="1"/>
-    <col min="8449" max="8449" width="12.125" style="11" customWidth="1"/>
-    <col min="8450" max="8450" width="20.125" style="11" customWidth="1"/>
-    <col min="8451" max="8451" width="26.75" style="11" customWidth="1"/>
-    <col min="8452" max="8452" width="13.375" style="11" customWidth="1"/>
-    <col min="8453" max="8453" width="17" style="11" customWidth="1"/>
-    <col min="8454" max="8454" width="19.125" style="11" customWidth="1"/>
-    <col min="8455" max="8456" width="5.875" style="11" customWidth="1"/>
-    <col min="8457" max="8457" width="6.625" style="11" customWidth="1"/>
-    <col min="8458" max="8458" width="8.125" style="11" customWidth="1"/>
-    <col min="8459" max="8459" width="10.125" style="11" customWidth="1"/>
-    <col min="8460" max="8460" width="7.25" style="11" customWidth="1"/>
-    <col min="8461" max="8461" width="11.875" style="11" customWidth="1"/>
-    <col min="8462" max="8462" width="2.125" style="11" customWidth="1"/>
-    <col min="8463" max="8464" width="12.5" style="11" customWidth="1"/>
-    <col min="8465" max="8698" width="9" style="11"/>
-    <col min="8699" max="8699" width="6.875" style="11" customWidth="1"/>
-    <col min="8700" max="8700" width="10.125" style="11" customWidth="1"/>
-    <col min="8701" max="8701" width="11.125" style="11" customWidth="1"/>
-    <col min="8702" max="8702" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="8703" max="8703" width="21.625" style="11" customWidth="1"/>
-    <col min="8704" max="8704" width="6.25" style="11" customWidth="1"/>
-    <col min="8705" max="8705" width="12.125" style="11" customWidth="1"/>
-    <col min="8706" max="8706" width="20.125" style="11" customWidth="1"/>
-    <col min="8707" max="8707" width="26.75" style="11" customWidth="1"/>
-    <col min="8708" max="8708" width="13.375" style="11" customWidth="1"/>
-    <col min="8709" max="8709" width="17" style="11" customWidth="1"/>
-    <col min="8710" max="8710" width="19.125" style="11" customWidth="1"/>
-    <col min="8711" max="8712" width="5.875" style="11" customWidth="1"/>
-    <col min="8713" max="8713" width="6.625" style="11" customWidth="1"/>
-    <col min="8714" max="8714" width="8.125" style="11" customWidth="1"/>
-    <col min="8715" max="8715" width="10.125" style="11" customWidth="1"/>
-    <col min="8716" max="8716" width="7.25" style="11" customWidth="1"/>
-    <col min="8717" max="8717" width="11.875" style="11" customWidth="1"/>
-    <col min="8718" max="8718" width="2.125" style="11" customWidth="1"/>
-    <col min="8719" max="8720" width="12.5" style="11" customWidth="1"/>
-    <col min="8721" max="8954" width="9" style="11"/>
-    <col min="8955" max="8955" width="6.875" style="11" customWidth="1"/>
-    <col min="8956" max="8956" width="10.125" style="11" customWidth="1"/>
-    <col min="8957" max="8957" width="11.125" style="11" customWidth="1"/>
-    <col min="8958" max="8958" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="8959" max="8959" width="21.625" style="11" customWidth="1"/>
-    <col min="8960" max="8960" width="6.25" style="11" customWidth="1"/>
-    <col min="8961" max="8961" width="12.125" style="11" customWidth="1"/>
-    <col min="8962" max="8962" width="20.125" style="11" customWidth="1"/>
-    <col min="8963" max="8963" width="26.75" style="11" customWidth="1"/>
-    <col min="8964" max="8964" width="13.375" style="11" customWidth="1"/>
-    <col min="8965" max="8965" width="17" style="11" customWidth="1"/>
-    <col min="8966" max="8966" width="19.125" style="11" customWidth="1"/>
-    <col min="8967" max="8968" width="5.875" style="11" customWidth="1"/>
-    <col min="8969" max="8969" width="6.625" style="11" customWidth="1"/>
-    <col min="8970" max="8970" width="8.125" style="11" customWidth="1"/>
-    <col min="8971" max="8971" width="10.125" style="11" customWidth="1"/>
-    <col min="8972" max="8972" width="7.25" style="11" customWidth="1"/>
-    <col min="8973" max="8973" width="11.875" style="11" customWidth="1"/>
-    <col min="8974" max="8974" width="2.125" style="11" customWidth="1"/>
-    <col min="8975" max="8976" width="12.5" style="11" customWidth="1"/>
-    <col min="8977" max="9210" width="9" style="11"/>
-    <col min="9211" max="9211" width="6.875" style="11" customWidth="1"/>
-    <col min="9212" max="9212" width="10.125" style="11" customWidth="1"/>
-    <col min="9213" max="9213" width="11.125" style="11" customWidth="1"/>
-    <col min="9214" max="9214" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="9215" max="9215" width="21.625" style="11" customWidth="1"/>
-    <col min="9216" max="9216" width="6.25" style="11" customWidth="1"/>
-    <col min="9217" max="9217" width="12.125" style="11" customWidth="1"/>
-    <col min="9218" max="9218" width="20.125" style="11" customWidth="1"/>
-    <col min="9219" max="9219" width="26.75" style="11" customWidth="1"/>
-    <col min="9220" max="9220" width="13.375" style="11" customWidth="1"/>
-    <col min="9221" max="9221" width="17" style="11" customWidth="1"/>
-    <col min="9222" max="9222" width="19.125" style="11" customWidth="1"/>
-    <col min="9223" max="9224" width="5.875" style="11" customWidth="1"/>
-    <col min="9225" max="9225" width="6.625" style="11" customWidth="1"/>
-    <col min="9226" max="9226" width="8.125" style="11" customWidth="1"/>
-    <col min="9227" max="9227" width="10.125" style="11" customWidth="1"/>
-    <col min="9228" max="9228" width="7.25" style="11" customWidth="1"/>
-    <col min="9229" max="9229" width="11.875" style="11" customWidth="1"/>
-    <col min="9230" max="9230" width="2.125" style="11" customWidth="1"/>
-    <col min="9231" max="9232" width="12.5" style="11" customWidth="1"/>
-    <col min="9233" max="9466" width="9" style="11"/>
-    <col min="9467" max="9467" width="6.875" style="11" customWidth="1"/>
-    <col min="9468" max="9468" width="10.125" style="11" customWidth="1"/>
-    <col min="9469" max="9469" width="11.125" style="11" customWidth="1"/>
-    <col min="9470" max="9470" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="9471" max="9471" width="21.625" style="11" customWidth="1"/>
-    <col min="9472" max="9472" width="6.25" style="11" customWidth="1"/>
-    <col min="9473" max="9473" width="12.125" style="11" customWidth="1"/>
-    <col min="9474" max="9474" width="20.125" style="11" customWidth="1"/>
-    <col min="9475" max="9475" width="26.75" style="11" customWidth="1"/>
-    <col min="9476" max="9476" width="13.375" style="11" customWidth="1"/>
-    <col min="9477" max="9477" width="17" style="11" customWidth="1"/>
-    <col min="9478" max="9478" width="19.125" style="11" customWidth="1"/>
-    <col min="9479" max="9480" width="5.875" style="11" customWidth="1"/>
-    <col min="9481" max="9481" width="6.625" style="11" customWidth="1"/>
-    <col min="9482" max="9482" width="8.125" style="11" customWidth="1"/>
-    <col min="9483" max="9483" width="10.125" style="11" customWidth="1"/>
-    <col min="9484" max="9484" width="7.25" style="11" customWidth="1"/>
-    <col min="9485" max="9485" width="11.875" style="11" customWidth="1"/>
-    <col min="9486" max="9486" width="2.125" style="11" customWidth="1"/>
-    <col min="9487" max="9488" width="12.5" style="11" customWidth="1"/>
-    <col min="9489" max="9722" width="9" style="11"/>
-    <col min="9723" max="9723" width="6.875" style="11" customWidth="1"/>
-    <col min="9724" max="9724" width="10.125" style="11" customWidth="1"/>
-    <col min="9725" max="9725" width="11.125" style="11" customWidth="1"/>
-    <col min="9726" max="9726" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="9727" max="9727" width="21.625" style="11" customWidth="1"/>
-    <col min="9728" max="9728" width="6.25" style="11" customWidth="1"/>
-    <col min="9729" max="9729" width="12.125" style="11" customWidth="1"/>
-    <col min="9730" max="9730" width="20.125" style="11" customWidth="1"/>
-    <col min="9731" max="9731" width="26.75" style="11" customWidth="1"/>
-    <col min="9732" max="9732" width="13.375" style="11" customWidth="1"/>
-    <col min="9733" max="9733" width="17" style="11" customWidth="1"/>
-    <col min="9734" max="9734" width="19.125" style="11" customWidth="1"/>
-    <col min="9735" max="9736" width="5.875" style="11" customWidth="1"/>
-    <col min="9737" max="9737" width="6.625" style="11" customWidth="1"/>
-    <col min="9738" max="9738" width="8.125" style="11" customWidth="1"/>
-    <col min="9739" max="9739" width="10.125" style="11" customWidth="1"/>
-    <col min="9740" max="9740" width="7.25" style="11" customWidth="1"/>
-    <col min="9741" max="9741" width="11.875" style="11" customWidth="1"/>
-    <col min="9742" max="9742" width="2.125" style="11" customWidth="1"/>
-    <col min="9743" max="9744" width="12.5" style="11" customWidth="1"/>
-    <col min="9745" max="9978" width="9" style="11"/>
-    <col min="9979" max="9979" width="6.875" style="11" customWidth="1"/>
-    <col min="9980" max="9980" width="10.125" style="11" customWidth="1"/>
-    <col min="9981" max="9981" width="11.125" style="11" customWidth="1"/>
-    <col min="9982" max="9982" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="9983" max="9983" width="21.625" style="11" customWidth="1"/>
-    <col min="9984" max="9984" width="6.25" style="11" customWidth="1"/>
-    <col min="9985" max="9985" width="12.125" style="11" customWidth="1"/>
-    <col min="9986" max="9986" width="20.125" style="11" customWidth="1"/>
-    <col min="9987" max="9987" width="26.75" style="11" customWidth="1"/>
-    <col min="9988" max="9988" width="13.375" style="11" customWidth="1"/>
-    <col min="9989" max="9989" width="17" style="11" customWidth="1"/>
-    <col min="9990" max="9990" width="19.125" style="11" customWidth="1"/>
-    <col min="9991" max="9992" width="5.875" style="11" customWidth="1"/>
-    <col min="9993" max="9993" width="6.625" style="11" customWidth="1"/>
-    <col min="9994" max="9994" width="8.125" style="11" customWidth="1"/>
-    <col min="9995" max="9995" width="10.125" style="11" customWidth="1"/>
-    <col min="9996" max="9996" width="7.25" style="11" customWidth="1"/>
-    <col min="9997" max="9997" width="11.875" style="11" customWidth="1"/>
-    <col min="9998" max="9998" width="2.125" style="11" customWidth="1"/>
-    <col min="9999" max="10000" width="12.5" style="11" customWidth="1"/>
-    <col min="10001" max="10234" width="9" style="11"/>
-    <col min="10235" max="10235" width="6.875" style="11" customWidth="1"/>
-    <col min="10236" max="10236" width="10.125" style="11" customWidth="1"/>
-    <col min="10237" max="10237" width="11.125" style="11" customWidth="1"/>
-    <col min="10238" max="10238" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="10239" max="10239" width="21.625" style="11" customWidth="1"/>
-    <col min="10240" max="10240" width="6.25" style="11" customWidth="1"/>
-    <col min="10241" max="10241" width="12.125" style="11" customWidth="1"/>
-    <col min="10242" max="10242" width="20.125" style="11" customWidth="1"/>
-    <col min="10243" max="10243" width="26.75" style="11" customWidth="1"/>
-    <col min="10244" max="10244" width="13.375" style="11" customWidth="1"/>
-    <col min="10245" max="10245" width="17" style="11" customWidth="1"/>
-    <col min="10246" max="10246" width="19.125" style="11" customWidth="1"/>
-    <col min="10247" max="10248" width="5.875" style="11" customWidth="1"/>
-    <col min="10249" max="10249" width="6.625" style="11" customWidth="1"/>
-    <col min="10250" max="10250" width="8.125" style="11" customWidth="1"/>
-    <col min="10251" max="10251" width="10.125" style="11" customWidth="1"/>
-    <col min="10252" max="10252" width="7.25" style="11" customWidth="1"/>
-    <col min="10253" max="10253" width="11.875" style="11" customWidth="1"/>
-    <col min="10254" max="10254" width="2.125" style="11" customWidth="1"/>
-    <col min="10255" max="10256" width="12.5" style="11" customWidth="1"/>
-    <col min="10257" max="10490" width="9" style="11"/>
-    <col min="10491" max="10491" width="6.875" style="11" customWidth="1"/>
-    <col min="10492" max="10492" width="10.125" style="11" customWidth="1"/>
-    <col min="10493" max="10493" width="11.125" style="11" customWidth="1"/>
-    <col min="10494" max="10494" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="10495" max="10495" width="21.625" style="11" customWidth="1"/>
-    <col min="10496" max="10496" width="6.25" style="11" customWidth="1"/>
-    <col min="10497" max="10497" width="12.125" style="11" customWidth="1"/>
-    <col min="10498" max="10498" width="20.125" style="11" customWidth="1"/>
-    <col min="10499" max="10499" width="26.75" style="11" customWidth="1"/>
-    <col min="10500" max="10500" width="13.375" style="11" customWidth="1"/>
-    <col min="10501" max="10501" width="17" style="11" customWidth="1"/>
-    <col min="10502" max="10502" width="19.125" style="11" customWidth="1"/>
-    <col min="10503" max="10504" width="5.875" style="11" customWidth="1"/>
-    <col min="10505" max="10505" width="6.625" style="11" customWidth="1"/>
-    <col min="10506" max="10506" width="8.125" style="11" customWidth="1"/>
-    <col min="10507" max="10507" width="10.125" style="11" customWidth="1"/>
-    <col min="10508" max="10508" width="7.25" style="11" customWidth="1"/>
-    <col min="10509" max="10509" width="11.875" style="11" customWidth="1"/>
-    <col min="10510" max="10510" width="2.125" style="11" customWidth="1"/>
-    <col min="10511" max="10512" width="12.5" style="11" customWidth="1"/>
-    <col min="10513" max="10746" width="9" style="11"/>
-    <col min="10747" max="10747" width="6.875" style="11" customWidth="1"/>
-    <col min="10748" max="10748" width="10.125" style="11" customWidth="1"/>
-    <col min="10749" max="10749" width="11.125" style="11" customWidth="1"/>
-    <col min="10750" max="10750" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="10751" max="10751" width="21.625" style="11" customWidth="1"/>
-    <col min="10752" max="10752" width="6.25" style="11" customWidth="1"/>
-    <col min="10753" max="10753" width="12.125" style="11" customWidth="1"/>
-    <col min="10754" max="10754" width="20.125" style="11" customWidth="1"/>
-    <col min="10755" max="10755" width="26.75" style="11" customWidth="1"/>
-    <col min="10756" max="10756" width="13.375" style="11" customWidth="1"/>
-    <col min="10757" max="10757" width="17" style="11" customWidth="1"/>
-    <col min="10758" max="10758" width="19.125" style="11" customWidth="1"/>
-    <col min="10759" max="10760" width="5.875" style="11" customWidth="1"/>
-    <col min="10761" max="10761" width="6.625" style="11" customWidth="1"/>
-    <col min="10762" max="10762" width="8.125" style="11" customWidth="1"/>
-    <col min="10763" max="10763" width="10.125" style="11" customWidth="1"/>
-    <col min="10764" max="10764" width="7.25" style="11" customWidth="1"/>
-    <col min="10765" max="10765" width="11.875" style="11" customWidth="1"/>
-    <col min="10766" max="10766" width="2.125" style="11" customWidth="1"/>
-    <col min="10767" max="10768" width="12.5" style="11" customWidth="1"/>
-    <col min="10769" max="11002" width="9" style="11"/>
-    <col min="11003" max="11003" width="6.875" style="11" customWidth="1"/>
-    <col min="11004" max="11004" width="10.125" style="11" customWidth="1"/>
-    <col min="11005" max="11005" width="11.125" style="11" customWidth="1"/>
-    <col min="11006" max="11006" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="11007" max="11007" width="21.625" style="11" customWidth="1"/>
-    <col min="11008" max="11008" width="6.25" style="11" customWidth="1"/>
-    <col min="11009" max="11009" width="12.125" style="11" customWidth="1"/>
-    <col min="11010" max="11010" width="20.125" style="11" customWidth="1"/>
-    <col min="11011" max="11011" width="26.75" style="11" customWidth="1"/>
-    <col min="11012" max="11012" width="13.375" style="11" customWidth="1"/>
-    <col min="11013" max="11013" width="17" style="11" customWidth="1"/>
-    <col min="11014" max="11014" width="19.125" style="11" customWidth="1"/>
-    <col min="11015" max="11016" width="5.875" style="11" customWidth="1"/>
-    <col min="11017" max="11017" width="6.625" style="11" customWidth="1"/>
-    <col min="11018" max="11018" width="8.125" style="11" customWidth="1"/>
-    <col min="11019" max="11019" width="10.125" style="11" customWidth="1"/>
-    <col min="11020" max="11020" width="7.25" style="11" customWidth="1"/>
-    <col min="11021" max="11021" width="11.875" style="11" customWidth="1"/>
-    <col min="11022" max="11022" width="2.125" style="11" customWidth="1"/>
-    <col min="11023" max="11024" width="12.5" style="11" customWidth="1"/>
-    <col min="11025" max="11258" width="9" style="11"/>
-    <col min="11259" max="11259" width="6.875" style="11" customWidth="1"/>
-    <col min="11260" max="11260" width="10.125" style="11" customWidth="1"/>
-    <col min="11261" max="11261" width="11.125" style="11" customWidth="1"/>
-    <col min="11262" max="11262" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="11263" max="11263" width="21.625" style="11" customWidth="1"/>
-    <col min="11264" max="11264" width="6.25" style="11" customWidth="1"/>
-    <col min="11265" max="11265" width="12.125" style="11" customWidth="1"/>
-    <col min="11266" max="11266" width="20.125" style="11" customWidth="1"/>
-    <col min="11267" max="11267" width="26.75" style="11" customWidth="1"/>
-    <col min="11268" max="11268" width="13.375" style="11" customWidth="1"/>
-    <col min="11269" max="11269" width="17" style="11" customWidth="1"/>
-    <col min="11270" max="11270" width="19.125" style="11" customWidth="1"/>
-    <col min="11271" max="11272" width="5.875" style="11" customWidth="1"/>
-    <col min="11273" max="11273" width="6.625" style="11" customWidth="1"/>
-    <col min="11274" max="11274" width="8.125" style="11" customWidth="1"/>
-    <col min="11275" max="11275" width="10.125" style="11" customWidth="1"/>
-    <col min="11276" max="11276" width="7.25" style="11" customWidth="1"/>
-    <col min="11277" max="11277" width="11.875" style="11" customWidth="1"/>
-    <col min="11278" max="11278" width="2.125" style="11" customWidth="1"/>
-    <col min="11279" max="11280" width="12.5" style="11" customWidth="1"/>
-    <col min="11281" max="11514" width="9" style="11"/>
-    <col min="11515" max="11515" width="6.875" style="11" customWidth="1"/>
-    <col min="11516" max="11516" width="10.125" style="11" customWidth="1"/>
-    <col min="11517" max="11517" width="11.125" style="11" customWidth="1"/>
-    <col min="11518" max="11518" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="11519" max="11519" width="21.625" style="11" customWidth="1"/>
-    <col min="11520" max="11520" width="6.25" style="11" customWidth="1"/>
-    <col min="11521" max="11521" width="12.125" style="11" customWidth="1"/>
-    <col min="11522" max="11522" width="20.125" style="11" customWidth="1"/>
-    <col min="11523" max="11523" width="26.75" style="11" customWidth="1"/>
-    <col min="11524" max="11524" width="13.375" style="11" customWidth="1"/>
-    <col min="11525" max="11525" width="17" style="11" customWidth="1"/>
-    <col min="11526" max="11526" width="19.125" style="11" customWidth="1"/>
-    <col min="11527" max="11528" width="5.875" style="11" customWidth="1"/>
-    <col min="11529" max="11529" width="6.625" style="11" customWidth="1"/>
-    <col min="11530" max="11530" width="8.125" style="11" customWidth="1"/>
-    <col min="11531" max="11531" width="10.125" style="11" customWidth="1"/>
-    <col min="11532" max="11532" width="7.25" style="11" customWidth="1"/>
-    <col min="11533" max="11533" width="11.875" style="11" customWidth="1"/>
-    <col min="11534" max="11534" width="2.125" style="11" customWidth="1"/>
-    <col min="11535" max="11536" width="12.5" style="11" customWidth="1"/>
-    <col min="11537" max="11770" width="9" style="11"/>
-    <col min="11771" max="11771" width="6.875" style="11" customWidth="1"/>
-    <col min="11772" max="11772" width="10.125" style="11" customWidth="1"/>
-    <col min="11773" max="11773" width="11.125" style="11" customWidth="1"/>
-    <col min="11774" max="11774" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="11775" max="11775" width="21.625" style="11" customWidth="1"/>
-    <col min="11776" max="11776" width="6.25" style="11" customWidth="1"/>
-    <col min="11777" max="11777" width="12.125" style="11" customWidth="1"/>
-    <col min="11778" max="11778" width="20.125" style="11" customWidth="1"/>
-    <col min="11779" max="11779" width="26.75" style="11" customWidth="1"/>
-    <col min="11780" max="11780" width="13.375" style="11" customWidth="1"/>
-    <col min="11781" max="11781" width="17" style="11" customWidth="1"/>
-    <col min="11782" max="11782" width="19.125" style="11" customWidth="1"/>
-    <col min="11783" max="11784" width="5.875" style="11" customWidth="1"/>
-    <col min="11785" max="11785" width="6.625" style="11" customWidth="1"/>
-    <col min="11786" max="11786" width="8.125" style="11" customWidth="1"/>
-    <col min="11787" max="11787" width="10.125" style="11" customWidth="1"/>
-    <col min="11788" max="11788" width="7.25" style="11" customWidth="1"/>
-    <col min="11789" max="11789" width="11.875" style="11" customWidth="1"/>
-    <col min="11790" max="11790" width="2.125" style="11" customWidth="1"/>
-    <col min="11791" max="11792" width="12.5" style="11" customWidth="1"/>
-    <col min="11793" max="12026" width="9" style="11"/>
-    <col min="12027" max="12027" width="6.875" style="11" customWidth="1"/>
-    <col min="12028" max="12028" width="10.125" style="11" customWidth="1"/>
-    <col min="12029" max="12029" width="11.125" style="11" customWidth="1"/>
-    <col min="12030" max="12030" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="12031" max="12031" width="21.625" style="11" customWidth="1"/>
-    <col min="12032" max="12032" width="6.25" style="11" customWidth="1"/>
-    <col min="12033" max="12033" width="12.125" style="11" customWidth="1"/>
-    <col min="12034" max="12034" width="20.125" style="11" customWidth="1"/>
-    <col min="12035" max="12035" width="26.75" style="11" customWidth="1"/>
-    <col min="12036" max="12036" width="13.375" style="11" customWidth="1"/>
-    <col min="12037" max="12037" width="17" style="11" customWidth="1"/>
-    <col min="12038" max="12038" width="19.125" style="11" customWidth="1"/>
-    <col min="12039" max="12040" width="5.875" style="11" customWidth="1"/>
-    <col min="12041" max="12041" width="6.625" style="11" customWidth="1"/>
-    <col min="12042" max="12042" width="8.125" style="11" customWidth="1"/>
-    <col min="12043" max="12043" width="10.125" style="11" customWidth="1"/>
-    <col min="12044" max="12044" width="7.25" style="11" customWidth="1"/>
-    <col min="12045" max="12045" width="11.875" style="11" customWidth="1"/>
-    <col min="12046" max="12046" width="2.125" style="11" customWidth="1"/>
-    <col min="12047" max="12048" width="12.5" style="11" customWidth="1"/>
-    <col min="12049" max="12282" width="9" style="11"/>
-    <col min="12283" max="12283" width="6.875" style="11" customWidth="1"/>
-    <col min="12284" max="12284" width="10.125" style="11" customWidth="1"/>
-    <col min="12285" max="12285" width="11.125" style="11" customWidth="1"/>
-    <col min="12286" max="12286" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="12287" max="12287" width="21.625" style="11" customWidth="1"/>
-    <col min="12288" max="12288" width="6.25" style="11" customWidth="1"/>
-    <col min="12289" max="12289" width="12.125" style="11" customWidth="1"/>
-    <col min="12290" max="12290" width="20.125" style="11" customWidth="1"/>
-    <col min="12291" max="12291" width="26.75" style="11" customWidth="1"/>
-    <col min="12292" max="12292" width="13.375" style="11" customWidth="1"/>
-    <col min="12293" max="12293" width="17" style="11" customWidth="1"/>
-    <col min="12294" max="12294" width="19.125" style="11" customWidth="1"/>
-    <col min="12295" max="12296" width="5.875" style="11" customWidth="1"/>
-    <col min="12297" max="12297" width="6.625" style="11" customWidth="1"/>
-    <col min="12298" max="12298" width="8.125" style="11" customWidth="1"/>
-    <col min="12299" max="12299" width="10.125" style="11" customWidth="1"/>
-    <col min="12300" max="12300" width="7.25" style="11" customWidth="1"/>
-    <col min="12301" max="12301" width="11.875" style="11" customWidth="1"/>
-    <col min="12302" max="12302" width="2.125" style="11" customWidth="1"/>
-    <col min="12303" max="12304" width="12.5" style="11" customWidth="1"/>
-    <col min="12305" max="12538" width="9" style="11"/>
-    <col min="12539" max="12539" width="6.875" style="11" customWidth="1"/>
-    <col min="12540" max="12540" width="10.125" style="11" customWidth="1"/>
-    <col min="12541" max="12541" width="11.125" style="11" customWidth="1"/>
-    <col min="12542" max="12542" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="12543" max="12543" width="21.625" style="11" customWidth="1"/>
-    <col min="12544" max="12544" width="6.25" style="11" customWidth="1"/>
-    <col min="12545" max="12545" width="12.125" style="11" customWidth="1"/>
-    <col min="12546" max="12546" width="20.125" style="11" customWidth="1"/>
-    <col min="12547" max="12547" width="26.75" style="11" customWidth="1"/>
-    <col min="12548" max="12548" width="13.375" style="11" customWidth="1"/>
-    <col min="12549" max="12549" width="17" style="11" customWidth="1"/>
-    <col min="12550" max="12550" width="19.125" style="11" customWidth="1"/>
-    <col min="12551" max="12552" width="5.875" style="11" customWidth="1"/>
-    <col min="12553" max="12553" width="6.625" style="11" customWidth="1"/>
-    <col min="12554" max="12554" width="8.125" style="11" customWidth="1"/>
-    <col min="12555" max="12555" width="10.125" style="11" customWidth="1"/>
-    <col min="12556" max="12556" width="7.25" style="11" customWidth="1"/>
-    <col min="12557" max="12557" width="11.875" style="11" customWidth="1"/>
-    <col min="12558" max="12558" width="2.125" style="11" customWidth="1"/>
-    <col min="12559" max="12560" width="12.5" style="11" customWidth="1"/>
-    <col min="12561" max="12794" width="9" style="11"/>
-    <col min="12795" max="12795" width="6.875" style="11" customWidth="1"/>
-    <col min="12796" max="12796" width="10.125" style="11" customWidth="1"/>
-    <col min="12797" max="12797" width="11.125" style="11" customWidth="1"/>
-    <col min="12798" max="12798" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="12799" max="12799" width="21.625" style="11" customWidth="1"/>
-    <col min="12800" max="12800" width="6.25" style="11" customWidth="1"/>
-    <col min="12801" max="12801" width="12.125" style="11" customWidth="1"/>
-    <col min="12802" max="12802" width="20.125" style="11" customWidth="1"/>
-    <col min="12803" max="12803" width="26.75" style="11" customWidth="1"/>
-    <col min="12804" max="12804" width="13.375" style="11" customWidth="1"/>
-    <col min="12805" max="12805" width="17" style="11" customWidth="1"/>
-    <col min="12806" max="12806" width="19.125" style="11" customWidth="1"/>
-    <col min="12807" max="12808" width="5.875" style="11" customWidth="1"/>
-    <col min="12809" max="12809" width="6.625" style="11" customWidth="1"/>
-    <col min="12810" max="12810" width="8.125" style="11" customWidth="1"/>
-    <col min="12811" max="12811" width="10.125" style="11" customWidth="1"/>
-    <col min="12812" max="12812" width="7.25" style="11" customWidth="1"/>
-    <col min="12813" max="12813" width="11.875" style="11" customWidth="1"/>
-    <col min="12814" max="12814" width="2.125" style="11" customWidth="1"/>
-    <col min="12815" max="12816" width="12.5" style="11" customWidth="1"/>
-    <col min="12817" max="13050" width="9" style="11"/>
-    <col min="13051" max="13051" width="6.875" style="11" customWidth="1"/>
-    <col min="13052" max="13052" width="10.125" style="11" customWidth="1"/>
-    <col min="13053" max="13053" width="11.125" style="11" customWidth="1"/>
-    <col min="13054" max="13054" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="13055" max="13055" width="21.625" style="11" customWidth="1"/>
-    <col min="13056" max="13056" width="6.25" style="11" customWidth="1"/>
-    <col min="13057" max="13057" width="12.125" style="11" customWidth="1"/>
-    <col min="13058" max="13058" width="20.125" style="11" customWidth="1"/>
-    <col min="13059" max="13059" width="26.75" style="11" customWidth="1"/>
-    <col min="13060" max="13060" width="13.375" style="11" customWidth="1"/>
-    <col min="13061" max="13061" width="17" style="11" customWidth="1"/>
-    <col min="13062" max="13062" width="19.125" style="11" customWidth="1"/>
-    <col min="13063" max="13064" width="5.875" style="11" customWidth="1"/>
-    <col min="13065" max="13065" width="6.625" style="11" customWidth="1"/>
-    <col min="13066" max="13066" width="8.125" style="11" customWidth="1"/>
-    <col min="13067" max="13067" width="10.125" style="11" customWidth="1"/>
-    <col min="13068" max="13068" width="7.25" style="11" customWidth="1"/>
-    <col min="13069" max="13069" width="11.875" style="11" customWidth="1"/>
-    <col min="13070" max="13070" width="2.125" style="11" customWidth="1"/>
-    <col min="13071" max="13072" width="12.5" style="11" customWidth="1"/>
-    <col min="13073" max="13306" width="9" style="11"/>
-    <col min="13307" max="13307" width="6.875" style="11" customWidth="1"/>
-    <col min="13308" max="13308" width="10.125" style="11" customWidth="1"/>
-    <col min="13309" max="13309" width="11.125" style="11" customWidth="1"/>
-    <col min="13310" max="13310" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="13311" max="13311" width="21.625" style="11" customWidth="1"/>
-    <col min="13312" max="13312" width="6.25" style="11" customWidth="1"/>
-    <col min="13313" max="13313" width="12.125" style="11" customWidth="1"/>
-    <col min="13314" max="13314" width="20.125" style="11" customWidth="1"/>
-    <col min="13315" max="13315" width="26.75" style="11" customWidth="1"/>
-    <col min="13316" max="13316" width="13.375" style="11" customWidth="1"/>
-    <col min="13317" max="13317" width="17" style="11" customWidth="1"/>
-    <col min="13318" max="13318" width="19.125" style="11" customWidth="1"/>
-    <col min="13319" max="13320" width="5.875" style="11" customWidth="1"/>
-    <col min="13321" max="13321" width="6.625" style="11" customWidth="1"/>
-    <col min="13322" max="13322" width="8.125" style="11" customWidth="1"/>
-    <col min="13323" max="13323" width="10.125" style="11" customWidth="1"/>
-    <col min="13324" max="13324" width="7.25" style="11" customWidth="1"/>
-    <col min="13325" max="13325" width="11.875" style="11" customWidth="1"/>
-    <col min="13326" max="13326" width="2.125" style="11" customWidth="1"/>
-    <col min="13327" max="13328" width="12.5" style="11" customWidth="1"/>
-    <col min="13329" max="13562" width="9" style="11"/>
-    <col min="13563" max="13563" width="6.875" style="11" customWidth="1"/>
-    <col min="13564" max="13564" width="10.125" style="11" customWidth="1"/>
-    <col min="13565" max="13565" width="11.125" style="11" customWidth="1"/>
-    <col min="13566" max="13566" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="13567" max="13567" width="21.625" style="11" customWidth="1"/>
-    <col min="13568" max="13568" width="6.25" style="11" customWidth="1"/>
-    <col min="13569" max="13569" width="12.125" style="11" customWidth="1"/>
-    <col min="13570" max="13570" width="20.125" style="11" customWidth="1"/>
-    <col min="13571" max="13571" width="26.75" style="11" customWidth="1"/>
-    <col min="13572" max="13572" width="13.375" style="11" customWidth="1"/>
-    <col min="13573" max="13573" width="17" style="11" customWidth="1"/>
-    <col min="13574" max="13574" width="19.125" style="11" customWidth="1"/>
-    <col min="13575" max="13576" width="5.875" style="11" customWidth="1"/>
-    <col min="13577" max="13577" width="6.625" style="11" customWidth="1"/>
-    <col min="13578" max="13578" width="8.125" style="11" customWidth="1"/>
-    <col min="13579" max="13579" width="10.125" style="11" customWidth="1"/>
-    <col min="13580" max="13580" width="7.25" style="11" customWidth="1"/>
-    <col min="13581" max="13581" width="11.875" style="11" customWidth="1"/>
-    <col min="13582" max="13582" width="2.125" style="11" customWidth="1"/>
-    <col min="13583" max="13584" width="12.5" style="11" customWidth="1"/>
-    <col min="13585" max="13818" width="9" style="11"/>
-    <col min="13819" max="13819" width="6.875" style="11" customWidth="1"/>
-    <col min="13820" max="13820" width="10.125" style="11" customWidth="1"/>
-    <col min="13821" max="13821" width="11.125" style="11" customWidth="1"/>
-    <col min="13822" max="13822" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="13823" max="13823" width="21.625" style="11" customWidth="1"/>
-    <col min="13824" max="13824" width="6.25" style="11" customWidth="1"/>
-    <col min="13825" max="13825" width="12.125" style="11" customWidth="1"/>
-    <col min="13826" max="13826" width="20.125" style="11" customWidth="1"/>
-    <col min="13827" max="13827" width="26.75" style="11" customWidth="1"/>
-    <col min="13828" max="13828" width="13.375" style="11" customWidth="1"/>
-    <col min="13829" max="13829" width="17" style="11" customWidth="1"/>
-    <col min="13830" max="13830" width="19.125" style="11" customWidth="1"/>
-    <col min="13831" max="13832" width="5.875" style="11" customWidth="1"/>
-    <col min="13833" max="13833" width="6.625" style="11" customWidth="1"/>
-    <col min="13834" max="13834" width="8.125" style="11" customWidth="1"/>
-    <col min="13835" max="13835" width="10.125" style="11" customWidth="1"/>
-    <col min="13836" max="13836" width="7.25" style="11" customWidth="1"/>
-    <col min="13837" max="13837" width="11.875" style="11" customWidth="1"/>
-    <col min="13838" max="13838" width="2.125" style="11" customWidth="1"/>
-    <col min="13839" max="13840" width="12.5" style="11" customWidth="1"/>
-    <col min="13841" max="14074" width="9" style="11"/>
-    <col min="14075" max="14075" width="6.875" style="11" customWidth="1"/>
-    <col min="14076" max="14076" width="10.125" style="11" customWidth="1"/>
-    <col min="14077" max="14077" width="11.125" style="11" customWidth="1"/>
-    <col min="14078" max="14078" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="14079" max="14079" width="21.625" style="11" customWidth="1"/>
-    <col min="14080" max="14080" width="6.25" style="11" customWidth="1"/>
-    <col min="14081" max="14081" width="12.125" style="11" customWidth="1"/>
-    <col min="14082" max="14082" width="20.125" style="11" customWidth="1"/>
-    <col min="14083" max="14083" width="26.75" style="11" customWidth="1"/>
-    <col min="14084" max="14084" width="13.375" style="11" customWidth="1"/>
-    <col min="14085" max="14085" width="17" style="11" customWidth="1"/>
-    <col min="14086" max="14086" width="19.125" style="11" customWidth="1"/>
-    <col min="14087" max="14088" width="5.875" style="11" customWidth="1"/>
-    <col min="14089" max="14089" width="6.625" style="11" customWidth="1"/>
-    <col min="14090" max="14090" width="8.125" style="11" customWidth="1"/>
-    <col min="14091" max="14091" width="10.125" style="11" customWidth="1"/>
-    <col min="14092" max="14092" width="7.25" style="11" customWidth="1"/>
-    <col min="14093" max="14093" width="11.875" style="11" customWidth="1"/>
-    <col min="14094" max="14094" width="2.125" style="11" customWidth="1"/>
-    <col min="14095" max="14096" width="12.5" style="11" customWidth="1"/>
-    <col min="14097" max="14330" width="9" style="11"/>
-    <col min="14331" max="14331" width="6.875" style="11" customWidth="1"/>
-    <col min="14332" max="14332" width="10.125" style="11" customWidth="1"/>
-    <col min="14333" max="14333" width="11.125" style="11" customWidth="1"/>
-    <col min="14334" max="14334" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="14335" max="14335" width="21.625" style="11" customWidth="1"/>
-    <col min="14336" max="14336" width="6.25" style="11" customWidth="1"/>
-    <col min="14337" max="14337" width="12.125" style="11" customWidth="1"/>
-    <col min="14338" max="14338" width="20.125" style="11" customWidth="1"/>
-    <col min="14339" max="14339" width="26.75" style="11" customWidth="1"/>
-    <col min="14340" max="14340" width="13.375" style="11" customWidth="1"/>
-    <col min="14341" max="14341" width="17" style="11" customWidth="1"/>
-    <col min="14342" max="14342" width="19.125" style="11" customWidth="1"/>
-    <col min="14343" max="14344" width="5.875" style="11" customWidth="1"/>
-    <col min="14345" max="14345" width="6.625" style="11" customWidth="1"/>
-    <col min="14346" max="14346" width="8.125" style="11" customWidth="1"/>
-    <col min="14347" max="14347" width="10.125" style="11" customWidth="1"/>
-    <col min="14348" max="14348" width="7.25" style="11" customWidth="1"/>
-    <col min="14349" max="14349" width="11.875" style="11" customWidth="1"/>
-    <col min="14350" max="14350" width="2.125" style="11" customWidth="1"/>
-    <col min="14351" max="14352" width="12.5" style="11" customWidth="1"/>
-    <col min="14353" max="14586" width="9" style="11"/>
-    <col min="14587" max="14587" width="6.875" style="11" customWidth="1"/>
-    <col min="14588" max="14588" width="10.125" style="11" customWidth="1"/>
-    <col min="14589" max="14589" width="11.125" style="11" customWidth="1"/>
-    <col min="14590" max="14590" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="14591" max="14591" width="21.625" style="11" customWidth="1"/>
-    <col min="14592" max="14592" width="6.25" style="11" customWidth="1"/>
-    <col min="14593" max="14593" width="12.125" style="11" customWidth="1"/>
-    <col min="14594" max="14594" width="20.125" style="11" customWidth="1"/>
-    <col min="14595" max="14595" width="26.75" style="11" customWidth="1"/>
-    <col min="14596" max="14596" width="13.375" style="11" customWidth="1"/>
-    <col min="14597" max="14597" width="17" style="11" customWidth="1"/>
-    <col min="14598" max="14598" width="19.125" style="11" customWidth="1"/>
-    <col min="14599" max="14600" width="5.875" style="11" customWidth="1"/>
-    <col min="14601" max="14601" width="6.625" style="11" customWidth="1"/>
-    <col min="14602" max="14602" width="8.125" style="11" customWidth="1"/>
-    <col min="14603" max="14603" width="10.125" style="11" customWidth="1"/>
-    <col min="14604" max="14604" width="7.25" style="11" customWidth="1"/>
-    <col min="14605" max="14605" width="11.875" style="11" customWidth="1"/>
-    <col min="14606" max="14606" width="2.125" style="11" customWidth="1"/>
-    <col min="14607" max="14608" width="12.5" style="11" customWidth="1"/>
-    <col min="14609" max="14842" width="9" style="11"/>
-    <col min="14843" max="14843" width="6.875" style="11" customWidth="1"/>
-    <col min="14844" max="14844" width="10.125" style="11" customWidth="1"/>
-    <col min="14845" max="14845" width="11.125" style="11" customWidth="1"/>
-    <col min="14846" max="14846" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="14847" max="14847" width="21.625" style="11" customWidth="1"/>
-    <col min="14848" max="14848" width="6.25" style="11" customWidth="1"/>
-    <col min="14849" max="14849" width="12.125" style="11" customWidth="1"/>
-    <col min="14850" max="14850" width="20.125" style="11" customWidth="1"/>
-    <col min="14851" max="14851" width="26.75" style="11" customWidth="1"/>
-    <col min="14852" max="14852" width="13.375" style="11" customWidth="1"/>
-    <col min="14853" max="14853" width="17" style="11" customWidth="1"/>
-    <col min="14854" max="14854" width="19.125" style="11" customWidth="1"/>
-    <col min="14855" max="14856" width="5.875" style="11" customWidth="1"/>
-    <col min="14857" max="14857" width="6.625" style="11" customWidth="1"/>
-    <col min="14858" max="14858" width="8.125" style="11" customWidth="1"/>
-    <col min="14859" max="14859" width="10.125" style="11" customWidth="1"/>
-    <col min="14860" max="14860" width="7.25" style="11" customWidth="1"/>
-    <col min="14861" max="14861" width="11.875" style="11" customWidth="1"/>
-    <col min="14862" max="14862" width="2.125" style="11" customWidth="1"/>
-    <col min="14863" max="14864" width="12.5" style="11" customWidth="1"/>
-    <col min="14865" max="15098" width="9" style="11"/>
-    <col min="15099" max="15099" width="6.875" style="11" customWidth="1"/>
-    <col min="15100" max="15100" width="10.125" style="11" customWidth="1"/>
-    <col min="15101" max="15101" width="11.125" style="11" customWidth="1"/>
-    <col min="15102" max="15102" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="15103" max="15103" width="21.625" style="11" customWidth="1"/>
-    <col min="15104" max="15104" width="6.25" style="11" customWidth="1"/>
-    <col min="15105" max="15105" width="12.125" style="11" customWidth="1"/>
-    <col min="15106" max="15106" width="20.125" style="11" customWidth="1"/>
-    <col min="15107" max="15107" width="26.75" style="11" customWidth="1"/>
-    <col min="15108" max="15108" width="13.375" style="11" customWidth="1"/>
-    <col min="15109" max="15109" width="17" style="11" customWidth="1"/>
-    <col min="15110" max="15110" width="19.125" style="11" customWidth="1"/>
-    <col min="15111" max="15112" width="5.875" style="11" customWidth="1"/>
-    <col min="15113" max="15113" width="6.625" style="11" customWidth="1"/>
-    <col min="15114" max="15114" width="8.125" style="11" customWidth="1"/>
-    <col min="15115" max="15115" width="10.125" style="11" customWidth="1"/>
-    <col min="15116" max="15116" width="7.25" style="11" customWidth="1"/>
-    <col min="15117" max="15117" width="11.875" style="11" customWidth="1"/>
-    <col min="15118" max="15118" width="2.125" style="11" customWidth="1"/>
-    <col min="15119" max="15120" width="12.5" style="11" customWidth="1"/>
-    <col min="15121" max="15354" width="9" style="11"/>
-    <col min="15355" max="15355" width="6.875" style="11" customWidth="1"/>
-    <col min="15356" max="15356" width="10.125" style="11" customWidth="1"/>
-    <col min="15357" max="15357" width="11.125" style="11" customWidth="1"/>
-    <col min="15358" max="15358" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="15359" max="15359" width="21.625" style="11" customWidth="1"/>
-    <col min="15360" max="15360" width="6.25" style="11" customWidth="1"/>
-    <col min="15361" max="15361" width="12.125" style="11" customWidth="1"/>
-    <col min="15362" max="15362" width="20.125" style="11" customWidth="1"/>
-    <col min="15363" max="15363" width="26.75" style="11" customWidth="1"/>
-    <col min="15364" max="15364" width="13.375" style="11" customWidth="1"/>
-    <col min="15365" max="15365" width="17" style="11" customWidth="1"/>
-    <col min="15366" max="15366" width="19.125" style="11" customWidth="1"/>
-    <col min="15367" max="15368" width="5.875" style="11" customWidth="1"/>
-    <col min="15369" max="15369" width="6.625" style="11" customWidth="1"/>
-    <col min="15370" max="15370" width="8.125" style="11" customWidth="1"/>
-    <col min="15371" max="15371" width="10.125" style="11" customWidth="1"/>
-    <col min="15372" max="15372" width="7.25" style="11" customWidth="1"/>
-    <col min="15373" max="15373" width="11.875" style="11" customWidth="1"/>
-    <col min="15374" max="15374" width="2.125" style="11" customWidth="1"/>
-    <col min="15375" max="15376" width="12.5" style="11" customWidth="1"/>
-    <col min="15377" max="15610" width="9" style="11"/>
-    <col min="15611" max="15611" width="6.875" style="11" customWidth="1"/>
-    <col min="15612" max="15612" width="10.125" style="11" customWidth="1"/>
-    <col min="15613" max="15613" width="11.125" style="11" customWidth="1"/>
-    <col min="15614" max="15614" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="15615" max="15615" width="21.625" style="11" customWidth="1"/>
-    <col min="15616" max="15616" width="6.25" style="11" customWidth="1"/>
-    <col min="15617" max="15617" width="12.125" style="11" customWidth="1"/>
-    <col min="15618" max="15618" width="20.125" style="11" customWidth="1"/>
-    <col min="15619" max="15619" width="26.75" style="11" customWidth="1"/>
-    <col min="15620" max="15620" width="13.375" style="11" customWidth="1"/>
-    <col min="15621" max="15621" width="17" style="11" customWidth="1"/>
-    <col min="15622" max="15622" width="19.125" style="11" customWidth="1"/>
-    <col min="15623" max="15624" width="5.875" style="11" customWidth="1"/>
-    <col min="15625" max="15625" width="6.625" style="11" customWidth="1"/>
-    <col min="15626" max="15626" width="8.125" style="11" customWidth="1"/>
-    <col min="15627" max="15627" width="10.125" style="11" customWidth="1"/>
-    <col min="15628" max="15628" width="7.25" style="11" customWidth="1"/>
-    <col min="15629" max="15629" width="11.875" style="11" customWidth="1"/>
-    <col min="15630" max="15630" width="2.125" style="11" customWidth="1"/>
-    <col min="15631" max="15632" width="12.5" style="11" customWidth="1"/>
-    <col min="15633" max="15866" width="9" style="11"/>
-    <col min="15867" max="15867" width="6.875" style="11" customWidth="1"/>
-    <col min="15868" max="15868" width="10.125" style="11" customWidth="1"/>
-    <col min="15869" max="15869" width="11.125" style="11" customWidth="1"/>
-    <col min="15870" max="15870" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="15871" max="15871" width="21.625" style="11" customWidth="1"/>
-    <col min="15872" max="15872" width="6.25" style="11" customWidth="1"/>
-    <col min="15873" max="15873" width="12.125" style="11" customWidth="1"/>
-    <col min="15874" max="15874" width="20.125" style="11" customWidth="1"/>
-    <col min="15875" max="15875" width="26.75" style="11" customWidth="1"/>
-    <col min="15876" max="15876" width="13.375" style="11" customWidth="1"/>
-    <col min="15877" max="15877" width="17" style="11" customWidth="1"/>
-    <col min="15878" max="15878" width="19.125" style="11" customWidth="1"/>
-    <col min="15879" max="15880" width="5.875" style="11" customWidth="1"/>
-    <col min="15881" max="15881" width="6.625" style="11" customWidth="1"/>
-    <col min="15882" max="15882" width="8.125" style="11" customWidth="1"/>
-    <col min="15883" max="15883" width="10.125" style="11" customWidth="1"/>
-    <col min="15884" max="15884" width="7.25" style="11" customWidth="1"/>
-    <col min="15885" max="15885" width="11.875" style="11" customWidth="1"/>
-    <col min="15886" max="15886" width="2.125" style="11" customWidth="1"/>
-    <col min="15887" max="15888" width="12.5" style="11" customWidth="1"/>
-    <col min="15889" max="16122" width="9" style="11"/>
-    <col min="16123" max="16123" width="6.875" style="11" customWidth="1"/>
-    <col min="16124" max="16124" width="10.125" style="11" customWidth="1"/>
-    <col min="16125" max="16125" width="11.125" style="11" customWidth="1"/>
-    <col min="16126" max="16126" width="9" style="11" hidden="1" customWidth="1"/>
-    <col min="16127" max="16127" width="21.625" style="11" customWidth="1"/>
-    <col min="16128" max="16128" width="6.25" style="11" customWidth="1"/>
-    <col min="16129" max="16129" width="12.125" style="11" customWidth="1"/>
-    <col min="16130" max="16130" width="20.125" style="11" customWidth="1"/>
-    <col min="16131" max="16131" width="26.75" style="11" customWidth="1"/>
-    <col min="16132" max="16132" width="13.375" style="11" customWidth="1"/>
-    <col min="16133" max="16133" width="17" style="11" customWidth="1"/>
-    <col min="16134" max="16134" width="19.125" style="11" customWidth="1"/>
-    <col min="16135" max="16136" width="5.875" style="11" customWidth="1"/>
-    <col min="16137" max="16137" width="6.625" style="11" customWidth="1"/>
-    <col min="16138" max="16138" width="8.125" style="11" customWidth="1"/>
-    <col min="16139" max="16139" width="10.125" style="11" customWidth="1"/>
-    <col min="16140" max="16140" width="7.25" style="11" customWidth="1"/>
-    <col min="16141" max="16141" width="11.875" style="11" customWidth="1"/>
-    <col min="16142" max="16142" width="2.125" style="11" customWidth="1"/>
-    <col min="16143" max="16144" width="12.5" style="11" customWidth="1"/>
-    <col min="16145" max="16384" width="9" style="11"/>
+    <col min="15" max="15" width="11.125" style="9" customWidth="1"/>
+    <col min="16" max="16" width="11.25" style="10" customWidth="1"/>
+    <col min="17" max="250" width="9" style="10"/>
+    <col min="251" max="251" width="6.875" style="10" customWidth="1"/>
+    <col min="252" max="252" width="10.125" style="10" customWidth="1"/>
+    <col min="253" max="253" width="11.125" style="10" customWidth="1"/>
+    <col min="254" max="254" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="255" max="255" width="21.625" style="10" customWidth="1"/>
+    <col min="256" max="256" width="6.25" style="10" customWidth="1"/>
+    <col min="257" max="257" width="12.125" style="10" customWidth="1"/>
+    <col min="258" max="258" width="20.125" style="10" customWidth="1"/>
+    <col min="259" max="259" width="26.75" style="10" customWidth="1"/>
+    <col min="260" max="260" width="13.375" style="10" customWidth="1"/>
+    <col min="261" max="261" width="17" style="10" customWidth="1"/>
+    <col min="262" max="262" width="19.125" style="10" customWidth="1"/>
+    <col min="263" max="264" width="5.875" style="10" customWidth="1"/>
+    <col min="265" max="265" width="6.625" style="10" customWidth="1"/>
+    <col min="266" max="266" width="8.125" style="10" customWidth="1"/>
+    <col min="267" max="267" width="10.125" style="10" customWidth="1"/>
+    <col min="268" max="268" width="7.25" style="10" customWidth="1"/>
+    <col min="269" max="269" width="11.875" style="10" customWidth="1"/>
+    <col min="270" max="270" width="2.125" style="10" customWidth="1"/>
+    <col min="271" max="272" width="12.5" style="10" customWidth="1"/>
+    <col min="273" max="506" width="9" style="10"/>
+    <col min="507" max="507" width="6.875" style="10" customWidth="1"/>
+    <col min="508" max="508" width="10.125" style="10" customWidth="1"/>
+    <col min="509" max="509" width="11.125" style="10" customWidth="1"/>
+    <col min="510" max="510" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="511" max="511" width="21.625" style="10" customWidth="1"/>
+    <col min="512" max="512" width="6.25" style="10" customWidth="1"/>
+    <col min="513" max="513" width="12.125" style="10" customWidth="1"/>
+    <col min="514" max="514" width="20.125" style="10" customWidth="1"/>
+    <col min="515" max="515" width="26.75" style="10" customWidth="1"/>
+    <col min="516" max="516" width="13.375" style="10" customWidth="1"/>
+    <col min="517" max="517" width="17" style="10" customWidth="1"/>
+    <col min="518" max="518" width="19.125" style="10" customWidth="1"/>
+    <col min="519" max="520" width="5.875" style="10" customWidth="1"/>
+    <col min="521" max="521" width="6.625" style="10" customWidth="1"/>
+    <col min="522" max="522" width="8.125" style="10" customWidth="1"/>
+    <col min="523" max="523" width="10.125" style="10" customWidth="1"/>
+    <col min="524" max="524" width="7.25" style="10" customWidth="1"/>
+    <col min="525" max="525" width="11.875" style="10" customWidth="1"/>
+    <col min="526" max="526" width="2.125" style="10" customWidth="1"/>
+    <col min="527" max="528" width="12.5" style="10" customWidth="1"/>
+    <col min="529" max="762" width="9" style="10"/>
+    <col min="763" max="763" width="6.875" style="10" customWidth="1"/>
+    <col min="764" max="764" width="10.125" style="10" customWidth="1"/>
+    <col min="765" max="765" width="11.125" style="10" customWidth="1"/>
+    <col min="766" max="766" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="767" max="767" width="21.625" style="10" customWidth="1"/>
+    <col min="768" max="768" width="6.25" style="10" customWidth="1"/>
+    <col min="769" max="769" width="12.125" style="10" customWidth="1"/>
+    <col min="770" max="770" width="20.125" style="10" customWidth="1"/>
+    <col min="771" max="771" width="26.75" style="10" customWidth="1"/>
+    <col min="772" max="772" width="13.375" style="10" customWidth="1"/>
+    <col min="773" max="773" width="17" style="10" customWidth="1"/>
+    <col min="774" max="774" width="19.125" style="10" customWidth="1"/>
+    <col min="775" max="776" width="5.875" style="10" customWidth="1"/>
+    <col min="777" max="777" width="6.625" style="10" customWidth="1"/>
+    <col min="778" max="778" width="8.125" style="10" customWidth="1"/>
+    <col min="779" max="779" width="10.125" style="10" customWidth="1"/>
+    <col min="780" max="780" width="7.25" style="10" customWidth="1"/>
+    <col min="781" max="781" width="11.875" style="10" customWidth="1"/>
+    <col min="782" max="782" width="2.125" style="10" customWidth="1"/>
+    <col min="783" max="784" width="12.5" style="10" customWidth="1"/>
+    <col min="785" max="1018" width="9" style="10"/>
+    <col min="1019" max="1019" width="6.875" style="10" customWidth="1"/>
+    <col min="1020" max="1020" width="10.125" style="10" customWidth="1"/>
+    <col min="1021" max="1021" width="11.125" style="10" customWidth="1"/>
+    <col min="1022" max="1022" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="1023" max="1023" width="21.625" style="10" customWidth="1"/>
+    <col min="1024" max="1024" width="6.25" style="10" customWidth="1"/>
+    <col min="1025" max="1025" width="12.125" style="10" customWidth="1"/>
+    <col min="1026" max="1026" width="20.125" style="10" customWidth="1"/>
+    <col min="1027" max="1027" width="26.75" style="10" customWidth="1"/>
+    <col min="1028" max="1028" width="13.375" style="10" customWidth="1"/>
+    <col min="1029" max="1029" width="17" style="10" customWidth="1"/>
+    <col min="1030" max="1030" width="19.125" style="10" customWidth="1"/>
+    <col min="1031" max="1032" width="5.875" style="10" customWidth="1"/>
+    <col min="1033" max="1033" width="6.625" style="10" customWidth="1"/>
+    <col min="1034" max="1034" width="8.125" style="10" customWidth="1"/>
+    <col min="1035" max="1035" width="10.125" style="10" customWidth="1"/>
+    <col min="1036" max="1036" width="7.25" style="10" customWidth="1"/>
+    <col min="1037" max="1037" width="11.875" style="10" customWidth="1"/>
+    <col min="1038" max="1038" width="2.125" style="10" customWidth="1"/>
+    <col min="1039" max="1040" width="12.5" style="10" customWidth="1"/>
+    <col min="1041" max="1274" width="9" style="10"/>
+    <col min="1275" max="1275" width="6.875" style="10" customWidth="1"/>
+    <col min="1276" max="1276" width="10.125" style="10" customWidth="1"/>
+    <col min="1277" max="1277" width="11.125" style="10" customWidth="1"/>
+    <col min="1278" max="1278" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="1279" max="1279" width="21.625" style="10" customWidth="1"/>
+    <col min="1280" max="1280" width="6.25" style="10" customWidth="1"/>
+    <col min="1281" max="1281" width="12.125" style="10" customWidth="1"/>
+    <col min="1282" max="1282" width="20.125" style="10" customWidth="1"/>
+    <col min="1283" max="1283" width="26.75" style="10" customWidth="1"/>
+    <col min="1284" max="1284" width="13.375" style="10" customWidth="1"/>
+    <col min="1285" max="1285" width="17" style="10" customWidth="1"/>
+    <col min="1286" max="1286" width="19.125" style="10" customWidth="1"/>
+    <col min="1287" max="1288" width="5.875" style="10" customWidth="1"/>
+    <col min="1289" max="1289" width="6.625" style="10" customWidth="1"/>
+    <col min="1290" max="1290" width="8.125" style="10" customWidth="1"/>
+    <col min="1291" max="1291" width="10.125" style="10" customWidth="1"/>
+    <col min="1292" max="1292" width="7.25" style="10" customWidth="1"/>
+    <col min="1293" max="1293" width="11.875" style="10" customWidth="1"/>
+    <col min="1294" max="1294" width="2.125" style="10" customWidth="1"/>
+    <col min="1295" max="1296" width="12.5" style="10" customWidth="1"/>
+    <col min="1297" max="1530" width="9" style="10"/>
+    <col min="1531" max="1531" width="6.875" style="10" customWidth="1"/>
+    <col min="1532" max="1532" width="10.125" style="10" customWidth="1"/>
+    <col min="1533" max="1533" width="11.125" style="10" customWidth="1"/>
+    <col min="1534" max="1534" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="1535" max="1535" width="21.625" style="10" customWidth="1"/>
+    <col min="1536" max="1536" width="6.25" style="10" customWidth="1"/>
+    <col min="1537" max="1537" width="12.125" style="10" customWidth="1"/>
+    <col min="1538" max="1538" width="20.125" style="10" customWidth="1"/>
+    <col min="1539" max="1539" width="26.75" style="10" customWidth="1"/>
+    <col min="1540" max="1540" width="13.375" style="10" customWidth="1"/>
+    <col min="1541" max="1541" width="17" style="10" customWidth="1"/>
+    <col min="1542" max="1542" width="19.125" style="10" customWidth="1"/>
+    <col min="1543" max="1544" width="5.875" style="10" customWidth="1"/>
+    <col min="1545" max="1545" width="6.625" style="10" customWidth="1"/>
+    <col min="1546" max="1546" width="8.125" style="10" customWidth="1"/>
+    <col min="1547" max="1547" width="10.125" style="10" customWidth="1"/>
+    <col min="1548" max="1548" width="7.25" style="10" customWidth="1"/>
+    <col min="1549" max="1549" width="11.875" style="10" customWidth="1"/>
+    <col min="1550" max="1550" width="2.125" style="10" customWidth="1"/>
+    <col min="1551" max="1552" width="12.5" style="10" customWidth="1"/>
+    <col min="1553" max="1786" width="9" style="10"/>
+    <col min="1787" max="1787" width="6.875" style="10" customWidth="1"/>
+    <col min="1788" max="1788" width="10.125" style="10" customWidth="1"/>
+    <col min="1789" max="1789" width="11.125" style="10" customWidth="1"/>
+    <col min="1790" max="1790" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="1791" max="1791" width="21.625" style="10" customWidth="1"/>
+    <col min="1792" max="1792" width="6.25" style="10" customWidth="1"/>
+    <col min="1793" max="1793" width="12.125" style="10" customWidth="1"/>
+    <col min="1794" max="1794" width="20.125" style="10" customWidth="1"/>
+    <col min="1795" max="1795" width="26.75" style="10" customWidth="1"/>
+    <col min="1796" max="1796" width="13.375" style="10" customWidth="1"/>
+    <col min="1797" max="1797" width="17" style="10" customWidth="1"/>
+    <col min="1798" max="1798" width="19.125" style="10" customWidth="1"/>
+    <col min="1799" max="1800" width="5.875" style="10" customWidth="1"/>
+    <col min="1801" max="1801" width="6.625" style="10" customWidth="1"/>
+    <col min="1802" max="1802" width="8.125" style="10" customWidth="1"/>
+    <col min="1803" max="1803" width="10.125" style="10" customWidth="1"/>
+    <col min="1804" max="1804" width="7.25" style="10" customWidth="1"/>
+    <col min="1805" max="1805" width="11.875" style="10" customWidth="1"/>
+    <col min="1806" max="1806" width="2.125" style="10" customWidth="1"/>
+    <col min="1807" max="1808" width="12.5" style="10" customWidth="1"/>
+    <col min="1809" max="2042" width="9" style="10"/>
+    <col min="2043" max="2043" width="6.875" style="10" customWidth="1"/>
+    <col min="2044" max="2044" width="10.125" style="10" customWidth="1"/>
+    <col min="2045" max="2045" width="11.125" style="10" customWidth="1"/>
+    <col min="2046" max="2046" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="2047" max="2047" width="21.625" style="10" customWidth="1"/>
+    <col min="2048" max="2048" width="6.25" style="10" customWidth="1"/>
+    <col min="2049" max="2049" width="12.125" style="10" customWidth="1"/>
+    <col min="2050" max="2050" width="20.125" style="10" customWidth="1"/>
+    <col min="2051" max="2051" width="26.75" style="10" customWidth="1"/>
+    <col min="2052" max="2052" width="13.375" style="10" customWidth="1"/>
+    <col min="2053" max="2053" width="17" style="10" customWidth="1"/>
+    <col min="2054" max="2054" width="19.125" style="10" customWidth="1"/>
+    <col min="2055" max="2056" width="5.875" style="10" customWidth="1"/>
+    <col min="2057" max="2057" width="6.625" style="10" customWidth="1"/>
+    <col min="2058" max="2058" width="8.125" style="10" customWidth="1"/>
+    <col min="2059" max="2059" width="10.125" style="10" customWidth="1"/>
+    <col min="2060" max="2060" width="7.25" style="10" customWidth="1"/>
+    <col min="2061" max="2061" width="11.875" style="10" customWidth="1"/>
+    <col min="2062" max="2062" width="2.125" style="10" customWidth="1"/>
+    <col min="2063" max="2064" width="12.5" style="10" customWidth="1"/>
+    <col min="2065" max="2298" width="9" style="10"/>
+    <col min="2299" max="2299" width="6.875" style="10" customWidth="1"/>
+    <col min="2300" max="2300" width="10.125" style="10" customWidth="1"/>
+    <col min="2301" max="2301" width="11.125" style="10" customWidth="1"/>
+    <col min="2302" max="2302" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="2303" max="2303" width="21.625" style="10" customWidth="1"/>
+    <col min="2304" max="2304" width="6.25" style="10" customWidth="1"/>
+    <col min="2305" max="2305" width="12.125" style="10" customWidth="1"/>
+    <col min="2306" max="2306" width="20.125" style="10" customWidth="1"/>
+    <col min="2307" max="2307" width="26.75" style="10" customWidth="1"/>
+    <col min="2308" max="2308" width="13.375" style="10" customWidth="1"/>
+    <col min="2309" max="2309" width="17" style="10" customWidth="1"/>
+    <col min="2310" max="2310" width="19.125" style="10" customWidth="1"/>
+    <col min="2311" max="2312" width="5.875" style="10" customWidth="1"/>
+    <col min="2313" max="2313" width="6.625" style="10" customWidth="1"/>
+    <col min="2314" max="2314" width="8.125" style="10" customWidth="1"/>
+    <col min="2315" max="2315" width="10.125" style="10" customWidth="1"/>
+    <col min="2316" max="2316" width="7.25" style="10" customWidth="1"/>
+    <col min="2317" max="2317" width="11.875" style="10" customWidth="1"/>
+    <col min="2318" max="2318" width="2.125" style="10" customWidth="1"/>
+    <col min="2319" max="2320" width="12.5" style="10" customWidth="1"/>
+    <col min="2321" max="2554" width="9" style="10"/>
+    <col min="2555" max="2555" width="6.875" style="10" customWidth="1"/>
+    <col min="2556" max="2556" width="10.125" style="10" customWidth="1"/>
+    <col min="2557" max="2557" width="11.125" style="10" customWidth="1"/>
+    <col min="2558" max="2558" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="2559" max="2559" width="21.625" style="10" customWidth="1"/>
+    <col min="2560" max="2560" width="6.25" style="10" customWidth="1"/>
+    <col min="2561" max="2561" width="12.125" style="10" customWidth="1"/>
+    <col min="2562" max="2562" width="20.125" style="10" customWidth="1"/>
+    <col min="2563" max="2563" width="26.75" style="10" customWidth="1"/>
+    <col min="2564" max="2564" width="13.375" style="10" customWidth="1"/>
+    <col min="2565" max="2565" width="17" style="10" customWidth="1"/>
+    <col min="2566" max="2566" width="19.125" style="10" customWidth="1"/>
+    <col min="2567" max="2568" width="5.875" style="10" customWidth="1"/>
+    <col min="2569" max="2569" width="6.625" style="10" customWidth="1"/>
+    <col min="2570" max="2570" width="8.125" style="10" customWidth="1"/>
+    <col min="2571" max="2571" width="10.125" style="10" customWidth="1"/>
+    <col min="2572" max="2572" width="7.25" style="10" customWidth="1"/>
+    <col min="2573" max="2573" width="11.875" style="10" customWidth="1"/>
+    <col min="2574" max="2574" width="2.125" style="10" customWidth="1"/>
+    <col min="2575" max="2576" width="12.5" style="10" customWidth="1"/>
+    <col min="2577" max="2810" width="9" style="10"/>
+    <col min="2811" max="2811" width="6.875" style="10" customWidth="1"/>
+    <col min="2812" max="2812" width="10.125" style="10" customWidth="1"/>
+    <col min="2813" max="2813" width="11.125" style="10" customWidth="1"/>
+    <col min="2814" max="2814" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="2815" max="2815" width="21.625" style="10" customWidth="1"/>
+    <col min="2816" max="2816" width="6.25" style="10" customWidth="1"/>
+    <col min="2817" max="2817" width="12.125" style="10" customWidth="1"/>
+    <col min="2818" max="2818" width="20.125" style="10" customWidth="1"/>
+    <col min="2819" max="2819" width="26.75" style="10" customWidth="1"/>
+    <col min="2820" max="2820" width="13.375" style="10" customWidth="1"/>
+    <col min="2821" max="2821" width="17" style="10" customWidth="1"/>
+    <col min="2822" max="2822" width="19.125" style="10" customWidth="1"/>
+    <col min="2823" max="2824" width="5.875" style="10" customWidth="1"/>
+    <col min="2825" max="2825" width="6.625" style="10" customWidth="1"/>
+    <col min="2826" max="2826" width="8.125" style="10" customWidth="1"/>
+    <col min="2827" max="2827" width="10.125" style="10" customWidth="1"/>
+    <col min="2828" max="2828" width="7.25" style="10" customWidth="1"/>
+    <col min="2829" max="2829" width="11.875" style="10" customWidth="1"/>
+    <col min="2830" max="2830" width="2.125" style="10" customWidth="1"/>
+    <col min="2831" max="2832" width="12.5" style="10" customWidth="1"/>
+    <col min="2833" max="3066" width="9" style="10"/>
+    <col min="3067" max="3067" width="6.875" style="10" customWidth="1"/>
+    <col min="3068" max="3068" width="10.125" style="10" customWidth="1"/>
+    <col min="3069" max="3069" width="11.125" style="10" customWidth="1"/>
+    <col min="3070" max="3070" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="3071" max="3071" width="21.625" style="10" customWidth="1"/>
+    <col min="3072" max="3072" width="6.25" style="10" customWidth="1"/>
+    <col min="3073" max="3073" width="12.125" style="10" customWidth="1"/>
+    <col min="3074" max="3074" width="20.125" style="10" customWidth="1"/>
+    <col min="3075" max="3075" width="26.75" style="10" customWidth="1"/>
+    <col min="3076" max="3076" width="13.375" style="10" customWidth="1"/>
+    <col min="3077" max="3077" width="17" style="10" customWidth="1"/>
+    <col min="3078" max="3078" width="19.125" style="10" customWidth="1"/>
+    <col min="3079" max="3080" width="5.875" style="10" customWidth="1"/>
+    <col min="3081" max="3081" width="6.625" style="10" customWidth="1"/>
+    <col min="3082" max="3082" width="8.125" style="10" customWidth="1"/>
+    <col min="3083" max="3083" width="10.125" style="10" customWidth="1"/>
+    <col min="3084" max="3084" width="7.25" style="10" customWidth="1"/>
+    <col min="3085" max="3085" width="11.875" style="10" customWidth="1"/>
+    <col min="3086" max="3086" width="2.125" style="10" customWidth="1"/>
+    <col min="3087" max="3088" width="12.5" style="10" customWidth="1"/>
+    <col min="3089" max="3322" width="9" style="10"/>
+    <col min="3323" max="3323" width="6.875" style="10" customWidth="1"/>
+    <col min="3324" max="3324" width="10.125" style="10" customWidth="1"/>
+    <col min="3325" max="3325" width="11.125" style="10" customWidth="1"/>
+    <col min="3326" max="3326" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="3327" max="3327" width="21.625" style="10" customWidth="1"/>
+    <col min="3328" max="3328" width="6.25" style="10" customWidth="1"/>
+    <col min="3329" max="3329" width="12.125" style="10" customWidth="1"/>
+    <col min="3330" max="3330" width="20.125" style="10" customWidth="1"/>
+    <col min="3331" max="3331" width="26.75" style="10" customWidth="1"/>
+    <col min="3332" max="3332" width="13.375" style="10" customWidth="1"/>
+    <col min="3333" max="3333" width="17" style="10" customWidth="1"/>
+    <col min="3334" max="3334" width="19.125" style="10" customWidth="1"/>
+    <col min="3335" max="3336" width="5.875" style="10" customWidth="1"/>
+    <col min="3337" max="3337" width="6.625" style="10" customWidth="1"/>
+    <col min="3338" max="3338" width="8.125" style="10" customWidth="1"/>
+    <col min="3339" max="3339" width="10.125" style="10" customWidth="1"/>
+    <col min="3340" max="3340" width="7.25" style="10" customWidth="1"/>
+    <col min="3341" max="3341" width="11.875" style="10" customWidth="1"/>
+    <col min="3342" max="3342" width="2.125" style="10" customWidth="1"/>
+    <col min="3343" max="3344" width="12.5" style="10" customWidth="1"/>
+    <col min="3345" max="3578" width="9" style="10"/>
+    <col min="3579" max="3579" width="6.875" style="10" customWidth="1"/>
+    <col min="3580" max="3580" width="10.125" style="10" customWidth="1"/>
+    <col min="3581" max="3581" width="11.125" style="10" customWidth="1"/>
+    <col min="3582" max="3582" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="3583" max="3583" width="21.625" style="10" customWidth="1"/>
+    <col min="3584" max="3584" width="6.25" style="10" customWidth="1"/>
+    <col min="3585" max="3585" width="12.125" style="10" customWidth="1"/>
+    <col min="3586" max="3586" width="20.125" style="10" customWidth="1"/>
+    <col min="3587" max="3587" width="26.75" style="10" customWidth="1"/>
+    <col min="3588" max="3588" width="13.375" style="10" customWidth="1"/>
+    <col min="3589" max="3589" width="17" style="10" customWidth="1"/>
+    <col min="3590" max="3590" width="19.125" style="10" customWidth="1"/>
+    <col min="3591" max="3592" width="5.875" style="10" customWidth="1"/>
+    <col min="3593" max="3593" width="6.625" style="10" customWidth="1"/>
+    <col min="3594" max="3594" width="8.125" style="10" customWidth="1"/>
+    <col min="3595" max="3595" width="10.125" style="10" customWidth="1"/>
+    <col min="3596" max="3596" width="7.25" style="10" customWidth="1"/>
+    <col min="3597" max="3597" width="11.875" style="10" customWidth="1"/>
+    <col min="3598" max="3598" width="2.125" style="10" customWidth="1"/>
+    <col min="3599" max="3600" width="12.5" style="10" customWidth="1"/>
+    <col min="3601" max="3834" width="9" style="10"/>
+    <col min="3835" max="3835" width="6.875" style="10" customWidth="1"/>
+    <col min="3836" max="3836" width="10.125" style="10" customWidth="1"/>
+    <col min="3837" max="3837" width="11.125" style="10" customWidth="1"/>
+    <col min="3838" max="3838" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="3839" max="3839" width="21.625" style="10" customWidth="1"/>
+    <col min="3840" max="3840" width="6.25" style="10" customWidth="1"/>
+    <col min="3841" max="3841" width="12.125" style="10" customWidth="1"/>
+    <col min="3842" max="3842" width="20.125" style="10" customWidth="1"/>
+    <col min="3843" max="3843" width="26.75" style="10" customWidth="1"/>
+    <col min="3844" max="3844" width="13.375" style="10" customWidth="1"/>
+    <col min="3845" max="3845" width="17" style="10" customWidth="1"/>
+    <col min="3846" max="3846" width="19.125" style="10" customWidth="1"/>
+    <col min="3847" max="3848" width="5.875" style="10" customWidth="1"/>
+    <col min="3849" max="3849" width="6.625" style="10" customWidth="1"/>
+    <col min="3850" max="3850" width="8.125" style="10" customWidth="1"/>
+    <col min="3851" max="3851" width="10.125" style="10" customWidth="1"/>
+    <col min="3852" max="3852" width="7.25" style="10" customWidth="1"/>
+    <col min="3853" max="3853" width="11.875" style="10" customWidth="1"/>
+    <col min="3854" max="3854" width="2.125" style="10" customWidth="1"/>
+    <col min="3855" max="3856" width="12.5" style="10" customWidth="1"/>
+    <col min="3857" max="4090" width="9" style="10"/>
+    <col min="4091" max="4091" width="6.875" style="10" customWidth="1"/>
+    <col min="4092" max="4092" width="10.125" style="10" customWidth="1"/>
+    <col min="4093" max="4093" width="11.125" style="10" customWidth="1"/>
+    <col min="4094" max="4094" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="4095" max="4095" width="21.625" style="10" customWidth="1"/>
+    <col min="4096" max="4096" width="6.25" style="10" customWidth="1"/>
+    <col min="4097" max="4097" width="12.125" style="10" customWidth="1"/>
+    <col min="4098" max="4098" width="20.125" style="10" customWidth="1"/>
+    <col min="4099" max="4099" width="26.75" style="10" customWidth="1"/>
+    <col min="4100" max="4100" width="13.375" style="10" customWidth="1"/>
+    <col min="4101" max="4101" width="17" style="10" customWidth="1"/>
+    <col min="4102" max="4102" width="19.125" style="10" customWidth="1"/>
+    <col min="4103" max="4104" width="5.875" style="10" customWidth="1"/>
+    <col min="4105" max="4105" width="6.625" style="10" customWidth="1"/>
+    <col min="4106" max="4106" width="8.125" style="10" customWidth="1"/>
+    <col min="4107" max="4107" width="10.125" style="10" customWidth="1"/>
+    <col min="4108" max="4108" width="7.25" style="10" customWidth="1"/>
+    <col min="4109" max="4109" width="11.875" style="10" customWidth="1"/>
+    <col min="4110" max="4110" width="2.125" style="10" customWidth="1"/>
+    <col min="4111" max="4112" width="12.5" style="10" customWidth="1"/>
+    <col min="4113" max="4346" width="9" style="10"/>
+    <col min="4347" max="4347" width="6.875" style="10" customWidth="1"/>
+    <col min="4348" max="4348" width="10.125" style="10" customWidth="1"/>
+    <col min="4349" max="4349" width="11.125" style="10" customWidth="1"/>
+    <col min="4350" max="4350" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="4351" max="4351" width="21.625" style="10" customWidth="1"/>
+    <col min="4352" max="4352" width="6.25" style="10" customWidth="1"/>
+    <col min="4353" max="4353" width="12.125" style="10" customWidth="1"/>
+    <col min="4354" max="4354" width="20.125" style="10" customWidth="1"/>
+    <col min="4355" max="4355" width="26.75" style="10" customWidth="1"/>
+    <col min="4356" max="4356" width="13.375" style="10" customWidth="1"/>
+    <col min="4357" max="4357" width="17" style="10" customWidth="1"/>
+    <col min="4358" max="4358" width="19.125" style="10" customWidth="1"/>
+    <col min="4359" max="4360" width="5.875" style="10" customWidth="1"/>
+    <col min="4361" max="4361" width="6.625" style="10" customWidth="1"/>
+    <col min="4362" max="4362" width="8.125" style="10" customWidth="1"/>
+    <col min="4363" max="4363" width="10.125" style="10" customWidth="1"/>
+    <col min="4364" max="4364" width="7.25" style="10" customWidth="1"/>
+    <col min="4365" max="4365" width="11.875" style="10" customWidth="1"/>
+    <col min="4366" max="4366" width="2.125" style="10" customWidth="1"/>
+    <col min="4367" max="4368" width="12.5" style="10" customWidth="1"/>
+    <col min="4369" max="4602" width="9" style="10"/>
+    <col min="4603" max="4603" width="6.875" style="10" customWidth="1"/>
+    <col min="4604" max="4604" width="10.125" style="10" customWidth="1"/>
+    <col min="4605" max="4605" width="11.125" style="10" customWidth="1"/>
+    <col min="4606" max="4606" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="4607" max="4607" width="21.625" style="10" customWidth="1"/>
+    <col min="4608" max="4608" width="6.25" style="10" customWidth="1"/>
+    <col min="4609" max="4609" width="12.125" style="10" customWidth="1"/>
+    <col min="4610" max="4610" width="20.125" style="10" customWidth="1"/>
+    <col min="4611" max="4611" width="26.75" style="10" customWidth="1"/>
+    <col min="4612" max="4612" width="13.375" style="10" customWidth="1"/>
+    <col min="4613" max="4613" width="17" style="10" customWidth="1"/>
+    <col min="4614" max="4614" width="19.125" style="10" customWidth="1"/>
+    <col min="4615" max="4616" width="5.875" style="10" customWidth="1"/>
+    <col min="4617" max="4617" width="6.625" style="10" customWidth="1"/>
+    <col min="4618" max="4618" width="8.125" style="10" customWidth="1"/>
+    <col min="4619" max="4619" width="10.125" style="10" customWidth="1"/>
+    <col min="4620" max="4620" width="7.25" style="10" customWidth="1"/>
+    <col min="4621" max="4621" width="11.875" style="10" customWidth="1"/>
+    <col min="4622" max="4622" width="2.125" style="10" customWidth="1"/>
+    <col min="4623" max="4624" width="12.5" style="10" customWidth="1"/>
+    <col min="4625" max="4858" width="9" style="10"/>
+    <col min="4859" max="4859" width="6.875" style="10" customWidth="1"/>
+    <col min="4860" max="4860" width="10.125" style="10" customWidth="1"/>
+    <col min="4861" max="4861" width="11.125" style="10" customWidth="1"/>
+    <col min="4862" max="4862" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="4863" max="4863" width="21.625" style="10" customWidth="1"/>
+    <col min="4864" max="4864" width="6.25" style="10" customWidth="1"/>
+    <col min="4865" max="4865" width="12.125" style="10" customWidth="1"/>
+    <col min="4866" max="4866" width="20.125" style="10" customWidth="1"/>
+    <col min="4867" max="4867" width="26.75" style="10" customWidth="1"/>
+    <col min="4868" max="4868" width="13.375" style="10" customWidth="1"/>
+    <col min="4869" max="4869" width="17" style="10" customWidth="1"/>
+    <col min="4870" max="4870" width="19.125" style="10" customWidth="1"/>
+    <col min="4871" max="4872" width="5.875" style="10" customWidth="1"/>
+    <col min="4873" max="4873" width="6.625" style="10" customWidth="1"/>
+    <col min="4874" max="4874" width="8.125" style="10" customWidth="1"/>
+    <col min="4875" max="4875" width="10.125" style="10" customWidth="1"/>
+    <col min="4876" max="4876" width="7.25" style="10" customWidth="1"/>
+    <col min="4877" max="4877" width="11.875" style="10" customWidth="1"/>
+    <col min="4878" max="4878" width="2.125" style="10" customWidth="1"/>
+    <col min="4879" max="4880" width="12.5" style="10" customWidth="1"/>
+    <col min="4881" max="5114" width="9" style="10"/>
+    <col min="5115" max="5115" width="6.875" style="10" customWidth="1"/>
+    <col min="5116" max="5116" width="10.125" style="10" customWidth="1"/>
+    <col min="5117" max="5117" width="11.125" style="10" customWidth="1"/>
+    <col min="5118" max="5118" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="5119" max="5119" width="21.625" style="10" customWidth="1"/>
+    <col min="5120" max="5120" width="6.25" style="10" customWidth="1"/>
+    <col min="5121" max="5121" width="12.125" style="10" customWidth="1"/>
+    <col min="5122" max="5122" width="20.125" style="10" customWidth="1"/>
+    <col min="5123" max="5123" width="26.75" style="10" customWidth="1"/>
+    <col min="5124" max="5124" width="13.375" style="10" customWidth="1"/>
+    <col min="5125" max="5125" width="17" style="10" customWidth="1"/>
+    <col min="5126" max="5126" width="19.125" style="10" customWidth="1"/>
+    <col min="5127" max="5128" width="5.875" style="10" customWidth="1"/>
+    <col min="5129" max="5129" width="6.625" style="10" customWidth="1"/>
+    <col min="5130" max="5130" width="8.125" style="10" customWidth="1"/>
+    <col min="5131" max="5131" width="10.125" style="10" customWidth="1"/>
+    <col min="5132" max="5132" width="7.25" style="10" customWidth="1"/>
+    <col min="5133" max="5133" width="11.875" style="10" customWidth="1"/>
+    <col min="5134" max="5134" width="2.125" style="10" customWidth="1"/>
+    <col min="5135" max="5136" width="12.5" style="10" customWidth="1"/>
+    <col min="5137" max="5370" width="9" style="10"/>
+    <col min="5371" max="5371" width="6.875" style="10" customWidth="1"/>
+    <col min="5372" max="5372" width="10.125" style="10" customWidth="1"/>
+    <col min="5373" max="5373" width="11.125" style="10" customWidth="1"/>
+    <col min="5374" max="5374" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="5375" max="5375" width="21.625" style="10" customWidth="1"/>
+    <col min="5376" max="5376" width="6.25" style="10" customWidth="1"/>
+    <col min="5377" max="5377" width="12.125" style="10" customWidth="1"/>
+    <col min="5378" max="5378" width="20.125" style="10" customWidth="1"/>
+    <col min="5379" max="5379" width="26.75" style="10" customWidth="1"/>
+    <col min="5380" max="5380" width="13.375" style="10" customWidth="1"/>
+    <col min="5381" max="5381" width="17" style="10" customWidth="1"/>
+    <col min="5382" max="5382" width="19.125" style="10" customWidth="1"/>
+    <col min="5383" max="5384" width="5.875" style="10" customWidth="1"/>
+    <col min="5385" max="5385" width="6.625" style="10" customWidth="1"/>
+    <col min="5386" max="5386" width="8.125" style="10" customWidth="1"/>
+    <col min="5387" max="5387" width="10.125" style="10" customWidth="1"/>
+    <col min="5388" max="5388" width="7.25" style="10" customWidth="1"/>
+    <col min="5389" max="5389" width="11.875" style="10" customWidth="1"/>
+    <col min="5390" max="5390" width="2.125" style="10" customWidth="1"/>
+    <col min="5391" max="5392" width="12.5" style="10" customWidth="1"/>
+    <col min="5393" max="5626" width="9" style="10"/>
+    <col min="5627" max="5627" width="6.875" style="10" customWidth="1"/>
+    <col min="5628" max="5628" width="10.125" style="10" customWidth="1"/>
+    <col min="5629" max="5629" width="11.125" style="10" customWidth="1"/>
+    <col min="5630" max="5630" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="5631" max="5631" width="21.625" style="10" customWidth="1"/>
+    <col min="5632" max="5632" width="6.25" style="10" customWidth="1"/>
+    <col min="5633" max="5633" width="12.125" style="10" customWidth="1"/>
+    <col min="5634" max="5634" width="20.125" style="10" customWidth="1"/>
+    <col min="5635" max="5635" width="26.75" style="10" customWidth="1"/>
+    <col min="5636" max="5636" width="13.375" style="10" customWidth="1"/>
+    <col min="5637" max="5637" width="17" style="10" customWidth="1"/>
+    <col min="5638" max="5638" width="19.125" style="10" customWidth="1"/>
+    <col min="5639" max="5640" width="5.875" style="10" customWidth="1"/>
+    <col min="5641" max="5641" width="6.625" style="10" customWidth="1"/>
+    <col min="5642" max="5642" width="8.125" style="10" customWidth="1"/>
+    <col min="5643" max="5643" width="10.125" style="10" customWidth="1"/>
+    <col min="5644" max="5644" width="7.25" style="10" customWidth="1"/>
+    <col min="5645" max="5645" width="11.875" style="10" customWidth="1"/>
+    <col min="5646" max="5646" width="2.125" style="10" customWidth="1"/>
+    <col min="5647" max="5648" width="12.5" style="10" customWidth="1"/>
+    <col min="5649" max="5882" width="9" style="10"/>
+    <col min="5883" max="5883" width="6.875" style="10" customWidth="1"/>
+    <col min="5884" max="5884" width="10.125" style="10" customWidth="1"/>
+    <col min="5885" max="5885" width="11.125" style="10" customWidth="1"/>
+    <col min="5886" max="5886" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="5887" max="5887" width="21.625" style="10" customWidth="1"/>
+    <col min="5888" max="5888" width="6.25" style="10" customWidth="1"/>
+    <col min="5889" max="5889" width="12.125" style="10" customWidth="1"/>
+    <col min="5890" max="5890" width="20.125" style="10" customWidth="1"/>
+    <col min="5891" max="5891" width="26.75" style="10" customWidth="1"/>
+    <col min="5892" max="5892" width="13.375" style="10" customWidth="1"/>
+    <col min="5893" max="5893" width="17" style="10" customWidth="1"/>
+    <col min="5894" max="5894" width="19.125" style="10" customWidth="1"/>
+    <col min="5895" max="5896" width="5.875" style="10" customWidth="1"/>
+    <col min="5897" max="5897" width="6.625" style="10" customWidth="1"/>
+    <col min="5898" max="5898" width="8.125" style="10" customWidth="1"/>
+    <col min="5899" max="5899" width="10.125" style="10" customWidth="1"/>
+    <col min="5900" max="5900" width="7.25" style="10" customWidth="1"/>
+    <col min="5901" max="5901" width="11.875" style="10" customWidth="1"/>
+    <col min="5902" max="5902" width="2.125" style="10" customWidth="1"/>
+    <col min="5903" max="5904" width="12.5" style="10" customWidth="1"/>
+    <col min="5905" max="6138" width="9" style="10"/>
+    <col min="6139" max="6139" width="6.875" style="10" customWidth="1"/>
+    <col min="6140" max="6140" width="10.125" style="10" customWidth="1"/>
+    <col min="6141" max="6141" width="11.125" style="10" customWidth="1"/>
+    <col min="6142" max="6142" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="6143" max="6143" width="21.625" style="10" customWidth="1"/>
+    <col min="6144" max="6144" width="6.25" style="10" customWidth="1"/>
+    <col min="6145" max="6145" width="12.125" style="10" customWidth="1"/>
+    <col min="6146" max="6146" width="20.125" style="10" customWidth="1"/>
+    <col min="6147" max="6147" width="26.75" style="10" customWidth="1"/>
+    <col min="6148" max="6148" width="13.375" style="10" customWidth="1"/>
+    <col min="6149" max="6149" width="17" style="10" customWidth="1"/>
+    <col min="6150" max="6150" width="19.125" style="10" customWidth="1"/>
+    <col min="6151" max="6152" width="5.875" style="10" customWidth="1"/>
+    <col min="6153" max="6153" width="6.625" style="10" customWidth="1"/>
+    <col min="6154" max="6154" width="8.125" style="10" customWidth="1"/>
+    <col min="6155" max="6155" width="10.125" style="10" customWidth="1"/>
+    <col min="6156" max="6156" width="7.25" style="10" customWidth="1"/>
+    <col min="6157" max="6157" width="11.875" style="10" customWidth="1"/>
+    <col min="6158" max="6158" width="2.125" style="10" customWidth="1"/>
+    <col min="6159" max="6160" width="12.5" style="10" customWidth="1"/>
+    <col min="6161" max="6394" width="9" style="10"/>
+    <col min="6395" max="6395" width="6.875" style="10" customWidth="1"/>
+    <col min="6396" max="6396" width="10.125" style="10" customWidth="1"/>
+    <col min="6397" max="6397" width="11.125" style="10" customWidth="1"/>
+    <col min="6398" max="6398" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="6399" max="6399" width="21.625" style="10" customWidth="1"/>
+    <col min="6400" max="6400" width="6.25" style="10" customWidth="1"/>
+    <col min="6401" max="6401" width="12.125" style="10" customWidth="1"/>
+    <col min="6402" max="6402" width="20.125" style="10" customWidth="1"/>
+    <col min="6403" max="6403" width="26.75" style="10" customWidth="1"/>
+    <col min="6404" max="6404" width="13.375" style="10" customWidth="1"/>
+    <col min="6405" max="6405" width="17" style="10" customWidth="1"/>
+    <col min="6406" max="6406" width="19.125" style="10" customWidth="1"/>
+    <col min="6407" max="6408" width="5.875" style="10" customWidth="1"/>
+    <col min="6409" max="6409" width="6.625" style="10" customWidth="1"/>
+    <col min="6410" max="6410" width="8.125" style="10" customWidth="1"/>
+    <col min="6411" max="6411" width="10.125" style="10" customWidth="1"/>
+    <col min="6412" max="6412" width="7.25" style="10" customWidth="1"/>
+    <col min="6413" max="6413" width="11.875" style="10" customWidth="1"/>
+    <col min="6414" max="6414" width="2.125" style="10" customWidth="1"/>
+    <col min="6415" max="6416" width="12.5" style="10" customWidth="1"/>
+    <col min="6417" max="6650" width="9" style="10"/>
+    <col min="6651" max="6651" width="6.875" style="10" customWidth="1"/>
+    <col min="6652" max="6652" width="10.125" style="10" customWidth="1"/>
+    <col min="6653" max="6653" width="11.125" style="10" customWidth="1"/>
+    <col min="6654" max="6654" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="6655" max="6655" width="21.625" style="10" customWidth="1"/>
+    <col min="6656" max="6656" width="6.25" style="10" customWidth="1"/>
+    <col min="6657" max="6657" width="12.125" style="10" customWidth="1"/>
+    <col min="6658" max="6658" width="20.125" style="10" customWidth="1"/>
+    <col min="6659" max="6659" width="26.75" style="10" customWidth="1"/>
+    <col min="6660" max="6660" width="13.375" style="10" customWidth="1"/>
+    <col min="6661" max="6661" width="17" style="10" customWidth="1"/>
+    <col min="6662" max="6662" width="19.125" style="10" customWidth="1"/>
+    <col min="6663" max="6664" width="5.875" style="10" customWidth="1"/>
+    <col min="6665" max="6665" width="6.625" style="10" customWidth="1"/>
+    <col min="6666" max="6666" width="8.125" style="10" customWidth="1"/>
+    <col min="6667" max="6667" width="10.125" style="10" customWidth="1"/>
+    <col min="6668" max="6668" width="7.25" style="10" customWidth="1"/>
+    <col min="6669" max="6669" width="11.875" style="10" customWidth="1"/>
+    <col min="6670" max="6670" width="2.125" style="10" customWidth="1"/>
+    <col min="6671" max="6672" width="12.5" style="10" customWidth="1"/>
+    <col min="6673" max="6906" width="9" style="10"/>
+    <col min="6907" max="6907" width="6.875" style="10" customWidth="1"/>
+    <col min="6908" max="6908" width="10.125" style="10" customWidth="1"/>
+    <col min="6909" max="6909" width="11.125" style="10" customWidth="1"/>
+    <col min="6910" max="6910" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="6911" max="6911" width="21.625" style="10" customWidth="1"/>
+    <col min="6912" max="6912" width="6.25" style="10" customWidth="1"/>
+    <col min="6913" max="6913" width="12.125" style="10" customWidth="1"/>
+    <col min="6914" max="6914" width="20.125" style="10" customWidth="1"/>
+    <col min="6915" max="6915" width="26.75" style="10" customWidth="1"/>
+    <col min="6916" max="6916" width="13.375" style="10" customWidth="1"/>
+    <col min="6917" max="6917" width="17" style="10" customWidth="1"/>
+    <col min="6918" max="6918" width="19.125" style="10" customWidth="1"/>
+    <col min="6919" max="6920" width="5.875" style="10" customWidth="1"/>
+    <col min="6921" max="6921" width="6.625" style="10" customWidth="1"/>
+    <col min="6922" max="6922" width="8.125" style="10" customWidth="1"/>
+    <col min="6923" max="6923" width="10.125" style="10" customWidth="1"/>
+    <col min="6924" max="6924" width="7.25" style="10" customWidth="1"/>
+    <col min="6925" max="6925" width="11.875" style="10" customWidth="1"/>
+    <col min="6926" max="6926" width="2.125" style="10" customWidth="1"/>
+    <col min="6927" max="6928" width="12.5" style="10" customWidth="1"/>
+    <col min="6929" max="7162" width="9" style="10"/>
+    <col min="7163" max="7163" width="6.875" style="10" customWidth="1"/>
+    <col min="7164" max="7164" width="10.125" style="10" customWidth="1"/>
+    <col min="7165" max="7165" width="11.125" style="10" customWidth="1"/>
+    <col min="7166" max="7166" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="7167" max="7167" width="21.625" style="10" customWidth="1"/>
+    <col min="7168" max="7168" width="6.25" style="10" customWidth="1"/>
+    <col min="7169" max="7169" width="12.125" style="10" customWidth="1"/>
+    <col min="7170" max="7170" width="20.125" style="10" customWidth="1"/>
+    <col min="7171" max="7171" width="26.75" style="10" customWidth="1"/>
+    <col min="7172" max="7172" width="13.375" style="10" customWidth="1"/>
+    <col min="7173" max="7173" width="17" style="10" customWidth="1"/>
+    <col min="7174" max="7174" width="19.125" style="10" customWidth="1"/>
+    <col min="7175" max="7176" width="5.875" style="10" customWidth="1"/>
+    <col min="7177" max="7177" width="6.625" style="10" customWidth="1"/>
+    <col min="7178" max="7178" width="8.125" style="10" customWidth="1"/>
+    <col min="7179" max="7179" width="10.125" style="10" customWidth="1"/>
+    <col min="7180" max="7180" width="7.25" style="10" customWidth="1"/>
+    <col min="7181" max="7181" width="11.875" style="10" customWidth="1"/>
+    <col min="7182" max="7182" width="2.125" style="10" customWidth="1"/>
+    <col min="7183" max="7184" width="12.5" style="10" customWidth="1"/>
+    <col min="7185" max="7418" width="9" style="10"/>
+    <col min="7419" max="7419" width="6.875" style="10" customWidth="1"/>
+    <col min="7420" max="7420" width="10.125" style="10" customWidth="1"/>
+    <col min="7421" max="7421" width="11.125" style="10" customWidth="1"/>
+    <col min="7422" max="7422" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="7423" max="7423" width="21.625" style="10" customWidth="1"/>
+    <col min="7424" max="7424" width="6.25" style="10" customWidth="1"/>
+    <col min="7425" max="7425" width="12.125" style="10" customWidth="1"/>
+    <col min="7426" max="7426" width="20.125" style="10" customWidth="1"/>
+    <col min="7427" max="7427" width="26.75" style="10" customWidth="1"/>
+    <col min="7428" max="7428" width="13.375" style="10" customWidth="1"/>
+    <col min="7429" max="7429" width="17" style="10" customWidth="1"/>
+    <col min="7430" max="7430" width="19.125" style="10" customWidth="1"/>
+    <col min="7431" max="7432" width="5.875" style="10" customWidth="1"/>
+    <col min="7433" max="7433" width="6.625" style="10" customWidth="1"/>
+    <col min="7434" max="7434" width="8.125" style="10" customWidth="1"/>
+    <col min="7435" max="7435" width="10.125" style="10" customWidth="1"/>
+    <col min="7436" max="7436" width="7.25" style="10" customWidth="1"/>
+    <col min="7437" max="7437" width="11.875" style="10" customWidth="1"/>
+    <col min="7438" max="7438" width="2.125" style="10" customWidth="1"/>
+    <col min="7439" max="7440" width="12.5" style="10" customWidth="1"/>
+    <col min="7441" max="7674" width="9" style="10"/>
+    <col min="7675" max="7675" width="6.875" style="10" customWidth="1"/>
+    <col min="7676" max="7676" width="10.125" style="10" customWidth="1"/>
+    <col min="7677" max="7677" width="11.125" style="10" customWidth="1"/>
+    <col min="7678" max="7678" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="7679" max="7679" width="21.625" style="10" customWidth="1"/>
+    <col min="7680" max="7680" width="6.25" style="10" customWidth="1"/>
+    <col min="7681" max="7681" width="12.125" style="10" customWidth="1"/>
+    <col min="7682" max="7682" width="20.125" style="10" customWidth="1"/>
+    <col min="7683" max="7683" width="26.75" style="10" customWidth="1"/>
+    <col min="7684" max="7684" width="13.375" style="10" customWidth="1"/>
+    <col min="7685" max="7685" width="17" style="10" customWidth="1"/>
+    <col min="7686" max="7686" width="19.125" style="10" customWidth="1"/>
+    <col min="7687" max="7688" width="5.875" style="10" customWidth="1"/>
+    <col min="7689" max="7689" width="6.625" style="10" customWidth="1"/>
+    <col min="7690" max="7690" width="8.125" style="10" customWidth="1"/>
+    <col min="7691" max="7691" width="10.125" style="10" customWidth="1"/>
+    <col min="7692" max="7692" width="7.25" style="10" customWidth="1"/>
+    <col min="7693" max="7693" width="11.875" style="10" customWidth="1"/>
+    <col min="7694" max="7694" width="2.125" style="10" customWidth="1"/>
+    <col min="7695" max="7696" width="12.5" style="10" customWidth="1"/>
+    <col min="7697" max="7930" width="9" style="10"/>
+    <col min="7931" max="7931" width="6.875" style="10" customWidth="1"/>
+    <col min="7932" max="7932" width="10.125" style="10" customWidth="1"/>
+    <col min="7933" max="7933" width="11.125" style="10" customWidth="1"/>
+    <col min="7934" max="7934" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="7935" max="7935" width="21.625" style="10" customWidth="1"/>
+    <col min="7936" max="7936" width="6.25" style="10" customWidth="1"/>
+    <col min="7937" max="7937" width="12.125" style="10" customWidth="1"/>
+    <col min="7938" max="7938" width="20.125" style="10" customWidth="1"/>
+    <col min="7939" max="7939" width="26.75" style="10" customWidth="1"/>
+    <col min="7940" max="7940" width="13.375" style="10" customWidth="1"/>
+    <col min="7941" max="7941" width="17" style="10" customWidth="1"/>
+    <col min="7942" max="7942" width="19.125" style="10" customWidth="1"/>
+    <col min="7943" max="7944" width="5.875" style="10" customWidth="1"/>
+    <col min="7945" max="7945" width="6.625" style="10" customWidth="1"/>
+    <col min="7946" max="7946" width="8.125" style="10" customWidth="1"/>
+    <col min="7947" max="7947" width="10.125" style="10" customWidth="1"/>
+    <col min="7948" max="7948" width="7.25" style="10" customWidth="1"/>
+    <col min="7949" max="7949" width="11.875" style="10" customWidth="1"/>
+    <col min="7950" max="7950" width="2.125" style="10" customWidth="1"/>
+    <col min="7951" max="7952" width="12.5" style="10" customWidth="1"/>
+    <col min="7953" max="8186" width="9" style="10"/>
+    <col min="8187" max="8187" width="6.875" style="10" customWidth="1"/>
+    <col min="8188" max="8188" width="10.125" style="10" customWidth="1"/>
+    <col min="8189" max="8189" width="11.125" style="10" customWidth="1"/>
+    <col min="8190" max="8190" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="8191" max="8191" width="21.625" style="10" customWidth="1"/>
+    <col min="8192" max="8192" width="6.25" style="10" customWidth="1"/>
+    <col min="8193" max="8193" width="12.125" style="10" customWidth="1"/>
+    <col min="8194" max="8194" width="20.125" style="10" customWidth="1"/>
+    <col min="8195" max="8195" width="26.75" style="10" customWidth="1"/>
+    <col min="8196" max="8196" width="13.375" style="10" customWidth="1"/>
+    <col min="8197" max="8197" width="17" style="10" customWidth="1"/>
+    <col min="8198" max="8198" width="19.125" style="10" customWidth="1"/>
+    <col min="8199" max="8200" width="5.875" style="10" customWidth="1"/>
+    <col min="8201" max="8201" width="6.625" style="10" customWidth="1"/>
+    <col min="8202" max="8202" width="8.125" style="10" customWidth="1"/>
+    <col min="8203" max="8203" width="10.125" style="10" customWidth="1"/>
+    <col min="8204" max="8204" width="7.25" style="10" customWidth="1"/>
+    <col min="8205" max="8205" width="11.875" style="10" customWidth="1"/>
+    <col min="8206" max="8206" width="2.125" style="10" customWidth="1"/>
+    <col min="8207" max="8208" width="12.5" style="10" customWidth="1"/>
+    <col min="8209" max="8442" width="9" style="10"/>
+    <col min="8443" max="8443" width="6.875" style="10" customWidth="1"/>
+    <col min="8444" max="8444" width="10.125" style="10" customWidth="1"/>
+    <col min="8445" max="8445" width="11.125" style="10" customWidth="1"/>
+    <col min="8446" max="8446" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="8447" max="8447" width="21.625" style="10" customWidth="1"/>
+    <col min="8448" max="8448" width="6.25" style="10" customWidth="1"/>
+    <col min="8449" max="8449" width="12.125" style="10" customWidth="1"/>
+    <col min="8450" max="8450" width="20.125" style="10" customWidth="1"/>
+    <col min="8451" max="8451" width="26.75" style="10" customWidth="1"/>
+    <col min="8452" max="8452" width="13.375" style="10" customWidth="1"/>
+    <col min="8453" max="8453" width="17" style="10" customWidth="1"/>
+    <col min="8454" max="8454" width="19.125" style="10" customWidth="1"/>
+    <col min="8455" max="8456" width="5.875" style="10" customWidth="1"/>
+    <col min="8457" max="8457" width="6.625" style="10" customWidth="1"/>
+    <col min="8458" max="8458" width="8.125" style="10" customWidth="1"/>
+    <col min="8459" max="8459" width="10.125" style="10" customWidth="1"/>
+    <col min="8460" max="8460" width="7.25" style="10" customWidth="1"/>
+    <col min="8461" max="8461" width="11.875" style="10" customWidth="1"/>
+    <col min="8462" max="8462" width="2.125" style="10" customWidth="1"/>
+    <col min="8463" max="8464" width="12.5" style="10" customWidth="1"/>
+    <col min="8465" max="8698" width="9" style="10"/>
+    <col min="8699" max="8699" width="6.875" style="10" customWidth="1"/>
+    <col min="8700" max="8700" width="10.125" style="10" customWidth="1"/>
+    <col min="8701" max="8701" width="11.125" style="10" customWidth="1"/>
+    <col min="8702" max="8702" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="8703" max="8703" width="21.625" style="10" customWidth="1"/>
+    <col min="8704" max="8704" width="6.25" style="10" customWidth="1"/>
+    <col min="8705" max="8705" width="12.125" style="10" customWidth="1"/>
+    <col min="8706" max="8706" width="20.125" style="10" customWidth="1"/>
+    <col min="8707" max="8707" width="26.75" style="10" customWidth="1"/>
+    <col min="8708" max="8708" width="13.375" style="10" customWidth="1"/>
+    <col min="8709" max="8709" width="17" style="10" customWidth="1"/>
+    <col min="8710" max="8710" width="19.125" style="10" customWidth="1"/>
+    <col min="8711" max="8712" width="5.875" style="10" customWidth="1"/>
+    <col min="8713" max="8713" width="6.625" style="10" customWidth="1"/>
+    <col min="8714" max="8714" width="8.125" style="10" customWidth="1"/>
+    <col min="8715" max="8715" width="10.125" style="10" customWidth="1"/>
+    <col min="8716" max="8716" width="7.25" style="10" customWidth="1"/>
+    <col min="8717" max="8717" width="11.875" style="10" customWidth="1"/>
+    <col min="8718" max="8718" width="2.125" style="10" customWidth="1"/>
+    <col min="8719" max="8720" width="12.5" style="10" customWidth="1"/>
+    <col min="8721" max="8954" width="9" style="10"/>
+    <col min="8955" max="8955" width="6.875" style="10" customWidth="1"/>
+    <col min="8956" max="8956" width="10.125" style="10" customWidth="1"/>
+    <col min="8957" max="8957" width="11.125" style="10" customWidth="1"/>
+    <col min="8958" max="8958" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="8959" max="8959" width="21.625" style="10" customWidth="1"/>
+    <col min="8960" max="8960" width="6.25" style="10" customWidth="1"/>
+    <col min="8961" max="8961" width="12.125" style="10" customWidth="1"/>
+    <col min="8962" max="8962" width="20.125" style="10" customWidth="1"/>
+    <col min="8963" max="8963" width="26.75" style="10" customWidth="1"/>
+    <col min="8964" max="8964" width="13.375" style="10" customWidth="1"/>
+    <col min="8965" max="8965" width="17" style="10" customWidth="1"/>
+    <col min="8966" max="8966" width="19.125" style="10" customWidth="1"/>
+    <col min="8967" max="8968" width="5.875" style="10" customWidth="1"/>
+    <col min="8969" max="8969" width="6.625" style="10" customWidth="1"/>
+    <col min="8970" max="8970" width="8.125" style="10" customWidth="1"/>
+    <col min="8971" max="8971" width="10.125" style="10" customWidth="1"/>
+    <col min="8972" max="8972" width="7.25" style="10" customWidth="1"/>
+    <col min="8973" max="8973" width="11.875" style="10" customWidth="1"/>
+    <col min="8974" max="8974" width="2.125" style="10" customWidth="1"/>
+    <col min="8975" max="8976" width="12.5" style="10" customWidth="1"/>
+    <col min="8977" max="9210" width="9" style="10"/>
+    <col min="9211" max="9211" width="6.875" style="10" customWidth="1"/>
+    <col min="9212" max="9212" width="10.125" style="10" customWidth="1"/>
+    <col min="9213" max="9213" width="11.125" style="10" customWidth="1"/>
+    <col min="9214" max="9214" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="9215" max="9215" width="21.625" style="10" customWidth="1"/>
+    <col min="9216" max="9216" width="6.25" style="10" customWidth="1"/>
+    <col min="9217" max="9217" width="12.125" style="10" customWidth="1"/>
+    <col min="9218" max="9218" width="20.125" style="10" customWidth="1"/>
+    <col min="9219" max="9219" width="26.75" style="10" customWidth="1"/>
+    <col min="9220" max="9220" width="13.375" style="10" customWidth="1"/>
+    <col min="9221" max="9221" width="17" style="10" customWidth="1"/>
+    <col min="9222" max="9222" width="19.125" style="10" customWidth="1"/>
+    <col min="9223" max="9224" width="5.875" style="10" customWidth="1"/>
+    <col min="9225" max="9225" width="6.625" style="10" customWidth="1"/>
+    <col min="9226" max="9226" width="8.125" style="10" customWidth="1"/>
+    <col min="9227" max="9227" width="10.125" style="10" customWidth="1"/>
+    <col min="9228" max="9228" width="7.25" style="10" customWidth="1"/>
+    <col min="9229" max="9229" width="11.875" style="10" customWidth="1"/>
+    <col min="9230" max="9230" width="2.125" style="10" customWidth="1"/>
+    <col min="9231" max="9232" width="12.5" style="10" customWidth="1"/>
+    <col min="9233" max="9466" width="9" style="10"/>
+    <col min="9467" max="9467" width="6.875" style="10" customWidth="1"/>
+    <col min="9468" max="9468" width="10.125" style="10" customWidth="1"/>
+    <col min="9469" max="9469" width="11.125" style="10" customWidth="1"/>
+    <col min="9470" max="9470" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="9471" max="9471" width="21.625" style="10" customWidth="1"/>
+    <col min="9472" max="9472" width="6.25" style="10" customWidth="1"/>
+    <col min="9473" max="9473" width="12.125" style="10" customWidth="1"/>
+    <col min="9474" max="9474" width="20.125" style="10" customWidth="1"/>
+    <col min="9475" max="9475" width="26.75" style="10" customWidth="1"/>
+    <col min="9476" max="9476" width="13.375" style="10" customWidth="1"/>
+    <col min="9477" max="9477" width="17" style="10" customWidth="1"/>
+    <col min="9478" max="9478" width="19.125" style="10" customWidth="1"/>
+    <col min="9479" max="9480" width="5.875" style="10" customWidth="1"/>
+    <col min="9481" max="9481" width="6.625" style="10" customWidth="1"/>
+    <col min="9482" max="9482" width="8.125" style="10" customWidth="1"/>
+    <col min="9483" max="9483" width="10.125" style="10" customWidth="1"/>
+    <col min="9484" max="9484" width="7.25" style="10" customWidth="1"/>
+    <col min="9485" max="9485" width="11.875" style="10" customWidth="1"/>
+    <col min="9486" max="9486" width="2.125" style="10" customWidth="1"/>
+    <col min="9487" max="9488" width="12.5" style="10" customWidth="1"/>
+    <col min="9489" max="9722" width="9" style="10"/>
+    <col min="9723" max="9723" width="6.875" style="10" customWidth="1"/>
+    <col min="9724" max="9724" width="10.125" style="10" customWidth="1"/>
+    <col min="9725" max="9725" width="11.125" style="10" customWidth="1"/>
+    <col min="9726" max="9726" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="9727" max="9727" width="21.625" style="10" customWidth="1"/>
+    <col min="9728" max="9728" width="6.25" style="10" customWidth="1"/>
+    <col min="9729" max="9729" width="12.125" style="10" customWidth="1"/>
+    <col min="9730" max="9730" width="20.125" style="10" customWidth="1"/>
+    <col min="9731" max="9731" width="26.75" style="10" customWidth="1"/>
+    <col min="9732" max="9732" width="13.375" style="10" customWidth="1"/>
+    <col min="9733" max="9733" width="17" style="10" customWidth="1"/>
+    <col min="9734" max="9734" width="19.125" style="10" customWidth="1"/>
+    <col min="9735" max="9736" width="5.875" style="10" customWidth="1"/>
+    <col min="9737" max="9737" width="6.625" style="10" customWidth="1"/>
+    <col min="9738" max="9738" width="8.125" style="10" customWidth="1"/>
+    <col min="9739" max="9739" width="10.125" style="10" customWidth="1"/>
+    <col min="9740" max="9740" width="7.25" style="10" customWidth="1"/>
+    <col min="9741" max="9741" width="11.875" style="10" customWidth="1"/>
+    <col min="9742" max="9742" width="2.125" style="10" customWidth="1"/>
+    <col min="9743" max="9744" width="12.5" style="10" customWidth="1"/>
+    <col min="9745" max="9978" width="9" style="10"/>
+    <col min="9979" max="9979" width="6.875" style="10" customWidth="1"/>
+    <col min="9980" max="9980" width="10.125" style="10" customWidth="1"/>
+    <col min="9981" max="9981" width="11.125" style="10" customWidth="1"/>
+    <col min="9982" max="9982" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="9983" max="9983" width="21.625" style="10" customWidth="1"/>
+    <col min="9984" max="9984" width="6.25" style="10" customWidth="1"/>
+    <col min="9985" max="9985" width="12.125" style="10" customWidth="1"/>
+    <col min="9986" max="9986" width="20.125" style="10" customWidth="1"/>
+    <col min="9987" max="9987" width="26.75" style="10" customWidth="1"/>
+    <col min="9988" max="9988" width="13.375" style="10" customWidth="1"/>
+    <col min="9989" max="9989" width="17" style="10" customWidth="1"/>
+    <col min="9990" max="9990" width="19.125" style="10" customWidth="1"/>
+    <col min="9991" max="9992" width="5.875" style="10" customWidth="1"/>
+    <col min="9993" max="9993" width="6.625" style="10" customWidth="1"/>
+    <col min="9994" max="9994" width="8.125" style="10" customWidth="1"/>
+    <col min="9995" max="9995" width="10.125" style="10" customWidth="1"/>
+    <col min="9996" max="9996" width="7.25" style="10" customWidth="1"/>
+    <col min="9997" max="9997" width="11.875" style="10" customWidth="1"/>
+    <col min="9998" max="9998" width="2.125" style="10" customWidth="1"/>
+    <col min="9999" max="10000" width="12.5" style="10" customWidth="1"/>
+    <col min="10001" max="10234" width="9" style="10"/>
+    <col min="10235" max="10235" width="6.875" style="10" customWidth="1"/>
+    <col min="10236" max="10236" width="10.125" style="10" customWidth="1"/>
+    <col min="10237" max="10237" width="11.125" style="10" customWidth="1"/>
+    <col min="10238" max="10238" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="10239" max="10239" width="21.625" style="10" customWidth="1"/>
+    <col min="10240" max="10240" width="6.25" style="10" customWidth="1"/>
+    <col min="10241" max="10241" width="12.125" style="10" customWidth="1"/>
+    <col min="10242" max="10242" width="20.125" style="10" customWidth="1"/>
+    <col min="10243" max="10243" width="26.75" style="10" customWidth="1"/>
+    <col min="10244" max="10244" width="13.375" style="10" customWidth="1"/>
+    <col min="10245" max="10245" width="17" style="10" customWidth="1"/>
+    <col min="10246" max="10246" width="19.125" style="10" customWidth="1"/>
+    <col min="10247" max="10248" width="5.875" style="10" customWidth="1"/>
+    <col min="10249" max="10249" width="6.625" style="10" customWidth="1"/>
+    <col min="10250" max="10250" width="8.125" style="10" customWidth="1"/>
+    <col min="10251" max="10251" width="10.125" style="10" customWidth="1"/>
+    <col min="10252" max="10252" width="7.25" style="10" customWidth="1"/>
+    <col min="10253" max="10253" width="11.875" style="10" customWidth="1"/>
+    <col min="10254" max="10254" width="2.125" style="10" customWidth="1"/>
+    <col min="10255" max="10256" width="12.5" style="10" customWidth="1"/>
+    <col min="10257" max="10490" width="9" style="10"/>
+    <col min="10491" max="10491" width="6.875" style="10" customWidth="1"/>
+    <col min="10492" max="10492" width="10.125" style="10" customWidth="1"/>
+    <col min="10493" max="10493" width="11.125" style="10" customWidth="1"/>
+    <col min="10494" max="10494" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="10495" max="10495" width="21.625" style="10" customWidth="1"/>
+    <col min="10496" max="10496" width="6.25" style="10" customWidth="1"/>
+    <col min="10497" max="10497" width="12.125" style="10" customWidth="1"/>
+    <col min="10498" max="10498" width="20.125" style="10" customWidth="1"/>
+    <col min="10499" max="10499" width="26.75" style="10" customWidth="1"/>
+    <col min="10500" max="10500" width="13.375" style="10" customWidth="1"/>
+    <col min="10501" max="10501" width="17" style="10" customWidth="1"/>
+    <col min="10502" max="10502" width="19.125" style="10" customWidth="1"/>
+    <col min="10503" max="10504" width="5.875" style="10" customWidth="1"/>
+    <col min="10505" max="10505" width="6.625" style="10" customWidth="1"/>
+    <col min="10506" max="10506" width="8.125" style="10" customWidth="1"/>
+    <col min="10507" max="10507" width="10.125" style="10" customWidth="1"/>
+    <col min="10508" max="10508" width="7.25" style="10" customWidth="1"/>
+    <col min="10509" max="10509" width="11.875" style="10" customWidth="1"/>
+    <col min="10510" max="10510" width="2.125" style="10" customWidth="1"/>
+    <col min="10511" max="10512" width="12.5" style="10" customWidth="1"/>
+    <col min="10513" max="10746" width="9" style="10"/>
+    <col min="10747" max="10747" width="6.875" style="10" customWidth="1"/>
+    <col min="10748" max="10748" width="10.125" style="10" customWidth="1"/>
+    <col min="10749" max="10749" width="11.125" style="10" customWidth="1"/>
+    <col min="10750" max="10750" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="10751" max="10751" width="21.625" style="10" customWidth="1"/>
+    <col min="10752" max="10752" width="6.25" style="10" customWidth="1"/>
+    <col min="10753" max="10753" width="12.125" style="10" customWidth="1"/>
+    <col min="10754" max="10754" width="20.125" style="10" customWidth="1"/>
+    <col min="10755" max="10755" width="26.75" style="10" customWidth="1"/>
+    <col min="10756" max="10756" width="13.375" style="10" customWidth="1"/>
+    <col min="10757" max="10757" width="17" style="10" customWidth="1"/>
+    <col min="10758" max="10758" width="19.125" style="10" customWidth="1"/>
+    <col min="10759" max="10760" width="5.875" style="10" customWidth="1"/>
+    <col min="10761" max="10761" width="6.625" style="10" customWidth="1"/>
+    <col min="10762" max="10762" width="8.125" style="10" customWidth="1"/>
+    <col min="10763" max="10763" width="10.125" style="10" customWidth="1"/>
+    <col min="10764" max="10764" width="7.25" style="10" customWidth="1"/>
+    <col min="10765" max="10765" width="11.875" style="10" customWidth="1"/>
+    <col min="10766" max="10766" width="2.125" style="10" customWidth="1"/>
+    <col min="10767" max="10768" width="12.5" style="10" customWidth="1"/>
+    <col min="10769" max="11002" width="9" style="10"/>
+    <col min="11003" max="11003" width="6.875" style="10" customWidth="1"/>
+    <col min="11004" max="11004" width="10.125" style="10" customWidth="1"/>
+    <col min="11005" max="11005" width="11.125" style="10" customWidth="1"/>
+    <col min="11006" max="11006" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="11007" max="11007" width="21.625" style="10" customWidth="1"/>
+    <col min="11008" max="11008" width="6.25" style="10" customWidth="1"/>
+    <col min="11009" max="11009" width="12.125" style="10" customWidth="1"/>
+    <col min="11010" max="11010" width="20.125" style="10" customWidth="1"/>
+    <col min="11011" max="11011" width="26.75" style="10" customWidth="1"/>
+    <col min="11012" max="11012" width="13.375" style="10" customWidth="1"/>
+    <col min="11013" max="11013" width="17" style="10" customWidth="1"/>
+    <col min="11014" max="11014" width="19.125" style="10" customWidth="1"/>
+    <col min="11015" max="11016" width="5.875" style="10" customWidth="1"/>
+    <col min="11017" max="11017" width="6.625" style="10" customWidth="1"/>
+    <col min="11018" max="11018" width="8.125" style="10" customWidth="1"/>
+    <col min="11019" max="11019" width="10.125" style="10" customWidth="1"/>
+    <col min="11020" max="11020" width="7.25" style="10" customWidth="1"/>
+    <col min="11021" max="11021" width="11.875" style="10" customWidth="1"/>
+    <col min="11022" max="11022" width="2.125" style="10" customWidth="1"/>
+    <col min="11023" max="11024" width="12.5" style="10" customWidth="1"/>
+    <col min="11025" max="11258" width="9" style="10"/>
+    <col min="11259" max="11259" width="6.875" style="10" customWidth="1"/>
+    <col min="11260" max="11260" width="10.125" style="10" customWidth="1"/>
+    <col min="11261" max="11261" width="11.125" style="10" customWidth="1"/>
+    <col min="11262" max="11262" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="11263" max="11263" width="21.625" style="10" customWidth="1"/>
+    <col min="11264" max="11264" width="6.25" style="10" customWidth="1"/>
+    <col min="11265" max="11265" width="12.125" style="10" customWidth="1"/>
+    <col min="11266" max="11266" width="20.125" style="10" customWidth="1"/>
+    <col min="11267" max="11267" width="26.75" style="10" customWidth="1"/>
+    <col min="11268" max="11268" width="13.375" style="10" customWidth="1"/>
+    <col min="11269" max="11269" width="17" style="10" customWidth="1"/>
+    <col min="11270" max="11270" width="19.125" style="10" customWidth="1"/>
+    <col min="11271" max="11272" width="5.875" style="10" customWidth="1"/>
+    <col min="11273" max="11273" width="6.625" style="10" customWidth="1"/>
+    <col min="11274" max="11274" width="8.125" style="10" customWidth="1"/>
+    <col min="11275" max="11275" width="10.125" style="10" customWidth="1"/>
+    <col min="11276" max="11276" width="7.25" style="10" customWidth="1"/>
+    <col min="11277" max="11277" width="11.875" style="10" customWidth="1"/>
+    <col min="11278" max="11278" width="2.125" style="10" customWidth="1"/>
+    <col min="11279" max="11280" width="12.5" style="10" customWidth="1"/>
+    <col min="11281" max="11514" width="9" style="10"/>
+    <col min="11515" max="11515" width="6.875" style="10" customWidth="1"/>
+    <col min="11516" max="11516" width="10.125" style="10" customWidth="1"/>
+    <col min="11517" max="11517" width="11.125" style="10" customWidth="1"/>
+    <col min="11518" max="11518" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="11519" max="11519" width="21.625" style="10" customWidth="1"/>
+    <col min="11520" max="11520" width="6.25" style="10" customWidth="1"/>
+    <col min="11521" max="11521" width="12.125" style="10" customWidth="1"/>
+    <col min="11522" max="11522" width="20.125" style="10" customWidth="1"/>
+    <col min="11523" max="11523" width="26.75" style="10" customWidth="1"/>
+    <col min="11524" max="11524" width="13.375" style="10" customWidth="1"/>
+    <col min="11525" max="11525" width="17" style="10" customWidth="1"/>
+    <col min="11526" max="11526" width="19.125" style="10" customWidth="1"/>
+    <col min="11527" max="11528" width="5.875" style="10" customWidth="1"/>
+    <col min="11529" max="11529" width="6.625" style="10" customWidth="1"/>
+    <col min="11530" max="11530" width="8.125" style="10" customWidth="1"/>
+    <col min="11531" max="11531" width="10.125" style="10" customWidth="1"/>
+    <col min="11532" max="11532" width="7.25" style="10" customWidth="1"/>
+    <col min="11533" max="11533" width="11.875" style="10" customWidth="1"/>
+    <col min="11534" max="11534" width="2.125" style="10" customWidth="1"/>
+    <col min="11535" max="11536" width="12.5" style="10" customWidth="1"/>
+    <col min="11537" max="11770" width="9" style="10"/>
+    <col min="11771" max="11771" width="6.875" style="10" customWidth="1"/>
+    <col min="11772" max="11772" width="10.125" style="10" customWidth="1"/>
+    <col min="11773" max="11773" width="11.125" style="10" customWidth="1"/>
+    <col min="11774" max="11774" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="11775" max="11775" width="21.625" style="10" customWidth="1"/>
+    <col min="11776" max="11776" width="6.25" style="10" customWidth="1"/>
+    <col min="11777" max="11777" width="12.125" style="10" customWidth="1"/>
+    <col min="11778" max="11778" width="20.125" style="10" customWidth="1"/>
+    <col min="11779" max="11779" width="26.75" style="10" customWidth="1"/>
+    <col min="11780" max="11780" width="13.375" style="10" customWidth="1"/>
+    <col min="11781" max="11781" width="17" style="10" customWidth="1"/>
+    <col min="11782" max="11782" width="19.125" style="10" customWidth="1"/>
+    <col min="11783" max="11784" width="5.875" style="10" customWidth="1"/>
+    <col min="11785" max="11785" width="6.625" style="10" customWidth="1"/>
+    <col min="11786" max="11786" width="8.125" style="10" customWidth="1"/>
+    <col min="11787" max="11787" width="10.125" style="10" customWidth="1"/>
+    <col min="11788" max="11788" width="7.25" style="10" customWidth="1"/>
+    <col min="11789" max="11789" width="11.875" style="10" customWidth="1"/>
+    <col min="11790" max="11790" width="2.125" style="10" customWidth="1"/>
+    <col min="11791" max="11792" width="12.5" style="10" customWidth="1"/>
+    <col min="11793" max="12026" width="9" style="10"/>
+    <col min="12027" max="12027" width="6.875" style="10" customWidth="1"/>
+    <col min="12028" max="12028" width="10.125" style="10" customWidth="1"/>
+    <col min="12029" max="12029" width="11.125" style="10" customWidth="1"/>
+    <col min="12030" max="12030" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="12031" max="12031" width="21.625" style="10" customWidth="1"/>
+    <col min="12032" max="12032" width="6.25" style="10" customWidth="1"/>
+    <col min="12033" max="12033" width="12.125" style="10" customWidth="1"/>
+    <col min="12034" max="12034" width="20.125" style="10" customWidth="1"/>
+    <col min="12035" max="12035" width="26.75" style="10" customWidth="1"/>
+    <col min="12036" max="12036" width="13.375" style="10" customWidth="1"/>
+    <col min="12037" max="12037" width="17" style="10" customWidth="1"/>
+    <col min="12038" max="12038" width="19.125" style="10" customWidth="1"/>
+    <col min="12039" max="12040" width="5.875" style="10" customWidth="1"/>
+    <col min="12041" max="12041" width="6.625" style="10" customWidth="1"/>
+    <col min="12042" max="12042" width="8.125" style="10" customWidth="1"/>
+    <col min="12043" max="12043" width="10.125" style="10" customWidth="1"/>
+    <col min="12044" max="12044" width="7.25" style="10" customWidth="1"/>
+    <col min="12045" max="12045" width="11.875" style="10" customWidth="1"/>
+    <col min="12046" max="12046" width="2.125" style="10" customWidth="1"/>
+    <col min="12047" max="12048" width="12.5" style="10" customWidth="1"/>
+    <col min="12049" max="12282" width="9" style="10"/>
+    <col min="12283" max="12283" width="6.875" style="10" customWidth="1"/>
+    <col min="12284" max="12284" width="10.125" style="10" customWidth="1"/>
+    <col min="12285" max="12285" width="11.125" style="10" customWidth="1"/>
+    <col min="12286" max="12286" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="12287" max="12287" width="21.625" style="10" customWidth="1"/>
+    <col min="12288" max="12288" width="6.25" style="10" customWidth="1"/>
+    <col min="12289" max="12289" width="12.125" style="10" customWidth="1"/>
+    <col min="12290" max="12290" width="20.125" style="10" customWidth="1"/>
+    <col min="12291" max="12291" width="26.75" style="10" customWidth="1"/>
+    <col min="12292" max="12292" width="13.375" style="10" customWidth="1"/>
+    <col min="12293" max="12293" width="17" style="10" customWidth="1"/>
+    <col min="12294" max="12294" width="19.125" style="10" customWidth="1"/>
+    <col min="12295" max="12296" width="5.875" style="10" customWidth="1"/>
+    <col min="12297" max="12297" width="6.625" style="10" customWidth="1"/>
+    <col min="12298" max="12298" width="8.125" style="10" customWidth="1"/>
+    <col min="12299" max="12299" width="10.125" style="10" customWidth="1"/>
+    <col min="12300" max="12300" width="7.25" style="10" customWidth="1"/>
+    <col min="12301" max="12301" width="11.875" style="10" customWidth="1"/>
+    <col min="12302" max="12302" width="2.125" style="10" customWidth="1"/>
+    <col min="12303" max="12304" width="12.5" style="10" customWidth="1"/>
+    <col min="12305" max="12538" width="9" style="10"/>
+    <col min="12539" max="12539" width="6.875" style="10" customWidth="1"/>
+    <col min="12540" max="12540" width="10.125" style="10" customWidth="1"/>
+    <col min="12541" max="12541" width="11.125" style="10" customWidth="1"/>
+    <col min="12542" max="12542" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="12543" max="12543" width="21.625" style="10" customWidth="1"/>
+    <col min="12544" max="12544" width="6.25" style="10" customWidth="1"/>
+    <col min="12545" max="12545" width="12.125" style="10" customWidth="1"/>
+    <col min="12546" max="12546" width="20.125" style="10" customWidth="1"/>
+    <col min="12547" max="12547" width="26.75" style="10" customWidth="1"/>
+    <col min="12548" max="12548" width="13.375" style="10" customWidth="1"/>
+    <col min="12549" max="12549" width="17" style="10" customWidth="1"/>
+    <col min="12550" max="12550" width="19.125" style="10" customWidth="1"/>
+    <col min="12551" max="12552" width="5.875" style="10" customWidth="1"/>
+    <col min="12553" max="12553" width="6.625" style="10" customWidth="1"/>
+    <col min="12554" max="12554" width="8.125" style="10" customWidth="1"/>
+    <col min="12555" max="12555" width="10.125" style="10" customWidth="1"/>
+    <col min="12556" max="12556" width="7.25" style="10" customWidth="1"/>
+    <col min="12557" max="12557" width="11.875" style="10" customWidth="1"/>
+    <col min="12558" max="12558" width="2.125" style="10" customWidth="1"/>
+    <col min="12559" max="12560" width="12.5" style="10" customWidth="1"/>
+    <col min="12561" max="12794" width="9" style="10"/>
+    <col min="12795" max="12795" width="6.875" style="10" customWidth="1"/>
+    <col min="12796" max="12796" width="10.125" style="10" customWidth="1"/>
+    <col min="12797" max="12797" width="11.125" style="10" customWidth="1"/>
+    <col min="12798" max="12798" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="12799" max="12799" width="21.625" style="10" customWidth="1"/>
+    <col min="12800" max="12800" width="6.25" style="10" customWidth="1"/>
+    <col min="12801" max="12801" width="12.125" style="10" customWidth="1"/>
+    <col min="12802" max="12802" width="20.125" style="10" customWidth="1"/>
+    <col min="12803" max="12803" width="26.75" style="10" customWidth="1"/>
+    <col min="12804" max="12804" width="13.375" style="10" customWidth="1"/>
+    <col min="12805" max="12805" width="17" style="10" customWidth="1"/>
+    <col min="12806" max="12806" width="19.125" style="10" customWidth="1"/>
+    <col min="12807" max="12808" width="5.875" style="10" customWidth="1"/>
+    <col min="12809" max="12809" width="6.625" style="10" customWidth="1"/>
+    <col min="12810" max="12810" width="8.125" style="10" customWidth="1"/>
+    <col min="12811" max="12811" width="10.125" style="10" customWidth="1"/>
+    <col min="12812" max="12812" width="7.25" style="10" customWidth="1"/>
+    <col min="12813" max="12813" width="11.875" style="10" customWidth="1"/>
+    <col min="12814" max="12814" width="2.125" style="10" customWidth="1"/>
+    <col min="12815" max="12816" width="12.5" style="10" customWidth="1"/>
+    <col min="12817" max="13050" width="9" style="10"/>
+    <col min="13051" max="13051" width="6.875" style="10" customWidth="1"/>
+    <col min="13052" max="13052" width="10.125" style="10" customWidth="1"/>
+    <col min="13053" max="13053" width="11.125" style="10" customWidth="1"/>
+    <col min="13054" max="13054" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="13055" max="13055" width="21.625" style="10" customWidth="1"/>
+    <col min="13056" max="13056" width="6.25" style="10" customWidth="1"/>
+    <col min="13057" max="13057" width="12.125" style="10" customWidth="1"/>
+    <col min="13058" max="13058" width="20.125" style="10" customWidth="1"/>
+    <col min="13059" max="13059" width="26.75" style="10" customWidth="1"/>
+    <col min="13060" max="13060" width="13.375" style="10" customWidth="1"/>
+    <col min="13061" max="13061" width="17" style="10" customWidth="1"/>
+    <col min="13062" max="13062" width="19.125" style="10" customWidth="1"/>
+    <col min="13063" max="13064" width="5.875" style="10" customWidth="1"/>
+    <col min="13065" max="13065" width="6.625" style="10" customWidth="1"/>
+    <col min="13066" max="13066" width="8.125" style="10" customWidth="1"/>
+    <col min="13067" max="13067" width="10.125" style="10" customWidth="1"/>
+    <col min="13068" max="13068" width="7.25" style="10" customWidth="1"/>
+    <col min="13069" max="13069" width="11.875" style="10" customWidth="1"/>
+    <col min="13070" max="13070" width="2.125" style="10" customWidth="1"/>
+    <col min="13071" max="13072" width="12.5" style="10" customWidth="1"/>
+    <col min="13073" max="13306" width="9" style="10"/>
+    <col min="13307" max="13307" width="6.875" style="10" customWidth="1"/>
+    <col min="13308" max="13308" width="10.125" style="10" customWidth="1"/>
+    <col min="13309" max="13309" width="11.125" style="10" customWidth="1"/>
+    <col min="13310" max="13310" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="13311" max="13311" width="21.625" style="10" customWidth="1"/>
+    <col min="13312" max="13312" width="6.25" style="10" customWidth="1"/>
+    <col min="13313" max="13313" width="12.125" style="10" customWidth="1"/>
+    <col min="13314" max="13314" width="20.125" style="10" customWidth="1"/>
+    <col min="13315" max="13315" width="26.75" style="10" customWidth="1"/>
+    <col min="13316" max="13316" width="13.375" style="10" customWidth="1"/>
+    <col min="13317" max="13317" width="17" style="10" customWidth="1"/>
+    <col min="13318" max="13318" width="19.125" style="10" customWidth="1"/>
+    <col min="13319" max="13320" width="5.875" style="10" customWidth="1"/>
+    <col min="13321" max="13321" width="6.625" style="10" customWidth="1"/>
+    <col min="13322" max="13322" width="8.125" style="10" customWidth="1"/>
+    <col min="13323" max="13323" width="10.125" style="10" customWidth="1"/>
+    <col min="13324" max="13324" width="7.25" style="10" customWidth="1"/>
+    <col min="13325" max="13325" width="11.875" style="10" customWidth="1"/>
+    <col min="13326" max="13326" width="2.125" style="10" customWidth="1"/>
+    <col min="13327" max="13328" width="12.5" style="10" customWidth="1"/>
+    <col min="13329" max="13562" width="9" style="10"/>
+    <col min="13563" max="13563" width="6.875" style="10" customWidth="1"/>
+    <col min="13564" max="13564" width="10.125" style="10" customWidth="1"/>
+    <col min="13565" max="13565" width="11.125" style="10" customWidth="1"/>
+    <col min="13566" max="13566" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="13567" max="13567" width="21.625" style="10" customWidth="1"/>
+    <col min="13568" max="13568" width="6.25" style="10" customWidth="1"/>
+    <col min="13569" max="13569" width="12.125" style="10" customWidth="1"/>
+    <col min="13570" max="13570" width="20.125" style="10" customWidth="1"/>
+    <col min="13571" max="13571" width="26.75" style="10" customWidth="1"/>
+    <col min="13572" max="13572" width="13.375" style="10" customWidth="1"/>
+    <col min="13573" max="13573" width="17" style="10" customWidth="1"/>
+    <col min="13574" max="13574" width="19.125" style="10" customWidth="1"/>
+    <col min="13575" max="13576" width="5.875" style="10" customWidth="1"/>
+    <col min="13577" max="13577" width="6.625" style="10" customWidth="1"/>
+    <col min="13578" max="13578" width="8.125" style="10" customWidth="1"/>
+    <col min="13579" max="13579" width="10.125" style="10" customWidth="1"/>
+    <col min="13580" max="13580" width="7.25" style="10" customWidth="1"/>
+    <col min="13581" max="13581" width="11.875" style="10" customWidth="1"/>
+    <col min="13582" max="13582" width="2.125" style="10" customWidth="1"/>
+    <col min="13583" max="13584" width="12.5" style="10" customWidth="1"/>
+    <col min="13585" max="13818" width="9" style="10"/>
+    <col min="13819" max="13819" width="6.875" style="10" customWidth="1"/>
+    <col min="13820" max="13820" width="10.125" style="10" customWidth="1"/>
+    <col min="13821" max="13821" width="11.125" style="10" customWidth="1"/>
+    <col min="13822" max="13822" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="13823" max="13823" width="21.625" style="10" customWidth="1"/>
+    <col min="13824" max="13824" width="6.25" style="10" customWidth="1"/>
+    <col min="13825" max="13825" width="12.125" style="10" customWidth="1"/>
+    <col min="13826" max="13826" width="20.125" style="10" customWidth="1"/>
+    <col min="13827" max="13827" width="26.75" style="10" customWidth="1"/>
+    <col min="13828" max="13828" width="13.375" style="10" customWidth="1"/>
+    <col min="13829" max="13829" width="17" style="10" customWidth="1"/>
+    <col min="13830" max="13830" width="19.125" style="10" customWidth="1"/>
+    <col min="13831" max="13832" width="5.875" style="10" customWidth="1"/>
+    <col min="13833" max="13833" width="6.625" style="10" customWidth="1"/>
+    <col min="13834" max="13834" width="8.125" style="10" customWidth="1"/>
+    <col min="13835" max="13835" width="10.125" style="10" customWidth="1"/>
+    <col min="13836" max="13836" width="7.25" style="10" customWidth="1"/>
+    <col min="13837" max="13837" width="11.875" style="10" customWidth="1"/>
+    <col min="13838" max="13838" width="2.125" style="10" customWidth="1"/>
+    <col min="13839" max="13840" width="12.5" style="10" customWidth="1"/>
+    <col min="13841" max="14074" width="9" style="10"/>
+    <col min="14075" max="14075" width="6.875" style="10" customWidth="1"/>
+    <col min="14076" max="14076" width="10.125" style="10" customWidth="1"/>
+    <col min="14077" max="14077" width="11.125" style="10" customWidth="1"/>
+    <col min="14078" max="14078" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="14079" max="14079" width="21.625" style="10" customWidth="1"/>
+    <col min="14080" max="14080" width="6.25" style="10" customWidth="1"/>
+    <col min="14081" max="14081" width="12.125" style="10" customWidth="1"/>
+    <col min="14082" max="14082" width="20.125" style="10" customWidth="1"/>
+    <col min="14083" max="14083" width="26.75" style="10" customWidth="1"/>
+    <col min="14084" max="14084" width="13.375" style="10" customWidth="1"/>
+    <col min="14085" max="14085" width="17" style="10" customWidth="1"/>
+    <col min="14086" max="14086" width="19.125" style="10" customWidth="1"/>
+    <col min="14087" max="14088" width="5.875" style="10" customWidth="1"/>
+    <col min="14089" max="14089" width="6.625" style="10" customWidth="1"/>
+    <col min="14090" max="14090" width="8.125" style="10" customWidth="1"/>
+    <col min="14091" max="14091" width="10.125" style="10" customWidth="1"/>
+    <col min="14092" max="14092" width="7.25" style="10" customWidth="1"/>
+    <col min="14093" max="14093" width="11.875" style="10" customWidth="1"/>
+    <col min="14094" max="14094" width="2.125" style="10" customWidth="1"/>
+    <col min="14095" max="14096" width="12.5" style="10" customWidth="1"/>
+    <col min="14097" max="14330" width="9" style="10"/>
+    <col min="14331" max="14331" width="6.875" style="10" customWidth="1"/>
+    <col min="14332" max="14332" width="10.125" style="10" customWidth="1"/>
+    <col min="14333" max="14333" width="11.125" style="10" customWidth="1"/>
+    <col min="14334" max="14334" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="14335" max="14335" width="21.625" style="10" customWidth="1"/>
+    <col min="14336" max="14336" width="6.25" style="10" customWidth="1"/>
+    <col min="14337" max="14337" width="12.125" style="10" customWidth="1"/>
+    <col min="14338" max="14338" width="20.125" style="10" customWidth="1"/>
+    <col min="14339" max="14339" width="26.75" style="10" customWidth="1"/>
+    <col min="14340" max="14340" width="13.375" style="10" customWidth="1"/>
+    <col min="14341" max="14341" width="17" style="10" customWidth="1"/>
+    <col min="14342" max="14342" width="19.125" style="10" customWidth="1"/>
+    <col min="14343" max="14344" width="5.875" style="10" customWidth="1"/>
+    <col min="14345" max="14345" width="6.625" style="10" customWidth="1"/>
+    <col min="14346" max="14346" width="8.125" style="10" customWidth="1"/>
+    <col min="14347" max="14347" width="10.125" style="10" customWidth="1"/>
+    <col min="14348" max="14348" width="7.25" style="10" customWidth="1"/>
+    <col min="14349" max="14349" width="11.875" style="10" customWidth="1"/>
+    <col min="14350" max="14350" width="2.125" style="10" customWidth="1"/>
+    <col min="14351" max="14352" width="12.5" style="10" customWidth="1"/>
+    <col min="14353" max="14586" width="9" style="10"/>
+    <col min="14587" max="14587" width="6.875" style="10" customWidth="1"/>
+    <col min="14588" max="14588" width="10.125" style="10" customWidth="1"/>
+    <col min="14589" max="14589" width="11.125" style="10" customWidth="1"/>
+    <col min="14590" max="14590" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="14591" max="14591" width="21.625" style="10" customWidth="1"/>
+    <col min="14592" max="14592" width="6.25" style="10" customWidth="1"/>
+    <col min="14593" max="14593" width="12.125" style="10" customWidth="1"/>
+    <col min="14594" max="14594" width="20.125" style="10" customWidth="1"/>
+    <col min="14595" max="14595" width="26.75" style="10" customWidth="1"/>
+    <col min="14596" max="14596" width="13.375" style="10" customWidth="1"/>
+    <col min="14597" max="14597" width="17" style="10" customWidth="1"/>
+    <col min="14598" max="14598" width="19.125" style="10" customWidth="1"/>
+    <col min="14599" max="14600" width="5.875" style="10" customWidth="1"/>
+    <col min="14601" max="14601" width="6.625" style="10" customWidth="1"/>
+    <col min="14602" max="14602" width="8.125" style="10" customWidth="1"/>
+    <col min="14603" max="14603" width="10.125" style="10" customWidth="1"/>
+    <col min="14604" max="14604" width="7.25" style="10" customWidth="1"/>
+    <col min="14605" max="14605" width="11.875" style="10" customWidth="1"/>
+    <col min="14606" max="14606" width="2.125" style="10" customWidth="1"/>
+    <col min="14607" max="14608" width="12.5" style="10" customWidth="1"/>
+    <col min="14609" max="14842" width="9" style="10"/>
+    <col min="14843" max="14843" width="6.875" style="10" customWidth="1"/>
+    <col min="14844" max="14844" width="10.125" style="10" customWidth="1"/>
+    <col min="14845" max="14845" width="11.125" style="10" customWidth="1"/>
+    <col min="14846" max="14846" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="14847" max="14847" width="21.625" style="10" customWidth="1"/>
+    <col min="14848" max="14848" width="6.25" style="10" customWidth="1"/>
+    <col min="14849" max="14849" width="12.125" style="10" customWidth="1"/>
+    <col min="14850" max="14850" width="20.125" style="10" customWidth="1"/>
+    <col min="14851" max="14851" width="26.75" style="10" customWidth="1"/>
+    <col min="14852" max="14852" width="13.375" style="10" customWidth="1"/>
+    <col min="14853" max="14853" width="17" style="10" customWidth="1"/>
+    <col min="14854" max="14854" width="19.125" style="10" customWidth="1"/>
+    <col min="14855" max="14856" width="5.875" style="10" customWidth="1"/>
+    <col min="14857" max="14857" width="6.625" style="10" customWidth="1"/>
+    <col min="14858" max="14858" width="8.125" style="10" customWidth="1"/>
+    <col min="14859" max="14859" width="10.125" style="10" customWidth="1"/>
+    <col min="14860" max="14860" width="7.25" style="10" customWidth="1"/>
+    <col min="14861" max="14861" width="11.875" style="10" customWidth="1"/>
+    <col min="14862" max="14862" width="2.125" style="10" customWidth="1"/>
+    <col min="14863" max="14864" width="12.5" style="10" customWidth="1"/>
+    <col min="14865" max="15098" width="9" style="10"/>
+    <col min="15099" max="15099" width="6.875" style="10" customWidth="1"/>
+    <col min="15100" max="15100" width="10.125" style="10" customWidth="1"/>
+    <col min="15101" max="15101" width="11.125" style="10" customWidth="1"/>
+    <col min="15102" max="15102" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="15103" max="15103" width="21.625" style="10" customWidth="1"/>
+    <col min="15104" max="15104" width="6.25" style="10" customWidth="1"/>
+    <col min="15105" max="15105" width="12.125" style="10" customWidth="1"/>
+    <col min="15106" max="15106" width="20.125" style="10" customWidth="1"/>
+    <col min="15107" max="15107" width="26.75" style="10" customWidth="1"/>
+    <col min="15108" max="15108" width="13.375" style="10" customWidth="1"/>
+    <col min="15109" max="15109" width="17" style="10" customWidth="1"/>
+    <col min="15110" max="15110" width="19.125" style="10" customWidth="1"/>
+    <col min="15111" max="15112" width="5.875" style="10" customWidth="1"/>
+    <col min="15113" max="15113" width="6.625" style="10" customWidth="1"/>
+    <col min="15114" max="15114" width="8.125" style="10" customWidth="1"/>
+    <col min="15115" max="15115" width="10.125" style="10" customWidth="1"/>
+    <col min="15116" max="15116" width="7.25" style="10" customWidth="1"/>
+    <col min="15117" max="15117" width="11.875" style="10" customWidth="1"/>
+    <col min="15118" max="15118" width="2.125" style="10" customWidth="1"/>
+    <col min="15119" max="15120" width="12.5" style="10" customWidth="1"/>
+    <col min="15121" max="15354" width="9" style="10"/>
+    <col min="15355" max="15355" width="6.875" style="10" customWidth="1"/>
+    <col min="15356" max="15356" width="10.125" style="10" customWidth="1"/>
+    <col min="15357" max="15357" width="11.125" style="10" customWidth="1"/>
+    <col min="15358" max="15358" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="15359" max="15359" width="21.625" style="10" customWidth="1"/>
+    <col min="15360" max="15360" width="6.25" style="10" customWidth="1"/>
+    <col min="15361" max="15361" width="12.125" style="10" customWidth="1"/>
+    <col min="15362" max="15362" width="20.125" style="10" customWidth="1"/>
+    <col min="15363" max="15363" width="26.75" style="10" customWidth="1"/>
+    <col min="15364" max="15364" width="13.375" style="10" customWidth="1"/>
+    <col min="15365" max="15365" width="17" style="10" customWidth="1"/>
+    <col min="15366" max="15366" width="19.125" style="10" customWidth="1"/>
+    <col min="15367" max="15368" width="5.875" style="10" customWidth="1"/>
+    <col min="15369" max="15369" width="6.625" style="10" customWidth="1"/>
+    <col min="15370" max="15370" width="8.125" style="10" customWidth="1"/>
+    <col min="15371" max="15371" width="10.125" style="10" customWidth="1"/>
+    <col min="15372" max="15372" width="7.25" style="10" customWidth="1"/>
+    <col min="15373" max="15373" width="11.875" style="10" customWidth="1"/>
+    <col min="15374" max="15374" width="2.125" style="10" customWidth="1"/>
+    <col min="15375" max="15376" width="12.5" style="10" customWidth="1"/>
+    <col min="15377" max="15610" width="9" style="10"/>
+    <col min="15611" max="15611" width="6.875" style="10" customWidth="1"/>
+    <col min="15612" max="15612" width="10.125" style="10" customWidth="1"/>
+    <col min="15613" max="15613" width="11.125" style="10" customWidth="1"/>
+    <col min="15614" max="15614" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="15615" max="15615" width="21.625" style="10" customWidth="1"/>
+    <col min="15616" max="15616" width="6.25" style="10" customWidth="1"/>
+    <col min="15617" max="15617" width="12.125" style="10" customWidth="1"/>
+    <col min="15618" max="15618" width="20.125" style="10" customWidth="1"/>
+    <col min="15619" max="15619" width="26.75" style="10" customWidth="1"/>
+    <col min="15620" max="15620" width="13.375" style="10" customWidth="1"/>
+    <col min="15621" max="15621" width="17" style="10" customWidth="1"/>
+    <col min="15622" max="15622" width="19.125" style="10" customWidth="1"/>
+    <col min="15623" max="15624" width="5.875" style="10" customWidth="1"/>
+    <col min="15625" max="15625" width="6.625" style="10" customWidth="1"/>
+    <col min="15626" max="15626" width="8.125" style="10" customWidth="1"/>
+    <col min="15627" max="15627" width="10.125" style="10" customWidth="1"/>
+    <col min="15628" max="15628" width="7.25" style="10" customWidth="1"/>
+    <col min="15629" max="15629" width="11.875" style="10" customWidth="1"/>
+    <col min="15630" max="15630" width="2.125" style="10" customWidth="1"/>
+    <col min="15631" max="15632" width="12.5" style="10" customWidth="1"/>
+    <col min="15633" max="15866" width="9" style="10"/>
+    <col min="15867" max="15867" width="6.875" style="10" customWidth="1"/>
+    <col min="15868" max="15868" width="10.125" style="10" customWidth="1"/>
+    <col min="15869" max="15869" width="11.125" style="10" customWidth="1"/>
+    <col min="15870" max="15870" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="15871" max="15871" width="21.625" style="10" customWidth="1"/>
+    <col min="15872" max="15872" width="6.25" style="10" customWidth="1"/>
+    <col min="15873" max="15873" width="12.125" style="10" customWidth="1"/>
+    <col min="15874" max="15874" width="20.125" style="10" customWidth="1"/>
+    <col min="15875" max="15875" width="26.75" style="10" customWidth="1"/>
+    <col min="15876" max="15876" width="13.375" style="10" customWidth="1"/>
+    <col min="15877" max="15877" width="17" style="10" customWidth="1"/>
+    <col min="15878" max="15878" width="19.125" style="10" customWidth="1"/>
+    <col min="15879" max="15880" width="5.875" style="10" customWidth="1"/>
+    <col min="15881" max="15881" width="6.625" style="10" customWidth="1"/>
+    <col min="15882" max="15882" width="8.125" style="10" customWidth="1"/>
+    <col min="15883" max="15883" width="10.125" style="10" customWidth="1"/>
+    <col min="15884" max="15884" width="7.25" style="10" customWidth="1"/>
+    <col min="15885" max="15885" width="11.875" style="10" customWidth="1"/>
+    <col min="15886" max="15886" width="2.125" style="10" customWidth="1"/>
+    <col min="15887" max="15888" width="12.5" style="10" customWidth="1"/>
+    <col min="15889" max="16122" width="9" style="10"/>
+    <col min="16123" max="16123" width="6.875" style="10" customWidth="1"/>
+    <col min="16124" max="16124" width="10.125" style="10" customWidth="1"/>
+    <col min="16125" max="16125" width="11.125" style="10" customWidth="1"/>
+    <col min="16126" max="16126" width="9" style="10" hidden="1" customWidth="1"/>
+    <col min="16127" max="16127" width="21.625" style="10" customWidth="1"/>
+    <col min="16128" max="16128" width="6.25" style="10" customWidth="1"/>
+    <col min="16129" max="16129" width="12.125" style="10" customWidth="1"/>
+    <col min="16130" max="16130" width="20.125" style="10" customWidth="1"/>
+    <col min="16131" max="16131" width="26.75" style="10" customWidth="1"/>
+    <col min="16132" max="16132" width="13.375" style="10" customWidth="1"/>
+    <col min="16133" max="16133" width="17" style="10" customWidth="1"/>
+    <col min="16134" max="16134" width="19.125" style="10" customWidth="1"/>
+    <col min="16135" max="16136" width="5.875" style="10" customWidth="1"/>
+    <col min="16137" max="16137" width="6.625" style="10" customWidth="1"/>
+    <col min="16138" max="16138" width="8.125" style="10" customWidth="1"/>
+    <col min="16139" max="16139" width="10.125" style="10" customWidth="1"/>
+    <col min="16140" max="16140" width="7.25" style="10" customWidth="1"/>
+    <col min="16141" max="16141" width="11.875" style="10" customWidth="1"/>
+    <col min="16142" max="16142" width="2.125" style="10" customWidth="1"/>
+    <col min="16143" max="16144" width="12.5" style="10" customWidth="1"/>
+    <col min="16145" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="57"/>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="51"/>
+      <c r="B1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="72" t="s">
+      <c r="C1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="72"/>
-      <c r="E1" s="53" t="s">
+      <c r="D1" s="53"/>
+      <c r="E1" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="54"/>
-      <c r="G1" s="57" t="s">
+      <c r="F1" s="59"/>
+      <c r="G1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="57"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="53" t="s">
+      <c r="H1" s="51"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="57" t="s">
+      <c r="K1" s="59"/>
+      <c r="L1" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="57"/>
-      <c r="N1" s="53" t="s">
+      <c r="M1" s="51"/>
+      <c r="N1" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="56"/>
-      <c r="P1" s="54"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="59"/>
     </row>
     <row r="2" spans="1:16" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="57"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="66" t="s">
+      <c r="A2" s="51"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="70">
+      <c r="F2" s="57"/>
+      <c r="G2" s="65">
         <v>1</v>
       </c>
-      <c r="H2" s="70"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="54"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="59"/>
     </row>
     <row r="3" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="57"/>
-      <c r="B3" s="14" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="53" t="s">
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="54"/>
-      <c r="L3" s="57" t="s">
+      <c r="K3" s="59"/>
+      <c r="L3" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="57"/>
-      <c r="N3" s="53" t="s">
+      <c r="M3" s="51"/>
+      <c r="N3" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="56"/>
-      <c r="P3" s="54"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="59"/>
     </row>
     <row r="4" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="55"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="55" t="s">
+      <c r="A4" s="52"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="54"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="59"/>
     </row>
     <row r="5" spans="1:16" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="59" t="s">
+      <c r="B5" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="C5" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="51"/>
+      <c r="H5" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="69" t="s">
+        <v>118</v>
+      </c>
+      <c r="L5" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" s="51" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.15">
+      <c r="A6" s="72"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="68"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="51"/>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="14">
+        <v>1</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="20">
+        <v>1121</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="15">
+        <v>1</v>
+      </c>
+      <c r="J7" s="15"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+    </row>
+    <row r="8" spans="1:16" s="4" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="14">
+        <v>2</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20">
+        <v>2122</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="22"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="20">
+        <v>4</v>
+      </c>
+      <c r="J8" s="20"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+    </row>
+    <row r="9" spans="1:16" s="4" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="14">
+        <v>3</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20">
+        <v>1113</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20">
+        <v>34</v>
+      </c>
+      <c r="J9" s="20"/>
+      <c r="K9" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L9" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+    </row>
+    <row r="10" spans="1:16" s="4" customFormat="1" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="14">
+        <v>4</v>
+      </c>
+      <c r="B10" s="23"/>
+      <c r="C10" s="20">
+        <v>1312</v>
+      </c>
+      <c r="D10" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="62" t="s">
+      <c r="E10" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="27"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="24">
+        <v>14</v>
+      </c>
+      <c r="J10" s="20"/>
+      <c r="K10" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L10" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="27"/>
+      <c r="P10" s="27"/>
+    </row>
+    <row r="11" spans="1:16" s="4" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="14">
+        <v>5</v>
+      </c>
+      <c r="B11" s="23"/>
+      <c r="C11" s="20">
+        <v>1221</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="22"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="24">
+        <v>2</v>
+      </c>
+      <c r="J11" s="20"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+    </row>
+    <row r="12" spans="1:16" s="4" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="14">
+        <v>6</v>
+      </c>
+      <c r="B12" s="23"/>
+      <c r="C12" s="20">
+        <v>1222</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="24">
+        <v>2</v>
+      </c>
+      <c r="J12" s="20"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+    </row>
+    <row r="13" spans="1:16" s="4" customFormat="1" ht="127.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="14">
+        <v>7</v>
+      </c>
+      <c r="B13" s="23"/>
+      <c r="C13" s="20">
+        <v>1213</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="22"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="24">
+        <v>4</v>
+      </c>
+      <c r="J13" s="20"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+    </row>
+    <row r="14" spans="1:16" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="14">
+        <v>8</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="20">
+        <v>1224</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="22"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="40">
+        <v>2</v>
+      </c>
+      <c r="J14" s="15"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+    </row>
+    <row r="15" spans="1:16" s="4" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="14">
+        <v>9</v>
+      </c>
+      <c r="B15" s="23"/>
+      <c r="C15" s="20">
+        <v>1214</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="22"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="24">
+        <v>4</v>
+      </c>
+      <c r="J15" s="20"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+    </row>
+    <row r="16" spans="1:16" s="4" customFormat="1" ht="117" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="14">
+        <v>10</v>
+      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="20">
+        <v>1218</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="22"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="24">
+        <v>2</v>
+      </c>
+      <c r="J16" s="20"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+    </row>
+    <row r="17" spans="1:16" s="4" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="14">
+        <v>11</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="20">
+        <v>1225</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="22"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" s="24">
+        <v>1</v>
+      </c>
+      <c r="J17" s="20"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+    </row>
+    <row r="18" spans="1:16" s="4" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="14">
+        <v>12</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20">
+        <v>1215</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="20">
+        <v>2</v>
+      </c>
+      <c r="J18" s="20"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
+    </row>
+    <row r="19" spans="1:16" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="14">
+        <v>13</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="20">
+        <v>1212</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="20">
+        <v>2</v>
+      </c>
+      <c r="J19" s="20"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
+    </row>
+    <row r="20" spans="1:16" ht="109.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="14">
+        <v>14</v>
+      </c>
+      <c r="B20" s="26"/>
+      <c r="C20" s="20">
+        <v>1217</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="20">
+        <v>8</v>
+      </c>
+      <c r="J20" s="20"/>
+      <c r="K20" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L20" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="120.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="14">
+        <v>15</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="20">
+        <v>1218</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="20">
+        <v>8</v>
+      </c>
+      <c r="J21" s="20"/>
+      <c r="K21" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L21" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="111" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="14">
+        <v>16</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="20">
+        <v>1216</v>
+      </c>
+      <c r="D22" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="20">
+        <v>2</v>
+      </c>
+      <c r="J22" s="20"/>
+      <c r="K22" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L22" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
+    </row>
+    <row r="23" spans="1:16" ht="58.5" x14ac:dyDescent="0.15">
+      <c r="A23" s="14">
         <v>17</v>
       </c>
-      <c r="E5" s="62" t="s">
+      <c r="B23" s="7"/>
+      <c r="C23" s="20">
+        <v>1223</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="22"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="20">
+        <v>1</v>
+      </c>
+      <c r="J23" s="20"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+    </row>
+    <row r="24" spans="1:16" ht="54" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="14">
         <v>18</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="20">
+        <v>1521</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="22"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="20">
+        <v>1</v>
+      </c>
+      <c r="J24" s="20"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="M24" s="27">
+        <v>1</v>
+      </c>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="27"/>
+    </row>
+    <row r="25" spans="1:16" ht="117" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="14">
         <v>19</v>
       </c>
-      <c r="G5" s="57"/>
-      <c r="H5" s="62" t="s">
+      <c r="B25" s="7"/>
+      <c r="C25" s="20">
+        <v>1515</v>
+      </c>
+      <c r="D25" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="20">
+        <v>6</v>
+      </c>
+      <c r="J25" s="20"/>
+      <c r="K25" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L25" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="27"/>
+    </row>
+    <row r="26" spans="1:16" ht="122.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="14">
         <v>20</v>
       </c>
-      <c r="I5" s="57" t="s">
+      <c r="B26" s="7"/>
+      <c r="C26" s="20">
+        <v>1516</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="20">
+        <v>2</v>
+      </c>
+      <c r="J26" s="20"/>
+      <c r="K26" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L26" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="27"/>
+    </row>
+    <row r="27" spans="1:16" ht="96" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="14">
         <v>21</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="B27" s="7"/>
+      <c r="C27" s="20">
+        <v>1522</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" s="22"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="20">
+        <v>1</v>
+      </c>
+      <c r="J27" s="20"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="M27" s="27">
+        <v>1</v>
+      </c>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+    </row>
+    <row r="28" spans="1:16" ht="129.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="14">
         <v>22</v>
       </c>
-      <c r="K5" s="63" t="s">
+      <c r="B28" s="7"/>
+      <c r="C28" s="20">
+        <v>1577</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="20">
+        <v>18</v>
+      </c>
+      <c r="J28" s="20"/>
+      <c r="K28" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L28" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="27"/>
+    </row>
+    <row r="29" spans="1:16" ht="129" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="14">
         <v>23</v>
       </c>
-      <c r="L5" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="M5" s="57" t="s">
+      <c r="B29" s="7"/>
+      <c r="C29" s="20">
+        <v>1411</v>
+      </c>
+      <c r="D29" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="22"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="20">
+        <v>2</v>
+      </c>
+      <c r="J29" s="20"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="27"/>
+    </row>
+    <row r="30" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="A30" s="14">
         <v>24</v>
       </c>
-      <c r="N5" s="64" t="s">
+      <c r="B30" s="7"/>
+      <c r="C30" s="20">
+        <v>1421</v>
+      </c>
+      <c r="D30" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="22"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="20">
+        <v>2</v>
+      </c>
+      <c r="J30" s="20"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="M30" s="27">
+        <v>1</v>
+      </c>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="27"/>
+    </row>
+    <row r="31" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="A31" s="14">
         <v>25</v>
       </c>
-      <c r="O5" s="57" t="s">
+      <c r="B31" s="7"/>
+      <c r="C31" s="20">
+        <v>1621</v>
+      </c>
+      <c r="D31" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="22"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="20">
+        <v>1</v>
+      </c>
+      <c r="J31" s="20"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="27"/>
+      <c r="P31" s="27"/>
+    </row>
+    <row r="32" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="14">
         <v>26</v>
       </c>
-      <c r="P5" s="57" t="s">
+      <c r="B32" s="7"/>
+      <c r="C32" s="20">
+        <v>1713</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="20">
+        <v>8</v>
+      </c>
+      <c r="J32" s="20"/>
+      <c r="K32" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L32" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="27"/>
+      <c r="P32" s="27"/>
+    </row>
+    <row r="33" spans="1:16" ht="110.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="14">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.15">
-      <c r="A6" s="58"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="12" t="s">
+      <c r="B33" s="7"/>
+      <c r="C33" s="20">
+        <v>1712</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="20">
+        <v>8</v>
+      </c>
+      <c r="J33" s="20"/>
+      <c r="K33" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L33" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="27"/>
+      <c r="P33" s="27"/>
+    </row>
+    <row r="34" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="A34" s="14">
         <v>28</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="B34" s="7"/>
+      <c r="C34" s="20">
+        <v>1721</v>
+      </c>
+      <c r="D34" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="22"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="20">
+        <v>1</v>
+      </c>
+      <c r="J34" s="20"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="M34" s="27">
+        <v>1</v>
+      </c>
+      <c r="N34" s="27"/>
+      <c r="O34" s="27"/>
+      <c r="P34" s="27"/>
+    </row>
+    <row r="35" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="A35" s="14">
         <v>29</v>
       </c>
-      <c r="H6" s="62"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="57"/>
-      <c r="P6" s="57"/>
-    </row>
-    <row r="7" spans="1:16" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="15">
+      <c r="C35" s="20">
+        <v>2121</v>
+      </c>
+      <c r="D35" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="22"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="20">
         <v>1</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20" t="s">
+      <c r="J35" s="20"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="M35" s="27">
+        <v>1</v>
+      </c>
+      <c r="N35" s="27"/>
+      <c r="O35" s="27"/>
+      <c r="P35" s="27"/>
+    </row>
+    <row r="36" spans="1:16" ht="137.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="14">
         <v>30</v>
       </c>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-    </row>
-    <row r="8" spans="1:16" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="15">
+      <c r="C36" s="20">
+        <v>2111</v>
+      </c>
+      <c r="D36" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="22"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="20">
+        <v>3</v>
+      </c>
+      <c r="J36" s="20"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="M36" s="27"/>
+      <c r="N36" s="27"/>
+      <c r="O36" s="27"/>
+      <c r="P36" s="27"/>
+    </row>
+    <row r="37" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="A37" s="14">
+        <v>32</v>
+      </c>
+      <c r="C37" s="20">
+        <v>121</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="22"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="20">
+        <v>1</v>
+      </c>
+      <c r="J37" s="20"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="M37" s="27">
+        <v>1</v>
+      </c>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="P37" s="27"/>
+    </row>
+    <row r="38" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="A38" s="14">
+        <v>34</v>
+      </c>
+      <c r="C38" s="20">
+        <v>122</v>
+      </c>
+      <c r="D38" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="E38" s="22"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="20">
+        <v>1</v>
+      </c>
+      <c r="J38" s="20"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="M38" s="27">
+        <v>1</v>
+      </c>
+      <c r="N38" s="27"/>
+      <c r="O38" s="27"/>
+      <c r="P38" s="27"/>
+    </row>
+    <row r="39" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="A39" s="14">
+        <v>35</v>
+      </c>
+      <c r="C39" s="20">
+        <v>123</v>
+      </c>
+      <c r="D39" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="22"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="20">
+        <v>1</v>
+      </c>
+      <c r="J39" s="20"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="M39" s="27">
+        <v>1</v>
+      </c>
+      <c r="N39" s="27"/>
+      <c r="O39" s="27"/>
+      <c r="P39" s="27"/>
+    </row>
+    <row r="40" spans="1:16" ht="117" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="14">
+        <v>36</v>
+      </c>
+      <c r="C40" s="20">
+        <v>116</v>
+      </c>
+      <c r="D40" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="20">
+        <v>6</v>
+      </c>
+      <c r="J40" s="20"/>
+      <c r="K40" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L40" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="27"/>
+      <c r="P40" s="27"/>
+    </row>
+    <row r="41" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="A41" s="14">
+        <v>38</v>
+      </c>
+      <c r="C41" s="20">
+        <v>124</v>
+      </c>
+      <c r="D41" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" s="22"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="20">
         <v>2</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-    </row>
-    <row r="9" spans="1:16" s="4" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="15">
-        <v>3</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-    </row>
-    <row r="10" spans="1:16" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A10" s="15">
-        <v>4</v>
-      </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-    </row>
-    <row r="11" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="15">
-        <v>5</v>
-      </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-    </row>
-    <row r="12" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="15">
-        <v>6</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-    </row>
-    <row r="13" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="15">
-        <v>7</v>
-      </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-    </row>
-    <row r="14" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="15">
-        <v>8</v>
-      </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-    </row>
-    <row r="15" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="15">
-        <v>9</v>
-      </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-    </row>
-    <row r="16" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="15">
-        <v>10</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-    </row>
-    <row r="17" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="15">
-        <v>11</v>
-      </c>
-      <c r="B17" s="31"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-    </row>
-    <row r="18" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="15">
-        <v>12</v>
-      </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-    </row>
-    <row r="19" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="15">
-        <v>13</v>
-      </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-    </row>
-    <row r="20" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="15">
-        <v>14</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-    </row>
-    <row r="21" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="15">
-        <v>15</v>
-      </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-    </row>
-    <row r="22" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="15">
-        <v>16</v>
-      </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-    </row>
-    <row r="23" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="15">
-        <v>17</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="37"/>
-      <c r="P23" s="37"/>
-    </row>
-    <row r="24" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="15">
-        <v>18</v>
-      </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="37"/>
-      <c r="P24" s="37"/>
-    </row>
-    <row r="25" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="15">
-        <v>19</v>
-      </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-    </row>
-    <row r="26" spans="1:16" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="15">
-        <v>20</v>
-      </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="37"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="37"/>
-      <c r="P26" s="37"/>
-    </row>
-    <row r="27" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="P27" s="42" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="32"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="P28" s="43"/>
-    </row>
-    <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="M41" s="27">
+        <v>1</v>
+      </c>
+      <c r="N41" s="27"/>
+      <c r="O41" s="27"/>
+      <c r="P41" s="27"/>
+    </row>
+    <row r="42" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="A42" s="14">
+        <v>39</v>
+      </c>
+      <c r="C42" s="20">
+        <v>125</v>
+      </c>
+      <c r="D42" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="22"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="20">
+        <v>1</v>
+      </c>
+      <c r="J42" s="20"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="M42" s="27">
+        <v>1</v>
+      </c>
+      <c r="N42" s="27"/>
+      <c r="O42" s="27"/>
+      <c r="P42" s="27"/>
+    </row>
+    <row r="43" spans="1:16" ht="121.5" x14ac:dyDescent="0.15">
+      <c r="A43" s="14">
+        <v>40</v>
+      </c>
+      <c r="C43" s="20">
+        <v>126</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="20">
+        <v>1</v>
+      </c>
+      <c r="J43" s="20"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="M43" s="27"/>
+      <c r="N43" s="27"/>
+      <c r="O43" s="27"/>
+      <c r="P43" s="27"/>
+    </row>
+    <row r="44" spans="1:16" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A44" s="14">
+        <v>41</v>
+      </c>
+      <c r="C44" s="20">
+        <v>127</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="20">
+        <v>1</v>
+      </c>
+      <c r="J44" s="20"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="M44" s="27"/>
+      <c r="N44" s="27"/>
+      <c r="O44" s="27"/>
+      <c r="P44" s="27"/>
+    </row>
+    <row r="45" spans="1:16" ht="243" x14ac:dyDescent="0.15">
+      <c r="A45" s="14">
+        <v>42</v>
+      </c>
+      <c r="C45" s="20">
+        <v>128</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="20">
+        <v>1</v>
+      </c>
+      <c r="J45" s="20"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="M45" s="27"/>
+      <c r="N45" s="27"/>
+      <c r="O45" s="27"/>
+      <c r="P45" s="27"/>
+    </row>
+    <row r="46" spans="1:16" ht="162" x14ac:dyDescent="0.15">
+      <c r="A46" s="14">
+        <v>43</v>
+      </c>
+      <c r="C46" s="20">
+        <v>129</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="20">
+        <v>1</v>
+      </c>
+      <c r="J46" s="20"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="M46" s="27"/>
+      <c r="N46" s="27"/>
+      <c r="O46" s="27"/>
+      <c r="P46" s="27"/>
+    </row>
+    <row r="47" spans="1:16" ht="162" x14ac:dyDescent="0.15">
+      <c r="A47" s="14">
+        <v>44</v>
+      </c>
+      <c r="C47" s="20">
+        <v>130</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" s="22"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="20">
+        <v>1</v>
+      </c>
+      <c r="J47" s="20"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="M47" s="27"/>
+      <c r="N47" s="27"/>
+      <c r="O47" s="27"/>
+      <c r="P47" s="27"/>
+    </row>
+    <row r="48" spans="1:16" ht="256.5" x14ac:dyDescent="0.15">
+      <c r="A48" s="14">
+        <v>45</v>
+      </c>
+      <c r="C48" s="20">
+        <v>131</v>
+      </c>
+      <c r="D48" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="20">
+        <v>50</v>
+      </c>
+      <c r="J48" s="20"/>
+      <c r="K48" s="21"/>
+      <c r="L48" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="M48" s="27"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="27"/>
+      <c r="P48" s="27"/>
+    </row>
+    <row r="49" spans="1:16" ht="243" x14ac:dyDescent="0.15">
+      <c r="A49" s="14">
+        <v>46</v>
+      </c>
+      <c r="C49" s="20">
+        <v>132</v>
+      </c>
+      <c r="D49" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="E49" s="22"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="20">
+        <v>1</v>
+      </c>
+      <c r="J49" s="20"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="M49" s="27"/>
+      <c r="N49" s="27"/>
+      <c r="O49" s="27"/>
+      <c r="P49" s="27"/>
+    </row>
+    <row r="50" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A50" s="14">
+        <v>47</v>
+      </c>
+      <c r="C50" s="20">
+        <v>133</v>
+      </c>
+      <c r="D50" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="20">
+        <v>1</v>
+      </c>
+      <c r="J50" s="20"/>
+      <c r="K50" s="21"/>
+      <c r="L50" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="M50" s="27"/>
+      <c r="N50" s="27"/>
+      <c r="O50" s="27"/>
+      <c r="P50" s="27"/>
+    </row>
+    <row r="51" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A51" s="14">
+        <v>48</v>
+      </c>
+      <c r="C51" s="20">
+        <v>134</v>
+      </c>
+      <c r="D51" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="E51" s="22"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="20">
+        <v>1</v>
+      </c>
+      <c r="J51" s="20"/>
+      <c r="K51" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L51" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="M51" s="27"/>
+      <c r="N51" s="27"/>
+      <c r="O51" s="27"/>
+      <c r="P51" s="27"/>
+    </row>
+    <row r="52" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A52" s="14">
+        <v>49</v>
+      </c>
+      <c r="C52" s="20">
+        <v>135</v>
+      </c>
+      <c r="D52" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52" s="22"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="20">
+        <v>1</v>
+      </c>
+      <c r="J52" s="20"/>
+      <c r="K52" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L52" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="M52" s="27"/>
+      <c r="N52" s="27"/>
+      <c r="O52" s="27"/>
+      <c r="P52" s="27"/>
+    </row>
+    <row r="53" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A53" s="14">
+        <v>50</v>
+      </c>
+      <c r="C53" s="20">
+        <v>136</v>
+      </c>
+      <c r="D53" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="20">
+        <v>1</v>
+      </c>
+      <c r="J53" s="20"/>
+      <c r="K53" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L53" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="M53" s="27"/>
+      <c r="N53" s="27"/>
+      <c r="O53" s="27"/>
+      <c r="P53" s="27"/>
+    </row>
+    <row r="54" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="A54" s="14">
+        <v>50</v>
+      </c>
+      <c r="C54" s="20">
+        <v>1312</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="E54" s="22"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="20">
+        <v>2</v>
+      </c>
+      <c r="J54" s="20"/>
+      <c r="K54" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="L54" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="M54" s="27"/>
+      <c r="N54" s="27"/>
+      <c r="O54" s="27"/>
+      <c r="P54" s="27"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.15">
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.15">
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.15">
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.15">
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.15">
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.15">
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.15">
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.15">
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.15">
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.15">
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
+    <row r="65" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8"/>
+    <row r="66" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
+    <row r="67" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
+    <row r="68" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A69" s="8"/>
-      <c r="B69" s="8"/>
+    <row r="69" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="70" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="71" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="72" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="73" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="74" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="75" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="76" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="77" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="78" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="79" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="80" spans="9:10" x14ac:dyDescent="0.15">
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
     </row>
@@ -9921,239 +11489,22 @@
       <c r="I1221" s="2"/>
       <c r="J1221" s="2"/>
     </row>
-    <row r="1222" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1222" s="2"/>
-      <c r="J1222" s="2"/>
-    </row>
-    <row r="1223" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1223" s="2"/>
-      <c r="J1223" s="2"/>
-    </row>
-    <row r="1224" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1224" s="2"/>
-      <c r="J1224" s="2"/>
-    </row>
-    <row r="1225" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1225" s="2"/>
-      <c r="J1225" s="2"/>
-    </row>
-    <row r="1226" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1226" s="2"/>
-      <c r="J1226" s="2"/>
-    </row>
-    <row r="1227" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1227" s="2"/>
-      <c r="J1227" s="2"/>
-    </row>
-    <row r="1228" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1228" s="2"/>
-      <c r="J1228" s="2"/>
-    </row>
-    <row r="1229" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1229" s="2"/>
-      <c r="J1229" s="2"/>
-    </row>
-    <row r="1230" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1230" s="2"/>
-      <c r="J1230" s="2"/>
-    </row>
-    <row r="1231" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1231" s="2"/>
-      <c r="J1231" s="2"/>
-    </row>
-    <row r="1232" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1232" s="2"/>
-      <c r="J1232" s="2"/>
-    </row>
-    <row r="1233" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1233" s="2"/>
-      <c r="J1233" s="2"/>
-    </row>
-    <row r="1234" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1234" s="2"/>
-      <c r="J1234" s="2"/>
-    </row>
-    <row r="1235" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1235" s="2"/>
-      <c r="J1235" s="2"/>
-    </row>
-    <row r="1236" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1236" s="2"/>
-      <c r="J1236" s="2"/>
-    </row>
-    <row r="1237" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1237" s="2"/>
-      <c r="J1237" s="2"/>
-    </row>
-    <row r="1238" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1238" s="2"/>
-      <c r="J1238" s="2"/>
-    </row>
-    <row r="1239" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1239" s="2"/>
-      <c r="J1239" s="2"/>
-    </row>
-    <row r="1240" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1240" s="2"/>
-      <c r="J1240" s="2"/>
-    </row>
-    <row r="1241" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1241" s="2"/>
-      <c r="J1241" s="2"/>
-    </row>
-    <row r="1242" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1242" s="2"/>
-      <c r="J1242" s="2"/>
-    </row>
-    <row r="1243" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1243" s="2"/>
-      <c r="J1243" s="2"/>
-    </row>
-    <row r="1244" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1244" s="2"/>
-      <c r="J1244" s="2"/>
-    </row>
-    <row r="1245" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1245" s="2"/>
-      <c r="J1245" s="2"/>
-    </row>
-    <row r="1246" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1246" s="2"/>
-      <c r="J1246" s="2"/>
-    </row>
-    <row r="1247" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1247" s="2"/>
-      <c r="J1247" s="2"/>
-    </row>
-    <row r="1248" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1248" s="2"/>
-      <c r="J1248" s="2"/>
-    </row>
-    <row r="1249" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1249" s="2"/>
-      <c r="J1249" s="2"/>
-    </row>
-    <row r="1250" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1250" s="2"/>
-      <c r="J1250" s="2"/>
-    </row>
-    <row r="1251" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1251" s="2"/>
-      <c r="J1251" s="2"/>
-    </row>
-    <row r="1252" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1252" s="2"/>
-      <c r="J1252" s="2"/>
-    </row>
-    <row r="1253" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1253" s="2"/>
-      <c r="J1253" s="2"/>
-    </row>
-    <row r="1254" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1254" s="2"/>
-      <c r="J1254" s="2"/>
-    </row>
-    <row r="1255" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1255" s="2"/>
-      <c r="J1255" s="2"/>
-    </row>
-    <row r="1256" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1256" s="2"/>
-      <c r="J1256" s="2"/>
-    </row>
-    <row r="1257" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1257" s="2"/>
-      <c r="J1257" s="2"/>
-    </row>
-    <row r="1258" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1258" s="2"/>
-      <c r="J1258" s="2"/>
-    </row>
-    <row r="1259" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1259" s="2"/>
-      <c r="J1259" s="2"/>
-    </row>
-    <row r="1260" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1260" s="2"/>
-      <c r="J1260" s="2"/>
-    </row>
-    <row r="1261" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1261" s="2"/>
-      <c r="J1261" s="2"/>
-    </row>
-    <row r="1262" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1262" s="2"/>
-      <c r="J1262" s="2"/>
-    </row>
-    <row r="1263" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1263" s="2"/>
-      <c r="J1263" s="2"/>
-    </row>
-    <row r="1264" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1264" s="2"/>
-      <c r="J1264" s="2"/>
-    </row>
-    <row r="1265" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1265" s="2"/>
-      <c r="J1265" s="2"/>
-    </row>
-    <row r="1266" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1266" s="2"/>
-      <c r="J1266" s="2"/>
-    </row>
-    <row r="1267" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1267" s="2"/>
-      <c r="J1267" s="2"/>
-    </row>
-    <row r="1268" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1268" s="2"/>
-      <c r="J1268" s="2"/>
-    </row>
-    <row r="1269" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1269" s="2"/>
-      <c r="J1269" s="2"/>
-    </row>
-    <row r="1270" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1270" s="2"/>
-      <c r="J1270" s="2"/>
-    </row>
-    <row r="1271" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1271" s="2"/>
-      <c r="J1271" s="2"/>
-    </row>
-    <row r="1272" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1272" s="2"/>
-      <c r="J1272" s="2"/>
-    </row>
-    <row r="1273" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1273" s="2"/>
-      <c r="J1273" s="2"/>
-    </row>
-    <row r="1274" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1274" s="2"/>
-      <c r="J1274" s="2"/>
-    </row>
-    <row r="1275" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1275" s="2"/>
-      <c r="J1275" s="2"/>
-    </row>
-    <row r="1276" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1276" s="2"/>
-      <c r="J1276" s="2"/>
-    </row>
-    <row r="1277" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1277" s="2"/>
-      <c r="J1277" s="2"/>
-    </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="C1:D2"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="O5:O6"/>
@@ -10167,25 +11518,27 @@
     <mergeCell ref="K5:K6"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
   </mergeCells>
-  <phoneticPr fontId="64" type="noConversion"/>
+  <phoneticPr fontId="61" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="L43" r:id="rId1" xr:uid="{9A51B0C7-8481-4F5F-96C9-71A2DF3DDCA7}"/>
+    <hyperlink ref="L44" r:id="rId2" xr:uid="{BC501510-C86E-4A45-BAA8-5F5E22C20442}"/>
+    <hyperlink ref="L45" r:id="rId3" display="https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1563820041%3AH%3AjEXVXFz29uWhSPA32SdLxq18tbGVRP6N%3Ab1e44a53e68312397166bdb38376f31f&amp;ali_trackid=318_b1e44a53e68312397166bdb38376f31f&amp;id=668804973431&amp;mi_id=0000kh4JsEhs_IKQwaZwLe5GPzZBrKEtnqIAl4nMzgEcpGs&amp;mm_sceneid=0_0_2198670068_0&amp;priceTId=213e097817677727727551092e11ab&amp;skuId=6072168990782&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%220ce0092ebee4bb5c990e1ed0aae83472%22%7D&amp;xxc=ad_ztc" xr:uid="{EE7187D2-5C29-4C71-8BF0-14CC690401EB}"/>
+    <hyperlink ref="L46" r:id="rId4" display="https://item.taobao.com/item.htm?abbucket=15&amp;id=684180101591&amp;mi_id=0000kHsnKO9vrl_xXRKAYuWwfk1ZxpJzkY1oGgmAntBdN2A&amp;ns=1&amp;priceTId=215040db17693197452846906e10bd&amp;skuId=5066190559427&amp;spm=a21n57.1.hoverItem.13&amp;utparam=%7B%22aplus_abtest%22%3A%2200fb48171d68baf920a6c2997ba800f5%22%7D&amp;xxc=taobaoSearch" xr:uid="{640829AA-10E2-4344-B84B-AF14836FC0FA}"/>
+    <hyperlink ref="L47" r:id="rId5" display="https://item.taobao.com/item.htm?abbucket=15&amp;id=885444239746&amp;mi_id=00004gN7JSgLTLqH9NscZa5BV-fDjGIRhn7dS2llqgBEm-I&amp;ns=1&amp;priceTId=215040db17693199893824488e10bd&amp;skuId=5729109569961&amp;spm=a21n57.1.hoverItem.3&amp;utparam=%7B%22aplus_abtest%22%3A%220d184a79d8dee207c56cd615483888e0%22%7D&amp;xxc=taobaoSearch" xr:uid="{D9E14E51-6908-4600-BF1B-1BE5E52130FA}"/>
+    <hyperlink ref="L49" r:id="rId6" display="https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1202830031%3AH%3A5NEVSZWkfH5vk10Gx8WsEg%3D%3D%3A0e3224a199436b146fadd1013df40d50&amp;ali_trackid=282_0e3224a199436b146fadd1013df40d50&amp;id=589213401941&amp;mi_id=0000tXboOyQ6vKwx8WiuBo_0I904yCwGgBZQ-DEtp9Eidvc&amp;mm_sceneid=1_0_343370108_0&amp;priceTId=214782f517694062736734983e1fe1&amp;skuId=4715656587781&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%2243f96ce6df79319aabdbd4973057b1b5%22%7D&amp;xxc=ad_ztc" xr:uid="{A4FE5950-5A28-4F3D-B42C-E6D6ECC79B08}"/>
+    <hyperlink ref="L48" r:id="rId7" display="https://item.taobao.com/item.htm?ali_refid=a3_430673_1006%3A1109974134%3AH%3AS9mt8%2FS9IPRAnlGXK23dCRerfi2%2BAYZj%3A75421c7a1bf937df626379b8de81db84&amp;ali_trackid=282_75421c7a1bf937df626379b8de81db84&amp;id=774427618182&amp;loginBonus=1&amp;mi_id=0000OtzXamOT9vAra9TbUQiBvRLBsdZJRcmzsekmz3yUyS0&amp;mm_sceneid=1_0_99588015_0&amp;priceTId=2150467817696032421462002e22b0&amp;skuId=5300832301565&amp;spm=a21n57.sem.item.4&amp;utparam=%7B%22aplus_abtest%22%3A%22c7bbb9e8de08729fc098be83e797fb13%22%7D&amp;xxc=ad_ztc" xr:uid="{FC3750A0-F3B8-4313-B9DE-37439F3E109E}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="68" orientation="landscape"/>

--- a/Body/5-Office/BOM表.xlsx
+++ b/Body/5-Office/BOM表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\win-daolaj3j0nc\F\internal class\N2500-25N\N2571-YBJ\N2571-YBJ-2603\3-office文件\供应\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\win-daolaj3j0nc\F\internal class\N2500-25N\N2571-YBJ\N2571-YBJ-2604\3-office文件\供应\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E153A097-F61A-4577-ACB2-D0A134EE198D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9262237-BA8F-4BBB-96AB-C003ABA7DB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="149">
   <si>
     <r>
       <rPr>
@@ -485,10 +485,6 @@
     </r>
   </si>
   <si>
-    <t>Optimized
-优选等级</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -632,9 +628,6 @@
     <t>1225-左梁</t>
   </si>
   <si>
-    <t>1215-平头圆柱销</t>
-  </si>
-  <si>
     <t>1212-销</t>
   </si>
   <si>
@@ -693,9 +686,6 @@
   </si>
   <si>
     <t>0116-内六角平圆头螺钉-GBT70.2-2015_M5X12</t>
-  </si>
-  <si>
-    <t>0124-钢轧带</t>
   </si>
   <si>
     <t>0125-电器架</t>
@@ -798,39 +788,6 @@
   </si>
   <si>
     <r>
-      <t>【淘宝】</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>天无理由退货</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> https://e.tb.cn/h.7mlCpa3CT8fUR1f?tk=w2zsUfW92Ot </t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>【淘宝】大促价保</t>
     </r>
     <r>
@@ -848,16 +805,471 @@
     <phoneticPr fontId="61" type="noConversion"/>
   </si>
   <si>
-    <t>直径10</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
     <t>M10</t>
     <phoneticPr fontId="61" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>3.82</t>
+    <t>2111-电箱din导轨 130</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【淘宝】假一赔四</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> https://e.tb.cn/h.7MJcgNyqDq0lb4x?tk=nxhCUgh63I7 CZ193 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>304</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不锈钢垫片圆形加大加厚金属螺丝平垫圈超薄介子华司平垫大全」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击链接直接打开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>淘宝搜索直接打开</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【淘宝】退货运费险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> https://e.tb.cn/h.7Lm8guSC0Ux0SfB?tk=6AuNUghRivr CZ028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「进口模具弹簧高强度耐高温矩形扁线压缩磨具压簧黄蓝红绿棕褐茶色」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击链接直接打开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>淘宝搜索直接打开</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【淘宝】大促价保</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> https://e.tb.cn/h.7MJ4SWmHd5yGuXb?tk=qO5IUghjzTA CZ028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寸重型万向轮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>低重心尼龙脚轮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寸双轮轱辘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寸推车带刹加重轮子」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点击链接直接打开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>淘宝搜索直接打开</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0126-miniPC电源</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>19V10A</t>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?id=553788314091&amp;last_time=1768143784&amp;mi_id=0000i7eOrBKgQD4GnhXhm9jjujyg938wVli_lWGICSqSW3s&amp;scm=1007.13982.82927.0&amp;skuId=4092429570913&amp;spm=tbpc.mytb_footmark.item.goods&amp;upStreamPrice=3915</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0127-变压器</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>24V6.35A</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>24V15A</t>
+  </si>
+  <si>
+    <t>https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1563820041%3AH%3AjEXVXFz29uWhSPA32SdLxq18tbGVRP6N%3Ab1e44a53e68312397166bdb38376f31f&amp;ali_trackid=318_b1e44a53e68312397166bdb38376f31f&amp;id=668804973431&amp;mi_id=0000kh4JsEhs_IKQwaZwLe5GPzZBrKEtnqIAl4nMzgEcpGs&amp;mm_sceneid=0_0_2198670068_0&amp;priceTId=213e097817677727727551092e11ab&amp;skuId=6072168990782&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%220ce0092ebee4bb5c990e1ed0aae83472%22%7D&amp;xxc=ad_ztc</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0128-屏幕电源</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0129-接触器</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>12A, 24 V</t>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=15&amp;id=684180101591&amp;mi_id=0000kHsnKO9vrl_xXRKAYuWwfk1ZxpJzkY1oGgmAntBdN2A&amp;ns=1&amp;priceTId=215040db17693197452846906e10bd&amp;skuId=5066190559427&amp;spm=a21n57.1.hoverItem.13&amp;utparam=%7B%22aplus_abtest%22%3A%2200fb48171d68baf920a6c2997ba800f5%22%7D&amp;xxc=taobaoSearch</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0130-空开</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=15&amp;id=885444239746&amp;mi_id=00004gN7JSgLTLqH9NscZa5BV-fDjGIRhn7dS2llqgBEm-I&amp;ns=1&amp;priceTId=215040db17693199893824488e10bd&amp;skuId=5729109569961&amp;spm=a21n57.1.hoverItem.3&amp;utparam=%7B%22aplus_abtest%22%3A%220d184a79d8dee207c56cd615483888e0%22%7D&amp;xxc=taobaoSearch</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.jndz021.com/dc/132（淘宝没有货源，在官网上采购）</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1202830031%3AH%3A5NEVSZWkfH5vk10Gx8WsEg%3D%3D%3A0e3224a199436b146fadd1013df40d50&amp;ali_trackid=282_0e3224a199436b146fadd1013df40d50&amp;id=589213401941&amp;mi_id=0000tXboOyQ6vKwx8WiuBo_0I904yCwGgBZQ-DEtp9Eidvc&amp;mm_sceneid=1_0_343370108_0&amp;priceTId=214782f517694062736734983e1fe1&amp;skuId=4715656587781&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%2243f96ce6df79319aabdbd4973057b1b5%22%7D&amp;xxc=ad_ztc</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0132-焊枪（一套）</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0133-电池</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>电池客服：13662632158</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>48V20AH</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0134-仙工控制器</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经购买</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0135-激光雷达</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0135-导航雷达</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>0131-接线端子</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>PT2.5-QUATTRO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>灰色</t>
+    </r>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?ali_refid=a3_430673_1006%3A1109974134%3AH%3AS9mt8%2FS9IPRAnlGXK23dCRerfi2%2BAYZj%3A75421c7a1bf937df626379b8de81db84&amp;ali_trackid=282_75421c7a1bf937df626379b8de81db84&amp;id=774427618182&amp;loginBonus=1&amp;mi_id=0000OtzXamOT9vAra9TbUQiBvRLBsdZJRcmzsekmz3yUyS0&amp;mm_sceneid=1_0_99588015_0&amp;priceTId=2150467817696032421462002e22b0&amp;skuId=5300832301565&amp;spm=a21n57.sem.item.4&amp;utparam=%7B%22aplus_abtest%22%3A%22c7bbb9e8de08729fc098be83e797fb13%22%7D&amp;xxc=ad_ztc</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>1312-电机</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否验收</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>对</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>3129-顶板</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>269</t>
     </r>
     <r>
       <rPr>
@@ -872,7 +1284,7 @@
   </si>
   <si>
     <r>
-      <t>1.8</t>
+      <t>118</t>
     </r>
     <r>
       <rPr>
@@ -886,15 +1298,9 @@
     <phoneticPr fontId="61" type="noConversion"/>
   </si>
   <si>
-    <t>2111-电箱din导轨 130</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>【淘宝】7天无理由退货 https://e.tb.cn/h.7LmgfPhmD1WJjfq?tk=UthlUghUNJc CZ321 「国标卡固氧化C45导轨U型TH35MM宽断路器端子空开电气加厚铝卡轨条」
-点击链接直接打开 或者 淘宝搜索直接打开</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
+    <r>
+      <t>231</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -902,15 +1308,13 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>【淘宝】假一赔四</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> https://e.tb.cn/h.7MJcgNyqDq0lb4x?tk=nxhCUgh63I7 CZ193 </t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>160</t>
     </r>
     <r>
       <rPr>
@@ -919,15 +1323,13 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>304</t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>83</t>
     </r>
     <r>
       <rPr>
@@ -936,16 +1338,13 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>不锈钢垫片圆形加大加厚金属螺丝平垫圈超薄介子华司平垫大全」</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>63.5</t>
     </r>
     <r>
       <rPr>
@@ -954,15 +1353,46 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>点击链接直接打开</t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>还未咨询</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>钣金统一计价</t>
+  </si>
+  <si>
+    <t>钣金统一计价</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经购买</t>
+  </si>
+  <si>
+    <r>
+      <t>【淘宝】大促价保</t>
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="11"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> https://e.tb.cn/h.7mOc2Ra9KZEBda1?tk=7f3aUfWpWek</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>钣金件合计</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>20.2</t>
     </r>
     <r>
       <rPr>
@@ -971,15 +1401,13 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>或者</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>40.4</t>
     </r>
     <r>
       <rPr>
@@ -988,11 +1416,30 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>淘宝搜索直接打开</t>
+      <t>元</t>
     </r>
     <phoneticPr fontId="61" type="noConversion"/>
   </si>
   <si>
+    <t>加工件统一计价</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>加工件合计</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>1215-平头圆柱销</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>直径10x45</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1000,15 +1447,25 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>【淘宝】退货运费险</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> https://e.tb.cn/h.7Lm8guSC0Ux0SfB?tk=6AuNUghRivr CZ028 </t>
+      <t>个</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>组</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.05元</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>细则</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7.05</t>
     </r>
     <r>
       <rPr>
@@ -1017,16 +1474,13 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>「进口模具弹簧高强度耐高温矩形扁线压缩磨具压簧黄蓝红绿棕褐茶色」</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4.37</t>
     </r>
     <r>
       <rPr>
@@ -1035,15 +1489,13 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>点击链接直接打开</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4.64</t>
     </r>
     <r>
       <rPr>
@@ -1052,15 +1504,13 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>或者</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>13.92</t>
     </r>
     <r>
       <rPr>
@@ -1069,11 +1519,22 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>淘宝搜索直接打开</t>
+      <t>元</t>
     </r>
     <phoneticPr fontId="61" type="noConversion"/>
   </si>
   <si>
+    <t>https://item.taobao.com/item.htm?abbucket=11&amp;id=749064062909&amp;mi_id=0000D_lgnxXXWYg6uIU45wamE0Zv9ob04zflYhEBkPv_GQo&amp;ns=1&amp;skuId=5394057435750&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%220457ff662cd3c9532cc0680e1a87dd2b%22%7D&amp;xxc=taobaoSearch</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>10*30*2</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.13</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1081,15 +1542,13 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>【淘宝】大促价保</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> https://e.tb.cn/h.7MJ4SWmHd5yGuXb?tk=qO5IUghjzTA CZ028 </t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.58</t>
     </r>
     <r>
       <rPr>
@@ -1098,15 +1557,13 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2.73</t>
     </r>
     <r>
       <rPr>
@@ -1115,15 +1572,13 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>寸重型万向轮</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5.46</t>
     </r>
     <r>
       <rPr>
@@ -1132,217 +1587,34 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>低重心尼龙脚轮</t>
+      <t>元</t>
+    </r>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>个</t>
+  </si>
+  <si>
+    <t>个</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <t>【淘宝】https://e.tb.cn/h.iJUYQFq3IH6uaaV?tk=fsBd5SyIRlW</t>
+    <phoneticPr fontId="61" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    360</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <rFont val="宋体"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>寸双轮轱辘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>寸推车带刹加重轮子」</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点击链接直接打开</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>或者</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>淘宝搜索直接打开</t>
-    </r>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>0126-miniPC电源</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>19V10A</t>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?id=553788314091&amp;last_time=1768143784&amp;mi_id=0000i7eOrBKgQD4GnhXhm9jjujyg938wVli_lWGICSqSW3s&amp;scm=1007.13982.82927.0&amp;skuId=4092429570913&amp;spm=tbpc.mytb_footmark.item.goods&amp;upStreamPrice=3915</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>0127-变压器</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>24V6.35A</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>24V15A</t>
-  </si>
-  <si>
-    <t>https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1563820041%3AH%3AjEXVXFz29uWhSPA32SdLxq18tbGVRP6N%3Ab1e44a53e68312397166bdb38376f31f&amp;ali_trackid=318_b1e44a53e68312397166bdb38376f31f&amp;id=668804973431&amp;mi_id=0000kh4JsEhs_IKQwaZwLe5GPzZBrKEtnqIAl4nMzgEcpGs&amp;mm_sceneid=0_0_2198670068_0&amp;priceTId=213e097817677727727551092e11ab&amp;skuId=6072168990782&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%220ce0092ebee4bb5c990e1ed0aae83472%22%7D&amp;xxc=ad_ztc</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>0128-屏幕电源</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>0129-接触器</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>12A, 24 V</t>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?abbucket=15&amp;id=684180101591&amp;mi_id=0000kHsnKO9vrl_xXRKAYuWwfk1ZxpJzkY1oGgmAntBdN2A&amp;ns=1&amp;priceTId=215040db17693197452846906e10bd&amp;skuId=5066190559427&amp;spm=a21n57.1.hoverItem.13&amp;utparam=%7B%22aplus_abtest%22%3A%2200fb48171d68baf920a6c2997ba800f5%22%7D&amp;xxc=taobaoSearch</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>0130-空开</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?abbucket=15&amp;id=885444239746&amp;mi_id=00004gN7JSgLTLqH9NscZa5BV-fDjGIRhn7dS2llqgBEm-I&amp;ns=1&amp;priceTId=215040db17693199893824488e10bd&amp;skuId=5729109569961&amp;spm=a21n57.1.hoverItem.3&amp;utparam=%7B%22aplus_abtest%22%3A%220d184a79d8dee207c56cd615483888e0%22%7D&amp;xxc=taobaoSearch</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.jndz021.com/dc/132（淘宝没有货源，在官网上采购）</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1202830031%3AH%3A5NEVSZWkfH5vk10Gx8WsEg%3D%3D%3A0e3224a199436b146fadd1013df40d50&amp;ali_trackid=282_0e3224a199436b146fadd1013df40d50&amp;id=589213401941&amp;mi_id=0000tXboOyQ6vKwx8WiuBo_0I904yCwGgBZQ-DEtp9Eidvc&amp;mm_sceneid=1_0_343370108_0&amp;priceTId=214782f517694062736734983e1fe1&amp;skuId=4715656587781&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%2243f96ce6df79319aabdbd4973057b1b5%22%7D&amp;xxc=ad_ztc</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>0132-焊枪（一套）</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>0133-电池</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>电池客服：13662632158</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>48V20AH</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>0134-仙工控制器</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>已经购买</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>0135-激光雷达</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>0135-导航雷达</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>0131-接线端子</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>PT2.5-QUATTRO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>灰色</t>
-    </r>
-  </si>
-  <si>
-    <t>https://item.taobao.com/item.htm?ali_refid=a3_430673_1006%3A1109974134%3AH%3AS9mt8%2FS9IPRAnlGXK23dCRerfi2%2BAYZj%3A75421c7a1bf937df626379b8de81db84&amp;ali_trackid=282_75421c7a1bf937df626379b8de81db84&amp;id=774427618182&amp;loginBonus=1&amp;mi_id=0000OtzXamOT9vAra9TbUQiBvRLBsdZJRcmzsekmz3yUyS0&amp;mm_sceneid=1_0_99588015_0&amp;priceTId=2150467817696032421462002e22b0&amp;skuId=5300832301565&amp;spm=a21n57.sem.item.4&amp;utparam=%7B%22aplus_abtest%22%3A%22c7bbb9e8de08729fc098be83e797fb13%22%7D&amp;xxc=ad_ztc</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>1312-电机</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否验收</t>
-    <phoneticPr fontId="61" type="noConversion"/>
-  </si>
-  <si>
-    <t>对</t>
+      <t>元</t>
+    </r>
     <phoneticPr fontId="61" type="noConversion"/>
   </si>
 </sst>
@@ -1362,7 +1634,7 @@
     <numFmt numFmtId="182" formatCode="0.00_ "/>
     <numFmt numFmtId="183" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="69" x14ac:knownFonts="1">
+  <fonts count="72" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1818,6 +2090,27 @@
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -3001,7 +3294,7 @@
     </xf>
     <xf numFmtId="176" fontId="67" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="83">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3149,9 +3442,87 @@
     <xf numFmtId="181" fontId="65" fillId="33" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="65" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="67" fillId="4" borderId="1" xfId="266" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="62" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="62" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="62" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3165,63 +3536,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="62" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="62" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="62" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3879,7 +4193,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:WVF1221"/>
+  <dimension ref="A1:WVF1220"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.625" style="5" customWidth="1"/>
@@ -5224,174 +5538,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="51"/>
+      <c r="A1" s="61"/>
       <c r="B1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="53"/>
+      <c r="D1" s="79"/>
       <c r="E1" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="59"/>
-      <c r="G1" s="51" t="s">
+      <c r="F1" s="60"/>
+      <c r="G1" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="51"/>
+      <c r="H1" s="61"/>
       <c r="I1" s="11"/>
       <c r="J1" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="59"/>
-      <c r="L1" s="51" t="s">
+      <c r="K1" s="60"/>
+      <c r="L1" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="51"/>
+      <c r="M1" s="61"/>
       <c r="N1" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="71"/>
-      <c r="P1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="60"/>
     </row>
     <row r="2" spans="1:16" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="51"/>
+      <c r="A2" s="61"/>
       <c r="B2" s="12"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="62" t="s">
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="57"/>
-      <c r="G2" s="65">
+      <c r="F2" s="70"/>
+      <c r="G2" s="73">
         <v>1</v>
       </c>
-      <c r="H2" s="65"/>
-      <c r="I2" s="66"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="74"/>
       <c r="J2" s="58"/>
-      <c r="K2" s="59"/>
+      <c r="K2" s="60"/>
       <c r="L2" s="58"/>
-      <c r="M2" s="59"/>
+      <c r="M2" s="60"/>
       <c r="N2" s="58"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="60"/>
     </row>
     <row r="3" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="51"/>
+      <c r="A3" s="61"/>
       <c r="B3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="66"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="74"/>
       <c r="J3" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="59"/>
-      <c r="L3" s="51" t="s">
+      <c r="K3" s="60"/>
+      <c r="L3" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="51"/>
+      <c r="M3" s="61"/>
       <c r="N3" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="71"/>
-      <c r="P3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="60"/>
     </row>
     <row r="4" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="52"/>
+      <c r="A4" s="78"/>
       <c r="B4" s="12"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="52" t="s">
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="52"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="57"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="70"/>
       <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="78"/>
       <c r="N4" s="58"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="59"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="60"/>
     </row>
     <row r="5" spans="1:16" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="68" t="s">
+      <c r="C5" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="51"/>
-      <c r="H5" s="67" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" s="51" t="s">
+      <c r="G5" s="61"/>
+      <c r="H5" s="75" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="51" t="s">
+      <c r="J5" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="69" t="s">
-        <v>118</v>
-      </c>
-      <c r="L5" s="51" t="s">
+      <c r="K5" s="76" t="s">
+        <v>110</v>
+      </c>
+      <c r="L5" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="51" t="s">
+      <c r="M5" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="N5" s="60" t="s">
+      <c r="N5" s="67" t="s">
+        <v>134</v>
+      </c>
+      <c r="O5" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="O5" s="51" t="s">
+      <c r="P5" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="P5" s="51" t="s">
+    </row>
+    <row r="6" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.15">
+      <c r="A6" s="62"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.15">
-      <c r="A6" s="72"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="11" t="s">
+      <c r="G6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="68"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
     </row>
     <row r="7" spans="1:16" s="3" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="14">
@@ -5402,26 +5716,30 @@
         <v>1121</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" s="18"/>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I7" s="15">
         <v>1</v>
       </c>
-      <c r="J7" s="15"/>
+      <c r="J7" s="57" t="s">
+        <v>146</v>
+      </c>
       <c r="K7" s="17"/>
       <c r="L7" s="42" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M7" s="16"/>
       <c r="N7" s="16"/>
       <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
+      <c r="P7" s="54" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="8" spans="1:16" s="4" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="14">
@@ -5432,26 +5750,30 @@
         <v>2122</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="22"/>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
       <c r="H8" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I8" s="20">
         <v>4</v>
       </c>
-      <c r="J8" s="20"/>
+      <c r="J8" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K8" s="21"/>
       <c r="L8" s="42" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M8" s="27"/>
       <c r="N8" s="27"/>
       <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
+      <c r="P8" s="51" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="9" spans="1:16" s="4" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="14">
@@ -5462,10 +5784,10 @@
         <v>1113</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
@@ -5473,17 +5795,21 @@
       <c r="I9" s="20">
         <v>34</v>
       </c>
-      <c r="J9" s="20"/>
+      <c r="J9" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K9" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L9" s="50" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M9" s="27"/>
       <c r="N9" s="27"/>
       <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
+      <c r="P9" s="51" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="10" spans="1:16" s="4" customFormat="1" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="14">
@@ -5494,10 +5820,10 @@
         <v>1312</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F10" s="27"/>
       <c r="G10" s="20"/>
@@ -5505,17 +5831,21 @@
       <c r="I10" s="24">
         <v>14</v>
       </c>
-      <c r="J10" s="20"/>
+      <c r="J10" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K10" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L10" s="50" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M10" s="27"/>
       <c r="N10" s="27"/>
       <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
+      <c r="P10" s="51" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="11" spans="1:16" s="4" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="14">
@@ -5526,26 +5856,30 @@
         <v>1221</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="27"/>
       <c r="G11" s="20"/>
       <c r="H11" s="37" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I11" s="24">
         <v>2</v>
       </c>
-      <c r="J11" s="20"/>
+      <c r="J11" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K11" s="21"/>
       <c r="L11" s="42" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M11" s="27"/>
       <c r="N11" s="27"/>
       <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
+      <c r="P11" s="51" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="12" spans="1:16" s="4" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="14">
@@ -5556,26 +5890,30 @@
         <v>1222</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="27"/>
       <c r="G12" s="20"/>
       <c r="H12" s="37" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I12" s="24">
         <v>2</v>
       </c>
-      <c r="J12" s="20"/>
+      <c r="J12" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K12" s="21"/>
       <c r="L12" s="42" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M12" s="27"/>
       <c r="N12" s="27"/>
       <c r="O12" s="27"/>
-      <c r="P12" s="27"/>
+      <c r="P12" s="51" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="13" spans="1:16" s="4" customFormat="1" ht="127.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="14">
@@ -5586,24 +5924,34 @@
         <v>1213</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="22"/>
+        <v>34</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>140</v>
+      </c>
       <c r="F13" s="27"/>
       <c r="G13" s="20"/>
       <c r="H13" s="22"/>
       <c r="I13" s="24">
-        <v>4</v>
-      </c>
-      <c r="J13" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="J13" s="55" t="s">
+        <v>132</v>
+      </c>
       <c r="K13" s="21"/>
       <c r="L13" s="44" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
+      <c r="N13" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="O13" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="P13" s="27" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="14" spans="1:16" s="4" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="14">
@@ -5614,13 +5962,13 @@
         <v>1224</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="15"/>
       <c r="G14" s="20"/>
       <c r="H14" s="39" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I14" s="40">
         <v>2</v>
@@ -5628,12 +5976,14 @@
       <c r="J14" s="15"/>
       <c r="K14" s="28"/>
       <c r="L14" s="42" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M14" s="27"/>
       <c r="N14" s="27"/>
       <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
+      <c r="P14" s="51" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="15" spans="1:16" s="4" customFormat="1" ht="134.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="14">
@@ -5644,24 +5994,32 @@
         <v>1214</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="27"/>
       <c r="G15" s="20"/>
       <c r="H15" s="22"/>
       <c r="I15" s="24">
-        <v>4</v>
-      </c>
-      <c r="J15" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="J15" s="55" t="s">
+        <v>132</v>
+      </c>
       <c r="K15" s="21"/>
       <c r="L15" s="44" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
+      <c r="N15" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="O15" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="P15" s="27" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="16" spans="1:16" s="4" customFormat="1" ht="117" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="14">
@@ -5672,7 +6030,7 @@
         <v>1218</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" s="22"/>
       <c r="F16" s="27"/>
@@ -5681,15 +6039,21 @@
       <c r="I16" s="24">
         <v>2</v>
       </c>
-      <c r="J16" s="20"/>
+      <c r="J16" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K16" s="21"/>
       <c r="L16" s="44" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="M16" s="27"/>
       <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
+      <c r="O16" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="P16" s="27" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="17" spans="1:16" s="4" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="14">
@@ -5700,26 +6064,30 @@
         <v>1225</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="27"/>
       <c r="G17" s="20"/>
       <c r="H17" s="48" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I17" s="24">
         <v>1</v>
       </c>
-      <c r="J17" s="20"/>
+      <c r="J17" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K17" s="21"/>
       <c r="L17" s="42" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M17" s="27"/>
       <c r="N17" s="27"/>
       <c r="O17" s="27"/>
-      <c r="P17" s="27"/>
+      <c r="P17" s="51" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="18" spans="1:16" s="4" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="14">
@@ -5729,27 +6097,35 @@
       <c r="C18" s="20">
         <v>1215</v>
       </c>
-      <c r="D18" s="35" t="s">
-        <v>40</v>
+      <c r="D18" s="36" t="s">
+        <v>129</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
       <c r="H18" s="22"/>
       <c r="I18" s="20">
-        <v>2</v>
-      </c>
-      <c r="J18" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="J18" s="55" t="s">
+        <v>132</v>
+      </c>
       <c r="K18" s="21"/>
       <c r="L18" s="43" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="M18" s="27"/>
-      <c r="N18" s="27"/>
-      <c r="O18" s="27"/>
-      <c r="P18" s="27"/>
+      <c r="N18" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="O18" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="P18" s="27" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="14">
@@ -5760,26 +6136,34 @@
         <v>1212</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
       <c r="H19" s="22"/>
       <c r="I19" s="20">
-        <v>2</v>
-      </c>
-      <c r="J19" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="J19" s="55" t="s">
+        <v>132</v>
+      </c>
       <c r="K19" s="21"/>
       <c r="L19" s="43" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="27"/>
+      <c r="N19" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="O19" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="P19" s="27" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="109.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="14">
@@ -5790,10 +6174,10 @@
         <v>1217</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
@@ -5801,18 +6185,20 @@
       <c r="I20" s="20">
         <v>8</v>
       </c>
-      <c r="J20" s="20"/>
+      <c r="J20" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K20" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L20" s="45" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M20" s="27"/>
       <c r="N20" s="27"/>
       <c r="O20" s="27"/>
-      <c r="P20" s="27" t="s">
-        <v>84</v>
+      <c r="P20" s="51" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="120.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5824,10 +6210,10 @@
         <v>1218</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
@@ -5835,18 +6221,20 @@
       <c r="I21" s="20">
         <v>8</v>
       </c>
-      <c r="J21" s="20"/>
+      <c r="J21" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K21" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L21" s="45" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M21" s="27"/>
       <c r="N21" s="27"/>
       <c r="O21" s="27"/>
-      <c r="P21" s="27" t="s">
-        <v>85</v>
+      <c r="P21" s="51" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="111" customHeight="1" x14ac:dyDescent="0.15">
@@ -5858,10 +6246,10 @@
         <v>1216</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
@@ -5869,17 +6257,21 @@
       <c r="I22" s="20">
         <v>2</v>
       </c>
-      <c r="J22" s="20"/>
+      <c r="J22" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K22" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L22" s="50" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M22" s="27"/>
       <c r="N22" s="27"/>
       <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
+      <c r="P22" s="52" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="58.5" x14ac:dyDescent="0.15">
       <c r="A23" s="14">
@@ -5890,7 +6282,7 @@
         <v>1223</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="20"/>
@@ -5899,15 +6291,19 @@
       <c r="I23" s="20">
         <v>1</v>
       </c>
-      <c r="J23" s="20"/>
+      <c r="J23" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K23" s="21"/>
       <c r="L23" s="42" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M23" s="27"/>
       <c r="N23" s="27"/>
       <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
+      <c r="P23" s="51" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="14">
@@ -5918,7 +6314,7 @@
         <v>1521</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="20"/>
@@ -5927,17 +6323,21 @@
       <c r="I24" s="20">
         <v>1</v>
       </c>
-      <c r="J24" s="20"/>
+      <c r="J24" s="46" t="s">
+        <v>145</v>
+      </c>
       <c r="K24" s="21"/>
       <c r="L24" s="41" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="M24" s="27">
         <v>1</v>
       </c>
       <c r="N24" s="27"/>
       <c r="O24" s="27"/>
-      <c r="P24" s="27"/>
+      <c r="P24" s="51" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="117" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="14">
@@ -5948,10 +6348,10 @@
         <v>1515</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F25" s="20"/>
       <c r="G25" s="20"/>
@@ -5959,17 +6359,21 @@
       <c r="I25" s="20">
         <v>6</v>
       </c>
-      <c r="J25" s="20"/>
+      <c r="J25" s="46" t="s">
+        <v>145</v>
+      </c>
       <c r="K25" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L25" s="45" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M25" s="27"/>
       <c r="N25" s="27"/>
       <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
+      <c r="P25" s="52" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="122.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="14">
@@ -5980,10 +6384,10 @@
         <v>1516</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
@@ -5991,17 +6395,21 @@
       <c r="I26" s="20">
         <v>2</v>
       </c>
-      <c r="J26" s="20"/>
+      <c r="J26" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K26" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L26" s="45" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M26" s="27"/>
       <c r="N26" s="27"/>
       <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
+      <c r="P26" s="52" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="96" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="14">
@@ -6012,7 +6420,7 @@
         <v>1522</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="20"/>
@@ -6021,17 +6429,21 @@
       <c r="I27" s="20">
         <v>1</v>
       </c>
-      <c r="J27" s="20"/>
+      <c r="J27" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K27" s="21"/>
       <c r="L27" s="41" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="M27" s="27">
         <v>1</v>
       </c>
       <c r="N27" s="27"/>
       <c r="O27" s="27"/>
-      <c r="P27" s="27"/>
+      <c r="P27" s="51" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="28" spans="1:16" ht="129.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="14">
@@ -6042,10 +6454,10 @@
         <v>1577</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
@@ -6053,17 +6465,21 @@
       <c r="I28" s="20">
         <v>18</v>
       </c>
-      <c r="J28" s="20"/>
+      <c r="J28" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K28" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L28" s="45" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M28" s="27"/>
       <c r="N28" s="27"/>
       <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
+      <c r="P28" s="52" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="29" spans="1:16" ht="129" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="14">
@@ -6074,7 +6490,7 @@
         <v>1411</v>
       </c>
       <c r="D29" s="35" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E29" s="22"/>
       <c r="F29" s="20"/>
@@ -6083,17 +6499,23 @@
       <c r="I29" s="20">
         <v>2</v>
       </c>
-      <c r="J29" s="20"/>
+      <c r="J29" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K29" s="21"/>
       <c r="L29" s="44" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="M29" s="27"/>
       <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-    </row>
-    <row r="30" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="O29" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="P29" s="27" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="54" x14ac:dyDescent="0.15">
       <c r="A30" s="14">
         <v>24</v>
       </c>
@@ -6102,7 +6524,7 @@
         <v>1421</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E30" s="22"/>
       <c r="F30" s="20"/>
@@ -6111,19 +6533,23 @@
       <c r="I30" s="20">
         <v>2</v>
       </c>
-      <c r="J30" s="20"/>
+      <c r="J30" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K30" s="21"/>
       <c r="L30" s="41" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="M30" s="27">
         <v>1</v>
       </c>
       <c r="N30" s="27"/>
       <c r="O30" s="27"/>
-      <c r="P30" s="27"/>
-    </row>
-    <row r="31" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="P30" s="51" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="54" x14ac:dyDescent="0.15">
       <c r="A31" s="14">
         <v>25</v>
       </c>
@@ -6132,7 +6558,7 @@
         <v>1621</v>
       </c>
       <c r="D31" s="35" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="20"/>
@@ -6141,15 +6567,19 @@
       <c r="I31" s="20">
         <v>1</v>
       </c>
-      <c r="J31" s="20"/>
+      <c r="J31" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K31" s="21"/>
       <c r="L31" s="41" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="M31" s="27"/>
       <c r="N31" s="27"/>
       <c r="O31" s="27"/>
-      <c r="P31" s="27"/>
+      <c r="P31" s="51" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="32" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="14">
@@ -6160,10 +6590,10 @@
         <v>1713</v>
       </c>
       <c r="D32" s="35" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F32" s="20"/>
       <c r="G32" s="20"/>
@@ -6171,17 +6601,21 @@
       <c r="I32" s="20">
         <v>8</v>
       </c>
-      <c r="J32" s="20"/>
+      <c r="J32" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K32" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L32" s="50" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M32" s="27"/>
       <c r="N32" s="27"/>
       <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
+      <c r="P32" s="52" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="33" spans="1:16" ht="110.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="14">
@@ -6192,10 +6626,10 @@
         <v>1712</v>
       </c>
       <c r="D33" s="35" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
@@ -6203,19 +6637,23 @@
       <c r="I33" s="20">
         <v>8</v>
       </c>
-      <c r="J33" s="20"/>
+      <c r="J33" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K33" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L33" s="45" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M33" s="27"/>
       <c r="N33" s="27"/>
       <c r="O33" s="27"/>
-      <c r="P33" s="27"/>
-    </row>
-    <row r="34" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="P33" s="52" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="54" x14ac:dyDescent="0.15">
       <c r="A34" s="14">
         <v>28</v>
       </c>
@@ -6224,7 +6662,7 @@
         <v>1721</v>
       </c>
       <c r="D34" s="35" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="20"/>
@@ -6233,19 +6671,23 @@
       <c r="I34" s="20">
         <v>1</v>
       </c>
-      <c r="J34" s="20"/>
+      <c r="J34" s="46" t="s">
+        <v>145</v>
+      </c>
       <c r="K34" s="21"/>
       <c r="L34" s="41" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="M34" s="27">
         <v>1</v>
       </c>
       <c r="N34" s="27"/>
       <c r="O34" s="27"/>
-      <c r="P34" s="27"/>
-    </row>
-    <row r="35" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="P34" s="51" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="54" x14ac:dyDescent="0.15">
       <c r="A35" s="14">
         <v>29</v>
       </c>
@@ -6253,7 +6695,7 @@
         <v>2121</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="20"/>
@@ -6262,17 +6704,21 @@
       <c r="I35" s="20">
         <v>1</v>
       </c>
-      <c r="J35" s="20"/>
+      <c r="J35" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K35" s="21"/>
       <c r="L35" s="41" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="M35" s="27">
         <v>1</v>
       </c>
       <c r="N35" s="27"/>
       <c r="O35" s="27"/>
-      <c r="P35" s="27"/>
+      <c r="P35" s="51" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="36" spans="1:16" ht="137.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="14">
@@ -6282,7 +6728,7 @@
         <v>2111</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="20"/>
@@ -6291,17 +6737,23 @@
       <c r="I36" s="20">
         <v>3</v>
       </c>
-      <c r="J36" s="20"/>
+      <c r="J36" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K36" s="21"/>
-      <c r="L36" s="46" t="s">
-        <v>87</v>
+      <c r="L36" s="56" t="s">
+        <v>139</v>
       </c>
       <c r="M36" s="27"/>
       <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="P36" s="27"/>
-    </row>
-    <row r="37" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="O36" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="P36" s="27" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="54" x14ac:dyDescent="0.15">
       <c r="A37" s="14">
         <v>32</v>
       </c>
@@ -6309,7 +6761,7 @@
         <v>121</v>
       </c>
       <c r="D37" s="35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="20"/>
@@ -6318,19 +6770,23 @@
       <c r="I37" s="20">
         <v>1</v>
       </c>
-      <c r="J37" s="20"/>
+      <c r="J37" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K37" s="21"/>
       <c r="L37" s="41" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="M37" s="27">
         <v>1</v>
       </c>
       <c r="N37" s="27"/>
       <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-    </row>
-    <row r="38" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="P37" s="52" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="54" x14ac:dyDescent="0.15">
       <c r="A38" s="14">
         <v>34</v>
       </c>
@@ -6338,7 +6794,7 @@
         <v>122</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="20"/>
@@ -6347,19 +6803,23 @@
       <c r="I38" s="20">
         <v>1</v>
       </c>
-      <c r="J38" s="20"/>
+      <c r="J38" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K38" s="21"/>
       <c r="L38" s="41" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="M38" s="27">
         <v>1</v>
       </c>
       <c r="N38" s="27"/>
       <c r="O38" s="27"/>
-      <c r="P38" s="27"/>
-    </row>
-    <row r="39" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="P38" s="51" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="54" x14ac:dyDescent="0.15">
       <c r="A39" s="14">
         <v>35</v>
       </c>
@@ -6367,7 +6827,7 @@
         <v>123</v>
       </c>
       <c r="D39" s="35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="20"/>
@@ -6376,17 +6836,21 @@
       <c r="I39" s="20">
         <v>1</v>
       </c>
-      <c r="J39" s="20"/>
+      <c r="J39" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K39" s="21"/>
       <c r="L39" s="41" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="M39" s="27">
         <v>1</v>
       </c>
       <c r="N39" s="27"/>
       <c r="O39" s="27"/>
-      <c r="P39" s="27"/>
+      <c r="P39" s="51" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="40" spans="1:16" ht="117" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="14">
@@ -6396,10 +6860,10 @@
         <v>116</v>
       </c>
       <c r="D40" s="35" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F40" s="20"/>
       <c r="G40" s="20"/>
@@ -6407,88 +6871,102 @@
       <c r="I40" s="20">
         <v>6</v>
       </c>
-      <c r="J40" s="20"/>
+      <c r="J40" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K40" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L40" s="45" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M40" s="27"/>
       <c r="N40" s="27"/>
       <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-    </row>
-    <row r="41" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="P40" s="51" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="54" x14ac:dyDescent="0.15">
       <c r="A41" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C41" s="20">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="20"/>
       <c r="G41" s="20"/>
       <c r="H41" s="22"/>
       <c r="I41" s="20">
-        <v>2</v>
-      </c>
-      <c r="J41" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="J41" s="46" t="s">
+        <v>145</v>
+      </c>
       <c r="K41" s="21"/>
       <c r="L41" s="41" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="M41" s="27">
         <v>1</v>
       </c>
       <c r="N41" s="27"/>
       <c r="O41" s="27"/>
-      <c r="P41" s="27"/>
-    </row>
-    <row r="42" spans="1:16" ht="45" x14ac:dyDescent="0.15">
+      <c r="P41" s="51" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="121.5" x14ac:dyDescent="0.15">
       <c r="A42" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C42" s="20">
-        <v>125</v>
-      </c>
-      <c r="D42" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42" s="22"/>
+        <v>126</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>84</v>
+      </c>
       <c r="F42" s="20"/>
       <c r="G42" s="20"/>
       <c r="H42" s="22"/>
       <c r="I42" s="20">
         <v>1</v>
       </c>
-      <c r="J42" s="20"/>
+      <c r="J42" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K42" s="21"/>
-      <c r="L42" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="M42" s="27">
-        <v>1</v>
-      </c>
+      <c r="L42" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="M42" s="27"/>
       <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
-    </row>
-    <row r="43" spans="1:16" ht="121.5" x14ac:dyDescent="0.15">
+      <c r="O42" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="P42" s="27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A43" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C43" s="20">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D43" s="36" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F43" s="20"/>
       <c r="G43" s="20"/>
@@ -6496,28 +6974,30 @@
       <c r="I43" s="20">
         <v>1</v>
       </c>
-      <c r="J43" s="20"/>
+      <c r="J43" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K43" s="21"/>
       <c r="L43" s="47" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M43" s="27"/>
       <c r="N43" s="27"/>
       <c r="O43" s="27"/>
       <c r="P43" s="27"/>
     </row>
-    <row r="44" spans="1:16" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:16" ht="243" x14ac:dyDescent="0.15">
       <c r="A44" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C44" s="20">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F44" s="20"/>
       <c r="G44" s="20"/>
@@ -6525,28 +7005,34 @@
       <c r="I44" s="20">
         <v>1</v>
       </c>
-      <c r="J44" s="20"/>
+      <c r="J44" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K44" s="21"/>
       <c r="L44" s="47" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="M44" s="27"/>
       <c r="N44" s="27"/>
-      <c r="O44" s="27"/>
-      <c r="P44" s="27"/>
-    </row>
-    <row r="45" spans="1:16" ht="243" x14ac:dyDescent="0.15">
+      <c r="O44" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="P44" s="27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="162" x14ac:dyDescent="0.15">
       <c r="A45" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C45" s="20">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D45" s="36" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F45" s="20"/>
       <c r="G45" s="20"/>
@@ -6554,166 +7040,198 @@
       <c r="I45" s="20">
         <v>1</v>
       </c>
-      <c r="J45" s="20"/>
+      <c r="J45" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K45" s="21"/>
       <c r="L45" s="47" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M45" s="27"/>
       <c r="N45" s="27"/>
-      <c r="O45" s="27"/>
-      <c r="P45" s="27"/>
+      <c r="O45" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="P45" s="27" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="46" spans="1:16" ht="162" x14ac:dyDescent="0.15">
       <c r="A46" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C46" s="20">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D46" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>100</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="E46" s="22"/>
       <c r="F46" s="20"/>
       <c r="G46" s="20"/>
       <c r="H46" s="22"/>
       <c r="I46" s="20">
         <v>1</v>
       </c>
-      <c r="J46" s="20"/>
+      <c r="J46" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K46" s="21"/>
       <c r="L46" s="47" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="M46" s="27"/>
       <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-    </row>
-    <row r="47" spans="1:16" ht="162" x14ac:dyDescent="0.15">
+      <c r="O46" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="P46" s="27" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="256.5" x14ac:dyDescent="0.15">
       <c r="A47" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C47" s="20">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D47" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="E47" s="22"/>
+        <v>106</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>107</v>
+      </c>
       <c r="F47" s="20"/>
       <c r="G47" s="20"/>
       <c r="H47" s="22"/>
       <c r="I47" s="20">
-        <v>1</v>
-      </c>
-      <c r="J47" s="20"/>
+        <v>50</v>
+      </c>
+      <c r="J47" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K47" s="21"/>
       <c r="L47" s="47" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="M47" s="27"/>
       <c r="N47" s="27"/>
-      <c r="O47" s="27"/>
-      <c r="P47" s="27"/>
-    </row>
-    <row r="48" spans="1:16" ht="256.5" x14ac:dyDescent="0.15">
+      <c r="O47" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="P47" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="243" x14ac:dyDescent="0.15">
       <c r="A48" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C48" s="20">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D48" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>115</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="E48" s="22"/>
       <c r="F48" s="20"/>
       <c r="G48" s="20"/>
       <c r="H48" s="22"/>
       <c r="I48" s="20">
-        <v>50</v>
-      </c>
-      <c r="J48" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="J48" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K48" s="21"/>
       <c r="L48" s="47" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="M48" s="27"/>
       <c r="N48" s="27"/>
-      <c r="O48" s="27"/>
-      <c r="P48" s="27"/>
-    </row>
-    <row r="49" spans="1:16" ht="243" x14ac:dyDescent="0.15">
+      <c r="O48" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="P48" s="27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A49" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C49" s="20">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D49" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="E49" s="22"/>
+        <v>99</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>101</v>
+      </c>
       <c r="F49" s="20"/>
       <c r="G49" s="20"/>
       <c r="H49" s="22"/>
       <c r="I49" s="20">
         <v>1</v>
       </c>
-      <c r="J49" s="20"/>
+      <c r="J49" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K49" s="21"/>
-      <c r="L49" s="47" t="s">
-        <v>105</v>
+      <c r="L49" s="41" t="s">
+        <v>100</v>
       </c>
       <c r="M49" s="27"/>
       <c r="N49" s="27"/>
       <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
+      <c r="P49" s="51" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="50" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C50" s="20">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D50" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="E50" s="22"/>
       <c r="F50" s="20"/>
       <c r="G50" s="20"/>
       <c r="H50" s="22"/>
       <c r="I50" s="20">
         <v>1</v>
       </c>
-      <c r="J50" s="20"/>
-      <c r="K50" s="21"/>
+      <c r="J50" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="K50" s="49" t="s">
+        <v>111</v>
+      </c>
       <c r="L50" s="41" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M50" s="27"/>
       <c r="N50" s="27"/>
       <c r="O50" s="27"/>
-      <c r="P50" s="27"/>
+      <c r="P50" s="51" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="51" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C51" s="20">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D51" s="36" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="20"/>
@@ -6722,27 +7240,31 @@
       <c r="I51" s="20">
         <v>1</v>
       </c>
-      <c r="J51" s="20"/>
+      <c r="J51" s="46" t="s">
+        <v>145</v>
+      </c>
       <c r="K51" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L51" s="41" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M51" s="27"/>
       <c r="N51" s="27"/>
       <c r="O51" s="27"/>
-      <c r="P51" s="27"/>
+      <c r="P51" s="51" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="52" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C52" s="20">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D52" s="36" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E52" s="22"/>
       <c r="F52" s="20"/>
@@ -6751,83 +7273,102 @@
       <c r="I52" s="20">
         <v>1</v>
       </c>
-      <c r="J52" s="20"/>
+      <c r="J52" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K52" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L52" s="41" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M52" s="27"/>
       <c r="N52" s="27"/>
       <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
+      <c r="P52" s="52" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="53" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="14">
         <v>50</v>
       </c>
       <c r="C53" s="20">
-        <v>136</v>
+        <v>1312</v>
       </c>
       <c r="D53" s="36" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="20"/>
       <c r="G53" s="20"/>
       <c r="H53" s="22"/>
       <c r="I53" s="20">
-        <v>1</v>
-      </c>
-      <c r="J53" s="20"/>
+        <v>2</v>
+      </c>
+      <c r="J53" s="55" t="s">
+        <v>146</v>
+      </c>
       <c r="K53" s="49" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L53" s="41" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M53" s="27"/>
       <c r="N53" s="27"/>
       <c r="O53" s="27"/>
-      <c r="P53" s="27"/>
-    </row>
-    <row r="54" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="P53" s="51" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="58.5" x14ac:dyDescent="0.15">
       <c r="A54" s="14">
         <v>50</v>
       </c>
       <c r="C54" s="20">
-        <v>1312</v>
+        <v>3129</v>
       </c>
       <c r="D54" s="36" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="20"/>
       <c r="G54" s="20"/>
       <c r="H54" s="22"/>
       <c r="I54" s="20">
-        <v>2</v>
-      </c>
-      <c r="J54" s="20"/>
-      <c r="K54" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="L54" s="41" t="s">
-        <v>111</v>
+        <v>1</v>
+      </c>
+      <c r="J54" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="K54" s="49"/>
+      <c r="L54" s="42" t="s">
+        <v>73</v>
       </c>
       <c r="M54" s="27"/>
       <c r="N54" s="27"/>
       <c r="O54" s="27"/>
-      <c r="P54" s="27"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="P54" s="51" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="28.5" x14ac:dyDescent="0.15">
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="O55" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="28.5" x14ac:dyDescent="0.15">
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
+      <c r="O56" s="53" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.15">
       <c r="I57" s="2"/>
@@ -11485,26 +12026,15 @@
       <c r="I1220" s="2"/>
       <c r="J1220" s="2"/>
     </row>
-    <row r="1221" spans="9:10" x14ac:dyDescent="0.15">
-      <c r="I1221" s="2"/>
-      <c r="J1221" s="2"/>
-    </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="O5:O6"/>
@@ -11521,23 +12051,31 @@
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:P4"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="C1:D2"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
   </mergeCells>
   <phoneticPr fontId="61" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="L43" r:id="rId1" xr:uid="{9A51B0C7-8481-4F5F-96C9-71A2DF3DDCA7}"/>
-    <hyperlink ref="L44" r:id="rId2" xr:uid="{BC501510-C86E-4A45-BAA8-5F5E22C20442}"/>
-    <hyperlink ref="L45" r:id="rId3" display="https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1563820041%3AH%3AjEXVXFz29uWhSPA32SdLxq18tbGVRP6N%3Ab1e44a53e68312397166bdb38376f31f&amp;ali_trackid=318_b1e44a53e68312397166bdb38376f31f&amp;id=668804973431&amp;mi_id=0000kh4JsEhs_IKQwaZwLe5GPzZBrKEtnqIAl4nMzgEcpGs&amp;mm_sceneid=0_0_2198670068_0&amp;priceTId=213e097817677727727551092e11ab&amp;skuId=6072168990782&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%220ce0092ebee4bb5c990e1ed0aae83472%22%7D&amp;xxc=ad_ztc" xr:uid="{EE7187D2-5C29-4C71-8BF0-14CC690401EB}"/>
-    <hyperlink ref="L46" r:id="rId4" display="https://item.taobao.com/item.htm?abbucket=15&amp;id=684180101591&amp;mi_id=0000kHsnKO9vrl_xXRKAYuWwfk1ZxpJzkY1oGgmAntBdN2A&amp;ns=1&amp;priceTId=215040db17693197452846906e10bd&amp;skuId=5066190559427&amp;spm=a21n57.1.hoverItem.13&amp;utparam=%7B%22aplus_abtest%22%3A%2200fb48171d68baf920a6c2997ba800f5%22%7D&amp;xxc=taobaoSearch" xr:uid="{640829AA-10E2-4344-B84B-AF14836FC0FA}"/>
-    <hyperlink ref="L47" r:id="rId5" display="https://item.taobao.com/item.htm?abbucket=15&amp;id=885444239746&amp;mi_id=00004gN7JSgLTLqH9NscZa5BV-fDjGIRhn7dS2llqgBEm-I&amp;ns=1&amp;priceTId=215040db17693199893824488e10bd&amp;skuId=5729109569961&amp;spm=a21n57.1.hoverItem.3&amp;utparam=%7B%22aplus_abtest%22%3A%220d184a79d8dee207c56cd615483888e0%22%7D&amp;xxc=taobaoSearch" xr:uid="{D9E14E51-6908-4600-BF1B-1BE5E52130FA}"/>
-    <hyperlink ref="L49" r:id="rId6" display="https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1202830031%3AH%3A5NEVSZWkfH5vk10Gx8WsEg%3D%3D%3A0e3224a199436b146fadd1013df40d50&amp;ali_trackid=282_0e3224a199436b146fadd1013df40d50&amp;id=589213401941&amp;mi_id=0000tXboOyQ6vKwx8WiuBo_0I904yCwGgBZQ-DEtp9Eidvc&amp;mm_sceneid=1_0_343370108_0&amp;priceTId=214782f517694062736734983e1fe1&amp;skuId=4715656587781&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%2243f96ce6df79319aabdbd4973057b1b5%22%7D&amp;xxc=ad_ztc" xr:uid="{A4FE5950-5A28-4F3D-B42C-E6D6ECC79B08}"/>
-    <hyperlink ref="L48" r:id="rId7" display="https://item.taobao.com/item.htm?ali_refid=a3_430673_1006%3A1109974134%3AH%3AS9mt8%2FS9IPRAnlGXK23dCRerfi2%2BAYZj%3A75421c7a1bf937df626379b8de81db84&amp;ali_trackid=282_75421c7a1bf937df626379b8de81db84&amp;id=774427618182&amp;loginBonus=1&amp;mi_id=0000OtzXamOT9vAra9TbUQiBvRLBsdZJRcmzsekmz3yUyS0&amp;mm_sceneid=1_0_99588015_0&amp;priceTId=2150467817696032421462002e22b0&amp;skuId=5300832301565&amp;spm=a21n57.sem.item.4&amp;utparam=%7B%22aplus_abtest%22%3A%22c7bbb9e8de08729fc098be83e797fb13%22%7D&amp;xxc=ad_ztc" xr:uid="{FC3750A0-F3B8-4313-B9DE-37439F3E109E}"/>
+    <hyperlink ref="L42" r:id="rId1" xr:uid="{9A51B0C7-8481-4F5F-96C9-71A2DF3DDCA7}"/>
+    <hyperlink ref="L43" r:id="rId2" xr:uid="{BC501510-C86E-4A45-BAA8-5F5E22C20442}"/>
+    <hyperlink ref="L44" r:id="rId3" display="https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1563820041%3AH%3AjEXVXFz29uWhSPA32SdLxq18tbGVRP6N%3Ab1e44a53e68312397166bdb38376f31f&amp;ali_trackid=318_b1e44a53e68312397166bdb38376f31f&amp;id=668804973431&amp;mi_id=0000kh4JsEhs_IKQwaZwLe5GPzZBrKEtnqIAl4nMzgEcpGs&amp;mm_sceneid=0_0_2198670068_0&amp;priceTId=213e097817677727727551092e11ab&amp;skuId=6072168990782&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%220ce0092ebee4bb5c990e1ed0aae83472%22%7D&amp;xxc=ad_ztc" xr:uid="{EE7187D2-5C29-4C71-8BF0-14CC690401EB}"/>
+    <hyperlink ref="L45" r:id="rId4" display="https://item.taobao.com/item.htm?abbucket=15&amp;id=684180101591&amp;mi_id=0000kHsnKO9vrl_xXRKAYuWwfk1ZxpJzkY1oGgmAntBdN2A&amp;ns=1&amp;priceTId=215040db17693197452846906e10bd&amp;skuId=5066190559427&amp;spm=a21n57.1.hoverItem.13&amp;utparam=%7B%22aplus_abtest%22%3A%2200fb48171d68baf920a6c2997ba800f5%22%7D&amp;xxc=taobaoSearch" xr:uid="{640829AA-10E2-4344-B84B-AF14836FC0FA}"/>
+    <hyperlink ref="L46" r:id="rId5" display="https://item.taobao.com/item.htm?abbucket=15&amp;id=885444239746&amp;mi_id=00004gN7JSgLTLqH9NscZa5BV-fDjGIRhn7dS2llqgBEm-I&amp;ns=1&amp;priceTId=215040db17693199893824488e10bd&amp;skuId=5729109569961&amp;spm=a21n57.1.hoverItem.3&amp;utparam=%7B%22aplus_abtest%22%3A%220d184a79d8dee207c56cd615483888e0%22%7D&amp;xxc=taobaoSearch" xr:uid="{D9E14E51-6908-4600-BF1B-1BE5E52130FA}"/>
+    <hyperlink ref="L48" r:id="rId6" display="https://detail.tmall.com/item.htm?ali_refid=a3_430582_1006%3A1202830031%3AH%3A5NEVSZWkfH5vk10Gx8WsEg%3D%3D%3A0e3224a199436b146fadd1013df40d50&amp;ali_trackid=282_0e3224a199436b146fadd1013df40d50&amp;id=589213401941&amp;mi_id=0000tXboOyQ6vKwx8WiuBo_0I904yCwGgBZQ-DEtp9Eidvc&amp;mm_sceneid=1_0_343370108_0&amp;priceTId=214782f517694062736734983e1fe1&amp;skuId=4715656587781&amp;spm=a21n57.1.hoverItem.1&amp;utparam=%7B%22aplus_abtest%22%3A%2243f96ce6df79319aabdbd4973057b1b5%22%7D&amp;xxc=ad_ztc" xr:uid="{A4FE5950-5A28-4F3D-B42C-E6D6ECC79B08}"/>
+    <hyperlink ref="L47" r:id="rId7" display="https://item.taobao.com/item.htm?ali_refid=a3_430673_1006%3A1109974134%3AH%3AS9mt8%2FS9IPRAnlGXK23dCRerfi2%2BAYZj%3A75421c7a1bf937df626379b8de81db84&amp;ali_trackid=282_75421c7a1bf937df626379b8de81db84&amp;id=774427618182&amp;loginBonus=1&amp;mi_id=0000OtzXamOT9vAra9TbUQiBvRLBsdZJRcmzsekmz3yUyS0&amp;mm_sceneid=1_0_99588015_0&amp;priceTId=2150467817696032421462002e22b0&amp;skuId=5300832301565&amp;spm=a21n57.sem.item.4&amp;utparam=%7B%22aplus_abtest%22%3A%22c7bbb9e8de08729fc098be83e797fb13%22%7D&amp;xxc=ad_ztc" xr:uid="{FC3750A0-F3B8-4313-B9DE-37439F3E109E}"/>
+    <hyperlink ref="L36" r:id="rId8" xr:uid="{B9066E40-3620-40FD-976E-186331CB00E7}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
